--- a/tame_output/ON/bt/strategyON_20241004.xlsx
+++ b/tame_output/ON/bt/strategyON_20241004.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>107.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-49.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.6%</t>
+          <t>417.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-650.5%</t>
+          <t>-651.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-88.5%</t>
+          <t>-89.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>73.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.0%</t>
+          <t>-394.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-102.5%</t>
+          <t>-102.2%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>120.8%</t>
+          <t>121.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>110.0%</t>
+          <t>112.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>110.2%</t>
+          <t>110.4%</t>
         </is>
       </c>
     </row>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -46562,16 +46562,16 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.998319956880341</v>
+        <v>-4.156588389002801</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.896548276414628</v>
+        <v>0.8332409035656438</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4601766312433394</v>
+        <v>0.3180532111465192</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.772338662226516</v>
+        <v>2.687064610168424</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.043334170400946</v>
+        <v>-4.201602602523407</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8593500463379753</v>
+        <v>0.7960426734889914</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4298277359287348</v>
+        <v>0.2877043158319146</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.734936780369343</v>
+        <v>2.649662728311251</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.131345356959644</v>
+        <v>-4.289613789082104</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8298371340534423</v>
+        <v>0.7665297612044581</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3643512280695618</v>
+        <v>0.2222278079727416</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.701342437992785</v>
+        <v>2.616068385934693</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.232543138396816</v>
+        <v>-4.390811570519277</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7885619433750746</v>
+        <v>0.7252545705260904</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2959424145242426</v>
+        <v>0.1538189944274224</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.659501071762095</v>
+        <v>2.574227019704003</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.226032171782504</v>
+        <v>-4.384300603904964</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7887662915751164</v>
+        <v>0.7254589187261322</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2959424145242426</v>
+        <v>0.1538189944274224</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.657101033316412</v>
+        <v>2.57182698125832</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.206994044075206</v>
+        <v>-4.365262476197667</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7929062618662801</v>
+        <v>0.7295988890172962</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2377588031930481</v>
+        <v>0.09563538309622788</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.61871558572594</v>
+        <v>2.533441533667848</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.259509846350027</v>
+        <v>-4.417778278472487</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8911943425905424</v>
+        <v>0.8278869697415583</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2377588031930481</v>
+        <v>0.09563538309622788</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.73800998736013</v>
+        <v>2.652735935302038</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.262918157784607</v>
+        <v>-4.421186589907067</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8906643470028439</v>
+        <v>0.82735697415386</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2702753722024255</v>
+        <v>0.1281519521056053</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.75835325775189</v>
+        <v>2.673079205693798</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.243562021890759</v>
+        <v>-4.401830454013219</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9044153317573089</v>
+        <v>0.8411079589083248</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2702753722024255</v>
+        <v>0.1281519521056053</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.764361788148816</v>
+        <v>2.679087736090724</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.316891550628852</v>
+        <v>-4.475159982751312</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7730337415392714</v>
+        <v>0.7097263686902873</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2706700346220474</v>
+        <v>0.1285466145252272</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.662548806877789</v>
+        <v>2.577274754819697</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.409870503348191</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.40071277190355</v>
+        <v>-4.55898120402601</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.6492289702730232</v>
+        <v>0.585921597424039</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2706700346220474</v>
+        <v>0.1285466145252272</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.57227252412142</v>
+        <v>2.486998472063328</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.41053285173985</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.394560065850766</v>
+        <v>-4.552828497973226</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.6523524010857953</v>
+        <v>0.5890450282368112</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2768227406748317</v>
+        <v>0.1346993205780115</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.576626496144749</v>
+        <v>2.491352444086657</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.40961332847996</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.411369364001268</v>
+        <v>-4.569637796123728</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.6447091585657048</v>
+        <v>0.5814017857167206</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2600134425243301</v>
+        <v>0.1178900224275098</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.565621393994558</v>
+        <v>2.480347341936466</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.475948882276781</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.349071365225146</v>
+        <v>-4.507339797347606</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.7359639118729746</v>
+        <v>0.6726565390239905</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3053077067987721</v>
+        <v>0.1631842867019519</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.659133506356044</v>
+        <v>2.573859454297952</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.278240883990908</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.147281167559988</v>
+        <v>-4.305549599682448</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6189719926531647</v>
+        <v>0.5556646198041808</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5033258989679266</v>
+        <v>0.3612024788711063</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.580236423371664</v>
+        <v>2.494962371313572</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.348531116313083</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.198167880246182</v>
+        <v>-4.356436312368642</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6689075399008622</v>
+        <v>0.605600167051878</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.452439186281732</v>
+        <v>0.3103157661849117</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.619994628082122</v>
+        <v>2.53472057602403</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.363158852429127</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.111557137596376</v>
+        <v>-4.269825569718836</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7181795730768286</v>
+        <v>0.6548722002278444</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5310649174868902</v>
+        <v>0.38894149739007</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.681797802921261</v>
+        <v>2.596523750863169</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.361694833253798</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.17176643560166</v>
+        <v>-4.33003486772412</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6926318346993863</v>
+        <v>0.6293244618504021</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4708556194816057</v>
+        <v>0.3287321993847855</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.644208204942762</v>
+        <v>2.55893415288467</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.360186451293727</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.122579786917309</v>
+        <v>-4.280848219039769</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7107981122130553</v>
+        <v>0.6474907393640712</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4708556194816057</v>
+        <v>0.3287321993847855</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.642699822982691</v>
+        <v>2.557425770924599</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.360049318729163</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.07820665527874</v>
+        <v>-4.2364750874012</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.728410232303919</v>
+        <v>0.6651028594549349</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5152287511201743</v>
+        <v>0.3731053310233541</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.669186569401268</v>
+        <v>2.583912517343176</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.354443112867754</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.04347533396024</v>
+        <v>-4.2017437660827</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7366965549699098</v>
+        <v>0.6733891821209257</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5152287511201743</v>
+        <v>0.3731053310233541</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.663580363539858</v>
+        <v>2.578306311481766</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.360824869895558</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.995819603399184</v>
+        <v>-4.154088035521644</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7621406042221368</v>
+        <v>0.6988332313731527</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.56288448168123</v>
+        <v>0.4207610615844097</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.698555558904296</v>
+        <v>2.613281506846204</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.365717243270283</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.895301444900429</v>
+        <v>-4.053569877022889</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8072402409963635</v>
+        <v>0.7439328681473794</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6634026401799845</v>
+        <v>0.5212792200831643</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.763758827378274</v>
+        <v>2.678484775320182</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.352471915746155</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.879396115468077</v>
+        <v>-4.037664547590537</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8003570452451767</v>
+        <v>0.7370496723961926</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5842899794707457</v>
+        <v>0.4421665593739254</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.703045903428603</v>
+        <v>2.617771851370511</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.356569618356784</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.834557713859679</v>
+        <v>-3.992826145982139</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8223901084991645</v>
+        <v>0.7590827356501804</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5888334124156152</v>
+        <v>0.4467099923187949</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.709869665806153</v>
+        <v>2.624595613748061</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.360730557987862</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.854056170101687</v>
+        <v>-4.012324602224147</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8187516656334393</v>
+        <v>0.7554442927844549</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5407487711357108</v>
+        <v>0.3986253510388906</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.685179820669289</v>
+        <v>2.599905768611197</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.366610160515699</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.809853333015786</v>
+        <v>-3.968121765138247</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8423124029956366</v>
+        <v>0.7790050301466522</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5849516082216113</v>
+        <v>0.442828188124791</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.717581125448666</v>
+        <v>2.632307073390574</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.365020160984947</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.817412998852833</v>
+        <v>-3.975681430975294</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8376985371300654</v>
+        <v>0.774391164281081</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6397550122314306</v>
+        <v>0.4976315921346104</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.748873168323805</v>
+        <v>2.663599116265713</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.416267926167986</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.659121581313561</v>
+        <v>-3.817390013436022</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9522628693288138</v>
+        <v>0.8889554964798296</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6397550122314306</v>
+        <v>0.4976315921346104</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.800120933506845</v>
+        <v>2.714846881448753</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.414708630762239</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.451479577679085</v>
+        <v>-3.609748009801546</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.033760375376857</v>
+        <v>0.9704530025278733</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8473970158659068</v>
+        <v>0.7052735957690865</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.923146840281784</v>
+        <v>2.837872788223692</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.409656859000509</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.400447484956557</v>
+        <v>-3.558715917079017</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.049121440704139</v>
+        <v>0.9858140678551544</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8984291085884347</v>
+        <v>0.7563056884916145</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.94871432415357</v>
+        <v>2.863440272095478</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.426844263093214</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.335223303829351</v>
+        <v>-3.493491735951812</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.092398517247726</v>
+        <v>1.029091144398742</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9636532897156403</v>
+        <v>0.8215298696188201</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.005036236922599</v>
+        <v>2.919762184864507</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.422805235392495</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.297796283758217</v>
+        <v>-3.456064715880678</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.10333029757546</v>
+        <v>1.040022924726475</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.968904827744822</v>
+        <v>0.8267814076480018</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.004148132039388</v>
+        <v>2.918874079981296</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.424062027723735</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.296438298784672</v>
+        <v>-3.454706730907133</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.105130283896118</v>
+        <v>1.041822911047134</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.043242953282641</v>
+        <v>0.9011195331858204</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.050007799693319</v>
+        <v>2.964733747635227</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.584619798744946</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.268025035684788</v>
+        <v>-3.426293467807249</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.277053360157282</v>
+        <v>1.213745987308298</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9842673905362118</v>
+        <v>0.8421439704393916</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.175180233066673</v>
+        <v>3.089906181008581</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.704732707962763</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.193242774659776</v>
+        <v>-3.351511206782237</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.427079173785105</v>
+        <v>1.36377180093612</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.059049651561224</v>
+        <v>0.9169262314644042</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.340162498899498</v>
+        <v>3.254888446841406</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.696440683976622</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.167158690395968</v>
+        <v>-3.325427122518429</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.429220783504487</v>
+        <v>1.365913410655502</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.059049651561224</v>
+        <v>0.9169262314644042</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.331870474913357</v>
+        <v>3.246596422855265</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.694633879560401</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.079280777286847</v>
+        <v>-3.237549209409308</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.462565144331915</v>
+        <v>1.39925777148293</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.174975293984576</v>
+        <v>1.032851873887755</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.399619055951147</v>
+        <v>3.314345003893055</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.712188285287193</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.070388315893564</v>
+        <v>-3.228656748016025</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.483676534616019</v>
+        <v>1.420369161767035</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.174975293984576</v>
+        <v>1.032851873887755</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.417173461677939</v>
+        <v>3.331899409619846</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.704043332691777</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.238864432863442</v>
+        <v>-3.397132864985903</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.408141135232652</v>
+        <v>1.344833762383668</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.147027458267995</v>
+        <v>1.004904038171175</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.392259807652574</v>
+        <v>3.306985755594482</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.685313029879639</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.792608240234002</v>
+        <v>-2.950876672356463</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.56791330947229</v>
+        <v>1.504605936623306</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.052308788598362</v>
+        <v>0.910185368501542</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.316698303038656</v>
+        <v>3.231424250980564</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.675977052376543</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.76988713655085</v>
+        <v>-2.928155568673311</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.567665773442456</v>
+        <v>1.504358400593471</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.052308788598362</v>
+        <v>0.910185368501542</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.307362325535561</v>
+        <v>3.222088273477469</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>2.834883178227712</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.899088949844892</v>
+        <v>-3.057357381967353</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.674891173976008</v>
+        <v>1.611583801127023</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.92310697530432</v>
+        <v>0.7809835552074997</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.388747363410304</v>
+        <v>3.303473311352212</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>2.871961000721359</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.924963348318918</v>
+        <v>-3.083231780441379</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.701619237080044</v>
+        <v>1.638311864231059</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9680185840160611</v>
+        <v>0.8258951639192409</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.452772151130996</v>
+        <v>3.367498099072904</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>2.868636356710904</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.917908658103744</v>
+        <v>-3.076177090226205</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.701116469155658</v>
+        <v>1.637809096306674</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9750732742312349</v>
+        <v>0.8329498541344147</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.453680321249645</v>
+        <v>3.368406269191553</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>2.878642510355645</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.890957433777256</v>
+        <v>-3.049225865899717</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.721903112530995</v>
+        <v>1.658595739682011</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9899536202589541</v>
+        <v>0.8478302001621338</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.472614682511018</v>
+        <v>3.387340630452926</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.062745642500605</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.912501661608043</v>
+        <v>-3.070770093730504</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.89738855354364</v>
+        <v>1.834081180694656</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9899536202589541</v>
+        <v>0.8478302001621338</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.656717814655978</v>
+        <v>3.571443762597886</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.054862337403598</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.934909779412915</v>
+        <v>-3.093178211535376</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.880542001324684</v>
+        <v>1.8172346284757</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9899536202589541</v>
+        <v>0.8478302001621338</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.648834509558971</v>
+        <v>3.563560457500879</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.056916336953236</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.963134014990516</v>
+        <v>-3.121402447112977</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.871306306643282</v>
+        <v>1.807998933794297</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.007930372710263</v>
+        <v>0.8658069526134424</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.661674560579394</v>
+        <v>3.576400508521302</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.113170054675083</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.972574940879046</v>
+        <v>-3.130843373001507</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.923783654009717</v>
+        <v>1.860476281160732</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.130357490253654</v>
+        <v>0.9882340701568338</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.791384548827275</v>
+        <v>3.706110496769183</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.116061149220384</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.178813878667479</v>
+        <v>-3.33708231078994</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.844179173439644</v>
+        <v>1.78087180059066</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9241185524652205</v>
+        <v>0.7819951323684002</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.670532280699516</v>
+        <v>3.585258228641424</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.114172962114159</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.255143856268385</v>
+        <v>-3.413412288390846</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.811758995293057</v>
+        <v>1.748451622444072</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9241185524652205</v>
+        <v>0.7819951323684002</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.668644093593291</v>
+        <v>3.583370041535199</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.108993191717021</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.410100641668514</v>
+        <v>-3.568369073790975</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.744596510735868</v>
+        <v>1.681289137886883</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7691617670650912</v>
+        <v>0.627038346968271</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.570490251956076</v>
+        <v>3.485216199897984</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.107427201927174</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.571669067195769</v>
+        <v>-3.72993749931823</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.678403150735118</v>
+        <v>1.615095777886133</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6423788432672118</v>
+        <v>0.5002554231703916</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.492854507887501</v>
+        <v>3.407580455829409</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.120500608793092</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.679969729065889</v>
+        <v>-3.83823816118835</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.648156292852989</v>
+        <v>1.584848920004004</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6423788432672118</v>
+        <v>0.5002554231703916</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.505927914753419</v>
+        <v>3.420653862695327</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.112505805576032</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.839520801829406</v>
+        <v>-3.997789233951867</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.576341060530522</v>
+        <v>1.513033687681538</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4901011764054604</v>
+        <v>0.3479777563086401</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.406566511419308</v>
+        <v>3.321292459361216</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.111029846703034</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.867421588938879</v>
+        <v>-4.025690021061339</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.563704786813735</v>
+        <v>1.50039741396475</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4555042522625256</v>
+        <v>0.3133808321657053</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.38433239806055</v>
+        <v>3.299058346002458</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.107794290680233</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.989947691641773</v>
+        <v>-4.148216123764233</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.511458789709776</v>
+        <v>1.448151416860792</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3329781495596317</v>
+        <v>0.1908547294628115</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.307581180416012</v>
+        <v>3.22230712835792</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.174500250270737</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.220462187827361</v>
+        <v>-4.378730619949822</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.485958950826044</v>
+        <v>1.42265157797706</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.102463653374043</v>
+        <v>-0.03965976672277727</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.235978442295163</v>
+        <v>3.15070439023707</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.314811969272584</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.569207273051805</v>
+        <v>-4.727475705174266</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.486772635738114</v>
+        <v>1.423465262889129</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.1484077206416751</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.311041388945671</v>
+        <v>3.225767336887579</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.383792238418224</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.723193690827945</v>
+        <v>-4.881462122950406</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.494158337773297</v>
+        <v>1.430850964924313</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.1484077206416751</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.380021658091311</v>
+        <v>3.294747606033219</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.369843440538344</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.927793125690954</v>
+        <v>-5.086061557813415</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.398369765948215</v>
+        <v>1.33506239309923</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.1484077206416751</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.366072860211432</v>
+        <v>3.28079880815334</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.381713929593758</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.180268279698678</v>
+        <v>-5.338536711821139</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.309250193400539</v>
+        <v>1.245942820551555</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.1484077206416751</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.377943349266846</v>
+        <v>3.292669297208754</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.382924464112702</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.47316403617809</v>
+        <v>-5.631432468300551</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.193302425327718</v>
+        <v>1.129995052478733</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.1484077206416751</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.37915388378579</v>
+        <v>3.293879831727697</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.387046206340024</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.659828164312898</v>
+        <v>-5.818096596435359</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.122758516301116</v>
+        <v>1.059451143452132</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.03302327136941474</v>
+        <v>-0.175146691466235</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.367232243518375</v>
+        <v>3.281958191460283</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.382124059076213</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.805848851226861</v>
+        <v>-5.964117283349322</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.059428094271721</v>
+        <v>0.9961207214227361</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.04210636316327171</v>
+        <v>-0.1842297832600919</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.35686024117825</v>
+        <v>3.271586189120158</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.544328115775257</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.897562860336446</v>
+        <v>-6.055831292458906</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.18494654732693</v>
+        <v>1.121639174477946</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.04210636316327171</v>
+        <v>-0.1842297832600919</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.519064297877294</v>
+        <v>3.433790245819202</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.539174753739071</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.929214519396416</v>
+        <v>-6.087482951518876</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.167132521666757</v>
+        <v>1.103825148817773</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.04727482040771191</v>
+        <v>-0.1893982405045321</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.510809861494444</v>
+        <v>3.425535809436352</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.549404171307562</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.998280573969352</v>
+        <v>-6.156549006091812</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.149735517406073</v>
+        <v>1.086428144557089</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1096456979013219</v>
+        <v>-0.2517691179981422</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.483616752566769</v>
+        <v>3.398342700508677</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.558329809763465</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.10025669621776</v>
+        <v>-6.25852512834022</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.117870706962613</v>
+        <v>1.054563334113629</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2116218201497295</v>
+        <v>-0.3537452402465497</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.431356717673627</v>
+        <v>3.346082665615535</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.55048269700764</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.990250412740538</v>
+        <v>-6.148518844862998</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.154026107597677</v>
+        <v>1.090718734748693</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1884172482324543</v>
+        <v>-0.3305406683292745</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.437432348068168</v>
+        <v>3.352158296010076</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.554732707729614</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.002780117852417</v>
+        <v>-6.161048549974877</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.1532642362749</v>
+        <v>1.089956863425916</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2022437476989773</v>
+        <v>-0.3443671677957976</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.433386459110229</v>
+        <v>3.348112407052136</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.56199359061215</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.70133339238058</v>
+        <v>-5.85960182450304</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.281103809346171</v>
+        <v>1.217796436497187</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.09920297777285991</v>
+        <v>-0.04292044232396031</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.621515377275867</v>
+        <v>3.536241325217774</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.562964768364861</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.725923636615764</v>
+        <v>-5.884192068738224</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.272238889404808</v>
+        <v>1.208931516555824</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.09920297777285991</v>
+        <v>-0.04292044232396031</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.622486555028577</v>
+        <v>3.537212502970485</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.563807672744617</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.674885260609243</v>
+        <v>-5.833153692731703</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.293497144187171</v>
+        <v>1.230189771338187</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.09920297777285991</v>
+        <v>-0.04292044232396031</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.623329459408333</v>
+        <v>3.538055407350241</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.582845771618762</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.646036583785783</v>
+        <v>-5.804305015908243</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.324074713790701</v>
+        <v>1.260767340941717</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1280516545963202</v>
+        <v>-0.01407176550050004</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.659676764376554</v>
+        <v>3.574402712318462</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.399029767742697</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.549401671767143</v>
+        <v>-5.707670103889603</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.178912674722091</v>
+        <v>1.115605301873107</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2246865666149601</v>
+        <v>0.0825631465181399</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.533841707711673</v>
+        <v>3.448567655653581</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.402531811816661</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.480363660818675</v>
+        <v>-5.638632092941135</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.210029923175443</v>
+        <v>1.146722550326459</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2937245775634282</v>
+        <v>0.151601157466608</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.578766558354718</v>
+        <v>3.493492506296626</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.386958630892743</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.461576560449736</v>
+        <v>-5.619844992572196</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.201971582399101</v>
+        <v>1.138664209550117</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3125116779323667</v>
+        <v>0.1703882578355465</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.574465637652164</v>
+        <v>3.489191585594071</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.386146341329173</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.384477958907864</v>
+        <v>-5.542746391030324</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.23199873345228</v>
+        <v>1.168691360603296</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3125116779323667</v>
+        <v>0.1703882578355465</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.573653348088593</v>
+        <v>3.488379296030501</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.396015120454245</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.394863153797753</v>
+        <v>-5.553131585920213</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.237713434621396</v>
+        <v>1.174406061772412</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3021264830424774</v>
+        <v>0.1600030629456571</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.577291010279732</v>
+        <v>3.49201695822164</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.466852126230671</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.413451312519978</v>
+        <v>-5.571719744642438</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.301115176908931</v>
+        <v>1.237807804059947</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.283538324320252</v>
+        <v>0.1414149042234318</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.636975120822822</v>
+        <v>3.55170106876473</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.463721137048969</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.413749859216014</v>
+        <v>-5.572018291338474</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.297864769048815</v>
+        <v>1.234557396199831</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2832397776242161</v>
+        <v>0.1411163575273959</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.633665003623499</v>
+        <v>3.548390951565407</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.468252031988361</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.312926725525586</v>
+        <v>-5.471195157648046</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.342724917464378</v>
+        <v>1.279417544615394</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2957039931085699</v>
+        <v>0.1535805730117497</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.645674427853503</v>
+        <v>3.560400375795411</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.468381285466904</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.122145364773178</v>
+        <v>-5.280413796895639</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.419166715243884</v>
+        <v>1.355859342394901</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4864853538609773</v>
+        <v>0.3443619337641571</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.76027249778349</v>
+        <v>3.674998445725398</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.015182006923757</v>
+        <v>-5.173450439046217</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.44178890412125</v>
+        <v>1.378481531272266</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5449499618207787</v>
+        <v>0.4028265417239585</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.775188108296968</v>
+        <v>3.689914056238876</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.959851419021994</v>
+        <v>-5.118119851144455</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.498888075894013</v>
+        <v>1.435580703045029</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6002805497225409</v>
+        <v>0.4581571296257207</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.843353397650084</v>
+        <v>3.758079345591991</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.947797292109032</v>
+        <v>-5.106065724231492</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.497396294560636</v>
+        <v>1.434088921711652</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6123346766355037</v>
+        <v>0.4702112565386835</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.844272441699299</v>
+        <v>3.758998389641207</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.025152782237001</v>
+        <v>-5.183421214359461</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.468334728693584</v>
+        <v>1.4050273558446</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5349791865075343</v>
+        <v>0.3928557664107141</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.799739777806653</v>
+        <v>3.714465725748561</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.957104219545471</v>
+        <v>-5.115372651667931</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.508405179648078</v>
+        <v>1.445097806799094</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.4609043291022439</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.853419941299454</v>
+        <v>3.768145889241362</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.188704612714972</v>
+        <v>-5.346973044837432</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.435967692553872</v>
+        <v>1.372660319704889</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.4609043291022439</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.873622611473048</v>
+        <v>3.788348559414956</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.238756158244191</v>
+        <v>-5.397024590366652</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.399553310409066</v>
+        <v>1.336245937560082</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.4609043291022439</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.85722884753993</v>
+        <v>3.771954795481838</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.413862990820636</v>
+        <v>-5.572131422943096</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.289762490971955</v>
+        <v>1.226455118122971</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.4609043291022439</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.817480761133397</v>
+        <v>3.732206709075304</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.217762837390113</v>
+        <v>-5.376031269512573</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.375225171341104</v>
+        <v>1.31191779849212</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.799127902629587</v>
+        <v>0.6570044825327668</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.94216347218865</v>
+        <v>3.856889420130558</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.064737445276829</v>
+        <v>-5.223005877399289</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.535606327759323</v>
+        <v>1.472298954910339</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9521532947428711</v>
+        <v>0.8100298746460509</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.133149707029525</v>
+        <v>4.047875654971433</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.093044759150099</v>
+        <v>-5.251313191272559</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.711749627118307</v>
+        <v>1.648442254269323</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9521532947428711</v>
+        <v>0.8100298746460509</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.320615931937818</v>
+        <v>4.235341879879726</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.259637984263621</v>
+        <v>-5.417906416386082</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.614515288426981</v>
+        <v>1.551207915577997</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.6434366495325285</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.190062948223787</v>
+        <v>4.104788896165695</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.236602190902055</v>
+        <v>-5.394870623024516</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.627406008433325</v>
+        <v>1.564098635584341</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.6434366495325285</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.193739350885505</v>
+        <v>4.108465298827412</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.207356210446359</v>
+        <v>-5.365624642568819</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.636722455739099</v>
+        <v>1.573415082890115</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.6434366495325285</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.191357406009</v>
+        <v>4.106083353950908</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.31428175832421</v>
+        <v>-5.47255019044667</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.591245475745593</v>
+        <v>1.527938102896609</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6786345217514974</v>
+        <v>0.5365111016546772</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.124495316439925</v>
+        <v>4.039221264381832</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.459300316831459</v>
+        <v>-5.617568748953919</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.534666854485928</v>
+        <v>1.471359481636944</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5336159632442489</v>
+        <v>0.3914925431474287</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.038912983478809</v>
+        <v>3.953638931420717</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.577642082616176</v>
+        <v>-5.735910514738636</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.587261387429794</v>
+        <v>1.52395401458081</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.4021785817103187</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.145255845874297</v>
+        <v>4.059981793816204</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.629052504936884</v>
+        <v>-5.787320937059344</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.56448291562745</v>
+        <v>1.501175542778466</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.4021785817103187</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.143041543000235</v>
+        <v>4.057767490942143</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.708471956144636</v>
+        <v>-5.866740388267096</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.532618263218639</v>
+        <v>1.469310890369655</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.4021785817103187</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.142944671074525</v>
+        <v>4.057670619016433</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.803934954061853</v>
+        <v>-5.962203386184314</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.494426957609794</v>
+        <v>1.431119584760811</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.4021785817103187</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.142938564632567</v>
+        <v>4.057664512574475</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.739559043211139</v>
+        <v>-5.897827475333599</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.518273718512691</v>
+        <v>1.454966345663707</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6086779126578541</v>
+        <v>0.4665544925610339</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.179660507705607</v>
+        <v>4.094386455647515</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.794928205343332</v>
+        <v>-5.953196637465792</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.50185987140754</v>
+        <v>1.438552498558556</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6086779126578541</v>
+        <v>0.4665544925610339</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.185394325453334</v>
+        <v>4.100120273395242</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.813146672340941</v>
+        <v>-5.971415104463401</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.494110847951429</v>
+        <v>1.430803475102445</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.4414480553051917</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.169868826442761</v>
+        <v>4.084594774384669</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.77446323699701</v>
+        <v>-5.93273166911947</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.52945861493932</v>
+        <v>1.466151242090336</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.4414480553051917</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.18974321929308</v>
+        <v>4.104469167234988</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.668428241791701</v>
+        <v>-5.826696673914161</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.555573313546172</v>
+        <v>1.492265940697188</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.4414480553051917</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.173443919817807</v>
+        <v>4.088169867759715</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.485216578658606</v>
+        <v>-5.643485010781066</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.631288928263456</v>
+        <v>1.567981555414472</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.4414480553051917</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.175874869281854</v>
+        <v>4.090600817223761</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.413495131644755</v>
+        <v>-5.571763563767215</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.642921913148373</v>
+        <v>1.579614540299389</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6552929224158626</v>
+        <v>0.5131695023190423</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.201852143569541</v>
+        <v>4.116578091511449</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.391122106037049</v>
+        <v>-5.549390538159509</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.598786869312627</v>
+        <v>1.535479496463643</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6665486735287641</v>
+        <v>0.5244252534319439</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.155521340158454</v>
+        <v>4.070247288100362</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.424138401947793</v>
+        <v>-5.582406834070254</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.770778555833684</v>
+        <v>1.707471182984701</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5971112968620125</v>
+        <v>0.4549878767651923</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.299057119043757</v>
+        <v>4.213783066985665</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.412610766298185</v>
+        <v>-5.570879198420645</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.767310835921777</v>
+        <v>1.704003463072793</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6561119550633749</v>
+        <v>0.5139885349665547</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.326378739792824</v>
+        <v>4.241104687734732</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.509952267640553</v>
+        <v>-5.668220699763014</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.732042347906618</v>
+        <v>1.668734975057634</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6116917728978866</v>
+        <v>0.4695683528010663</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.303394743015319</v>
+        <v>4.218120690957227</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.59580829698052</v>
+        <v>-5.75407672910298</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.69895101836347</v>
+        <v>1.635643645514486</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5693157036717515</v>
+        <v>0.4271922835749313</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.279220183672477</v>
+        <v>4.193946131614385</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.604645094396639</v>
+        <v>-5.7629135265191</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.677835501217524</v>
+        <v>1.61452812836854</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5618735310304008</v>
+        <v>0.4197501109335806</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.257174081908168</v>
+        <v>4.171900029850076</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.696027656962098</v>
+        <v>-5.854296089084558</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.65144698723639</v>
+        <v>1.588139614387406</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5253086463110561</v>
+        <v>0.3831852262142359</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.245399662121611</v>
+        <v>4.160125610063519</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.684320938975092</v>
+        <v>-5.842589371097552</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.75825793225546</v>
+        <v>1.694950559406476</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.3948919442012423</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.354551950738083</v>
+        <v>4.269277898679991</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.755233012717369</v>
+        <v>-5.913501444839829</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.732925441489954</v>
+        <v>1.669618068640971</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.3948919442012423</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.357584289469488</v>
+        <v>4.272310237411395</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.248279904168708</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.765549110883721</v>
+        <v>-5.923817543006181</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.941703835501472</v>
+        <v>1.878396462652488</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.3948919442012423</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.570489122747546</v>
+        <v>4.485215070689454</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.247458571080798</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.765455142866348</v>
+        <v>-5.923723574988808</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.94092008962051</v>
+        <v>1.877612716771526</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.3952618055485603</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.569889706468026</v>
+        <v>4.484615654409934</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.241690557025152</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.909056306889734</v>
+        <v>-6.067324739012194</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.87771160995551</v>
+        <v>1.814404237106526</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.3952618055485603</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.56412169241238</v>
+        <v>4.478847640354288</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.241690557025152</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.908107883771695</v>
+        <v>-6.066376315894155</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.878090979202725</v>
+        <v>1.814783606353741</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.3952618055485603</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.56412169241238</v>
+        <v>4.478847640354288</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.254418165006244</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.008377701730716</v>
+        <v>-6.166646133853176</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.850710660000209</v>
+        <v>1.787403287151225</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.3952618055485603</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.576849300393472</v>
+        <v>4.49157524833538</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.256364163430631</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.002385454941904</v>
+        <v>-6.160653887064364</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.855053557140122</v>
+        <v>1.791746184291138</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.3952618055485603</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.57879529881786</v>
+        <v>4.493521246759768</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.2500182994484</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.913827493811136</v>
+        <v>-6.072095925933596</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.884130877610198</v>
+        <v>1.820823504761214</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.3952618055485603</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.572449434835629</v>
+        <v>4.487175382777536</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.249326976887396</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.896068416308062</v>
+        <v>-6.054336848430522</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.890543186050423</v>
+        <v>1.827235813201439</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.3952618055485603</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.571758112274624</v>
+        <v>4.486484060216532</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.262109162795983</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.796438265258995</v>
+        <v>-5.954706697381455</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.943177432378637</v>
+        <v>1.879870059529653</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.637015376694448</v>
+        <v>0.4948919565976277</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.644318388812652</v>
+        <v>4.559044336754559</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.451263428294709</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.845837773948006</v>
+        <v>-6.004106206070466</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.112571894401759</v>
+        <v>2.049264521552775</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6472742101261927</v>
+        <v>0.5051507900293725</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.839627954370425</v>
+        <v>4.754353902312332</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.438452101397571</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.63915330030563</v>
+        <v>-5.79742173242809</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.182434356961571</v>
+        <v>2.119126984112587</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8539586837685683</v>
+        <v>0.7118352636717481</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.950827311658712</v>
+        <v>4.86555325960062</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.440453615051676</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.673310195303156</v>
+        <v>-5.831578627425616</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.170773112616666</v>
+        <v>2.107465739767682</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.6282514941309356</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.90267856358833</v>
+        <v>4.817404511530238</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.793950729041343</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.580720716241699</v>
+        <v>-5.738989148364159</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.561306018230916</v>
+        <v>2.497998645381932</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.6282514941309356</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.256175677577997</v>
+        <v>5.170901625519905</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.798513840608447</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.653881320014844</v>
+        <v>-5.812149752137304</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.536604888288761</v>
+        <v>2.473297515439777</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.6002302940966926</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.243926069124555</v>
+        <v>5.158652017066462</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.848343781931974</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.601665010218502</v>
+        <v>-5.759933442340962</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.607321353530825</v>
+        <v>2.544013980681841</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.6002302940966926</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.293756010448082</v>
+        <v>5.20848195838999</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.857157752141985</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.569767493133257</v>
+        <v>-5.728035925255717</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.628894330574934</v>
+        <v>2.56558695772595</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7742512312787586</v>
+        <v>0.6321278111819384</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.32170849090924</v>
+        <v>5.236434438851148</v>
       </c>
     </row>
     <row r="2094">
@@ -49713,16 +49713,16 @@
         <v>4.852795336181182</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.584522817333397</v>
+        <v>-5.742791249455857</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.618629784934075</v>
+        <v>2.555322412085091</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7742512312787586</v>
+        <v>0.6321278111819384</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.317346074948437</v>
+        <v>5.232072022890345</v>
       </c>
     </row>
     <row r="2095">
@@ -49736,16 +49736,16 @@
         <v>4.843719839597462</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.535058193963486</v>
+        <v>-5.693326626085946</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.62934013769832</v>
+        <v>2.566032764849336</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8237158546486703</v>
+        <v>0.68159243455185</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.337949352386664</v>
+        <v>5.252675300328572</v>
       </c>
     </row>
     <row r="2096">
@@ -49759,16 +49759,16 @@
         <v>4.840127507312396</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.37195020180987</v>
+        <v>-5.53021863393233</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.6909910022747</v>
+        <v>2.627683629425716</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.9868238468022855</v>
+        <v>0.8447004267054653</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.432221815393768</v>
+        <v>5.346947763335676</v>
       </c>
     </row>
     <row r="2097">
@@ -49782,16 +49782,16 @@
         <v>4.849174544003525</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.351307111008643</v>
+        <v>-5.509575543131103</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.70829527528632</v>
+        <v>2.644987902437336</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.9868238468022855</v>
+        <v>0.8447004267054653</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.441268852084896</v>
+        <v>5.355994800026804</v>
       </c>
     </row>
     <row r="2098">
@@ -49805,16 +49805,16 @@
         <v>4.850032008989646</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.414015027483201</v>
+        <v>-5.572283459605661</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.684069573682618</v>
+        <v>2.620762200833634</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9241159303277278</v>
+        <v>0.7819925102309075</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.404501567186283</v>
+        <v>5.31922751512819</v>
       </c>
     </row>
     <row r="2099">
@@ -49828,16 +49828,16 @@
         <v>4.812941425779998</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.366006903639508</v>
+        <v>-5.524275335761968</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.666182240010447</v>
+        <v>2.602874867161463</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9241159303277278</v>
+        <v>0.7819925102309075</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.367410983976635</v>
+        <v>5.282136931918543</v>
       </c>
     </row>
     <row r="2100">
@@ -49851,16 +49851,16 @@
         <v>4.816873679337949</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.287181246455917</v>
+        <v>-5.445449678578377</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.701644756441834</v>
+        <v>2.63833738359285</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.002941587511318</v>
+        <v>0.860818167414498</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.41863863184474</v>
+        <v>5.333364579786648</v>
       </c>
     </row>
     <row r="2101">
@@ -49874,16 +49874,16 @@
         <v>4.811772771944986</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.095246445202044</v>
+        <v>-5.253514877324504</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.77331776955042</v>
+        <v>2.710010396701436</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.002941587511318</v>
+        <v>0.860818167414498</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.413537724451777</v>
+        <v>5.328263672393684</v>
       </c>
     </row>
     <row r="2102">
@@ -49897,16 +49897,16 @@
         <v>4.807126681334081</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.977073067184117</v>
+        <v>-5.135341499306577</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.815941030146687</v>
+        <v>2.752633657297702</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.121114965529245</v>
+        <v>0.9789915454324253</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.479795660651629</v>
+        <v>5.394521608593537</v>
       </c>
     </row>
     <row r="2103">
@@ -49920,16 +49920,16 @@
         <v>4.836215274197108</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.863658384401385</v>
+        <v>-5.021926816523846</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.890395496122806</v>
+        <v>2.827088123273822</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.234529648311977</v>
+        <v>1.092406228215157</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.576933063184294</v>
+        <v>5.491659011126202</v>
       </c>
     </row>
     <row r="2104">
@@ -49943,16 +49943,16 @@
         <v>4.829775497208285</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.836609346708132</v>
+        <v>-4.994877778830592</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.894775334211285</v>
+        <v>2.8314679613623</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.26157868600523</v>
+        <v>1.11945526590841</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.586722708811424</v>
+        <v>5.501448656753332</v>
       </c>
     </row>
     <row r="2105">
@@ -49966,16 +49966,16 @@
         <v>4.829775497208285</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.842642626894902</v>
+        <v>-5.000911059017362</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.892362022136576</v>
+        <v>2.829054649287592</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.26157868600523</v>
+        <v>1.11945526590841</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.586722708811424</v>
+        <v>5.501448656753332</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.910975600932129</v>
+        <v>3.525194005201294</v>
       </c>
       <c r="C2106" t="n">
         <v>4.833413664350697</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.889625386560285</v>
+        <v>-4.902109887608193</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.877207085412835</v>
+        <v>2.872213284993673</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.214595926339848</v>
+        <v>1.21825643731758</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.562171220154606</v>
+        <v>5.564367526741246</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241004.xlsx
+++ b/tame_output/ON/bt/strategyON_20241004.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>63.7%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.2%</t>
+          <t>107.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-73.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>417.8%</t>
+          <t>421.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-651.8%</t>
+          <t>-640.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-89.0%</t>
+          <t>-84.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.2%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-394.1%</t>
+          <t>-367.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-102.2%</t>
+          <t>-97.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>121.0%</t>
+          <t>122.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>112.2%</t>
+          <t>111.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>110.4%</t>
+          <t>113.4%</t>
         </is>
       </c>
     </row>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108637</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232414</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631707943623</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839725</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388729</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626475</v>
+        <v>3.856161751626473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392988</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367686</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.611921115442204</v>
+        <v>-4.507460550996077</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.029017122313273</v>
+        <v>1.070801348091724</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.2642432373441193</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.99800785567689</v>
+        <v>3.032687935210375</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.488446844129186</v>
+        <v>-4.383986279683059</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.075404902058474</v>
+        <v>1.117189127836925</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.2642432373441193</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.995005926896884</v>
+        <v>3.029686006430368</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.43051101213097</v>
+        <v>-4.326050447684843</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.100158271868374</v>
+        <v>1.141942497646825</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2320049794710608</v>
+        <v>0.2898051120268685</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.011922088717147</v>
+        <v>3.046602168250632</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.297643323067692</v>
+        <v>-4.193182758621566</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.169199530295509</v>
+        <v>1.21098375607396</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2320049794710608</v>
+        <v>0.2898051120268685</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.02781627151897</v>
+        <v>3.062496351052455</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.177470239703194</v>
+        <v>-4.073009675257067</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.21841460808161</v>
+        <v>1.260198833860061</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3521780628355597</v>
+        <v>0.4099781953913675</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.101065965977972</v>
+        <v>3.135746045511457</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.042216878373217</v>
+        <v>-3.93775631392709</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.282604055175041</v>
+        <v>1.324388280953492</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.4874314241655369</v>
+        <v>0.5452315567213446</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.192306085337398</v>
+        <v>3.226986164870882</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.102091705730909</v>
+        <v>-3.997631141284782</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.24469161563339</v>
+        <v>1.28647584141184</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4275565968078447</v>
+        <v>0.4853567293636525</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.142418680324209</v>
+        <v>3.177098759857693</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674515</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.982271474820072</v>
+        <v>-3.877810910373945</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.307908877231933</v>
+        <v>1.349693103010384</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4275565968078447</v>
+        <v>0.4853567293636525</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.157707849558417</v>
+        <v>3.192387929091902</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.984741181281878</v>
+        <v>-3.880280616835751</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.214565193969652</v>
+        <v>1.256349419748103</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4250868903460386</v>
+        <v>0.4828870229018463</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.063870225003775</v>
+        <v>3.09855030453726</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.053111367605887</v>
+        <v>-3.948650803159761</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.10647898092535</v>
+        <v>1.148263206703801</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4921627219380613</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.988697505910805</v>
+        <v>3.02337758544429</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.164983647232038</v>
+        <v>-4.060523082785911</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.052166777706781</v>
+        <v>1.093951003485232</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4921627219380613</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.979134214542697</v>
+        <v>3.013814294076181</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.14900898174577</v>
+        <v>-4.044548417299644</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.025131168825316</v>
+        <v>1.066915394603766</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4921627219380613</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.945708739466724</v>
+        <v>2.980388819000209</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.153103528416768</v>
+        <v>-4.048642963970641</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.028060582148704</v>
+        <v>1.069844807927155</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4921627219380613</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.950275971458512</v>
+        <v>2.984956050991996</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.145179153831854</v>
+        <v>-4.040718589385727</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.006972360743877</v>
+        <v>1.048756586522328</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4921627219380613</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.926018000219719</v>
+        <v>2.960698079753203</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.138900951262005</v>
+        <v>-4.034440386815878</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9380219551732663</v>
+        <v>0.9798061809517171</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.4984409245079104</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.858323235163078</v>
+        <v>2.893003314696563</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.079048332058282</v>
+        <v>-3.974587767612155</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.972135389286888</v>
+        <v>1.013919615065339</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.4984409245079104</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.86849562159521</v>
+        <v>2.903175701128695</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742301</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.992804869031904</v>
+        <v>-3.888344304585777</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.001579045071299</v>
+        <v>1.04336327084975</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.4984409245079104</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.863441892169071</v>
+        <v>2.898121971702555</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.038111688430884</v>
+        <v>-3.933651123984757</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.975232092756233</v>
+        <v>1.017016318534684</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3998306289428718</v>
+        <v>0.4576307614986797</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.830731569808058</v>
+        <v>2.865411649341543</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.067144793133185</v>
+        <v>-3.962684228687058</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9641707239084141</v>
+        <v>1.005954949686865</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3998306289428718</v>
+        <v>0.4576307614986797</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.831283442841159</v>
+        <v>2.865963522374644</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.974334311682326</v>
+        <v>-3.869873747236199</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9305676083801235</v>
+        <v>0.972351834158574</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4926411103937312</v>
+        <v>0.550441242949539</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.816242423603041</v>
+        <v>2.850922503136525</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.018723781011754</v>
+        <v>-3.914263216565627</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9146852965729531</v>
+        <v>0.9564695223514037</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4482516410643035</v>
+        <v>0.5060517736201113</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.791482217929985</v>
+        <v>2.826162297463469</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.998220087126256</v>
+        <v>-3.89375952268013</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.917962482638875</v>
+        <v>0.9597467084173257</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4687553349498008</v>
+        <v>0.5265554675056087</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.798860142773006</v>
+        <v>2.833540222306491</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.081892183838589</v>
+        <v>-3.977431619392461</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8899849397846094</v>
+        <v>0.9317691655630602</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4687553349498008</v>
+        <v>0.5265554675056087</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.804351438603673</v>
+        <v>2.839031518137158</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.109672581739941</v>
+        <v>-4.005212017293815</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8903699823926072</v>
+        <v>0.9321542081710579</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4409749370484478</v>
+        <v>0.4987750696042557</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.799180401631401</v>
+        <v>2.833860481164885</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.22805325447008</v>
+        <v>-4.123592690023953</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6813734333012051</v>
+        <v>0.7231576590796558</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.4315572174532795</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.597205410341468</v>
+        <v>2.631885489874953</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.336667332913411</v>
+        <v>-4.232206768467284</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7580774626430784</v>
+        <v>0.799861688421529</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.4315572174532795</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.717355071060674</v>
+        <v>2.752035150594159</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.301258294665268</v>
+        <v>-4.196797730219141</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7867541040446584</v>
+        <v>0.8285383298231093</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.4315572174532795</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.731868097162997</v>
+        <v>2.766548176696482</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913428</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.309719463320729</v>
+        <v>-4.205258898874602</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.780789077924843</v>
+        <v>0.8225733037032936</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3652959162420105</v>
+        <v>0.4230960487978184</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.724210837312089</v>
+        <v>2.758890916845574</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.132603133285563</v>
+        <v>-4.028142568839436</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8483646387842116</v>
+        <v>0.8901488645626623</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3652959162420105</v>
+        <v>0.4230960487978184</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.720939866157391</v>
+        <v>2.755619945690876</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.177695378119108</v>
+        <v>-4.073234813672982</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8310111326127065</v>
+        <v>0.8727953583911572</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3033998730726207</v>
+        <v>0.3612000056284286</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.684485632017671</v>
+        <v>2.719165711551155</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011237</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.156588389002801</v>
+        <v>-3.893859392434214</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8332409035656438</v>
+        <v>0.9383325021930786</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.3180532111465192</v>
+        <v>0.5179767637991473</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.687064610168424</v>
+        <v>2.807018741760001</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.201602602523407</v>
+        <v>-3.93887360595482</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7960426734889914</v>
+        <v>0.9011342721164259</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.2877043158319146</v>
+        <v>0.4876278684845426</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.649662728311251</v>
+        <v>2.769616859902828</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509539</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.289613789082104</v>
+        <v>-4.026884792513517</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7665297612044581</v>
+        <v>0.8716213598318929</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2222278079727416</v>
+        <v>0.4221513606253697</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.616068385934693</v>
+        <v>2.73602251752627</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.390811570519277</v>
+        <v>-4.12808257395069</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7252545705260904</v>
+        <v>0.8303461691535252</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.1538189944274224</v>
+        <v>0.3537425470800505</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.574227019704003</v>
+        <v>2.69418115129558</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.384300603904964</v>
+        <v>-4.121571607336377</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7254589187261322</v>
+        <v>0.830550517353567</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.1538189944274224</v>
+        <v>0.3537425470800505</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.57182698125832</v>
+        <v>2.691781112849896</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.365262476197667</v>
+        <v>-4.10253347962908</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7295988890172962</v>
+        <v>0.834690487644731</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.09563538309622788</v>
+        <v>0.2955589357488559</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.533441533667848</v>
+        <v>2.653395665259425</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.417778278472487</v>
+        <v>-4.1550492819039</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8278869697415583</v>
+        <v>0.9329785683689931</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.09563538309622788</v>
+        <v>0.2955589357488559</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.652735935302038</v>
+        <v>2.772690066893615</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067861</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.421186589907067</v>
+        <v>-4.15845759333848</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.82735697415386</v>
+        <v>0.9324485727812948</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1281519521056053</v>
+        <v>0.3280755047582333</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.673079205693798</v>
+        <v>2.793033337285375</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.401830454013219</v>
+        <v>-4.139101457444633</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8411079589083248</v>
+        <v>0.9461995575357596</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1281519521056053</v>
+        <v>0.3280755047582333</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.679087736090724</v>
+        <v>2.799041867682301</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.475159982751312</v>
+        <v>-4.212430986182725</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7097263686902873</v>
+        <v>0.814817967317722</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.1285466145252272</v>
+        <v>0.3284701671778553</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.577274754819697</v>
+        <v>2.697228886411274</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.409870503348191</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.55898120402601</v>
+        <v>-4.296252207457424</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.585921597424039</v>
+        <v>0.6910131960514738</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.1285466145252272</v>
+        <v>0.3284701671778553</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.486998472063328</v>
+        <v>2.606952603654905</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.41053285173985</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.552828497973226</v>
+        <v>-4.290099501404639</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.5890450282368112</v>
+        <v>0.6941366268642459</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.1346993205780115</v>
+        <v>0.3346228732306396</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.491352444086657</v>
+        <v>2.611306575678234</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.40961332847996</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.569637796123728</v>
+        <v>-4.306908799555141</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.5814017857167206</v>
+        <v>0.6864933843441554</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.1178900224275098</v>
+        <v>0.3178135750801379</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.480347341936466</v>
+        <v>2.600301473528043</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.475948882276781</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.507339797347606</v>
+        <v>-4.244610800779019</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.6726565390239905</v>
+        <v>0.7777481376514253</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.1631842867019519</v>
+        <v>0.36310783935458</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.573859454297952</v>
+        <v>2.693813585889529</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.278240883990908</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.305549599682448</v>
+        <v>-4.042820603113861</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.5556646198041808</v>
+        <v>0.6607562184316156</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.3612024788711063</v>
+        <v>0.5611260315237343</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.494962371313572</v>
+        <v>2.614916502905149</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.348531116313083</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.356436312368642</v>
+        <v>-4.093707315800056</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.605600167051878</v>
+        <v>0.7106917656793128</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.3103157661849117</v>
+        <v>0.5102393188375398</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.53472057602403</v>
+        <v>2.654674707615607</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.363158852429127</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.269825569718836</v>
+        <v>-4.007096573150248</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6548722002278444</v>
+        <v>0.7599637988552794</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.38894149739007</v>
+        <v>0.5888650500426981</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.596523750863169</v>
+        <v>2.716477882454746</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.361694833253798</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.33003486772412</v>
+        <v>-4.067305871155533</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6293244618504021</v>
+        <v>0.7344160604778374</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3287321993847855</v>
+        <v>0.5286557520374136</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.55893415288467</v>
+        <v>2.678888284476247</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.360186451293727</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.280848219039769</v>
+        <v>-4.018119222471181</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6474907393640712</v>
+        <v>0.7525823379915064</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3287321993847855</v>
+        <v>0.5286557520374136</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.557425770924599</v>
+        <v>2.677379902516175</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316252</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
         <v>2.360049318729163</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.2364750874012</v>
+        <v>-3.973746090832613</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6651028594549349</v>
+        <v>0.7701944580823701</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3731053310233541</v>
+        <v>0.5730288836759821</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.583912517343176</v>
+        <v>2.703866648934753</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.354443112867754</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.2017437660827</v>
+        <v>-3.939014769514112</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6733891821209257</v>
+        <v>0.7784807807483609</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3731053310233541</v>
+        <v>0.5730288836759821</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.578306311481766</v>
+        <v>2.698260443073343</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.360824869895558</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.154088035521644</v>
+        <v>-3.891359038953056</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.6988332313731527</v>
+        <v>0.8039248300005877</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4207610615844097</v>
+        <v>0.6206846142370378</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.613281506846204</v>
+        <v>2.733235638437781</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.365717243270283</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.053569877022889</v>
+        <v>-3.790840880454302</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7439328681473794</v>
+        <v>0.8490244667748144</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5212792200831643</v>
+        <v>0.7212027727357924</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.678484775320182</v>
+        <v>2.798438906911759</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.352471915746155</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.037664547590537</v>
+        <v>-3.774935551021949</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7370496723961926</v>
+        <v>0.8421412710236278</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4421665593739254</v>
+        <v>0.6420901120265534</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.617771851370511</v>
+        <v>2.737725982962087</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.356569618356784</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.992826145982139</v>
+        <v>-3.730097149413551</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7590827356501804</v>
+        <v>0.8641743342776156</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4467099923187949</v>
+        <v>0.6466335449714229</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.624595613748061</v>
+        <v>2.744549745339638</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.360730557987862</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.012324602224147</v>
+        <v>-3.749595605655559</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7554442927844549</v>
+        <v>0.8605358914118901</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3986253510388906</v>
+        <v>0.5985489036915186</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.599905768611197</v>
+        <v>2.719859900202773</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.366610160515699</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.968121765138247</v>
+        <v>-3.705392768569659</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7790050301466522</v>
+        <v>0.8840966287740875</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.442828188124791</v>
+        <v>0.642751740777419</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.632307073390574</v>
+        <v>2.752261204982151</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.365020160984947</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.975681430975294</v>
+        <v>-3.712952434406706</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.774391164281081</v>
+        <v>0.8794827629085162</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4976315921346104</v>
+        <v>0.6975551447872383</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.663599116265713</v>
+        <v>2.78355324785729</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.416267926167986</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.817390013436022</v>
+        <v>-3.554661016867434</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8889554964798296</v>
+        <v>0.9940470951072649</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4976315921346104</v>
+        <v>0.6975551447872383</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.714846881448753</v>
+        <v>2.834801013040329</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.414708630762239</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.609748009801546</v>
+        <v>-3.347019013232957</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9704530025278733</v>
+        <v>1.075544601155308</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7052735957690865</v>
+        <v>0.9051971484217145</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.837872788223692</v>
+        <v>2.957826919815268</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
         <v>2.409656859000509</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.558715917079017</v>
+        <v>-3.295986920510429</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9858140678551544</v>
+        <v>1.09090566648259</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7563056884916145</v>
+        <v>0.9562292411442425</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.863440272095478</v>
+        <v>2.983394403687055</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.426844263093214</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.493491735951812</v>
+        <v>-3.230762739383223</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.029091144398742</v>
+        <v>1.134182743026177</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8215298696188201</v>
+        <v>1.021453422271448</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.919762184864507</v>
+        <v>3.039716316456083</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.422805235392495</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.456064715880678</v>
+        <v>-3.19333571931209</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.040022924726475</v>
+        <v>1.145114523353911</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8267814076480018</v>
+        <v>1.02670496030063</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.918874079981296</v>
+        <v>3.038828211572873</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.424062027723735</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.454706730907133</v>
+        <v>-3.191977734338544</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.041822911047134</v>
+        <v>1.146914509674569</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9011195331858204</v>
+        <v>1.101043085838448</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.964733747635227</v>
+        <v>3.084687879226804</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.584619798744946</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.426293467807249</v>
+        <v>-3.163564471238661</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.213745987308298</v>
+        <v>1.318837585935734</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8421439704393916</v>
+        <v>1.04206752309202</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.089906181008581</v>
+        <v>3.209860312600158</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957627</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.704732707962763</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.351511206782237</v>
+        <v>-3.088782210213648</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.36377180093612</v>
+        <v>1.468863399563556</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9169262314644042</v>
+        <v>1.116849784117032</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.254888446841406</v>
+        <v>3.374842578432983</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.696440683976622</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.325427122518429</v>
+        <v>-3.06269812594984</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.365913410655502</v>
+        <v>1.471005009282938</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9169262314644042</v>
+        <v>1.116849784117032</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.246596422855265</v>
+        <v>3.366550554446841</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.694633879560401</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.237549209409308</v>
+        <v>-2.97482021284072</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.39925777148293</v>
+        <v>1.504349370110366</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.032851873887755</v>
+        <v>1.232775426540383</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.314345003893055</v>
+        <v>3.434299135484632</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959858</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.712188285287193</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.228656748016025</v>
+        <v>-2.965927751447436</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.420369161767035</v>
+        <v>1.52546076039447</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.032851873887755</v>
+        <v>1.232775426540383</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.331899409619846</v>
+        <v>3.451853541211423</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.704043332691777</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.397132864985903</v>
+        <v>-3.134403868417314</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.344833762383668</v>
+        <v>1.449925361011103</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.004904038171175</v>
+        <v>1.204827590823802</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.306985755594482</v>
+        <v>3.426939887186058</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.685313029879639</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.950876672356463</v>
+        <v>-2.688147675787874</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.504605936623306</v>
+        <v>1.609697535250741</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.910185368501542</v>
+        <v>1.11010892115417</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.231424250980564</v>
+        <v>3.351378382572141</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.675977052376543</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.928155568673311</v>
+        <v>-2.665426572104722</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.504358400593471</v>
+        <v>1.609449999220906</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.910185368501542</v>
+        <v>1.11010892115417</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.222088273477469</v>
+        <v>3.342042405069045</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777674</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>2.834883178227712</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.057357381967353</v>
+        <v>-2.794628385398764</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.611583801127023</v>
+        <v>1.716675399754459</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7809835552074997</v>
+        <v>0.9809071078601275</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.303473311352212</v>
+        <v>3.423427442943789</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644414</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>2.871961000721359</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.083231780441379</v>
+        <v>-2.82050278387279</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.638311864231059</v>
+        <v>1.743403462858495</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8258951639192409</v>
+        <v>1.025818716571869</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.367498099072904</v>
+        <v>3.48745223066448</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799959</v>
       </c>
       <c r="C2001" t="n">
         <v>2.868636356710904</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.076177090226205</v>
+        <v>-2.813448093657616</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.637809096306674</v>
+        <v>1.742900694934109</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8329498541344147</v>
+        <v>1.032873406787042</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.368406269191553</v>
+        <v>3.488360400783129</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>2.878642510355645</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.049225865899717</v>
+        <v>-2.786496869331129</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.658595739682011</v>
+        <v>1.763687338309446</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8478302001621338</v>
+        <v>1.047753752814762</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.387340630452926</v>
+        <v>3.507294762044503</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.062745642500605</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.070770093730504</v>
+        <v>-2.808041097161916</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.834081180694656</v>
+        <v>1.939172779322091</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8478302001621338</v>
+        <v>1.047753752814762</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.571443762597886</v>
+        <v>3.691397894189462</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.054862337403598</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.093178211535376</v>
+        <v>-2.830449214966788</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.8172346284757</v>
+        <v>1.922326227103135</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8478302001621338</v>
+        <v>1.047753752814762</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.563560457500879</v>
+        <v>3.683514589092455</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.056916336953236</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.121402447112977</v>
+        <v>-2.858673450544388</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.807998933794297</v>
+        <v>1.913090532421733</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.8658069526134424</v>
+        <v>1.06573050526607</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.576400508521302</v>
+        <v>3.696354640112878</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.113170054675083</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.130843373001507</v>
+        <v>-2.868114376432918</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.860476281160732</v>
+        <v>1.965567879788168</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.9882340701568338</v>
+        <v>1.188157622809462</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.706110496769183</v>
+        <v>3.82606462836076</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.116061149220384</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.33708231078994</v>
+        <v>-3.074353314221351</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.78087180059066</v>
+        <v>1.885963399218095</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7819951323684002</v>
+        <v>0.981918685021028</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.585258228641424</v>
+        <v>3.705212360233001</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347708</v>
+        <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
         <v>3.114172962114159</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.413412288390846</v>
+        <v>-3.150683291822257</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.748451622444072</v>
+        <v>1.853543221071508</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7819951323684002</v>
+        <v>0.981918685021028</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.583370041535199</v>
+        <v>3.703324173126776</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887753</v>
+        <v>3.71065410488775</v>
       </c>
       <c r="C2009" t="n">
         <v>3.108993191717021</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.568369073790975</v>
+        <v>-3.305640077222387</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.681289137886883</v>
+        <v>1.786380736514319</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.627038346968271</v>
+        <v>0.8269618996208987</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.485216199897984</v>
+        <v>3.605170331489561</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343071</v>
+        <v>3.712897612343068</v>
       </c>
       <c r="C2010" t="n">
         <v>3.107427201927174</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.72993749931823</v>
+        <v>-3.467208502749642</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.615095777886133</v>
+        <v>1.720187376513569</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.5002554231703916</v>
+        <v>0.7001789758230194</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.407580455829409</v>
+        <v>3.527534587420985</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389354</v>
+        <v>3.754596135389351</v>
       </c>
       <c r="C2011" t="n">
         <v>3.120500608793092</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.83823816118835</v>
+        <v>-3.575509164619761</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.584848920004004</v>
+        <v>1.68994051863144</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.5002554231703916</v>
+        <v>0.7001789758230194</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.420653862695327</v>
+        <v>3.540607994286904</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378386</v>
       </c>
       <c r="C2012" t="n">
         <v>3.112505805576032</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.997789233951867</v>
+        <v>-3.735060237383278</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.513033687681538</v>
+        <v>1.618125286308973</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3479777563086401</v>
+        <v>0.5479013089612679</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.321292459361216</v>
+        <v>3.441246590952793</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.71581989500697</v>
       </c>
       <c r="C2013" t="n">
         <v>3.111029846703034</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.025690021061339</v>
+        <v>-3.762961024492751</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.50039741396475</v>
+        <v>1.605489012592186</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3133808321657053</v>
+        <v>0.5133043848183331</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.299058346002458</v>
+        <v>3.419012477594034</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787383</v>
       </c>
       <c r="C2014" t="n">
         <v>3.107794290680233</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.148216123764233</v>
+        <v>-3.885487127195645</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.448151416860792</v>
+        <v>1.553243015488227</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.1908547294628115</v>
+        <v>0.3907782821154392</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.22230712835792</v>
+        <v>3.342261259949497</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585932</v>
       </c>
       <c r="C2015" t="n">
         <v>3.174500250270737</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.378730619949822</v>
+        <v>-4.116001623381234</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.42265157797706</v>
+        <v>1.527743176604495</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.03965976672277727</v>
+        <v>0.1602637859298505</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.15070439023707</v>
+        <v>3.270658521828647</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814666</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
         <v>3.314811969272584</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.727475705174266</v>
+        <v>-4.464746708605677</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.423465262889129</v>
+        <v>1.528556861516565</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.1484077206416751</v>
+        <v>0.05151583201095267</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.225767336887579</v>
+        <v>3.345721468479156</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237091</v>
       </c>
       <c r="C2017" t="n">
         <v>3.383792238418224</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.881462122950406</v>
+        <v>-4.618733126381818</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.430850964924313</v>
+        <v>1.535942563551749</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.1484077206416751</v>
+        <v>0.05151583201095267</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.294747606033219</v>
+        <v>3.414701737624795</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
         <v>3.369843440538344</v>
       </c>
       <c r="D2018" t="n">
-        <v>-5.086061557813415</v>
+        <v>-4.823332561244826</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.33506239309923</v>
+        <v>1.440153991726666</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.1484077206416751</v>
+        <v>0.05151583201095267</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.28079880815334</v>
+        <v>3.400752939744916</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.65633273360975</v>
       </c>
       <c r="C2019" t="n">
         <v>3.381713929593758</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.338536711821139</v>
+        <v>-5.075807715252551</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.245942820551555</v>
+        <v>1.35103441917899</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.1484077206416751</v>
+        <v>0.05151583201095267</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.292669297208754</v>
+        <v>3.41262342880033</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973153</v>
       </c>
       <c r="C2020" t="n">
         <v>3.382924464112702</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.631432468300551</v>
+        <v>-5.368703471731963</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.129995052478733</v>
+        <v>1.235086651106169</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.1484077206416751</v>
+        <v>0.05151583201095267</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.293879831727697</v>
+        <v>3.413833963319274</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.387046206340024</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.818096596435359</v>
+        <v>-5.555367599866771</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.059451143452132</v>
+        <v>1.164542742079567</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.175146691466235</v>
+        <v>0.02477686118639277</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.281958191460283</v>
+        <v>3.401912323051859</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.382124059076213</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.964117283349322</v>
+        <v>-5.701388286780733</v>
       </c>
       <c r="E2022" t="n">
-        <v>0.9961207214227361</v>
+        <v>1.101212320050172</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.1842297832600919</v>
+        <v>0.01569376939253581</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.271586189120158</v>
+        <v>3.391540320711735</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
         <v>3.544328115775257</v>
       </c>
       <c r="D2023" t="n">
-        <v>-6.055831292458906</v>
+        <v>-5.793102295890318</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.121639174477946</v>
+        <v>1.226730773105382</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.1842297832600919</v>
+        <v>0.01569376939253581</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.433790245819202</v>
+        <v>3.553744377410779</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071552</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.539174753739071</v>
       </c>
       <c r="D2024" t="n">
-        <v>-6.087482951518876</v>
+        <v>-5.824753954950287</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.103825148817773</v>
+        <v>1.208916747445208</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.1893982405045321</v>
+        <v>0.0105253121480956</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.425535809436352</v>
+        <v>3.545489941027929</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868149</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.549404171307562</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.156549006091812</v>
+        <v>-5.893820009523224</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.086428144557089</v>
+        <v>1.191519743184525</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.2517691179981422</v>
+        <v>-0.05184556534551443</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.398342700508677</v>
+        <v>3.518296832100254</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332695</v>
+        <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
         <v>3.558329809763465</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.25852512834022</v>
+        <v>-5.995796131771631</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.054563334113629</v>
+        <v>1.159654932741064</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.3537452402465497</v>
+        <v>-0.153821687593922</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.346082665615535</v>
+        <v>3.466036797207112</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231812</v>
+        <v>3.798296784231811</v>
       </c>
       <c r="C2027" t="n">
         <v>3.55048269700764</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.148518844862998</v>
+        <v>-5.88578984829441</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.090718734748693</v>
+        <v>1.195810333376128</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.3305406683292745</v>
+        <v>-0.1306171156766468</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.352158296010076</v>
+        <v>3.472112427601652</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.554732707729614</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.161048549974877</v>
+        <v>-5.898319553406289</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.089956863425916</v>
+        <v>1.195048462053351</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.3443671677957976</v>
+        <v>-0.1444436151431698</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.348112407052136</v>
+        <v>3.468066538643713</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
         <v>3.56199359061215</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.85960182450304</v>
+        <v>-5.596872827934451</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.217796436497187</v>
+        <v>1.322888035124622</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.04292044232396031</v>
+        <v>0.1570031103286674</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.536241325217774</v>
+        <v>3.656195456809351</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.562964768364861</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.884192068738224</v>
+        <v>-5.621463072169635</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.208931516555824</v>
+        <v>1.314023115183259</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.04292044232396031</v>
+        <v>0.1570031103286674</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.537212502970485</v>
+        <v>3.657166634562062</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
         <v>3.563807672744617</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.833153692731703</v>
+        <v>-5.570424696163115</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.230189771338187</v>
+        <v>1.335281369965623</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.04292044232396031</v>
+        <v>0.1570031103286674</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.538055407350241</v>
+        <v>3.658009538941817</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.582845771618762</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.804305015908243</v>
+        <v>-5.541576019339654</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.260767340941717</v>
+        <v>1.365858939569152</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.01407176550050004</v>
+        <v>0.1858517871521277</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.574402712318462</v>
+        <v>3.694356843910039</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.399029767742697</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.707670103889603</v>
+        <v>-5.444941107321014</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.115605301873107</v>
+        <v>1.220696900500543</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.0825631465181399</v>
+        <v>0.2824866991707676</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.448567655653581</v>
+        <v>3.568521787245158</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077642</v>
+        <v>3.80468896107764</v>
       </c>
       <c r="C2034" t="n">
         <v>3.402531811816661</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.638632092941135</v>
+        <v>-5.375903096372546</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.146722550326459</v>
+        <v>1.251814148953894</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.151601157466608</v>
+        <v>0.3515247101192357</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.493492506296626</v>
+        <v>3.613446637888202</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833462</v>
+        <v>3.77502886083346</v>
       </c>
       <c r="C2035" t="n">
         <v>3.386958630892743</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.619844992572196</v>
+        <v>-5.357115996003608</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.138664209550117</v>
+        <v>1.243755808177552</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.1703882578355465</v>
+        <v>0.3703118104881742</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.489191585594071</v>
+        <v>3.609145717185648</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
         <v>3.386146341329173</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.542746391030324</v>
+        <v>-5.280017394461735</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.168691360603296</v>
+        <v>1.273782959230731</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.1703882578355465</v>
+        <v>0.3703118104881742</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.488379296030501</v>
+        <v>3.608333427622078</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.396015120454245</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.553131585920213</v>
+        <v>-5.290402589351625</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.174406061772412</v>
+        <v>1.279497660399848</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.1600030629456571</v>
+        <v>0.3599266155982849</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.49201695822164</v>
+        <v>3.611971089813216</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735285</v>
+        <v>3.834415493735283</v>
       </c>
       <c r="C2038" t="n">
         <v>3.466852126230671</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.571719744642438</v>
+        <v>-5.30899074807385</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.237807804059947</v>
+        <v>1.342899402687383</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1414149042234318</v>
+        <v>0.3413384568760595</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.55170106876473</v>
+        <v>3.671655200356307</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.463721137048969</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.572018291338474</v>
+        <v>-5.309289294769886</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.234557396199831</v>
+        <v>1.339648994827267</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.1411163575273959</v>
+        <v>0.3410399101800236</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.548390951565407</v>
+        <v>3.668345083156983</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.81564321210886</v>
+        <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
         <v>3.468252031988361</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.471195157648046</v>
+        <v>-5.208466161079458</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.279417544615394</v>
+        <v>1.38450914324283</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.1535805730117497</v>
+        <v>0.3535041256643774</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.560400375795411</v>
+        <v>3.680354507386987</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121471</v>
+        <v>3.807356168121469</v>
       </c>
       <c r="C2041" t="n">
         <v>3.468381285466904</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.280413796895639</v>
+        <v>-5.01768480032705</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.355859342394901</v>
+        <v>1.460950941022336</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.3443619337641571</v>
+        <v>0.5442854864167848</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.674998445725398</v>
+        <v>3.794952577316975</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906084</v>
+        <v>3.775233033906082</v>
       </c>
       <c r="C2042" t="n">
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.173450439046217</v>
+        <v>-4.910721442477628</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.378481531272266</v>
+        <v>1.483573129899701</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.4028265417239585</v>
+        <v>0.6027500943765862</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.689914056238876</v>
+        <v>3.809868187830452</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912989</v>
+        <v>3.785761685912987</v>
       </c>
       <c r="C2043" t="n">
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.118119851144455</v>
+        <v>-4.855390854575866</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.435580703045029</v>
+        <v>1.540672301672464</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.4581571296257207</v>
+        <v>0.6580806822783484</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.758079345591991</v>
+        <v>3.878033477183568</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539898</v>
+        <v>3.743767956539896</v>
       </c>
       <c r="C2044" t="n">
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-5.106065724231492</v>
+        <v>-4.843336727662903</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.434088921711652</v>
+        <v>1.539180520339087</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.4702112565386835</v>
+        <v>0.6701348091913112</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.758998389641207</v>
+        <v>3.878952521232784</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811013</v>
+        <v>3.725010844811012</v>
       </c>
       <c r="C2045" t="n">
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.183421214359461</v>
+        <v>-4.920692217790872</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.4050273558446</v>
+        <v>1.510118954472035</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.3928557664107141</v>
+        <v>0.5927793190633418</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.714465725748561</v>
+        <v>3.834419857340138</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382924</v>
+        <v>3.612322444382922</v>
       </c>
       <c r="C2046" t="n">
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-5.115372651667931</v>
+        <v>-4.852643655099342</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.445097806799094</v>
+        <v>1.55018940542653</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.4609043291022439</v>
+        <v>0.6608278817548716</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.768145889241362</v>
+        <v>3.888100020832938</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013431</v>
+        <v>3.64525678001343</v>
       </c>
       <c r="C2047" t="n">
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.346973044837432</v>
+        <v>-5.084244048268843</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.372660319704889</v>
+        <v>1.477751918332324</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.4609043291022439</v>
+        <v>0.6608278817548716</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.788348559414956</v>
+        <v>3.908302691006532</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.397024590366652</v>
+        <v>-5.134295593798063</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.336245937560082</v>
+        <v>1.441337536187518</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.4609043291022439</v>
+        <v>0.6608278817548716</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.771954795481838</v>
+        <v>3.891908927073414</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800098</v>
+        <v>3.670048702800096</v>
       </c>
       <c r="C2049" t="n">
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.572131422943096</v>
+        <v>-5.309402426374508</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.226455118122971</v>
+        <v>1.331546716750406</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.4609043291022439</v>
+        <v>0.6608278817548716</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.732206709075304</v>
+        <v>3.852160840666881</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.74557314866085</v>
+        <v>3.745573148660848</v>
       </c>
       <c r="C2050" t="n">
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.376031269512573</v>
+        <v>-5.113302272943985</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.31191779849212</v>
+        <v>1.417009397119556</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.6570044825327668</v>
+        <v>0.8569280351853945</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.856889420130558</v>
+        <v>3.976843551722134</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.223005877399289</v>
+        <v>-4.9602768808307</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.472298954910339</v>
+        <v>1.577390553537774</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8100298746460509</v>
+        <v>1.009953427298679</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.047875654971433</v>
+        <v>4.16782978656301</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791147</v>
       </c>
       <c r="C2052" t="n">
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.251313191272559</v>
+        <v>-4.988584194703971</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.648442254269323</v>
+        <v>1.753533852896759</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8100298746460509</v>
+        <v>1.009953427298679</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.235341879879726</v>
+        <v>4.355296011471302</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620433</v>
       </c>
       <c r="C2053" t="n">
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.417906416386082</v>
+        <v>-5.155177419817493</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.551207915577997</v>
+        <v>1.656299514205432</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.6434366495325285</v>
+        <v>0.8433602021851561</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.104788896165695</v>
+        <v>4.224743027757271</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.394870623024516</v>
+        <v>-5.132141626455927</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.564098635584341</v>
+        <v>1.669190234211777</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.6434366495325285</v>
+        <v>0.8433602021851561</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.108465298827412</v>
+        <v>4.228419430418989</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.365624642568819</v>
+        <v>-5.10289564600023</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.573415082890115</v>
+        <v>1.67850668151755</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.6434366495325285</v>
+        <v>0.8433602021851561</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.106083353950908</v>
+        <v>4.226037485542484</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.699404642256371</v>
       </c>
       <c r="C2056" t="n">
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.47255019044667</v>
+        <v>-5.209821193878081</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.527938102896609</v>
+        <v>1.633029701524045</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.5365111016546772</v>
+        <v>0.7364346543073047</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.039221264381832</v>
+        <v>4.159175395973408</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701002</v>
+        <v>3.689942600701001</v>
       </c>
       <c r="C2057" t="n">
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.617568748953919</v>
+        <v>-5.35483975238533</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.471359481636944</v>
+        <v>1.57645108026438</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.3914925431474287</v>
+        <v>0.5914160958000562</v>
       </c>
       <c r="G2057" t="n">
-        <v>3.953638931420717</v>
+        <v>4.073593063012294</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.735910514738636</v>
+        <v>-5.473181518170048</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.52395401458081</v>
+        <v>1.629045613208246</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.4021785817103187</v>
+        <v>0.6021021343629462</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.059981793816204</v>
+        <v>4.179935925407781</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790806</v>
+        <v>3.714879051790804</v>
       </c>
       <c r="C2059" t="n">
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.787320937059344</v>
+        <v>-5.524591940490756</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.501175542778466</v>
+        <v>1.606267141405902</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.4021785817103187</v>
+        <v>0.6021021343629462</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.057767490942143</v>
+        <v>4.17772162253372</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437335</v>
+        <v>3.704757949437333</v>
       </c>
       <c r="C2060" t="n">
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.866740388267096</v>
+        <v>-5.604011391698507</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.469310890369655</v>
+        <v>1.57440248899709</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.4021785817103187</v>
+        <v>0.6021021343629462</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.057670619016433</v>
+        <v>4.177624750608009</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298403</v>
+        <v>3.736804952298401</v>
       </c>
       <c r="C2061" t="n">
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.962203386184314</v>
+        <v>-5.699474389615725</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.431119584760811</v>
+        <v>1.536211183388246</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.4021785817103187</v>
+        <v>0.6021021343629462</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.057664512574475</v>
+        <v>4.177618644166052</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218005</v>
+        <v>3.715372960218003</v>
       </c>
       <c r="C2062" t="n">
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.897827475333599</v>
+        <v>-5.63509847876501</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.454966345663707</v>
+        <v>1.560057944291143</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.4665544925610339</v>
+        <v>0.6664780452136614</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.094386455647515</v>
+        <v>4.214340587239092</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353541</v>
+        <v>3.736089413353539</v>
       </c>
       <c r="C2063" t="n">
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.953196637465792</v>
+        <v>-5.690467640897204</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.438552498558556</v>
+        <v>1.543644097185992</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.4665544925610339</v>
+        <v>0.6664780452136614</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.100120273395242</v>
+        <v>4.220074404986819</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113284</v>
+        <v>3.736822870113282</v>
       </c>
       <c r="C2064" t="n">
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.971415104463401</v>
+        <v>-5.708686107894812</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.430803475102445</v>
+        <v>1.535895073729881</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.4414480553051917</v>
+        <v>0.6413716079578192</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.084594774384669</v>
+        <v>4.204548905976245</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113692</v>
+        <v>3.79027250011369</v>
       </c>
       <c r="C2065" t="n">
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.93273166911947</v>
+        <v>-5.670002672550882</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.466151242090336</v>
+        <v>1.571242840717772</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.4414480553051917</v>
+        <v>0.6413716079578192</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.104469167234988</v>
+        <v>4.224423298826564</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016437</v>
+        <v>3.794486844016435</v>
       </c>
       <c r="C2066" t="n">
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.826696673914161</v>
+        <v>-5.563967677345572</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.492265940697188</v>
+        <v>1.597357539324623</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.4414480553051917</v>
+        <v>0.6413716079578192</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.088169867759715</v>
+        <v>4.208123999351292</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307669</v>
+        <v>3.794705093307667</v>
       </c>
       <c r="C2067" t="n">
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.643485010781066</v>
+        <v>-5.380756014212477</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.567981555414472</v>
+        <v>1.673073154041907</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.4414480553051917</v>
+        <v>0.6413716079578192</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.090600817223761</v>
+        <v>4.210554948815338</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863548</v>
       </c>
       <c r="C2068" t="n">
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.571763563767215</v>
+        <v>-5.309034567198626</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.579614540299389</v>
+        <v>1.684706138926825</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.5131695023190423</v>
+        <v>0.7130930549716699</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.116578091511449</v>
+        <v>4.236532223103025</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394111</v>
+        <v>3.72378970539411</v>
       </c>
       <c r="C2069" t="n">
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.549390538159509</v>
+        <v>-5.28666154159092</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.535479496463643</v>
+        <v>1.640571095091079</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.5244252534319439</v>
+        <v>0.7243488060845714</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.070247288100362</v>
+        <v>4.190201419691938</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456728</v>
       </c>
       <c r="C2070" t="n">
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.582406834070254</v>
+        <v>-5.319677837501665</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.707471182984701</v>
+        <v>1.812562781612136</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.4549878767651923</v>
+        <v>0.6549114294178198</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.213783066985665</v>
+        <v>4.333737198577242</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.71376253688368</v>
+        <v>3.713762536883679</v>
       </c>
       <c r="C2071" t="n">
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.570879198420645</v>
+        <v>-5.308150201852056</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.704003463072793</v>
+        <v>1.809095061700229</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.5139885349665547</v>
+        <v>0.7139120876191822</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.241104687734732</v>
+        <v>4.361058819326309</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236301</v>
+        <v>3.7171506992363</v>
       </c>
       <c r="C2072" t="n">
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.668220699763014</v>
+        <v>-5.405491703194425</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.668734975057634</v>
+        <v>1.773826573685069</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.4695683528010663</v>
+        <v>0.6694919054536939</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.218120690957227</v>
+        <v>4.338074822548804</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427688</v>
+        <v>3.705201079427686</v>
       </c>
       <c r="C2073" t="n">
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.75407672910298</v>
+        <v>-5.491347732534392</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.635643645514486</v>
+        <v>1.740735244141921</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.4271922835749313</v>
+        <v>0.6271158362275588</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.193946131614385</v>
+        <v>4.313900263205961</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610378</v>
       </c>
       <c r="C2074" t="n">
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.7629135265191</v>
+        <v>-5.500184529950511</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.61452812836854</v>
+        <v>1.719619726995975</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.4197501109335806</v>
+        <v>0.6196736635862081</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.171900029850076</v>
+        <v>4.291854161441653</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667458</v>
+        <v>3.715544411667456</v>
       </c>
       <c r="C2075" t="n">
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.854296089084558</v>
+        <v>-5.59156709251597</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.588139614387406</v>
+        <v>1.693231213014841</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.3831852262142359</v>
+        <v>0.5831087788668634</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.160125610063519</v>
+        <v>4.280079741655095</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889195</v>
+        <v>3.673978374889193</v>
       </c>
       <c r="C2076" t="n">
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.842589371097552</v>
+        <v>-5.579860374528963</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.694950559406476</v>
+        <v>1.800042158033912</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.3948919442012423</v>
+        <v>0.5948154968538698</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.269277898679991</v>
+        <v>4.389232030271567</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409571</v>
+        <v>3.682476099409569</v>
       </c>
       <c r="C2077" t="n">
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.913501444839829</v>
+        <v>-5.65077244827124</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.669618068640971</v>
+        <v>1.774709667268406</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.3948919442012423</v>
+        <v>0.5948154968538698</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.272310237411395</v>
+        <v>4.392264369002972</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452568</v>
       </c>
       <c r="C2078" t="n">
         <v>4.248279904168708</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.923817543006181</v>
+        <v>-5.661088546437592</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.878396462652488</v>
+        <v>1.983488061279923</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.3948919442012423</v>
+        <v>0.5948154968538698</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.485215070689454</v>
+        <v>4.60516920228103</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762291</v>
+        <v>3.623960959762289</v>
       </c>
       <c r="C2079" t="n">
         <v>4.247458571080798</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.923723574988808</v>
+        <v>-5.66099457842022</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.877612716771526</v>
+        <v>1.982704315398962</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.3952618055485603</v>
+        <v>0.5951853582011878</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.484615654409934</v>
+        <v>4.604569786001511</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884084</v>
+        <v>3.800870306884082</v>
       </c>
       <c r="C2080" t="n">
         <v>4.241690557025152</v>
       </c>
       <c r="D2080" t="n">
-        <v>-6.067324739012194</v>
+        <v>-5.804595742443605</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.814404237106526</v>
+        <v>1.919495835733962</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.3952618055485603</v>
+        <v>0.5951853582011878</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.478847640354288</v>
+        <v>4.598801771945864</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129648</v>
+        <v>3.671015692129646</v>
       </c>
       <c r="C2081" t="n">
         <v>4.241690557025152</v>
       </c>
       <c r="D2081" t="n">
-        <v>-6.066376315894155</v>
+        <v>-5.803647319325567</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.814783606353741</v>
+        <v>1.919875204981177</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.3952618055485603</v>
+        <v>0.5951853582011878</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.478847640354288</v>
+        <v>4.598801771945864</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052351</v>
+        <v>3.904173816052349</v>
       </c>
       <c r="C2082" t="n">
         <v>4.254418165006244</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.166646133853176</v>
+        <v>-5.903917137284587</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.787403287151225</v>
+        <v>1.892494885778661</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.3952618055485603</v>
+        <v>0.5951853582011878</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.49157524833538</v>
+        <v>4.611529379926957</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813495</v>
+        <v>3.740179607813493</v>
       </c>
       <c r="C2083" t="n">
         <v>4.256364163430631</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.160653887064364</v>
+        <v>-5.897924890495776</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.791746184291138</v>
+        <v>1.896837782918573</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.3952618055485603</v>
+        <v>0.5951853582011878</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.493521246759768</v>
+        <v>4.613475378351344</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537944</v>
+        <v>3.765050796537942</v>
       </c>
       <c r="C2084" t="n">
         <v>4.2500182994484</v>
       </c>
       <c r="D2084" t="n">
-        <v>-6.072095925933596</v>
+        <v>-5.809366929365008</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.820823504761214</v>
+        <v>1.925915103388649</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.3952618055485603</v>
+        <v>0.5951853582011878</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.487175382777536</v>
+        <v>4.607129514369113</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771816</v>
+        <v>3.758409170771814</v>
       </c>
       <c r="C2085" t="n">
         <v>4.249326976887396</v>
       </c>
       <c r="D2085" t="n">
-        <v>-6.054336848430522</v>
+        <v>-5.791607851861934</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.827235813201439</v>
+        <v>1.932327411828874</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.3952618055485603</v>
+        <v>0.5951853582011878</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.486484060216532</v>
+        <v>4.606438191808109</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.801340597109721</v>
+        <v>3.80134059710972</v>
       </c>
       <c r="C2086" t="n">
         <v>4.262109162795983</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.954706697381455</v>
+        <v>-5.691977700812866</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.879870059529653</v>
+        <v>1.984961658157088</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.4948919565976277</v>
+        <v>0.6948155092502553</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.559044336754559</v>
+        <v>4.678998468346136</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546843996</v>
+        <v>3.798465546843994</v>
       </c>
       <c r="C2087" t="n">
         <v>4.451263428294709</v>
       </c>
       <c r="D2087" t="n">
-        <v>-6.004106206070466</v>
+        <v>-5.741377209501877</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.049264521552775</v>
+        <v>2.15435612018021</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.5051507900293725</v>
+        <v>0.705074342682</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.754353902312332</v>
+        <v>4.874308033903909</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.77218650835186</v>
+        <v>3.772186508351858</v>
       </c>
       <c r="C2088" t="n">
         <v>4.438452101397571</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.79742173242809</v>
+        <v>-5.534692735859501</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.119126984112587</v>
+        <v>2.224218582740022</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.7118352636717481</v>
+        <v>0.9117588163243756</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.86555325960062</v>
+        <v>4.985507391192197</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.76339283855127</v>
+        <v>3.763392838551268</v>
       </c>
       <c r="C2089" t="n">
         <v>4.440453615051676</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.831578627425616</v>
+        <v>-5.568849630857027</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.107465739767682</v>
+        <v>2.212557338395117</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.6282514941309356</v>
+        <v>0.8281750467835631</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.817404511530238</v>
+        <v>4.937358643121814</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041111</v>
+        <v>3.805590565041109</v>
       </c>
       <c r="C2090" t="n">
         <v>4.793950729041343</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.738989148364159</v>
+        <v>-5.476260151795571</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.497998645381932</v>
+        <v>2.603090244009367</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.6282514941309356</v>
+        <v>0.8281750467835631</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.170901625519905</v>
+        <v>5.290855757111482</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497403</v>
+        <v>3.832164354497401</v>
       </c>
       <c r="C2091" t="n">
         <v>4.798513840608447</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.812149752137304</v>
+        <v>-5.549420755568716</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.473297515439777</v>
+        <v>2.578389114067213</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.6002302940966926</v>
+        <v>0.8001538467493201</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.158652017066462</v>
+        <v>5.278606148658039</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492295</v>
+        <v>3.858310890492294</v>
       </c>
       <c r="C2092" t="n">
         <v>4.848343781931974</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.759933442340962</v>
+        <v>-5.497204445772374</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.544013980681841</v>
+        <v>2.649105579309277</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.6002302940966926</v>
+        <v>0.8001538467493201</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.20848195838999</v>
+        <v>5.328436089981566</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436477</v>
+        <v>3.844935596436475</v>
       </c>
       <c r="C2093" t="n">
         <v>4.857157752141985</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.728035925255717</v>
+        <v>-5.465306928687128</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.56558695772595</v>
+        <v>2.670678556353386</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.6321278111819384</v>
+        <v>0.8320513638345659</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.236434438851148</v>
+        <v>5.356388570442725</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039486</v>
+        <v>3.848376866039485</v>
       </c>
       <c r="C2094" t="n">
         <v>4.852795336181182</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.742791249455857</v>
+        <v>-5.480062252887269</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.555322412085091</v>
+        <v>2.660414010712527</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.6321278111819384</v>
+        <v>0.8320513638345659</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.232072022890345</v>
+        <v>5.352026154481922</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524481</v>
+        <v>3.868153115524479</v>
       </c>
       <c r="C2095" t="n">
         <v>4.843719839597462</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.693326626085946</v>
+        <v>-5.430597629517357</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.566032764849336</v>
+        <v>2.671124363476771</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.68159243455185</v>
+        <v>0.8815159872044775</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.252675300328572</v>
+        <v>5.372629431920148</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867955</v>
+        <v>3.849040239867954</v>
       </c>
       <c r="C2096" t="n">
         <v>4.840127507312396</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.53021863393233</v>
+        <v>-5.267489637363742</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.627683629425716</v>
+        <v>2.732775228053152</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.8447004267054653</v>
+        <v>1.044623979358093</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.346947763335676</v>
+        <v>5.466901894927252</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232972</v>
+        <v>3.87020492823297</v>
       </c>
       <c r="C2097" t="n">
         <v>4.849174544003525</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.509575543131103</v>
+        <v>-5.246846546562514</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.644987902437336</v>
+        <v>2.750079501064771</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.8447004267054653</v>
+        <v>1.044623979358093</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.355994800026804</v>
+        <v>5.47594893161838</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179675</v>
+        <v>3.855534437179673</v>
       </c>
       <c r="C2098" t="n">
         <v>4.850032008989646</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.572283459605661</v>
+        <v>-5.309554463037072</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.620762200833634</v>
+        <v>2.725853799461069</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.7819925102309075</v>
+        <v>0.9819160628835352</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.31922751512819</v>
+        <v>5.439181646719767</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967722</v>
+        <v>3.884687848967721</v>
       </c>
       <c r="C2099" t="n">
         <v>4.812941425779998</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.524275335761968</v>
+        <v>-5.261546339193379</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.602874867161463</v>
+        <v>2.707966465788898</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.7819925102309075</v>
+        <v>0.9819160628835352</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.282136931918543</v>
+        <v>5.402091063510119</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018613</v>
+        <v>3.895362357018612</v>
       </c>
       <c r="C2100" t="n">
         <v>4.816873679337949</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.445449678578377</v>
+        <v>-5.182720682009789</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.63833738359285</v>
+        <v>2.743428982220285</v>
       </c>
       <c r="F2100" t="n">
-        <v>0.860818167414498</v>
+        <v>1.060741720067126</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.333364579786648</v>
+        <v>5.453318711378224</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075137</v>
+        <v>3.891610981075135</v>
       </c>
       <c r="C2101" t="n">
         <v>4.811772771944986</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.253514877324504</v>
+        <v>-4.990785880755915</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.710010396701436</v>
+        <v>2.815101995328872</v>
       </c>
       <c r="F2101" t="n">
-        <v>0.860818167414498</v>
+        <v>1.060741720067126</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.328263672393684</v>
+        <v>5.448217803985261</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435446</v>
+        <v>3.872432493435444</v>
       </c>
       <c r="C2102" t="n">
         <v>4.807126681334081</v>
       </c>
       <c r="D2102" t="n">
-        <v>-5.135341499306577</v>
+        <v>-4.872612502737988</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.752633657297702</v>
+        <v>2.857725255925137</v>
       </c>
       <c r="F2102" t="n">
-        <v>0.9789915454324253</v>
+        <v>1.178915098085053</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.394521608593537</v>
+        <v>5.514475740185113</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917735</v>
+        <v>3.859571723917733</v>
       </c>
       <c r="C2103" t="n">
         <v>4.836215274197108</v>
       </c>
       <c r="D2103" t="n">
-        <v>-5.021926816523846</v>
+        <v>-4.759197819955257</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.827088123273822</v>
+        <v>2.932179721901257</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.092406228215157</v>
+        <v>1.292329780867784</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.491659011126202</v>
+        <v>5.611613142717779</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.82800627401364</v>
+        <v>3.828006274013639</v>
       </c>
       <c r="C2104" t="n">
         <v>4.829775497208285</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.994877778830592</v>
+        <v>-4.732148782262003</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.8314679613623</v>
+        <v>2.936559559989735</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.11945526590841</v>
+        <v>1.319378818561038</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.501448656753332</v>
+        <v>5.621402788344908</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.823987445263771</v>
+        <v>3.82398744526377</v>
       </c>
       <c r="C2105" t="n">
         <v>4.829775497208285</v>
       </c>
       <c r="D2105" t="n">
-        <v>-5.000911059017362</v>
+        <v>-4.738182062448773</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.829054649287592</v>
+        <v>2.934146247915027</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.11945526590841</v>
+        <v>1.319378818561038</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.501448656753332</v>
+        <v>5.621402788344908</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.525194005201294</v>
+        <v>3.917830833263249</v>
       </c>
       <c r="C2106" t="n">
         <v>4.833413664350697</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.902109887608193</v>
+        <v>-4.790033838021935</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.872213284993673</v>
+        <v>2.917043704828175</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.21825643731758</v>
+        <v>1.267527042987877</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.564367526741246</v>
+        <v>5.593929890143423</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241004.xlsx
+++ b/tame_output/ON/bt/strategyON_20241004.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>64.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.5%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.2%</t>
+          <t>-73.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.8%</t>
+          <t>421.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-640.6%</t>
+          <t>-644.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-84.5%</t>
+          <t>-86.0%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-367.7%</t>
+          <t>-203.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-97.2%</t>
+          <t>-96.8%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>122.0%</t>
+          <t>122.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>111.1%</t>
+          <t>111.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>113.4%</t>
+          <t>113.6%</t>
         </is>
       </c>
     </row>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.76631707943623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626473</v>
+        <v>3.856161751626475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.507460550996077</v>
+        <v>-4.611921115442204</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.070801348091724</v>
+        <v>1.029017122313273</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2642432373441193</v>
+        <v>0.2064431047883115</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.032687935210375</v>
+        <v>2.99800785567689</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.383986279683059</v>
+        <v>-4.488446844129186</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.117189127836925</v>
+        <v>1.075404902058474</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2642432373441193</v>
+        <v>0.2064431047883115</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.029686006430368</v>
+        <v>2.995005926896884</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.326050447684843</v>
+        <v>-4.43051101213097</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.141942497646825</v>
+        <v>1.100158271868374</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2898051120268685</v>
+        <v>0.2320049794710608</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.046602168250632</v>
+        <v>3.011922088717147</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.193182758621566</v>
+        <v>-4.297643323067692</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.21098375607396</v>
+        <v>1.169199530295509</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2898051120268685</v>
+        <v>0.2320049794710608</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.062496351052455</v>
+        <v>3.02781627151897</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.073009675257067</v>
+        <v>-4.177470239703194</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.260198833860061</v>
+        <v>1.21841460808161</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4099781953913675</v>
+        <v>0.3521780628355597</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.135746045511457</v>
+        <v>3.101065965977972</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.93775631392709</v>
+        <v>-4.042216878373217</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.324388280953492</v>
+        <v>1.282604055175041</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5452315567213446</v>
+        <v>0.4874314241655369</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.226986164870882</v>
+        <v>3.192306085337398</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.997631141284782</v>
+        <v>-4.102091705730909</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.28647584141184</v>
+        <v>1.24469161563339</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4853567293636525</v>
+        <v>0.4275565968078447</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.177098759857693</v>
+        <v>3.142418680324209</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.877810910373945</v>
+        <v>-3.982271474820072</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.349693103010384</v>
+        <v>1.307908877231933</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4853567293636525</v>
+        <v>0.4275565968078447</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.192387929091902</v>
+        <v>3.157707849558417</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.880280616835751</v>
+        <v>-3.984741181281878</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.256349419748103</v>
+        <v>1.214565193969652</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4828870229018463</v>
+        <v>0.4250868903460386</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.09855030453726</v>
+        <v>3.063870225003775</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.948650803159761</v>
+        <v>-4.053111367605887</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.148263206703801</v>
+        <v>1.10647898092535</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4921627219380613</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.02337758544429</v>
+        <v>2.988697505910805</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.060523082785911</v>
+        <v>-4.164983647232038</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.093951003485232</v>
+        <v>1.052166777706781</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4921627219380613</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.013814294076181</v>
+        <v>2.979134214542697</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.044548417299644</v>
+        <v>-4.14900898174577</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.066915394603766</v>
+        <v>1.025131168825316</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4921627219380613</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.980388819000209</v>
+        <v>2.945708739466724</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.048642963970641</v>
+        <v>-4.153103528416768</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.069844807927155</v>
+        <v>1.028060582148704</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4921627219380613</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.984956050991996</v>
+        <v>2.950275971458512</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.040718589385727</v>
+        <v>-4.145179153831854</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.048756586522328</v>
+        <v>1.006972360743877</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4921627219380613</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.960698079753203</v>
+        <v>2.926018000219719</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.034440386815878</v>
+        <v>-4.138900951262005</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9798061809517171</v>
+        <v>0.9380219551732663</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4984409245079104</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.893003314696563</v>
+        <v>2.858323235163078</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.974587767612155</v>
+        <v>-4.079048332058282</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.013919615065339</v>
+        <v>0.972135389286888</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4984409245079104</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.903175701128695</v>
+        <v>2.86849562159521</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.786949957742301</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.888344304585777</v>
+        <v>-3.992804869031904</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.04336327084975</v>
+        <v>1.001579045071299</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4984409245079104</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.898121971702555</v>
+        <v>2.863441892169071</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.933651123984757</v>
+        <v>-4.038111688430884</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.017016318534684</v>
+        <v>0.975232092756233</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4576307614986797</v>
+        <v>0.3998306289428718</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.865411649341543</v>
+        <v>2.830731569808058</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.962684228687058</v>
+        <v>-4.067144793133185</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.005954949686865</v>
+        <v>0.9641707239084141</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4576307614986797</v>
+        <v>0.3998306289428718</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.865963522374644</v>
+        <v>2.831283442841159</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.869873747236199</v>
+        <v>-3.974334311682326</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.972351834158574</v>
+        <v>0.9305676083801235</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.550441242949539</v>
+        <v>0.4926411103937312</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.850922503136525</v>
+        <v>2.816242423603041</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.914263216565627</v>
+        <v>-4.018723781011754</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9564695223514037</v>
+        <v>0.9146852965729531</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5060517736201113</v>
+        <v>0.4482516410643035</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.826162297463469</v>
+        <v>2.791482217929985</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.89375952268013</v>
+        <v>-3.998220087126256</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9597467084173257</v>
+        <v>0.917962482638875</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5265554675056087</v>
+        <v>0.4687553349498008</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.833540222306491</v>
+        <v>2.798860142773006</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.977431619392461</v>
+        <v>-4.081892183838589</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9317691655630602</v>
+        <v>0.8899849397846094</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5265554675056087</v>
+        <v>0.4687553349498008</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.839031518137158</v>
+        <v>2.804351438603673</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.005212017293815</v>
+        <v>-4.109672581739941</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9321542081710579</v>
+        <v>0.8903699823926072</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4987750696042557</v>
+        <v>0.4409749370484478</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.833860481164885</v>
+        <v>2.799180401631401</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.123592690023953</v>
+        <v>-4.22805325447008</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7231576590796558</v>
+        <v>0.6813734333012051</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4315572174532795</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.631885489874953</v>
+        <v>2.597205410341468</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.232206768467284</v>
+        <v>-4.336667332913411</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.799861688421529</v>
+        <v>0.7580774626430784</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4315572174532795</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.752035150594159</v>
+        <v>2.717355071060674</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.196797730219141</v>
+        <v>-4.301258294665268</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8285383298231093</v>
+        <v>0.7867541040446584</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4315572174532795</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.766548176696482</v>
+        <v>2.731868097162997</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913428</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.205258898874602</v>
+        <v>-4.309719463320729</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8225733037032936</v>
+        <v>0.780789077924843</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4230960487978184</v>
+        <v>0.3652959162420105</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.758890916845574</v>
+        <v>2.724210837312089</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.028142568839436</v>
+        <v>-4.132603133285563</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8901488645626623</v>
+        <v>0.8483646387842116</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4230960487978184</v>
+        <v>0.3652959162420105</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.755619945690876</v>
+        <v>2.720939866157391</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.073234813672982</v>
+        <v>-4.177695378119108</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8727953583911572</v>
+        <v>0.8310111326127065</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3612000056284286</v>
+        <v>0.3033998730726207</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.719165711551155</v>
+        <v>2.684485632017671</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011237</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.893859392434214</v>
+        <v>-3.998319956880341</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9383325021930786</v>
+        <v>0.896548276414628</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5179767637991473</v>
+        <v>0.4601766312433394</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.807018741760001</v>
+        <v>2.772338662226516</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.93887360595482</v>
+        <v>-4.043334170400946</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9011342721164259</v>
+        <v>0.8593500463379753</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4876278684845426</v>
+        <v>0.4298277359287348</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.769616859902828</v>
+        <v>2.734936780369343</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.026884792513517</v>
+        <v>-4.131345356959644</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8716213598318929</v>
+        <v>0.8298371340534423</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4221513606253697</v>
+        <v>0.3643512280695618</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.73602251752627</v>
+        <v>2.701342437992785</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.12808257395069</v>
+        <v>-4.232543138396816</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8303461691535252</v>
+        <v>0.7885619433750746</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3537425470800505</v>
+        <v>0.2959424145242426</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.69418115129558</v>
+        <v>2.659501071762095</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.121571607336377</v>
+        <v>-4.226032171782504</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.830550517353567</v>
+        <v>0.7887662915751164</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3537425470800505</v>
+        <v>0.2959424145242426</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.691781112849896</v>
+        <v>2.657101033316412</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.10253347962908</v>
+        <v>-4.206994044075206</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.834690487644731</v>
+        <v>0.7929062618662801</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2955589357488559</v>
+        <v>0.2377588031930481</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.653395665259425</v>
+        <v>2.61871558572594</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.1550492819039</v>
+        <v>-4.259509846350027</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9329785683689931</v>
+        <v>0.8911943425905424</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2955589357488559</v>
+        <v>0.2377588031930481</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.772690066893615</v>
+        <v>2.73800998736013</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067861</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.15845759333848</v>
+        <v>-4.262918157784607</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9324485727812948</v>
+        <v>0.8906643470028439</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3280755047582333</v>
+        <v>0.2702753722024255</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.793033337285375</v>
+        <v>2.75835325775189</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.139101457444633</v>
+        <v>-4.243562021890759</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9461995575357596</v>
+        <v>0.9044153317573089</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3280755047582333</v>
+        <v>0.2702753722024255</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.799041867682301</v>
+        <v>2.764361788148816</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.212430986182725</v>
+        <v>-4.316891550628852</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.814817967317722</v>
+        <v>0.7730337415392714</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3284701671778553</v>
+        <v>0.2706700346220474</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.697228886411274</v>
+        <v>2.662548806877789</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.409870503348191</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.296252207457424</v>
+        <v>-4.40071277190355</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.6910131960514738</v>
+        <v>0.6492289702730232</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3284701671778553</v>
+        <v>0.2706700346220474</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.606952603654905</v>
+        <v>2.57227252412142</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
         <v>2.41053285173985</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.290099501404639</v>
+        <v>-4.394560065850766</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.6941366268642459</v>
+        <v>0.6523524010857953</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3346228732306396</v>
+        <v>0.2768227406748317</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.611306575678234</v>
+        <v>2.576626496144749</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.40961332847996</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.306908799555141</v>
+        <v>-4.411369364001268</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.6864933843441554</v>
+        <v>0.6447091585657048</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3178135750801379</v>
+        <v>0.2600134425243301</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.600301473528043</v>
+        <v>2.565621393994558</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
         <v>2.475948882276781</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.244610800779019</v>
+        <v>-4.349071365225146</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.7777481376514253</v>
+        <v>0.7359639118729746</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.36310783935458</v>
+        <v>0.3053077067987721</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.693813585889529</v>
+        <v>2.659133506356044</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.278240883990908</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.042820603113861</v>
+        <v>-4.147281167559988</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6607562184316156</v>
+        <v>0.6189719926531647</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5611260315237343</v>
+        <v>0.5033258989679266</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.614916502905149</v>
+        <v>2.580236423371664</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.348531116313083</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.093707315800056</v>
+        <v>-4.198167880246182</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7106917656793128</v>
+        <v>0.6689075399008622</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5102393188375398</v>
+        <v>0.452439186281732</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.654674707615607</v>
+        <v>2.619994628082122</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
         <v>2.363158852429127</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.007096573150248</v>
+        <v>-4.111557137596376</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7599637988552794</v>
+        <v>0.7181795730768286</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5888650500426981</v>
+        <v>0.5310649174868902</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.716477882454746</v>
+        <v>2.681797802921261</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.361694833253798</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.067305871155533</v>
+        <v>-4.17176643560166</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7344160604778374</v>
+        <v>0.6926318346993863</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5286557520374136</v>
+        <v>0.4708556194816057</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.678888284476247</v>
+        <v>2.644208204942762</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
         <v>2.360186451293727</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.018119222471181</v>
+        <v>-4.122579786917309</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7525823379915064</v>
+        <v>0.7107981122130553</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5286557520374136</v>
+        <v>0.4708556194816057</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.677379902516175</v>
+        <v>2.642699822982691</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.833513460316254</v>
       </c>
       <c r="C1976" t="n">
         <v>2.360049318729163</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.973746090832613</v>
+        <v>-4.07820665527874</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7701944580823701</v>
+        <v>0.728410232303919</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5730288836759821</v>
+        <v>0.5152287511201743</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.703866648934753</v>
+        <v>2.669186569401268</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.354443112867754</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.939014769514112</v>
+        <v>-4.04347533396024</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7784807807483609</v>
+        <v>0.7366965549699098</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5730288836759821</v>
+        <v>0.5152287511201743</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.698260443073343</v>
+        <v>2.663580363539858</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190327</v>
       </c>
       <c r="C1978" t="n">
         <v>2.360824869895558</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.891359038953056</v>
+        <v>-3.995819603399184</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8039248300005877</v>
+        <v>0.7621406042221368</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6206846142370378</v>
+        <v>0.56288448168123</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.733235638437781</v>
+        <v>2.698555558904296</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569619</v>
       </c>
       <c r="C1979" t="n">
         <v>2.365717243270283</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.790840880454302</v>
+        <v>-3.895301444900429</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8490244667748144</v>
+        <v>0.8072402409963635</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7212027727357924</v>
+        <v>0.6634026401799845</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.798438906911759</v>
+        <v>2.763758827378274</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557297</v>
       </c>
       <c r="C1980" t="n">
         <v>2.352471915746155</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.774935551021949</v>
+        <v>-3.879396115468077</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8421412710236278</v>
+        <v>0.8003570452451767</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6420901120265534</v>
+        <v>0.5842899794707457</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.737725982962087</v>
+        <v>2.703045903428603</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932771</v>
       </c>
       <c r="C1981" t="n">
         <v>2.356569618356784</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.730097149413551</v>
+        <v>-3.834557713859679</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8641743342776156</v>
+        <v>0.8223901084991645</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6466335449714229</v>
+        <v>0.5888334124156152</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.744549745339638</v>
+        <v>2.709869665806153</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
         <v>2.360730557987862</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.749595605655559</v>
+        <v>-3.854056170101687</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8605358914118901</v>
+        <v>0.8187516656334393</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5985489036915186</v>
+        <v>0.5407487711357108</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.719859900202773</v>
+        <v>2.685179820669289</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405963</v>
       </c>
       <c r="C1983" t="n">
         <v>2.366610160515699</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.705392768569659</v>
+        <v>-3.809853333015786</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8840966287740875</v>
+        <v>0.8423124029956366</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.642751740777419</v>
+        <v>0.5849516082216113</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.752261204982151</v>
+        <v>2.717581125448666</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265647</v>
       </c>
       <c r="C1984" t="n">
         <v>2.365020160984947</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.712952434406706</v>
+        <v>-3.817412998852833</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8794827629085162</v>
+        <v>0.8376985371300654</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6975551447872383</v>
+        <v>0.6397550122314306</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.78355324785729</v>
+        <v>2.748873168323805</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284882</v>
       </c>
       <c r="C1985" t="n">
         <v>2.416267926167986</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.554661016867434</v>
+        <v>-3.659121581313561</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9940470951072649</v>
+        <v>0.9522628693288138</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6975551447872383</v>
+        <v>0.6397550122314306</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.834801013040329</v>
+        <v>2.800120933506845</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321025</v>
       </c>
       <c r="C1986" t="n">
         <v>2.414708630762239</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.347019013232957</v>
+        <v>-3.451479577679085</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.075544601155308</v>
+        <v>1.033760375376857</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9051971484217145</v>
+        <v>0.8473970158659068</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.957826919815268</v>
+        <v>2.923146840281784</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475141</v>
       </c>
       <c r="C1987" t="n">
         <v>2.409656859000509</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.295986920510429</v>
+        <v>-3.400447484956557</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.09090566648259</v>
+        <v>1.049121440704139</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9562292411442425</v>
+        <v>0.8984291085884347</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.983394403687055</v>
+        <v>2.94871432415357</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404856</v>
       </c>
       <c r="C1988" t="n">
         <v>2.426844263093214</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.230762739383223</v>
+        <v>-3.335223303829351</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.134182743026177</v>
+        <v>1.092398517247726</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.021453422271448</v>
+        <v>0.9636532897156403</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.039716316456083</v>
+        <v>3.005036236922599</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.84006118688256</v>
       </c>
       <c r="C1989" t="n">
         <v>2.422805235392495</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.19333571931209</v>
+        <v>-3.297796283758217</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.145114523353911</v>
+        <v>1.10333029757546</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.02670496030063</v>
+        <v>0.968904827744822</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.038828211572873</v>
+        <v>3.004148132039388</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992663</v>
       </c>
       <c r="C1990" t="n">
         <v>2.424062027723735</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.191977734338544</v>
+        <v>-3.296438298784672</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.146914509674569</v>
+        <v>1.105130283896118</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.101043085838448</v>
+        <v>1.043242953282641</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.084687879226804</v>
+        <v>3.050007799693319</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636289</v>
       </c>
       <c r="C1991" t="n">
         <v>2.584619798744946</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.163564471238661</v>
+        <v>-3.268025035684788</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.318837585935734</v>
+        <v>1.277053360157282</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.04206752309202</v>
+        <v>0.9842673905362118</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.209860312600158</v>
+        <v>3.175180233066673</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957629</v>
       </c>
       <c r="C1992" t="n">
         <v>2.704732707962763</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.088782210213648</v>
+        <v>-3.193242774659776</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.468863399563556</v>
+        <v>1.427079173785105</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.116849784117032</v>
+        <v>1.059049651561224</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.374842578432983</v>
+        <v>3.340162498899498</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
         <v>2.696440683976622</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.06269812594984</v>
+        <v>-3.167158690395968</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.471005009282938</v>
+        <v>1.429220783504487</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.116849784117032</v>
+        <v>1.059049651561224</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.366550554446841</v>
+        <v>3.331870474913357</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896931</v>
       </c>
       <c r="C1994" t="n">
         <v>2.694633879560401</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.97482021284072</v>
+        <v>-3.079280777286847</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.504349370110366</v>
+        <v>1.462565144331915</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.232775426540383</v>
+        <v>1.174975293984576</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.434299135484632</v>
+        <v>3.399619055951147</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.79626414395986</v>
       </c>
       <c r="C1995" t="n">
         <v>2.712188285287193</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.965927751447436</v>
+        <v>-3.070388315893564</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.52546076039447</v>
+        <v>1.483676534616019</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.232775426540383</v>
+        <v>1.174975293984576</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.451853541211423</v>
+        <v>3.417173461677939</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945369</v>
       </c>
       <c r="C1996" t="n">
         <v>2.704043332691777</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.134403868417314</v>
+        <v>-3.238864432863442</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.449925361011103</v>
+        <v>1.408141135232652</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.204827590823802</v>
+        <v>1.147027458267995</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.426939887186058</v>
+        <v>3.392259807652574</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782711</v>
       </c>
       <c r="C1997" t="n">
         <v>2.685313029879639</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.688147675787874</v>
+        <v>-2.792608240234002</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.609697535250741</v>
+        <v>1.56791330947229</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.11010892115417</v>
+        <v>1.052308788598362</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.351378382572141</v>
+        <v>3.316698303038656</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>2.675977052376543</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.665426572104722</v>
+        <v>-2.76988713655085</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.609449999220906</v>
+        <v>1.567665773442456</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.11010892115417</v>
+        <v>1.052308788598362</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.342042405069045</v>
+        <v>3.307362325535561</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777676</v>
       </c>
       <c r="C1999" t="n">
         <v>2.834883178227712</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.794628385398764</v>
+        <v>-2.899088949844892</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.716675399754459</v>
+        <v>1.674891173976008</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9809071078601275</v>
+        <v>0.92310697530432</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.423427442943789</v>
+        <v>3.388747363410304</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>2.871961000721359</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.82050278387279</v>
+        <v>-2.924963348318918</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.743403462858495</v>
+        <v>1.701619237080044</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.025818716571869</v>
+        <v>0.9680185840160611</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.48745223066448</v>
+        <v>3.452772151130996</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799959</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
         <v>2.868636356710904</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.813448093657616</v>
+        <v>-2.917908658103744</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.742900694934109</v>
+        <v>1.701116469155658</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.032873406787042</v>
+        <v>0.9750732742312349</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.488360400783129</v>
+        <v>3.453680321249645</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>2.878642510355645</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.786496869331129</v>
+        <v>-2.890957433777256</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.763687338309446</v>
+        <v>1.721903112530995</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.047753752814762</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.507294762044503</v>
+        <v>3.472614682511018</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.76805206778411</v>
       </c>
       <c r="C2003" t="n">
         <v>3.062745642500605</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.808041097161916</v>
+        <v>-2.912501661608043</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.939172779322091</v>
+        <v>1.89738855354364</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.047753752814762</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.691397894189462</v>
+        <v>3.656717814655978</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
         <v>3.054862337403598</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.830449214966788</v>
+        <v>-2.934909779412915</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.922326227103135</v>
+        <v>1.880542001324684</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.047753752814762</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.683514589092455</v>
+        <v>3.648834509558971</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155035</v>
       </c>
       <c r="C2005" t="n">
         <v>3.056916336953236</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.858673450544388</v>
+        <v>-2.963134014990516</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.913090532421733</v>
+        <v>1.871306306643282</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.06573050526607</v>
+        <v>1.007930372710263</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.696354640112878</v>
+        <v>3.661674560579394</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161981</v>
       </c>
       <c r="C2006" t="n">
         <v>3.113170054675083</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.868114376432918</v>
+        <v>-2.972574940879046</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.965567879788168</v>
+        <v>1.923783654009717</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.188157622809462</v>
+        <v>1.130357490253654</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.82606462836076</v>
+        <v>3.791384548827275</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321639</v>
       </c>
       <c r="C2007" t="n">
         <v>3.116061149220384</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.074353314221351</v>
+        <v>-3.178813878667479</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.885963399218095</v>
+        <v>1.844179173439644</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.981918685021028</v>
+        <v>0.9241185524652205</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.705212360233001</v>
+        <v>3.670532280699516</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347704</v>
+        <v>3.727898186347709</v>
       </c>
       <c r="C2008" t="n">
         <v>3.114172962114159</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.150683291822257</v>
+        <v>-3.255143856268385</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.853543221071508</v>
+        <v>1.811758995293057</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.981918685021028</v>
+        <v>0.9241185524652205</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.703324173126776</v>
+        <v>3.668644093593291</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.71065410488775</v>
+        <v>3.710654104887755</v>
       </c>
       <c r="C2009" t="n">
         <v>3.108993191717021</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.305640077222387</v>
+        <v>-3.410100641668514</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.786380736514319</v>
+        <v>1.744596510735868</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8269618996208987</v>
+        <v>0.7691617670650912</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.605170331489561</v>
+        <v>3.570490251956076</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343068</v>
+        <v>3.712897612343073</v>
       </c>
       <c r="C2010" t="n">
         <v>3.107427201927174</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.467208502749642</v>
+        <v>-3.571669067195769</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.720187376513569</v>
+        <v>1.678403150735118</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7001789758230194</v>
+        <v>0.6423788432672118</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.527534587420985</v>
+        <v>3.492854507887501</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389351</v>
+        <v>3.754596135389356</v>
       </c>
       <c r="C2011" t="n">
         <v>3.120500608793092</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.575509164619761</v>
+        <v>-3.679969729065889</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.68994051863144</v>
+        <v>1.648156292852989</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7001789758230194</v>
+        <v>0.6423788432672118</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.540607994286904</v>
+        <v>3.505927914753419</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378386</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.112505805576032</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.735060237383278</v>
+        <v>-3.839520801829406</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.618125286308973</v>
+        <v>1.576341060530522</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5479013089612679</v>
+        <v>0.4901011764054604</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.441246590952793</v>
+        <v>3.406566511419308</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.71581989500697</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.111029846703034</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.762961024492751</v>
+        <v>-3.867421588938879</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.605489012592186</v>
+        <v>1.563704786813735</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5133043848183331</v>
+        <v>0.4555042522625256</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.419012477594034</v>
+        <v>3.38433239806055</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787383</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.107794290680233</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.885487127195645</v>
+        <v>-3.989947691641773</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.553243015488227</v>
+        <v>1.511458789709776</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3907782821154392</v>
+        <v>0.3329781495596317</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.342261259949497</v>
+        <v>3.307581180416012</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585932</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.174500250270737</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.116001623381234</v>
+        <v>-4.220462187827361</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.527743176604495</v>
+        <v>1.485958950826044</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1602637859298505</v>
+        <v>0.102463653374043</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.270658521828647</v>
+        <v>3.235978442295163</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814662</v>
+        <v>3.640750087814668</v>
       </c>
       <c r="C2016" t="n">
         <v>3.314811969272584</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.464746708605677</v>
+        <v>-4.569207273051805</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.528556861516565</v>
+        <v>1.486772635738114</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.05151583201095267</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.345721468479156</v>
+        <v>3.311041388945671</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237091</v>
+        <v>3.668289004237097</v>
       </c>
       <c r="C2017" t="n">
         <v>3.383792238418224</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.618733126381818</v>
+        <v>-4.723193690827945</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.535942563551749</v>
+        <v>1.494158337773297</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.05151583201095267</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.414701737624795</v>
+        <v>3.380021658091311</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423384</v>
+        <v>3.61992301642339</v>
       </c>
       <c r="C2018" t="n">
         <v>3.369843440538344</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.823332561244826</v>
+        <v>-4.927793125690954</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.440153991726666</v>
+        <v>1.398369765948215</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.05151583201095267</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.400752939744916</v>
+        <v>3.366072860211432</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.65633273360975</v>
+        <v>3.656332733609755</v>
       </c>
       <c r="C2019" t="n">
         <v>3.381713929593758</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.075807715252551</v>
+        <v>-5.180268279698678</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.35103441917899</v>
+        <v>1.309250193400539</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.05151583201095267</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.41262342880033</v>
+        <v>3.377943349266846</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973153</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.382924464112702</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.368703471731963</v>
+        <v>-5.47316403617809</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.235086651106169</v>
+        <v>1.193302425327718</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.05151583201095267</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.413833963319274</v>
+        <v>3.37915388378579</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251948</v>
       </c>
       <c r="C2021" t="n">
         <v>3.387046206340024</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.555367599866771</v>
+        <v>-5.659828164312898</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.164542742079567</v>
+        <v>1.122758516301116</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.02477686118639277</v>
+        <v>-0.03302327136941474</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.401912323051859</v>
+        <v>3.367232243518375</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916203</v>
       </c>
       <c r="C2022" t="n">
         <v>3.382124059076213</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.701388286780733</v>
+        <v>-5.805848851226861</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.101212320050172</v>
+        <v>1.059428094271721</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.01569376939253581</v>
+        <v>-0.04210636316327171</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.391540320711735</v>
+        <v>3.35686024117825</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.66796230683033</v>
       </c>
       <c r="C2023" t="n">
         <v>3.544328115775257</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.793102295890318</v>
+        <v>-5.897562860336446</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.226730773105382</v>
+        <v>1.18494654732693</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.01569376939253581</v>
+        <v>-0.04210636316327171</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.553744377410779</v>
+        <v>3.519064297877294</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071554</v>
       </c>
       <c r="C2024" t="n">
         <v>3.539174753739071</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.824753954950287</v>
+        <v>-5.929214519396416</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.208916747445208</v>
+        <v>1.167132521666757</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.0105253121480956</v>
+        <v>-0.04727482040771191</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.545489941027929</v>
+        <v>3.510809861494444</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868151</v>
       </c>
       <c r="C2025" t="n">
         <v>3.549404171307562</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.893820009523224</v>
+        <v>-5.998280573969352</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.191519743184525</v>
+        <v>1.149735517406073</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.05184556534551443</v>
+        <v>-0.1096456979013219</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.518296832100254</v>
+        <v>3.483616752566769</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332694</v>
+        <v>3.783632867332697</v>
       </c>
       <c r="C2026" t="n">
         <v>3.558329809763465</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.995796131771631</v>
+        <v>-6.10025669621776</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.159654932741064</v>
+        <v>1.117870706962613</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.153821687593922</v>
+        <v>-0.2116218201497295</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.466036797207112</v>
+        <v>3.431356717673627</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231811</v>
+        <v>3.798296784231814</v>
       </c>
       <c r="C2027" t="n">
         <v>3.55048269700764</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.88578984829441</v>
+        <v>-5.990250412740538</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.195810333376128</v>
+        <v>1.154026107597677</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1306171156766468</v>
+        <v>-0.1884172482324543</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.472112427601652</v>
+        <v>3.437432348068168</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.554732707729614</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.898319553406289</v>
+        <v>-6.002780117852417</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.195048462053351</v>
+        <v>1.1532642362749</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1444436151431698</v>
+        <v>-0.2022437476989773</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.468066538643713</v>
+        <v>3.433386459110229</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051784</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.56199359061215</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.596872827934451</v>
+        <v>-5.70133339238058</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.322888035124622</v>
+        <v>1.281103809346171</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1570031103286674</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.656195456809351</v>
+        <v>3.621515377275867</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
         <v>3.562964768364861</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.621463072169635</v>
+        <v>-5.725923636615764</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.314023115183259</v>
+        <v>1.272238889404808</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1570031103286674</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.657166634562062</v>
+        <v>3.622486555028577</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474156</v>
+        <v>3.82118418247416</v>
       </c>
       <c r="C2031" t="n">
         <v>3.563807672744617</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.570424696163115</v>
+        <v>-5.674885260609243</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.335281369965623</v>
+        <v>1.293497144187171</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1570031103286674</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.658009538941817</v>
+        <v>3.623329459408333</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.582845771618762</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.541576019339654</v>
+        <v>-5.646036583785783</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.365858939569152</v>
+        <v>1.324074713790701</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1858517871521277</v>
+        <v>0.1280516545963202</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.694356843910039</v>
+        <v>3.659676764376554</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.82575293270048</v>
       </c>
       <c r="C2033" t="n">
         <v>3.399029767742697</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.444941107321014</v>
+        <v>-5.549401671767143</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.220696900500543</v>
+        <v>1.178912674722091</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2824866991707676</v>
+        <v>0.2246865666149601</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.568521787245158</v>
+        <v>3.533841707711673</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80468896107764</v>
+        <v>3.804688961077644</v>
       </c>
       <c r="C2034" t="n">
         <v>3.402531811816661</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.375903096372546</v>
+        <v>-5.480363660818675</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.251814148953894</v>
+        <v>1.210029923175443</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3515247101192357</v>
+        <v>0.2937245775634282</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.613446637888202</v>
+        <v>3.578766558354718</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.77502886083346</v>
+        <v>3.775028860833464</v>
       </c>
       <c r="C2035" t="n">
         <v>3.386958630892743</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.357115996003608</v>
+        <v>-5.461576560449736</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.243755808177552</v>
+        <v>1.201971582399101</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3703118104881742</v>
+        <v>0.3125116779323667</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.609145717185648</v>
+        <v>3.574465637652164</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.386146341329173</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.280017394461735</v>
+        <v>-5.384477958907864</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.273782959230731</v>
+        <v>1.23199873345228</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3703118104881742</v>
+        <v>0.3125116779323667</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.608333427622078</v>
+        <v>3.573653348088593</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.396015120454245</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.290402589351625</v>
+        <v>-5.394863153797753</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.279497660399848</v>
+        <v>1.237713434621396</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3599266155982849</v>
+        <v>0.3021264830424774</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.611971089813216</v>
+        <v>3.577291010279732</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735283</v>
+        <v>3.834415493735286</v>
       </c>
       <c r="C2038" t="n">
         <v>3.466852126230671</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.30899074807385</v>
+        <v>-5.413451312519978</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.342899402687383</v>
+        <v>1.301115176908931</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3413384568760595</v>
+        <v>0.283538324320252</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.671655200356307</v>
+        <v>3.636975120822822</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
         <v>3.463721137048969</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.309289294769886</v>
+        <v>-5.413749859216014</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.339648994827267</v>
+        <v>1.297864769048815</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3410399101800236</v>
+        <v>0.2832397776242161</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.668345083156983</v>
+        <v>3.633665003623499</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108858</v>
+        <v>3.815643212108862</v>
       </c>
       <c r="C2040" t="n">
         <v>3.468252031988361</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.208466161079458</v>
+        <v>-5.312926725525586</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.38450914324283</v>
+        <v>1.342724917464378</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3535041256643774</v>
+        <v>0.2957039931085699</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.680354507386987</v>
+        <v>3.645674427853503</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121469</v>
+        <v>3.807356168121473</v>
       </c>
       <c r="C2041" t="n">
         <v>3.468381285466904</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.01768480032705</v>
+        <v>-5.122145364773178</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.460950941022336</v>
+        <v>1.419166715243884</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5442854864167848</v>
+        <v>0.4864853538609773</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.794952577316975</v>
+        <v>3.76027249778349</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906082</v>
+        <v>3.775233033906086</v>
       </c>
       <c r="C2042" t="n">
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.910721442477628</v>
+        <v>-5.015182006923757</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.483573129899701</v>
+        <v>1.44178890412125</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6027500943765862</v>
+        <v>0.5449499618207787</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.809868187830452</v>
+        <v>3.775188108296968</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912987</v>
+        <v>3.78576168591299</v>
       </c>
       <c r="C2043" t="n">
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.855390854575866</v>
+        <v>-4.959851419021994</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.540672301672464</v>
+        <v>1.498888075894013</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6580806822783484</v>
+        <v>0.6002805497225409</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.878033477183568</v>
+        <v>3.843353397650084</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539896</v>
+        <v>3.7437679565399</v>
       </c>
       <c r="C2044" t="n">
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.843336727662903</v>
+        <v>-4.947797292109032</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.539180520339087</v>
+        <v>1.497396294560636</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6701348091913112</v>
+        <v>0.6123346766355037</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.878952521232784</v>
+        <v>3.844272441699299</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811012</v>
+        <v>3.725010844811015</v>
       </c>
       <c r="C2045" t="n">
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.920692217790872</v>
+        <v>-5.025152782237001</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.510118954472035</v>
+        <v>1.468334728693584</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5927793190633418</v>
+        <v>0.5349791865075343</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.834419857340138</v>
+        <v>3.799739777806653</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382922</v>
+        <v>3.612322444382926</v>
       </c>
       <c r="C2046" t="n">
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.852643655099342</v>
+        <v>-4.957104219545471</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.55018940542653</v>
+        <v>1.508405179648078</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6608278817548716</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.888100020832938</v>
+        <v>3.853419941299454</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.64525678001343</v>
+        <v>3.645256780013433</v>
       </c>
       <c r="C2047" t="n">
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.084244048268843</v>
+        <v>-5.188704612714972</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.477751918332324</v>
+        <v>1.435967692553872</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6608278817548716</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.908302691006532</v>
+        <v>3.873622611473048</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498966</v>
+        <v>3.66674720149897</v>
       </c>
       <c r="C2048" t="n">
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.134295593798063</v>
+        <v>-5.238756158244191</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.441337536187518</v>
+        <v>1.399553310409066</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6608278817548716</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.891908927073414</v>
+        <v>3.85722884753993</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800096</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.309402426374508</v>
+        <v>-5.413862990820636</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.331546716750406</v>
+        <v>1.289762490971955</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6608278817548716</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.852160840666881</v>
+        <v>3.817480761133397</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660848</v>
+        <v>3.745573148660852</v>
       </c>
       <c r="C2050" t="n">
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.113302272943985</v>
+        <v>-5.217762837390113</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.417009397119556</v>
+        <v>1.375225171341104</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8569280351853945</v>
+        <v>0.799127902629587</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.976843551722134</v>
+        <v>3.94216347218865</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395085</v>
+        <v>3.730570473395089</v>
       </c>
       <c r="C2051" t="n">
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.9602768808307</v>
+        <v>-5.064737445276829</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.577390553537774</v>
+        <v>1.535606327759323</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.009953427298679</v>
+        <v>0.9521532947428711</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.16782978656301</v>
+        <v>4.133149707029525</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791147</v>
+        <v>3.741278332791151</v>
       </c>
       <c r="C2052" t="n">
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.988584194703971</v>
+        <v>-5.093044759150099</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.753533852896759</v>
+        <v>1.711749627118307</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.009953427298679</v>
+        <v>0.9521532947428711</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.355296011471302</v>
+        <v>4.320615931937818</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620433</v>
+        <v>3.699115615620436</v>
       </c>
       <c r="C2053" t="n">
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.155177419817493</v>
+        <v>-5.259637984263621</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.656299514205432</v>
+        <v>1.614515288426981</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8433602021851561</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.224743027757271</v>
+        <v>4.190062948223787</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285649</v>
       </c>
       <c r="C2054" t="n">
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.132141626455927</v>
+        <v>-5.236602190902055</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.669190234211777</v>
+        <v>1.627406008433325</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8433602021851561</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.228419430418989</v>
+        <v>4.193739350885505</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.740581401399471</v>
       </c>
       <c r="C2055" t="n">
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.10289564600023</v>
+        <v>-5.207356210446359</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.67850668151755</v>
+        <v>1.636722455739099</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8433602021851561</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.226037485542484</v>
+        <v>4.191357406009</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256371</v>
+        <v>3.699404642256374</v>
       </c>
       <c r="C2056" t="n">
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.209821193878081</v>
+        <v>-5.31428175832421</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.633029701524045</v>
+        <v>1.591245475745593</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7364346543073047</v>
+        <v>0.6786345217514974</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.159175395973408</v>
+        <v>4.124495316439925</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701001</v>
+        <v>3.689942600701004</v>
       </c>
       <c r="C2057" t="n">
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.35483975238533</v>
+        <v>-5.459300316831459</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.57645108026438</v>
+        <v>1.534666854485928</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5914160958000562</v>
+        <v>0.5336159632442489</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.073593063012294</v>
+        <v>4.038912983478809</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.711852429687015</v>
       </c>
       <c r="C2058" t="n">
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.473181518170048</v>
+        <v>-5.577642082616176</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.629045613208246</v>
+        <v>1.587261387429794</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6021021343629462</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.179935925407781</v>
+        <v>4.145255845874297</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790804</v>
+        <v>3.714879051790808</v>
       </c>
       <c r="C2059" t="n">
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.524591940490756</v>
+        <v>-5.629052504936884</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.606267141405902</v>
+        <v>1.56448291562745</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6021021343629462</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.17772162253372</v>
+        <v>4.143041543000235</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437333</v>
+        <v>3.704757949437337</v>
       </c>
       <c r="C2060" t="n">
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.604011391698507</v>
+        <v>-5.708471956144636</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.57440248899709</v>
+        <v>1.532618263218639</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6021021343629462</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.177624750608009</v>
+        <v>4.142944671074525</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298401</v>
+        <v>3.736804952298405</v>
       </c>
       <c r="C2061" t="n">
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.699474389615725</v>
+        <v>-5.803934954061853</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.536211183388246</v>
+        <v>1.494426957609794</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6021021343629462</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.177618644166052</v>
+        <v>4.142938564632567</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218003</v>
+        <v>3.715372960218007</v>
       </c>
       <c r="C2062" t="n">
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.63509847876501</v>
+        <v>-5.739559043211139</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.560057944291143</v>
+        <v>1.518273718512691</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6664780452136614</v>
+        <v>0.6086779126578541</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.214340587239092</v>
+        <v>4.179660507705607</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353539</v>
+        <v>3.736089413353542</v>
       </c>
       <c r="C2063" t="n">
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.690467640897204</v>
+        <v>-5.794928205343332</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.543644097185992</v>
+        <v>1.50185987140754</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6664780452136614</v>
+        <v>0.6086779126578541</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.220074404986819</v>
+        <v>4.185394325453334</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113282</v>
+        <v>3.736822870113286</v>
       </c>
       <c r="C2064" t="n">
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.708686107894812</v>
+        <v>-5.813146672340941</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.535895073729881</v>
+        <v>1.494110847951429</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6413716079578192</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.204548905976245</v>
+        <v>4.169868826442761</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.79027250011369</v>
+        <v>3.790272500113693</v>
       </c>
       <c r="C2065" t="n">
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.670002672550882</v>
+        <v>-5.77446323699701</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.571242840717772</v>
+        <v>1.52945861493932</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6413716079578192</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.224423298826564</v>
+        <v>4.18974321929308</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016435</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.563967677345572</v>
+        <v>-5.668428241791701</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.597357539324623</v>
+        <v>1.555573313546172</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6413716079578192</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.208123999351292</v>
+        <v>4.173443919817807</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307667</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.380756014212477</v>
+        <v>-5.485216578658606</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.673073154041907</v>
+        <v>1.631288928263456</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6413716079578192</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.210554948815338</v>
+        <v>4.175874869281854</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863548</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.309034567198626</v>
+        <v>-5.413495131644755</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.684706138926825</v>
+        <v>1.642921913148373</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7130930549716699</v>
+        <v>0.6552929224158626</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.236532223103025</v>
+        <v>4.201852143569541</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72378970539411</v>
+        <v>3.723789705394113</v>
       </c>
       <c r="C2069" t="n">
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.28666154159092</v>
+        <v>-5.391122106037049</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.640571095091079</v>
+        <v>1.598786869312627</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7243488060845714</v>
+        <v>0.6665486735287641</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.190201419691938</v>
+        <v>4.155521340158454</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456728</v>
+        <v>3.715607446456731</v>
       </c>
       <c r="C2070" t="n">
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.319677837501665</v>
+        <v>-5.424138401947793</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.812562781612136</v>
+        <v>1.770778555833684</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6549114294178198</v>
+        <v>0.5971112968620125</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.333737198577242</v>
+        <v>4.299057119043757</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883679</v>
+        <v>3.713762536883682</v>
       </c>
       <c r="C2071" t="n">
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.308150201852056</v>
+        <v>-5.412610766298185</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.809095061700229</v>
+        <v>1.767310835921777</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7139120876191822</v>
+        <v>0.6561119550633749</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.361058819326309</v>
+        <v>4.326378739792824</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.7171506992363</v>
+        <v>3.717150699236303</v>
       </c>
       <c r="C2072" t="n">
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.405491703194425</v>
+        <v>-5.509952267640553</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.773826573685069</v>
+        <v>1.732042347906618</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6694919054536939</v>
+        <v>0.6116917728978866</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.338074822548804</v>
+        <v>4.303394743015319</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427686</v>
+        <v>3.70520107942769</v>
       </c>
       <c r="C2073" t="n">
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.491347732534392</v>
+        <v>-5.59580829698052</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.740735244141921</v>
+        <v>1.69895101836347</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6271158362275588</v>
+        <v>0.5693157036717515</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.313900263205961</v>
+        <v>4.279220183672477</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610378</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.500184529950511</v>
+        <v>-5.604645094396639</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.719619726995975</v>
+        <v>1.677835501217524</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6196736635862081</v>
+        <v>0.5618735310304008</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.291854161441653</v>
+        <v>4.257174081908168</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667456</v>
+        <v>3.71554441166746</v>
       </c>
       <c r="C2075" t="n">
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.59156709251597</v>
+        <v>-5.696027656962098</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.693231213014841</v>
+        <v>1.65144698723639</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5831087788668634</v>
+        <v>0.5253086463110561</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.280079741655095</v>
+        <v>4.245399662121611</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889193</v>
+        <v>3.673978374889197</v>
       </c>
       <c r="C2076" t="n">
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.579860374528963</v>
+        <v>-5.684320938975092</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.800042158033912</v>
+        <v>1.75825793225546</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5948154968538698</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.389232030271567</v>
+        <v>4.354551950738083</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409569</v>
+        <v>3.682476099409573</v>
       </c>
       <c r="C2077" t="n">
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.65077244827124</v>
+        <v>-5.755233012717369</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.774709667268406</v>
+        <v>1.732925441489954</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5948154968538698</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.392264369002972</v>
+        <v>4.357584289469488</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452568</v>
+        <v>3.672895177452572</v>
       </c>
       <c r="C2078" t="n">
         <v>4.248279904168708</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.661088546437592</v>
+        <v>-5.765549110883721</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.983488061279923</v>
+        <v>1.941703835501472</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5948154968538698</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.60516920228103</v>
+        <v>4.570489122747546</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762289</v>
+        <v>3.623960959762293</v>
       </c>
       <c r="C2079" t="n">
         <v>4.247458571080798</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.66099457842022</v>
+        <v>-5.765455142866348</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.982704315398962</v>
+        <v>1.94092008962051</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5951853582011878</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.604569786001511</v>
+        <v>4.569889706468026</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884082</v>
+        <v>3.800870306884086</v>
       </c>
       <c r="C2080" t="n">
         <v>4.241690557025152</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.804595742443605</v>
+        <v>-5.909056306889734</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.919495835733962</v>
+        <v>1.87771160995551</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5951853582011878</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.598801771945864</v>
+        <v>4.56412169241238</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129646</v>
+        <v>3.67101569212965</v>
       </c>
       <c r="C2081" t="n">
         <v>4.241690557025152</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.803647319325567</v>
+        <v>-5.908107883771695</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.919875204981177</v>
+        <v>1.878090979202725</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5951853582011878</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.598801771945864</v>
+        <v>4.56412169241238</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052349</v>
+        <v>3.904173816052353</v>
       </c>
       <c r="C2082" t="n">
         <v>4.254418165006244</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.903917137284587</v>
+        <v>-6.008377701730716</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.892494885778661</v>
+        <v>1.850710660000209</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5951853582011878</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.611529379926957</v>
+        <v>4.576849300393472</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813493</v>
+        <v>3.740179607813497</v>
       </c>
       <c r="C2083" t="n">
         <v>4.256364163430631</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.897924890495776</v>
+        <v>-6.002385454941904</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.896837782918573</v>
+        <v>1.855053557140122</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5951853582011878</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.613475378351344</v>
+        <v>4.57879529881786</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537942</v>
+        <v>3.765050796537945</v>
       </c>
       <c r="C2084" t="n">
         <v>4.2500182994484</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.809366929365008</v>
+        <v>-5.913827493811136</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.925915103388649</v>
+        <v>1.884130877610198</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5951853582011878</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.607129514369113</v>
+        <v>4.572449434835629</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771814</v>
+        <v>3.758409170771817</v>
       </c>
       <c r="C2085" t="n">
         <v>4.249326976887396</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.791607851861934</v>
+        <v>-5.896068416308062</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.932327411828874</v>
+        <v>1.890543186050423</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5951853582011878</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.606438191808109</v>
+        <v>4.571758112274624</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.80134059710972</v>
+        <v>3.801340597109723</v>
       </c>
       <c r="C2086" t="n">
         <v>4.262109162795983</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.691977700812866</v>
+        <v>-5.796438265258995</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.984961658157088</v>
+        <v>1.943177432378637</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.6948155092502553</v>
+        <v>0.637015376694448</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.678998468346136</v>
+        <v>4.644318388812652</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546843994</v>
+        <v>3.798465546843998</v>
       </c>
       <c r="C2087" t="n">
         <v>4.451263428294709</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.741377209501877</v>
+        <v>-5.845837773948006</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.15435612018021</v>
+        <v>2.112571894401759</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.705074342682</v>
+        <v>0.6472742101261927</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.874308033903909</v>
+        <v>4.839627954370425</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.772186508351858</v>
+        <v>3.772186508351862</v>
       </c>
       <c r="C2088" t="n">
         <v>4.438452101397571</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.534692735859501</v>
+        <v>-5.63915330030563</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.224218582740022</v>
+        <v>2.182434356961571</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.9117588163243756</v>
+        <v>0.8539586837685683</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.985507391192197</v>
+        <v>4.950827311658712</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.763392838551268</v>
+        <v>3.763392838551272</v>
       </c>
       <c r="C2089" t="n">
         <v>4.440453615051676</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.568849630857027</v>
+        <v>-5.60535229650209</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.212557338395117</v>
+        <v>2.197956272137092</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.8281750467835631</v>
+        <v>0.8323384425147884</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.937358643121814</v>
+        <v>4.939856680560549</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041109</v>
+        <v>3.805590565041113</v>
       </c>
       <c r="C2090" t="n">
         <v>4.793950729041343</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.476260151795571</v>
+        <v>-5.512762817440634</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.603090244009367</v>
+        <v>2.588489177751342</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.8281750467835631</v>
+        <v>0.8323384425147884</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.290855757111482</v>
+        <v>5.293353794550216</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497401</v>
+        <v>3.832164354497404</v>
       </c>
       <c r="C2091" t="n">
         <v>4.798513840608447</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.549420755568716</v>
+        <v>-5.585923421213779</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.578389114067213</v>
+        <v>2.563788047809187</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.8001538467493201</v>
+        <v>0.8043172424805454</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.278606148658039</v>
+        <v>5.281104186096774</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492294</v>
+        <v>3.858310890492297</v>
       </c>
       <c r="C2092" t="n">
         <v>4.848343781931974</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.497204445772374</v>
+        <v>-5.533707111417437</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.649105579309277</v>
+        <v>2.634504513051251</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.8001538467493201</v>
+        <v>0.8043172424805454</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.328436089981566</v>
+        <v>5.330934127420302</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436475</v>
+        <v>3.844935596436478</v>
       </c>
       <c r="C2093" t="n">
         <v>4.857157752141985</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.465306928687128</v>
+        <v>-5.501809594332191</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.670678556353386</v>
+        <v>2.656077490095361</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.8320513638345659</v>
+        <v>0.8362147595657912</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.356388570442725</v>
+        <v>5.35888660788146</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039485</v>
+        <v>3.848376866039488</v>
       </c>
       <c r="C2094" t="n">
         <v>4.852795336181182</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.480062252887269</v>
+        <v>-5.516564918532332</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.660414010712527</v>
+        <v>2.645812944454501</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.8320513638345659</v>
+        <v>0.8362147595657912</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.352026154481922</v>
+        <v>5.354524191920657</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524479</v>
+        <v>3.868153115524483</v>
       </c>
       <c r="C2095" t="n">
         <v>4.843719839597462</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.430597629517357</v>
+        <v>-5.46710029516242</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.671124363476771</v>
+        <v>2.656523297218746</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8815159872044775</v>
+        <v>0.8856793829357028</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.372629431920148</v>
+        <v>5.375127469358884</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867954</v>
+        <v>3.849040239867957</v>
       </c>
       <c r="C2096" t="n">
         <v>4.840127507312396</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.267489637363742</v>
+        <v>-5.303992303008805</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.732775228053152</v>
+        <v>2.718174161795126</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.044623979358093</v>
+        <v>1.048787375089318</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.466901894927252</v>
+        <v>5.469399932365987</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.87020492823297</v>
+        <v>3.870204928232973</v>
       </c>
       <c r="C2097" t="n">
         <v>4.849174544003525</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.246846546562514</v>
+        <v>-5.283349212207577</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.750079501064771</v>
+        <v>2.735478434806746</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.044623979358093</v>
+        <v>1.048787375089318</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.47594893161838</v>
+        <v>5.478446969057115</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179673</v>
+        <v>3.855534437179677</v>
       </c>
       <c r="C2098" t="n">
         <v>4.850032008989646</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.309554463037072</v>
+        <v>-5.346057128682135</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.725853799461069</v>
+        <v>2.711252733203044</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9819160628835352</v>
+        <v>0.9860794586147604</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.439181646719767</v>
+        <v>5.441679684158503</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967721</v>
+        <v>3.884687848967724</v>
       </c>
       <c r="C2099" t="n">
         <v>4.812941425779998</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.261546339193379</v>
+        <v>-5.298049004838442</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.707966465788898</v>
+        <v>2.693365399530873</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9819160628835352</v>
+        <v>0.9860794586147604</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.402091063510119</v>
+        <v>5.404589100948855</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018612</v>
+        <v>3.895362357018615</v>
       </c>
       <c r="C2100" t="n">
         <v>4.816873679337949</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.182720682009789</v>
+        <v>-5.219223347654852</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.743428982220285</v>
+        <v>2.72882791596226</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.060741720067126</v>
+        <v>1.064905115798351</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.453318711378224</v>
+        <v>5.455816748816959</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075135</v>
+        <v>3.891610981075138</v>
       </c>
       <c r="C2101" t="n">
         <v>4.811772771944986</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.990785880755915</v>
+        <v>-5.027288546400978</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.815101995328872</v>
+        <v>2.800500929070846</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.060741720067126</v>
+        <v>1.064905115798351</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.448217803985261</v>
+        <v>5.450715841423996</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435444</v>
+        <v>3.872432493435448</v>
       </c>
       <c r="C2102" t="n">
         <v>4.807126681334081</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.872612502737988</v>
+        <v>-4.909115168383051</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.857725255925137</v>
+        <v>2.843124189667113</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.178915098085053</v>
+        <v>1.183078493816278</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.514475740185113</v>
+        <v>5.516973777623848</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917733</v>
+        <v>3.859571723917736</v>
       </c>
       <c r="C2103" t="n">
         <v>4.836215274197108</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.759197819955257</v>
+        <v>-4.79570048560032</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.932179721901257</v>
+        <v>2.917578655643232</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.292329780867784</v>
+        <v>1.29649317659901</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.611613142717779</v>
+        <v>5.614111180156514</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.828006274013639</v>
+        <v>3.828006274013642</v>
       </c>
       <c r="C2104" t="n">
         <v>4.829775497208285</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.732148782262003</v>
+        <v>-4.768651447907066</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.936559559989735</v>
+        <v>2.921958493731711</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.319378818561038</v>
+        <v>1.323542214292263</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.621402788344908</v>
+        <v>5.623900825783643</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.82398744526377</v>
+        <v>3.823987445263773</v>
       </c>
       <c r="C2105" t="n">
         <v>4.829775497208285</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.738182062448773</v>
+        <v>-4.774684728093836</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.934146247915027</v>
+        <v>2.919545181657003</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.319378818561038</v>
+        <v>1.323542214292263</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.621402788344908</v>
+        <v>5.623900825783643</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.917830833263249</v>
+        <v>3.929832492771252</v>
       </c>
       <c r="C2106" t="n">
         <v>4.833413664350697</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.790033838021935</v>
+        <v>-4.826536503666998</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.917043704828175</v>
+        <v>2.90244263857015</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.267527042987877</v>
+        <v>1.271690438719102</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.593929890143423</v>
+        <v>5.596427927582159</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241004.xlsx
+++ b/tame_output/ON/bt/strategyON_20241004.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>63.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>110.2%</t>
+          <t>117.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>171.7%</t>
+          <t>192.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>124.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-49.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.3%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.6%</t>
+          <t>421.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-644.2%</t>
+          <t>-653.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-86.0%</t>
+          <t>-89.6%</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,11 +1247,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-203.7%</t>
+          <t>-281.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-96.8%</t>
+          <t>-97.1%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>122.2%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-14.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>111.3%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>113.6%</t>
+          <t>57.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2106"/>
+  <dimension ref="A1:G2107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.174907066817855</v>
+        <v>-6.276045836383243</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6383007519831203</v>
+        <v>0.5978452441569648</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.8103298254957174</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.536080696634842</v>
+        <v>-6.63721946620023</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5040899907250038</v>
+        <v>0.4636344828988488</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.8103298254957174</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.879339216277861</v>
+        <v>-6.980477985843249</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3628861480134917</v>
+        <v>0.3224306401873362</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.8103298254957174</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.927542033520205</v>
+        <v>-7.028680803085593</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3420099411715549</v>
+        <v>0.3015544333453999</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.8103298254957174</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.094350693494567</v>
+        <v>-7.195489463059955</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2790654531110186</v>
+        <v>0.2386099452848631</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.852613149208854</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.28107040180387</v>
+        <v>-7.382209171369258</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2003512652528943</v>
+        <v>0.1598957574267388</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.852613149208854</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.664071790546501</v>
+        <v>-7.765210560111889</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.04704860843425784</v>
+        <v>0.006593100608102365</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.852613149208854</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.66855823574789</v>
+        <v>-7.769697005313278</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.04782554632513225</v>
+        <v>0.007370038498977216</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.8570995944102426</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.028088558251891</v>
+        <v>-8.129227327817279</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.09063627937841856</v>
+        <v>-0.1310917872045736</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.8570995944102426</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.078437621706113</v>
+        <v>-8.179576391271501</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1028598848029296</v>
+        <v>-0.1433153926290851</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.9074486578644647</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.176056899127509</v>
+        <v>-8.277195668692897</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1388658451497196</v>
+        <v>-0.1793213529758746</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.005067935285861</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.230128398635868</v>
+        <v>-8.331267168201256</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1576008886314906</v>
+        <v>-0.1980563964576461</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.059139434794221</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.233704184727616</v>
+        <v>-8.334842954293004</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1535180059495476</v>
+        <v>-0.1939735137757026</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.084668356710713</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.267357023236089</v>
+        <v>-8.368495792801477</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1624965868685009</v>
+        <v>-0.2029520946946559</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.185081724627751</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.406443137854946</v>
+        <v>-8.507581907420334</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2027593312226226</v>
+        <v>-0.2432148390487776</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.324167839246607</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.58156755524149</v>
+        <v>-8.682706324806878</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2582538774297229</v>
+        <v>-0.2987093852558784</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.499292256633151</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.816019649255979</v>
+        <v>-8.917158418821368</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.359253879937115</v>
+        <v>-0.39970938776327</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.499292256633151</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.920394380282426</v>
+        <v>-9.021533149847814</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4076759631216698</v>
+        <v>-0.4481314709478248</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.603666987659597</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.08290784598101</v>
+        <v>-9.184046615546398</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.471565559562547</v>
+        <v>-0.5120210673887025</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.701300418078284</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.2089446393493</v>
+        <v>-9.310083408914688</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5192865482807481</v>
+        <v>-0.5597420561069035</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.676048795268541</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.151872867453369</v>
+        <v>-9.253011637018757</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4924675038359752</v>
+        <v>-0.5329230116621302</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.676048795268541</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.293544709177489</v>
+        <v>-9.394683478742877</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.550611467424365</v>
+        <v>-0.59106697525052</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.676048795268541</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.243953864752655</v>
+        <v>-9.345092634318043</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5157217194895587</v>
+        <v>-0.5561772273157142</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.626457950843708</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.095035530280798</v>
+        <v>-9.196174299846186</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4692055193474993</v>
+        <v>-0.5096610271736544</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.595208360108535</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.869190377561386</v>
+        <v>-8.970329147126774</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3692883852235256</v>
+        <v>-0.4097438930496811</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.553281684521371</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.744611721223794</v>
+        <v>-8.845750490789182</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.31831777813243</v>
+        <v>-0.3587732859585855</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.553281684521371</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.719575039655284</v>
+        <v>-8.820713809220672</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3056693313429184</v>
+        <v>-0.3461248391690734</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.527952596970635</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.647441864367403</v>
+        <v>-8.748580633932791</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2710823569891296</v>
+        <v>-0.3115378648152847</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.527952596970635</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.644238203941597</v>
+        <v>-8.745376973506986</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2795381552126726</v>
+        <v>-0.3199936630388276</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.524748936544829</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.550779169956373</v>
+        <v>-8.651917939521761</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2520380229314902</v>
+        <v>-0.2924935307576453</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.524748936544829</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.540125988402941</v>
+        <v>-8.641264757968329</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2496113108094913</v>
+        <v>-0.2900668186356463</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.524748936544829</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.442218949726451</v>
+        <v>-8.543357719291839</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.210748810312356</v>
+        <v>-0.2512043181385111</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.456763186684273</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.418265408750493</v>
+        <v>-8.519404178315881</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2004988877764791</v>
+        <v>-0.2409543956026341</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.432809645708315</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.154205470427696</v>
+        <v>-8.255344239993084</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1081352286091124</v>
+        <v>-0.1485907364352679</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.168749707385519</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.447125846922858</v>
+        <v>-7.548264616488246</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.171909587132522</v>
+        <v>0.1314540793063665</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.168749707385519</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.406941548556667</v>
+        <v>-7.508080318122055</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1883269303668396</v>
+        <v>0.1478714225406841</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.128565409019328</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.243541677617305</v>
+        <v>-7.344680447182693</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2530536999633415</v>
+        <v>0.212598192137186</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.9651655380799653</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.08542429823853</v>
+        <v>-7.186563067803918</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3242250805527038</v>
+        <v>0.2837695727265488</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.8070481587011898</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.935757907231014</v>
+        <v>-7.036896676796403</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.381199426642751</v>
+        <v>0.3407439188165955</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.7141446674586539</v>
@@ -45366,10 +45366,10 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.803482433600128</v>
+        <v>-6.904621203165516</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3353704021022601</v>
+        <v>0.2949148942761046</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.5818691938277673</v>
@@ -45389,10 +45389,10 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.631621218035225</v>
+        <v>-6.732759987600613</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4069299490158578</v>
+        <v>0.3664744411897027</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.4100079782628644</v>
@@ -45412,10 +45412,10 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.546656551305906</v>
+        <v>-6.647795320871294</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4538221569312442</v>
+        <v>0.4133666491050891</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.3250433115335448</v>
@@ -45435,10 +45435,10 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.652246541079011</v>
+        <v>-6.753385310644399</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2836102314227835</v>
+        <v>0.2431547235966285</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.4306333013066492</v>
@@ -45458,10 +45458,10 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.584011956453583</v>
+        <v>-6.685150726018971</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3594484071500412</v>
+        <v>0.3189928993238857</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.4122179784341132</v>
@@ -45481,10 +45481,10 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.436071915045984</v>
+        <v>-6.537210684611372</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3020036150746739</v>
+        <v>0.2615481072485184</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.3918970625255556</v>
@@ -45504,10 +45504,10 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.383102392791995</v>
+        <v>-6.484241162357383</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.314477437722791</v>
+        <v>0.2740219298966355</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.3389275402715667</v>
@@ -45527,10 +45527,10 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.217314196831705</v>
+        <v>-6.318452966397093</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.373832104011814</v>
+        <v>0.333376596185659</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.3389275402715667</v>
@@ -45550,10 +45550,10 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.183950990352936</v>
+        <v>-6.285089759918324</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4016397409844648</v>
+        <v>0.3611842331583093</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.3389275402715667</v>
@@ -45573,10 +45573,10 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.075691853230414</v>
+        <v>-6.176830622795802</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4394755162926685</v>
+        <v>0.399020008466513</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.3389275402715667</v>
@@ -45596,10 +45596,10 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.952400718413283</v>
+        <v>-6.053539487978671</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4862900642300976</v>
+        <v>0.4458345564039425</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.2156364054544362</v>
@@ -45619,10 +45619,10 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.899703851281992</v>
+        <v>-6.00084262084738</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5150697893199392</v>
+        <v>0.4746142814937842</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.1629395383231451</v>
@@ -45642,10 +45642,10 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.655938409298548</v>
+        <v>-5.757077178863936</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6083566744603677</v>
+        <v>0.5679011666342126</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.1629395383231451</v>
@@ -45665,10 +45665,10 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.566162736922076</v>
+        <v>-5.667301506487464</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6463912573309725</v>
+        <v>0.6059357495048174</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.101340093408835</v>
@@ -45688,10 +45688,10 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.316312342973001</v>
+        <v>-5.417451112538389</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7390734898943045</v>
+        <v>0.6986179820681495</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.101340093408835</v>
@@ -45711,10 +45711,10 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.140420250505569</v>
+        <v>-5.241559020070957</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8130294504019262</v>
+        <v>0.7725739425757712</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.101340093408835</v>
@@ -45734,10 +45734,10 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.968973787483105</v>
+        <v>-5.070112557048494</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8949355416654652</v>
+        <v>0.8544800338393101</v>
       </c>
       <c r="F1921" t="n">
         <v>0.07010636961362809</v>
@@ -45757,10 +45757,10 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.888951500373985</v>
+        <v>-4.990090269939373</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9259649341254106</v>
+        <v>0.8855094262992553</v>
       </c>
       <c r="F1922" t="n">
         <v>0.1501286567227491</v>
@@ -45780,10 +45780,10 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.82531575814005</v>
+        <v>-4.926454527705438</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9561140320733017</v>
+        <v>0.9156585242471464</v>
       </c>
       <c r="F1923" t="n">
         <v>0.2137643989566836</v>
@@ -45803,10 +45803,10 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.731618439923655</v>
+        <v>-4.832757209489043</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9747872181436554</v>
+        <v>0.9343317103175002</v>
       </c>
       <c r="F1924" t="n">
         <v>0.2137643989566836</v>
@@ -45826,10 +45826,10 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.742121062988944</v>
+        <v>-4.843259832554332</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9723292455424173</v>
+        <v>0.931873737716262</v>
       </c>
       <c r="F1925" t="n">
         <v>0.2032617758913947</v>
@@ -45849,10 +45849,10 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.629634802320069</v>
+        <v>-4.730773571885457</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.021253063644787</v>
+        <v>0.9807975558186319</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2032617758913947</v>
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.611921115442204</v>
+        <v>-4.6277643696278</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.029017122313273</v>
+        <v>1.022679820639035</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.255817562044439</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.99800785567689</v>
+        <v>3.027632530030567</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.488446844129186</v>
+        <v>-4.504290098314782</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.075404902058474</v>
+        <v>1.069067600384236</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.255817562044439</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.995005926896884</v>
+        <v>3.02463060125056</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.43051101213097</v>
+        <v>-4.446354266316566</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.100158271868374</v>
+        <v>1.093820970194136</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2320049794710608</v>
+        <v>0.2813794367271882</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.011922088717147</v>
+        <v>3.041546763070824</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.297643323067692</v>
+        <v>-4.313486577253289</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.169199530295509</v>
+        <v>1.16286222862127</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2320049794710608</v>
+        <v>0.2813794367271882</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.02781627151897</v>
+        <v>3.057440945872647</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.177470239703194</v>
+        <v>-4.19331349388879</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.21841460808161</v>
+        <v>1.212077306407372</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3521780628355597</v>
+        <v>0.4015525200916872</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.101065965977972</v>
+        <v>3.130690640331648</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.042216878373217</v>
+        <v>-4.058060132558813</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.282604055175041</v>
+        <v>1.276266753500802</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.4874314241655369</v>
+        <v>0.5368058814216643</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.192306085337398</v>
+        <v>3.221930759691074</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.102091705730909</v>
+        <v>-4.117934959916505</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.24469161563339</v>
+        <v>1.238354313959151</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4275565968078447</v>
+        <v>0.4769310540639722</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.142418680324209</v>
+        <v>3.172043354677885</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.982271474820072</v>
+        <v>-3.998114729005668</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.307908877231933</v>
+        <v>1.301571575557695</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4275565968078447</v>
+        <v>0.4769310540639722</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.157707849558417</v>
+        <v>3.187332523912094</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.984741181281878</v>
+        <v>-4.000584435467474</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.214565193969652</v>
+        <v>1.208227892295414</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4250868903460386</v>
+        <v>0.474461347602166</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.063870225003775</v>
+        <v>3.093494899357451</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.053111367605887</v>
+        <v>-4.068954621791484</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.10647898092535</v>
+        <v>1.100141679251111</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.483737046638381</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.988697505910805</v>
+        <v>3.018322180264482</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.164983647232038</v>
+        <v>-4.180826901417634</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.052166777706781</v>
+        <v>1.045829476032542</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.483737046638381</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.979134214542697</v>
+        <v>3.008758888896373</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.14900898174577</v>
+        <v>-4.164852235931367</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.025131168825316</v>
+        <v>1.018793867151077</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.483737046638381</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.945708739466724</v>
+        <v>2.975333413820401</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.153103528416768</v>
+        <v>-4.168946782602364</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.028060582148704</v>
+        <v>1.021723280474466</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.483737046638381</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.950275971458512</v>
+        <v>2.979900645812188</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.145179153831854</v>
+        <v>-4.16102240801745</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.006972360743877</v>
+        <v>1.000635059069638</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.483737046638381</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.926018000219719</v>
+        <v>2.955642674573395</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.138900951262005</v>
+        <v>-4.154744205447601</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9380219551732663</v>
+        <v>0.9316846534990277</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.49001524920823</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.858323235163078</v>
+        <v>2.887947909516754</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.079048332058282</v>
+        <v>-4.094891586243878</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.972135389286888</v>
+        <v>0.9657980876126495</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.49001524920823</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.86849562159521</v>
+        <v>2.898120295948887</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.992804869031904</v>
+        <v>-4.0086481232175</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.001579045071299</v>
+        <v>0.9952417433970608</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.49001524920823</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.863441892169071</v>
+        <v>2.893066566522747</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.038111688430884</v>
+        <v>-4.05395494261648</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.975232092756233</v>
+        <v>0.9688947910819945</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3998306289428718</v>
+        <v>0.4492050861989992</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.830731569808058</v>
+        <v>2.860356244161734</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.067144793133185</v>
+        <v>-4.082988047318781</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9641707239084141</v>
+        <v>0.9578334222341756</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3998306289428718</v>
+        <v>0.4492050861989992</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.831283442841159</v>
+        <v>2.860908117194836</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.974334311682326</v>
+        <v>-3.990177565867922</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9305676083801235</v>
+        <v>0.9242303067058848</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4926411103937312</v>
+        <v>0.5420155676498586</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.816242423603041</v>
+        <v>2.845867097956717</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.018723781011754</v>
+        <v>-4.03456703519735</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9146852965729531</v>
+        <v>0.9083479948987145</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4482516410643035</v>
+        <v>0.4976260983204309</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.791482217929985</v>
+        <v>2.821106892283662</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.998220087126256</v>
+        <v>-4.014063341311853</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.917962482638875</v>
+        <v>0.9116251809646365</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4687553349498008</v>
+        <v>0.5181297922059283</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.798860142773006</v>
+        <v>2.828484817126683</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.081892183838589</v>
+        <v>-4.097735438024185</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8899849397846094</v>
+        <v>0.8836476381103706</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4687553349498008</v>
+        <v>0.5181297922059283</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.804351438603673</v>
+        <v>2.83397611295735</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.109672581739941</v>
+        <v>-4.125515835925538</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8903699823926072</v>
+        <v>0.8840326807183687</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4409749370484478</v>
+        <v>0.4903493943045751</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.799180401631401</v>
+        <v>2.828805075985077</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.22805325447008</v>
+        <v>-4.243896508655676</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6813734333012051</v>
+        <v>0.6750361316269666</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.4231315421535989</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.597205410341468</v>
+        <v>2.626830084695145</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.336667332913411</v>
+        <v>-4.352510587099007</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7580774626430784</v>
+        <v>0.7517401609688399</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.4231315421535989</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.717355071060674</v>
+        <v>2.74697974541435</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.301258294665268</v>
+        <v>-4.317101548850864</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7867541040446584</v>
+        <v>0.7804168023704199</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.4231315421535989</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.731868097162997</v>
+        <v>2.761492771516673</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.309719463320729</v>
+        <v>-4.325562717506325</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.780789077924843</v>
+        <v>0.7744517762506042</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3652959162420105</v>
+        <v>0.4146703734981379</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.724210837312089</v>
+        <v>2.753835511665765</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.132603133285563</v>
+        <v>-4.148446387471159</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8483646387842116</v>
+        <v>0.8420273371099731</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3652959162420105</v>
+        <v>0.4146703734981379</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.720939866157391</v>
+        <v>2.750564540511068</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.177695378119108</v>
+        <v>-4.193538632304705</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8310111326127065</v>
+        <v>0.824673830938468</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3033998730726207</v>
+        <v>0.3527743303287481</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.684485632017671</v>
+        <v>2.714110306371347</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.998319956880341</v>
+        <v>-4.172431643188397</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.896548276414628</v>
+        <v>0.8269036018914053</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4601766312433394</v>
+        <v>0.3674276684026466</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.772338662226516</v>
+        <v>2.7166892845221</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982231</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.043334170400946</v>
+        <v>-4.217445856709004</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8593500463379753</v>
+        <v>0.7897053718147524</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4298277359287348</v>
+        <v>0.337078773088042</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.734936780369343</v>
+        <v>2.679287402664928</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850954</v>
+        <v>3.737026608509539</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.131345356959644</v>
+        <v>-4.305457043267701</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8298371340534423</v>
+        <v>0.7601924595302192</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3643512280695618</v>
+        <v>0.271602265228869</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.701342437992785</v>
+        <v>2.645693060288369</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.232543138396816</v>
+        <v>-4.406654824704874</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7885619433750746</v>
+        <v>0.7189172688518517</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2959424145242426</v>
+        <v>0.2031934516835498</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.659501071762095</v>
+        <v>2.603851694057679</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.226032171782504</v>
+        <v>-4.400143858090561</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7887662915751164</v>
+        <v>0.7191216170518935</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2959424145242426</v>
+        <v>0.2031934516835498</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.657101033316412</v>
+        <v>2.601451655611996</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.206994044075206</v>
+        <v>-4.381105730383264</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7929062618662801</v>
+        <v>0.7232615873430572</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2377588031930481</v>
+        <v>0.1450098403523553</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.61871558572594</v>
+        <v>2.563066208021524</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.259509846350027</v>
+        <v>-4.433621532658084</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8911943425905424</v>
+        <v>0.8215496680673193</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2377588031930481</v>
+        <v>0.1450098403523553</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.73800998736013</v>
+        <v>2.682360609655714</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.262918157784607</v>
+        <v>-4.437029844092664</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8906643470028439</v>
+        <v>0.821019672479621</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2702753722024255</v>
+        <v>0.1775264093617326</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.75835325775189</v>
+        <v>2.702703880047475</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.243562021890759</v>
+        <v>-4.417673708198817</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9044153317573089</v>
+        <v>0.8347706572340861</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2702753722024255</v>
+        <v>0.1775264093617326</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.764361788148816</v>
+        <v>2.7087124104444</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.316891550628852</v>
+        <v>-4.491003236936909</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7730337415392714</v>
+        <v>0.7033890670160483</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2706700346220474</v>
+        <v>0.1779210717813546</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.662548806877789</v>
+        <v>2.606899429173373</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.409870503348191</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.40071277190355</v>
+        <v>-4.574824458211608</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.6492289702730232</v>
+        <v>0.5795842957498003</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2706700346220474</v>
+        <v>0.1779210717813546</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.57227252412142</v>
+        <v>2.516623146417004</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.41053285173985</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.394560065850766</v>
+        <v>-4.568671752158823</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.6523524010857953</v>
+        <v>0.5827077265625724</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2768227406748317</v>
+        <v>0.1840737778341389</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.576626496144749</v>
+        <v>2.520977118440333</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.40961332847996</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.411369364001268</v>
+        <v>-4.585481050309325</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.6447091585657048</v>
+        <v>0.5750644840424819</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2600134425243301</v>
+        <v>0.1672644796836372</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.565621393994558</v>
+        <v>2.509972016290142</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798429</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.475948882276781</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.349071365225146</v>
+        <v>-4.523183051533203</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.7359639118729746</v>
+        <v>0.6663192373497515</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3053077067987721</v>
+        <v>0.2125587439580793</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.659133506356044</v>
+        <v>2.603484128651629</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.278240883990908</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.147281167559988</v>
+        <v>-4.321392853868045</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6189719926531647</v>
+        <v>0.5493273181299418</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5033258989679266</v>
+        <v>0.4105769361272337</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.580236423371664</v>
+        <v>2.524587045667248</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.348531116313083</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.198167880246182</v>
+        <v>-4.37227956655424</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6689075399008622</v>
+        <v>0.5992628653776393</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.452439186281732</v>
+        <v>0.3596902234410391</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.619994628082122</v>
+        <v>2.564345250377707</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.363158852429127</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.111557137596376</v>
+        <v>-4.285668823904433</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7181795730768286</v>
+        <v>0.6485348985536055</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5310649174868902</v>
+        <v>0.4383159546461974</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.681797802921261</v>
+        <v>2.626148425216845</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.361694833253798</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.17176643560166</v>
+        <v>-4.345878121909718</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6926318346993863</v>
+        <v>0.6229871601761632</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4708556194816057</v>
+        <v>0.3781066566409129</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.644208204942762</v>
+        <v>2.588558827238346</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.360186451293727</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.122579786917309</v>
+        <v>-4.296691473225366</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7107981122130553</v>
+        <v>0.6411534376898325</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4708556194816057</v>
+        <v>0.3781066566409129</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.642699822982691</v>
+        <v>2.587050445278275</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316254</v>
+        <v>3.833513460316252</v>
       </c>
       <c r="C1976" t="n">
         <v>2.360049318729163</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.07820665527874</v>
+        <v>-4.252318341586798</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.728410232303919</v>
+        <v>0.6587655577806961</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5152287511201743</v>
+        <v>0.4224797882794815</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.669186569401268</v>
+        <v>2.613537191696852</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.354443112867754</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.04347533396024</v>
+        <v>-4.217587020268297</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7366965549699098</v>
+        <v>0.6670518804466867</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5152287511201743</v>
+        <v>0.4224797882794815</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.663580363539858</v>
+        <v>2.607930985835443</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190327</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.360824869895558</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.995819603399184</v>
+        <v>-4.169931289707241</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7621406042221368</v>
+        <v>0.6924959296989137</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.56288448168123</v>
+        <v>0.4701355188405371</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.698555558904296</v>
+        <v>2.642906181199881</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569619</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.365717243270283</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.895301444900429</v>
+        <v>-4.069413131208487</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8072402409963635</v>
+        <v>0.7375955664731404</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6634026401799845</v>
+        <v>0.5706536773392916</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.763758827378274</v>
+        <v>2.708109449673858</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557297</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.352471915746155</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.879396115468077</v>
+        <v>-4.053507801776134</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8003570452451767</v>
+        <v>0.7307123707219536</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5842899794707457</v>
+        <v>0.4915410166300527</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.703045903428603</v>
+        <v>2.647396525724187</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932771</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.356569618356784</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.834557713859679</v>
+        <v>-4.008669400167737</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8223901084991645</v>
+        <v>0.7527454339759414</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5888334124156152</v>
+        <v>0.4960844495749221</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.709869665806153</v>
+        <v>2.654220288101738</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.360730557987862</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.854056170101687</v>
+        <v>-4.028167856409745</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8187516656334393</v>
+        <v>0.7491069911102159</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5407487711357108</v>
+        <v>0.4479998082950178</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.685179820669289</v>
+        <v>2.629530442964873</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405963</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.366610160515699</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.809853333015786</v>
+        <v>-3.983965019323844</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8423124029956366</v>
+        <v>0.7726677284724133</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5849516082216113</v>
+        <v>0.4922026453809183</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.717581125448666</v>
+        <v>2.66193174774425</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265647</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.365020160984947</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.817412998852833</v>
+        <v>-3.991524685160891</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8376985371300654</v>
+        <v>0.7680538626068421</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6397550122314306</v>
+        <v>0.5470060493907376</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.748873168323805</v>
+        <v>2.693223790619389</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284882</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.416267926167986</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.659121581313561</v>
+        <v>-3.833233267621619</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9522628693288138</v>
+        <v>0.8826181948055907</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6397550122314306</v>
+        <v>0.5470060493907376</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.800120933506845</v>
+        <v>2.744471555802429</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321025</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.414708630762239</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.451479577679085</v>
+        <v>-3.625591263987143</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.033760375376857</v>
+        <v>0.9641157008536343</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8473970158659068</v>
+        <v>0.7546480530252138</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.923146840281784</v>
+        <v>2.867497462577368</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475141</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.409656859000509</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.400447484956557</v>
+        <v>-3.574559171264615</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.049121440704139</v>
+        <v>0.9794767661809156</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8984291085884347</v>
+        <v>0.8056801457477417</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.94871432415357</v>
+        <v>2.893064946449154</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404856</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.426844263093214</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.335223303829351</v>
+        <v>-3.509334990137409</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.092398517247726</v>
+        <v>1.022753842724503</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9636532897156403</v>
+        <v>0.8709043268749473</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.005036236922599</v>
+        <v>2.949386859218183</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84006118688256</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.422805235392495</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.297796283758217</v>
+        <v>-3.471907970066276</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.10333029757546</v>
+        <v>1.033685623052236</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.968904827744822</v>
+        <v>0.876155864904129</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.004148132039388</v>
+        <v>2.948498754334972</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992663</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.424062027723735</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.296438298784672</v>
+        <v>-3.47054998509273</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.105130283896118</v>
+        <v>1.035485609372895</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.043242953282641</v>
+        <v>0.9504939904419476</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.050007799693319</v>
+        <v>2.994358421988904</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636289</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.584619798744946</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.268025035684788</v>
+        <v>-3.442136721992846</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.277053360157282</v>
+        <v>1.207408685634059</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9842673905362118</v>
+        <v>0.8915184276955188</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.175180233066673</v>
+        <v>3.119530855362257</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957629</v>
+        <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
         <v>2.704732707962763</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.193242774659776</v>
+        <v>-3.367354460967834</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.427079173785105</v>
+        <v>1.357434499261881</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.059049651561224</v>
+        <v>0.9663006887205314</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.340162498899498</v>
+        <v>3.284513121195082</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998756</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>2.696440683976622</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.167158690395968</v>
+        <v>-3.341270376704026</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.429220783504487</v>
+        <v>1.359576108981264</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.059049651561224</v>
+        <v>0.9663006887205314</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.331870474913357</v>
+        <v>3.276221097208941</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896931</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
         <v>2.694633879560401</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.079280777286847</v>
+        <v>-3.253392463594905</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.462565144331915</v>
+        <v>1.392920469808691</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.174975293984576</v>
+        <v>1.082226331143882</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.399619055951147</v>
+        <v>3.343969678246731</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.79626414395986</v>
+        <v>3.796264143959858</v>
       </c>
       <c r="C1995" t="n">
         <v>2.712188285287193</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.070388315893564</v>
+        <v>-3.244500002201622</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.483676534616019</v>
+        <v>1.414031860092796</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.174975293984576</v>
+        <v>1.082226331143882</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.417173461677939</v>
+        <v>3.361524083973523</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945369</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
         <v>2.704043332691777</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.238864432863442</v>
+        <v>-3.4129761191715</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.408141135232652</v>
+        <v>1.338496460709429</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.147027458267995</v>
+        <v>1.054278495427302</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.392259807652574</v>
+        <v>3.336610429948158</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782711</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>2.685313029879639</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.792608240234002</v>
+        <v>-2.96671992654206</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.56791330947229</v>
+        <v>1.498268634949067</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.052308788598362</v>
+        <v>0.959559825757669</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.316698303038656</v>
+        <v>3.26104892533424</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>2.675977052376543</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.76988713655085</v>
+        <v>-2.943998822858908</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.567665773442456</v>
+        <v>1.498021098919232</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.052308788598362</v>
+        <v>0.959559825757669</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.307362325535561</v>
+        <v>3.251712947831145</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777676</v>
+        <v>3.783205696777674</v>
       </c>
       <c r="C1999" t="n">
         <v>2.834883178227712</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.899088949844892</v>
+        <v>-3.07320063615295</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.674891173976008</v>
+        <v>1.605246499452784</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.92310697530432</v>
+        <v>0.8303580124636267</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.388747363410304</v>
+        <v>3.333097985705888</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644414</v>
       </c>
       <c r="C2000" t="n">
         <v>2.871961000721359</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.924963348318918</v>
+        <v>-3.099075034626976</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.701619237080044</v>
+        <v>1.63197456255682</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9680185840160611</v>
+        <v>0.8752696211753679</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.452772151130996</v>
+        <v>3.39712277342658</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799964</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>2.868636356710904</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.917908658103744</v>
+        <v>-3.092020344411802</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.701116469155658</v>
+        <v>1.631471794632435</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9750732742312349</v>
+        <v>0.8823243113905417</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.453680321249645</v>
+        <v>3.398030943545229</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>2.878642510355645</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.890957433777256</v>
+        <v>-3.065069120085314</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.721903112530995</v>
+        <v>1.652258438007772</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9899536202589541</v>
+        <v>0.8972046574182608</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.472614682511018</v>
+        <v>3.416965304806602</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76805206778411</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.062745642500605</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.912501661608043</v>
+        <v>-3.086613347916102</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.89738855354364</v>
+        <v>1.827743879020417</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9899536202589541</v>
+        <v>0.8972046574182608</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.656717814655978</v>
+        <v>3.601068436951562</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714426</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.054862337403598</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.934909779412915</v>
+        <v>-3.109021465720974</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.880542001324684</v>
+        <v>1.810897326801461</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9899536202589541</v>
+        <v>0.8972046574182608</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.648834509558971</v>
+        <v>3.593185131854555</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155035</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.056916336953236</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.963134014990516</v>
+        <v>-3.137245701298574</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.871306306643282</v>
+        <v>1.801661632120058</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.007930372710263</v>
+        <v>0.9151814098695694</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.661674560579394</v>
+        <v>3.606025182874978</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161981</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
         <v>3.113170054675083</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.972574940879046</v>
+        <v>-3.146686627187104</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.923783654009717</v>
+        <v>1.854138979486493</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.130357490253654</v>
+        <v>1.037608527412961</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.791384548827275</v>
+        <v>3.73573517112286</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321639</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
         <v>3.116061149220384</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.178813878667479</v>
+        <v>-3.352925564975537</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.844179173439644</v>
+        <v>1.774534498916421</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9241185524652205</v>
+        <v>0.8313695896245272</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.670532280699516</v>
+        <v>3.614882902995101</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347709</v>
+        <v>3.727898186347708</v>
       </c>
       <c r="C2008" t="n">
         <v>3.114172962114159</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.255143856268385</v>
+        <v>-3.429255542576443</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.811758995293057</v>
+        <v>1.742114320769834</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9241185524652205</v>
+        <v>0.8313695896245272</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.668644093593291</v>
+        <v>3.612994715888876</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887755</v>
+        <v>3.710654104887753</v>
       </c>
       <c r="C2009" t="n">
         <v>3.108993191717021</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.410100641668514</v>
+        <v>-3.584212327976573</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.744596510735868</v>
+        <v>1.674951836212644</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7691617670650912</v>
+        <v>0.676412804224398</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.570490251956076</v>
+        <v>3.51484087425166</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343073</v>
+        <v>3.712897612343071</v>
       </c>
       <c r="C2010" t="n">
         <v>3.107427201927174</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.571669067195769</v>
+        <v>-3.745780753503828</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.678403150735118</v>
+        <v>1.608758476211894</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6423788432672118</v>
+        <v>0.5496298804265186</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.492854507887501</v>
+        <v>3.437205130183085</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389356</v>
+        <v>3.754596135389354</v>
       </c>
       <c r="C2011" t="n">
         <v>3.120500608793092</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.679969729065889</v>
+        <v>-3.854081415373947</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.648156292852989</v>
+        <v>1.578511618329765</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6423788432672118</v>
+        <v>0.5496298804265186</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.505927914753419</v>
+        <v>3.450278537049003</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.112505805576032</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.839520801829406</v>
+        <v>-4.013632488137464</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.576341060530522</v>
+        <v>1.506696386007299</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4901011764054604</v>
+        <v>0.3973522135647671</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.406566511419308</v>
+        <v>3.350917133714893</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.111029846703034</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.867421588938879</v>
+        <v>-4.041533275246937</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.563704786813735</v>
+        <v>1.494060112290511</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4555042522625256</v>
+        <v>0.3627552894218323</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.38433239806055</v>
+        <v>3.328683020356134</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787388</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.107794290680233</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.989947691641773</v>
+        <v>-4.16405937794983</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.511458789709776</v>
+        <v>1.441814115186553</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3329781495596317</v>
+        <v>0.2402291867189384</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.307581180416012</v>
+        <v>3.251931802711596</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.174500250270737</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.220462187827361</v>
+        <v>-4.394573874135419</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.485958950826044</v>
+        <v>1.416314276302821</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.102463653374043</v>
+        <v>0.009714690533349724</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.235978442295163</v>
+        <v>3.180329064590747</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814668</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
         <v>3.314811969272584</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.569207273051805</v>
+        <v>-4.743318959359863</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.486772635738114</v>
+        <v>1.417127961214891</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.09903326338554808</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.311041388945671</v>
+        <v>3.255392011241255</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237097</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.383792238418224</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.723193690827945</v>
+        <v>-4.897305377136004</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.494158337773297</v>
+        <v>1.424513663250074</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.09903326338554808</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.380021658091311</v>
+        <v>3.324372280386895</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.61992301642339</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
         <v>3.369843440538344</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.927793125690954</v>
+        <v>-5.101904811999012</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.398369765948215</v>
+        <v>1.328725091424992</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.09903326338554808</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.366072860211432</v>
+        <v>3.310423482507016</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609755</v>
+        <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
         <v>3.381713929593758</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.180268279698678</v>
+        <v>-5.354379966006737</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.309250193400539</v>
+        <v>1.239605518877316</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.09903326338554808</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.377943349266846</v>
+        <v>3.32229397156243</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973159</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.382924464112702</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.47316403617809</v>
+        <v>-5.647275722486149</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.193302425327718</v>
+        <v>1.123657750804495</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.09903326338554808</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.37915388378579</v>
+        <v>3.323504506081373</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251948</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.387046206340024</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.659828164312898</v>
+        <v>-5.833939850620957</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.122758516301116</v>
+        <v>1.053113841777893</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.03302327136941474</v>
+        <v>-0.125772234210108</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.367232243518375</v>
+        <v>3.311582865813959</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916203</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.382124059076213</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.805848851226861</v>
+        <v>-5.979960537534919</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.059428094271721</v>
+        <v>0.9897834197484974</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.04210636316327171</v>
+        <v>-0.1348553260039649</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.35686024117825</v>
+        <v>3.301210863473834</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.66796230683033</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.544328115775257</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.897562860336446</v>
+        <v>-6.071674546644504</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.18494654732693</v>
+        <v>1.115301872803708</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.04210636316327171</v>
+        <v>-0.1348553260039649</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.519064297877294</v>
+        <v>3.463414920172879</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071554</v>
+        <v>3.696539468071552</v>
       </c>
       <c r="C2024" t="n">
         <v>3.539174753739071</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.929214519396416</v>
+        <v>-6.103326205704473</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.167132521666757</v>
+        <v>1.097487847143534</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.04727482040771191</v>
+        <v>-0.1400237832484051</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.510809861494444</v>
+        <v>3.455160483790028</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868151</v>
+        <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
         <v>3.549404171307562</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.998280573969352</v>
+        <v>-6.17239226027741</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.149735517406073</v>
+        <v>1.08009084288285</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1096456979013219</v>
+        <v>-0.2023946607420152</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.483616752566769</v>
+        <v>3.427967374862353</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332697</v>
+        <v>3.783632867332695</v>
       </c>
       <c r="C2026" t="n">
         <v>3.558329809763465</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.10025669621776</v>
+        <v>-6.274368382525817</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.117870706962613</v>
+        <v>1.04822603243939</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2116218201497295</v>
+        <v>-0.3043707829904228</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.431356717673627</v>
+        <v>3.375707339969211</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231814</v>
+        <v>3.798296784231812</v>
       </c>
       <c r="C2027" t="n">
         <v>3.55048269700764</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.990250412740538</v>
+        <v>-6.164362099048596</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.154026107597677</v>
+        <v>1.084381433074454</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1884172482324543</v>
+        <v>-0.2811662110731475</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.437432348068168</v>
+        <v>3.381782970363752</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.554732707729614</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.002780117852417</v>
+        <v>-6.176891804160475</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.1532642362749</v>
+        <v>1.083619561751676</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2022437476989773</v>
+        <v>-0.2949927105396706</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.433386459110229</v>
+        <v>3.377737081405813</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.56199359061215</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.70133339238058</v>
+        <v>-5.875445078688637</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.281103809346171</v>
+        <v>1.211459134822948</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.09920297777285991</v>
+        <v>0.006454014932166685</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.621515377275867</v>
+        <v>3.565865999571451</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.562964768364861</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.725923636615764</v>
+        <v>-5.900035322923821</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.272238889404808</v>
+        <v>1.202594214881585</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.09920297777285991</v>
+        <v>0.006454014932166685</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.622486555028577</v>
+        <v>3.566837177324161</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.82118418247416</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.563807672744617</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.674885260609243</v>
+        <v>-5.848996946917301</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.293497144187171</v>
+        <v>1.223852469663949</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.09920297777285991</v>
+        <v>0.006454014932166685</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.623329459408333</v>
+        <v>3.567680081703917</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
         <v>3.582845771618762</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.646036583785783</v>
+        <v>-5.82014827009384</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.324074713790701</v>
+        <v>1.254430039267478</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1280516545963202</v>
+        <v>0.03530269175562695</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.659676764376554</v>
+        <v>3.604027386672139</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.82575293270048</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
         <v>3.399029767742697</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.549401671767143</v>
+        <v>-5.7235133580752</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.178912674722091</v>
+        <v>1.109268000198869</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2246865666149601</v>
+        <v>0.1319376037742669</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.533841707711673</v>
+        <v>3.478192330007257</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077644</v>
+        <v>3.804688961077642</v>
       </c>
       <c r="C2034" t="n">
         <v>3.402531811816661</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.480363660818675</v>
+        <v>-5.654475347126732</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.210029923175443</v>
+        <v>1.14038524865222</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2937245775634282</v>
+        <v>0.200975614722735</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.578766558354718</v>
+        <v>3.523117180650302</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833464</v>
+        <v>3.775028860833462</v>
       </c>
       <c r="C2035" t="n">
         <v>3.386958630892743</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.461576560449736</v>
+        <v>-5.635688246757794</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.201971582399101</v>
+        <v>1.132326907875878</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3125116779323667</v>
+        <v>0.2197627150916734</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.574465637652164</v>
+        <v>3.518816259947747</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.386146341329173</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.384477958907864</v>
+        <v>-5.558589645215921</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.23199873345228</v>
+        <v>1.162354058929056</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3125116779323667</v>
+        <v>0.2197627150916734</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.573653348088593</v>
+        <v>3.518003970384177</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.396015120454245</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.394863153797753</v>
+        <v>-5.568974840105811</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.237713434621396</v>
+        <v>1.168068760098173</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3021264830424774</v>
+        <v>0.2093775202017841</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.577291010279732</v>
+        <v>3.521641632575316</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735286</v>
+        <v>3.834415493735285</v>
       </c>
       <c r="C2038" t="n">
         <v>3.466852126230671</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.413451312519978</v>
+        <v>-5.587562998828036</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.301115176908931</v>
+        <v>1.231470502385708</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.283538324320252</v>
+        <v>0.1907893614795588</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.636975120822822</v>
+        <v>3.581325743118406</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.463721137048969</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.413749859216014</v>
+        <v>-5.587861545524071</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.297864769048815</v>
+        <v>1.228220094525593</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2832397776242161</v>
+        <v>0.1904908147835229</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.633665003623499</v>
+        <v>3.578015625919083</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108862</v>
+        <v>3.81564321210886</v>
       </c>
       <c r="C2040" t="n">
         <v>3.468252031988361</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.312926725525586</v>
+        <v>-5.487038411833644</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.342724917464378</v>
+        <v>1.273080242941155</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2957039931085699</v>
+        <v>0.2029550302678767</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.645674427853503</v>
+        <v>3.590025050149087</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121473</v>
+        <v>3.807356168121471</v>
       </c>
       <c r="C2041" t="n">
         <v>3.468381285466904</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.122145364773178</v>
+        <v>-5.296257051081236</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.419166715243884</v>
+        <v>1.349522040720661</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4864853538609773</v>
+        <v>0.3937363910202841</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.76027249778349</v>
+        <v>3.704623120079074</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906086</v>
+        <v>3.775233033906084</v>
       </c>
       <c r="C2042" t="n">
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.015182006923757</v>
+        <v>-5.189293693231814</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.44178890412125</v>
+        <v>1.372144229598027</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5449499618207787</v>
+        <v>0.4522009989800855</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.775188108296968</v>
+        <v>3.719538730592552</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.78576168591299</v>
+        <v>3.785761685912989</v>
       </c>
       <c r="C2043" t="n">
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.959851419021994</v>
+        <v>-5.133963105330052</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.498888075894013</v>
+        <v>1.42924340137079</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6002805497225409</v>
+        <v>0.5075315868818477</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.843353397650084</v>
+        <v>3.787704019945668</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.7437679565399</v>
+        <v>3.743767956539898</v>
       </c>
       <c r="C2044" t="n">
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.947797292109032</v>
+        <v>-5.121908978417089</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.497396294560636</v>
+        <v>1.427751620037413</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6123346766355037</v>
+        <v>0.5195857137948106</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.844272441699299</v>
+        <v>3.788623063994883</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811015</v>
+        <v>3.725010844811013</v>
       </c>
       <c r="C2045" t="n">
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.025152782237001</v>
+        <v>-5.199264468545058</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.468334728693584</v>
+        <v>1.398690054170361</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5349791865075343</v>
+        <v>0.4422302236668412</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.799739777806653</v>
+        <v>3.744090400102237</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382926</v>
+        <v>3.612322444382924</v>
       </c>
       <c r="C2046" t="n">
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.957104219545471</v>
+        <v>-5.131215905853528</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.508405179648078</v>
+        <v>1.438760505124856</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.510278786358371</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.853419941299454</v>
+        <v>3.797770563595038</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013433</v>
+        <v>3.645256780013431</v>
       </c>
       <c r="C2047" t="n">
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.188704612714972</v>
+        <v>-5.362816299023029</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.435967692553872</v>
+        <v>1.366323018030649</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.510278786358371</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.873622611473048</v>
+        <v>3.817973233768632</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.66674720149897</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.238756158244191</v>
+        <v>-5.412867844552249</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.399553310409066</v>
+        <v>1.329908635885844</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.510278786358371</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.85722884753993</v>
+        <v>3.801579469835514</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800098</v>
       </c>
       <c r="C2049" t="n">
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.413862990820636</v>
+        <v>-5.587974677128694</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.289762490971955</v>
+        <v>1.220117816448732</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.510278786358371</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.817480761133397</v>
+        <v>3.76183138342898</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660852</v>
+        <v>3.74557314866085</v>
       </c>
       <c r="C2050" t="n">
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.217762837390113</v>
+        <v>-5.391874523698171</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.375225171341104</v>
+        <v>1.305580496817881</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.799127902629587</v>
+        <v>0.7063789397888939</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.94216347218865</v>
+        <v>3.886514094484234</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395089</v>
+        <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.064737445276829</v>
+        <v>-5.238849131584886</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.535606327759323</v>
+        <v>1.4659616532361</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9521532947428711</v>
+        <v>0.859404331902178</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.133149707029525</v>
+        <v>4.077500329325109</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791151</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.093044759150099</v>
+        <v>-5.267156445458157</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.711749627118307</v>
+        <v>1.642104952595084</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9521532947428711</v>
+        <v>0.859404331902178</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.320615931937818</v>
+        <v>4.264966554233402</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620436</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.259637984263621</v>
+        <v>-5.433749670571679</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.614515288426981</v>
+        <v>1.544870613903758</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.6928111067886555</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.190062948223787</v>
+        <v>4.134413570519371</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285649</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.236602190902055</v>
+        <v>-5.410713877210113</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.627406008433325</v>
+        <v>1.557761333910102</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.6928111067886555</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.193739350885505</v>
+        <v>4.138089973181089</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399471</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.207356210446359</v>
+        <v>-5.381467896754416</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.636722455739099</v>
+        <v>1.567077781215876</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.6928111067886555</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.191357406009</v>
+        <v>4.135708028304584</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256374</v>
+        <v>3.699404642256372</v>
       </c>
       <c r="C2056" t="n">
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.31428175832421</v>
+        <v>-5.488393444632267</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.591245475745593</v>
+        <v>1.521600801222371</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6786345217514974</v>
+        <v>0.5858855589108042</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.124495316439925</v>
+        <v>4.068845938735508</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701004</v>
+        <v>3.689942600701002</v>
       </c>
       <c r="C2057" t="n">
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.459300316831459</v>
+        <v>-5.633412003139516</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.534666854485928</v>
+        <v>1.465022179962705</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5336159632442489</v>
+        <v>0.4408670004035556</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.038912983478809</v>
+        <v>3.983263605774393</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687015</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.577642082616176</v>
+        <v>-5.751753768924234</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.587261387429794</v>
+        <v>1.517616712906571</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.4515530389664457</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.145255845874297</v>
+        <v>4.08960646816988</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790808</v>
+        <v>3.714879051790806</v>
       </c>
       <c r="C2059" t="n">
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.629052504936884</v>
+        <v>-5.803164191244941</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.56448291562745</v>
+        <v>1.494838241104227</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.4515530389664457</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.143041543000235</v>
+        <v>4.087392165295819</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437337</v>
+        <v>3.704757949437335</v>
       </c>
       <c r="C2060" t="n">
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.708471956144636</v>
+        <v>-5.882583642452693</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.532618263218639</v>
+        <v>1.462973588695416</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.4515530389664457</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.142944671074525</v>
+        <v>4.087295293370109</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298405</v>
+        <v>3.736804952298403</v>
       </c>
       <c r="C2061" t="n">
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.803934954061853</v>
+        <v>-5.978046640369911</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.494426957609794</v>
+        <v>1.424782283086572</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.4515530389664457</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.142938564632567</v>
+        <v>4.087289186928151</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218007</v>
+        <v>3.715372960218005</v>
       </c>
       <c r="C2062" t="n">
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.739559043211139</v>
+        <v>-5.913670729519196</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.518273718512691</v>
+        <v>1.448629043989468</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6086779126578541</v>
+        <v>0.5159289498171609</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.179660507705607</v>
+        <v>4.124011130001191</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353542</v>
+        <v>3.736089413353541</v>
       </c>
       <c r="C2063" t="n">
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.794928205343332</v>
+        <v>-5.96903989165139</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.50185987140754</v>
+        <v>1.432215196884318</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6086779126578541</v>
+        <v>0.5159289498171609</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.185394325453334</v>
+        <v>4.129744947748918</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113286</v>
+        <v>3.736822870113284</v>
       </c>
       <c r="C2064" t="n">
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.813146672340941</v>
+        <v>-5.987258358648998</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.494110847951429</v>
+        <v>1.424466173428206</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.4908225125613187</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.169868826442761</v>
+        <v>4.114219448738345</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113693</v>
+        <v>3.790272500113692</v>
       </c>
       <c r="C2065" t="n">
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.77446323699701</v>
+        <v>-5.948574923305068</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.52945861493932</v>
+        <v>1.459813940416097</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.4908225125613187</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.18974321929308</v>
+        <v>4.134093841588664</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016437</v>
       </c>
       <c r="C2066" t="n">
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.668428241791701</v>
+        <v>-5.842539928099758</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.555573313546172</v>
+        <v>1.485928639022949</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.4908225125613187</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.173443919817807</v>
+        <v>4.117794542113391</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307669</v>
       </c>
       <c r="C2067" t="n">
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.485216578658606</v>
+        <v>-5.659328264966663</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.631288928263456</v>
+        <v>1.561644253740233</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.4908225125613187</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.175874869281854</v>
+        <v>4.120225491577438</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.77684655786355</v>
       </c>
       <c r="C2068" t="n">
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.413495131644755</v>
+        <v>-5.587606817952812</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.642921913148373</v>
+        <v>1.57327723862515</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6552929224158626</v>
+        <v>0.5625439595751693</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.201852143569541</v>
+        <v>4.146202765865125</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394113</v>
+        <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.391122106037049</v>
+        <v>-5.565233792345106</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.598786869312627</v>
+        <v>1.529142194789404</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6665486735287641</v>
+        <v>0.5737997106880709</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.155521340158454</v>
+        <v>4.099871962454038</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456731</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.424138401947793</v>
+        <v>-5.598250088255851</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.770778555833684</v>
+        <v>1.701133881310462</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5971112968620125</v>
+        <v>0.5043623340213192</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.299057119043757</v>
+        <v>4.243407741339341</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883682</v>
+        <v>3.71376253688368</v>
       </c>
       <c r="C2071" t="n">
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.412610766298185</v>
+        <v>-5.586722452606242</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.767310835921777</v>
+        <v>1.697666161398554</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6561119550633749</v>
+        <v>0.5633629922226817</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.326378739792824</v>
+        <v>4.270729362088408</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236303</v>
+        <v>3.717150699236301</v>
       </c>
       <c r="C2072" t="n">
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.509952267640553</v>
+        <v>-5.684063953948611</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.732042347906618</v>
+        <v>1.662397673383395</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6116917728978866</v>
+        <v>0.5189428100571933</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.303394743015319</v>
+        <v>4.247745365310903</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.70520107942769</v>
+        <v>3.705201079427688</v>
       </c>
       <c r="C2073" t="n">
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.59580829698052</v>
+        <v>-5.769919983288577</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.69895101836347</v>
+        <v>1.629306343840247</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5693157036717515</v>
+        <v>0.4765667408310583</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.279220183672477</v>
+        <v>4.223570805968061</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.604645094396639</v>
+        <v>-5.778756780704697</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.677835501217524</v>
+        <v>1.608190826694301</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5618735310304008</v>
+        <v>0.4691245681897075</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.257174081908168</v>
+        <v>4.201524704203752</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.71554441166746</v>
+        <v>3.715544411667458</v>
       </c>
       <c r="C2075" t="n">
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.696027656962098</v>
+        <v>-5.870139343270155</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.65144698723639</v>
+        <v>1.581802312713167</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5253086463110561</v>
+        <v>0.4325596834703629</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.245399662121611</v>
+        <v>4.189750284417195</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889197</v>
+        <v>3.673978374889195</v>
       </c>
       <c r="C2076" t="n">
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.684320938975092</v>
+        <v>-5.858432625283149</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.75825793225546</v>
+        <v>1.688613257732237</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.4442664014573693</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.354551950738083</v>
+        <v>4.298902573033667</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409573</v>
+        <v>3.682476099409571</v>
       </c>
       <c r="C2077" t="n">
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.755233012717369</v>
+        <v>-5.929344699025426</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.732925441489954</v>
+        <v>1.663280766966731</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.4442664014573693</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.357584289469488</v>
+        <v>4.301934911765072</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452572</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
         <v>4.248279904168708</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.765549110883721</v>
+        <v>-5.939660797191778</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.941703835501472</v>
+        <v>1.872059160978249</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.4442664014573693</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.570489122747546</v>
+        <v>4.51483974504313</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762293</v>
+        <v>3.623960959762291</v>
       </c>
       <c r="C2079" t="n">
         <v>4.247458571080798</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.765455142866348</v>
+        <v>-5.939566829174406</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.94092008962051</v>
+        <v>1.871275415097287</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4446362628046873</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.569889706468026</v>
+        <v>4.51424032876361</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884086</v>
+        <v>3.800870306884084</v>
       </c>
       <c r="C2080" t="n">
         <v>4.241690557025152</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.909056306889734</v>
+        <v>-6.083167993197791</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.87771160995551</v>
+        <v>1.808066935432287</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4446362628046873</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.56412169241238</v>
+        <v>4.508472314707964</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.67101569212965</v>
+        <v>3.671015692129648</v>
       </c>
       <c r="C2081" t="n">
         <v>4.241690557025152</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.908107883771695</v>
+        <v>-6.082219570079753</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.878090979202725</v>
+        <v>1.808446304679503</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4446362628046873</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.56412169241238</v>
+        <v>4.508472314707964</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052353</v>
+        <v>3.904173816052351</v>
       </c>
       <c r="C2082" t="n">
         <v>4.254418165006244</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.008377701730716</v>
+        <v>-6.182489388038773</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.850710660000209</v>
+        <v>1.781065985476986</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4446362628046873</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.576849300393472</v>
+        <v>4.521199922689056</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813497</v>
+        <v>3.740179607813495</v>
       </c>
       <c r="C2083" t="n">
         <v>4.256364163430631</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.002385454941904</v>
+        <v>-6.176497141249961</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.855053557140122</v>
+        <v>1.785408882616899</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4446362628046873</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.57879529881786</v>
+        <v>4.523145921113444</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537945</v>
+        <v>3.765050796537944</v>
       </c>
       <c r="C2084" t="n">
         <v>4.2500182994484</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.913827493811136</v>
+        <v>-6.087939180119194</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.884130877610198</v>
+        <v>1.814486203086974</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4446362628046873</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.572449434835629</v>
+        <v>4.516800057131213</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771817</v>
+        <v>3.758409170771816</v>
       </c>
       <c r="C2085" t="n">
         <v>4.249326976887396</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.896068416308062</v>
+        <v>-6.07018010261612</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.890543186050423</v>
+        <v>1.8208985115272</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4446362628046873</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.571758112274624</v>
+        <v>4.516108734570208</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.801340597109723</v>
+        <v>3.801340597109721</v>
       </c>
       <c r="C2086" t="n">
         <v>4.262109162795983</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.796438265258995</v>
+        <v>-5.970549951567052</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.943177432378637</v>
+        <v>1.873532757855414</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.637015376694448</v>
+        <v>0.5442664138537547</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.644318388812652</v>
+        <v>4.588669011108236</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546843998</v>
+        <v>3.798465546843996</v>
       </c>
       <c r="C2087" t="n">
         <v>4.451263428294709</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.845837773948006</v>
+        <v>-6.019949460256063</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.112571894401759</v>
+        <v>2.042927219878536</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6472742101261927</v>
+        <v>0.5545252472854995</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.839627954370425</v>
+        <v>4.783978576666009</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.772186508351862</v>
+        <v>3.77218650835186</v>
       </c>
       <c r="C2088" t="n">
         <v>4.438452101397571</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.63915330030563</v>
+        <v>-5.813264986613687</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.182434356961571</v>
+        <v>2.112789682438348</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8539586837685683</v>
+        <v>0.7612097209278751</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.950827311658712</v>
+        <v>4.895177933954296</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.763392838551272</v>
+        <v>3.76339283855127</v>
       </c>
       <c r="C2089" t="n">
         <v>4.440453615051676</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.60535229650209</v>
+        <v>-5.847421881611213</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.197956272137092</v>
+        <v>2.101128438093443</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.8323384425147884</v>
+        <v>0.6776259513870626</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.939856680560549</v>
+        <v>4.847029185883914</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041113</v>
+        <v>3.805590565041111</v>
       </c>
       <c r="C2090" t="n">
         <v>4.793950729041343</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.512762817440634</v>
+        <v>-5.754832402549757</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.588489177751342</v>
+        <v>2.491661343707693</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.8323384425147884</v>
+        <v>0.6776259513870626</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.293353794550216</v>
+        <v>5.200526299873581</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497404</v>
+        <v>3.832164354497403</v>
       </c>
       <c r="C2091" t="n">
         <v>4.798513840608447</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.585923421213779</v>
+        <v>-5.827993006322902</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.563788047809187</v>
+        <v>2.466960213765538</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.8043172424805454</v>
+        <v>0.6496047513528196</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.281104186096774</v>
+        <v>5.188276691420139</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492297</v>
+        <v>3.858310890492295</v>
       </c>
       <c r="C2092" t="n">
         <v>4.848343781931974</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.533707111417437</v>
+        <v>-5.77577669652656</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.634504513051251</v>
+        <v>2.537676679007602</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.8043172424805454</v>
+        <v>0.6496047513528196</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.330934127420302</v>
+        <v>5.238106632743667</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436478</v>
+        <v>3.844935596436477</v>
       </c>
       <c r="C2093" t="n">
         <v>4.857157752141985</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.501809594332191</v>
+        <v>-5.743879179441314</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.656077490095361</v>
+        <v>2.559249656051712</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.8362147595657912</v>
+        <v>0.6815022684380654</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.35888660788146</v>
+        <v>5.266059113204824</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039488</v>
+        <v>3.848376866039486</v>
       </c>
       <c r="C2094" t="n">
         <v>4.852795336181182</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.516564918532332</v>
+        <v>-5.758634503641455</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.645812944454501</v>
+        <v>2.548985110410852</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.8362147595657912</v>
+        <v>0.6815022684380654</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.354524191920657</v>
+        <v>5.261696697244021</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524483</v>
+        <v>3.868153115524481</v>
       </c>
       <c r="C2095" t="n">
         <v>4.843719839597462</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.46710029516242</v>
+        <v>-5.709169880271543</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.656523297218746</v>
+        <v>2.559695463175097</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8856793829357028</v>
+        <v>0.730966891807977</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.375127469358884</v>
+        <v>5.282299974682249</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867957</v>
+        <v>3.849040239867955</v>
       </c>
       <c r="C2096" t="n">
         <v>4.840127507312396</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.303992303008805</v>
+        <v>-5.546061888117928</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.718174161795126</v>
+        <v>2.621346327751477</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.048787375089318</v>
+        <v>0.8940748839615923</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.469399932365987</v>
+        <v>5.376572437689352</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232973</v>
+        <v>3.870204928232972</v>
       </c>
       <c r="C2097" t="n">
         <v>4.849174544003525</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.283349212207577</v>
+        <v>-5.5254187973167</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.735478434806746</v>
+        <v>2.638650600763097</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.048787375089318</v>
+        <v>0.8940748839615923</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.478446969057115</v>
+        <v>5.38561947438048</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179677</v>
+        <v>3.855534437179675</v>
       </c>
       <c r="C2098" t="n">
         <v>4.850032008989646</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.346057128682135</v>
+        <v>-5.588126713791258</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.711252733203044</v>
+        <v>2.614424899159395</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9860794586147604</v>
+        <v>0.8313669674870345</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.441679684158503</v>
+        <v>5.348852189481867</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967724</v>
+        <v>3.884687848967722</v>
       </c>
       <c r="C2099" t="n">
         <v>4.812941425779998</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.298049004838442</v>
+        <v>-5.540118589947565</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.693365399530873</v>
+        <v>2.596537565487224</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9860794586147604</v>
+        <v>0.8313669674870345</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.404589100948855</v>
+        <v>5.311761606272219</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018615</v>
+        <v>3.895362357018613</v>
       </c>
       <c r="C2100" t="n">
         <v>4.816873679337949</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.219223347654852</v>
+        <v>-5.461292932763975</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.72882791596226</v>
+        <v>2.632000081918611</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.064905115798351</v>
+        <v>0.910192624670625</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.455816748816959</v>
+        <v>5.362989254140324</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075138</v>
+        <v>3.891610981075137</v>
       </c>
       <c r="C2101" t="n">
         <v>4.811772771944986</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.027288546400978</v>
+        <v>-5.269358131510101</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.800500929070846</v>
+        <v>2.703673095027197</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.064905115798351</v>
+        <v>0.910192624670625</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.450715841423996</v>
+        <v>5.357888346747361</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435448</v>
+        <v>3.872432493435446</v>
       </c>
       <c r="C2102" t="n">
         <v>4.807126681334081</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.909115168383051</v>
+        <v>-5.151184753492174</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.843124189667113</v>
+        <v>2.746296355623463</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.183078493816278</v>
+        <v>1.028366002688552</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.516973777623848</v>
+        <v>5.424146282947213</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917736</v>
+        <v>3.859571723917735</v>
       </c>
       <c r="C2103" t="n">
         <v>4.836215274197108</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.79570048560032</v>
+        <v>-5.037770070709443</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.917578655643232</v>
+        <v>2.820750821599583</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.29649317659901</v>
+        <v>1.141780685471284</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.614111180156514</v>
+        <v>5.521283685479879</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.828006274013642</v>
+        <v>3.82800627401364</v>
       </c>
       <c r="C2104" t="n">
         <v>4.829775497208285</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.768651447907066</v>
+        <v>-5.010721033016189</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.921958493731711</v>
+        <v>2.825130659688061</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.323542214292263</v>
+        <v>1.168829723164537</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.623900825783643</v>
+        <v>5.531073331107008</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.823987445263773</v>
+        <v>3.823987445263771</v>
       </c>
       <c r="C2105" t="n">
         <v>4.829775497208285</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.774684728093836</v>
+        <v>-5.016754313202959</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.919545181657003</v>
+        <v>2.822717347613353</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.323542214292263</v>
+        <v>1.168829723164537</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.623900825783643</v>
+        <v>5.531073331107008</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,45 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.929832492771252</v>
+        <v>3.815657203170837</v>
       </c>
       <c r="C2106" t="n">
         <v>4.833413664350697</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.826536503666998</v>
+        <v>-4.916956950629122</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.90244263857015</v>
+        <v>2.8662744597853</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.271690438719102</v>
+        <v>1.268627085738374</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.596427927582159</v>
+        <v>5.594589915793722</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="2" t="n">
+        <v>45569</v>
+      </c>
+      <c r="B2107" t="n">
+        <v>3.918689114023954</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>5.041541421513127</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>-4.916956950629122</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>2.8662744597853</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>1.268627085738374</v>
+      </c>
+      <c r="G2107" t="n">
+        <v>5.034605218499495</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241004.xlsx
+++ b/tame_output/ON/bt/strategyON_20241004.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>35.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>117.1%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>192.5%</t>
+          <t>168.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.6%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.6%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-74.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.4%</t>
+          <t>419.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-653.3%</t>
+          <t>-652.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-89.6%</t>
+          <t>-89.2%</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-281.0%</t>
+          <t>-204.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-97.1%</t>
+          <t>-96.8%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-14.1%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108637</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.276045836383243</v>
+        <v>-6.174907066817855</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.5978452441569648</v>
+        <v>0.6383007519831203</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.8103298254957174</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.63721946620023</v>
+        <v>-6.536080696634842</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4636344828988488</v>
+        <v>0.5040899907250038</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.8103298254957174</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.980477985843249</v>
+        <v>-6.879339216277861</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3224306401873362</v>
+        <v>0.3628861480134917</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.8103298254957174</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.028680803085593</v>
+        <v>-6.927542033520205</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3015544333453999</v>
+        <v>0.3420099411715549</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.8103298254957174</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.195489463059955</v>
+        <v>-7.094350693494567</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2386099452848631</v>
+        <v>0.2790654531110186</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.852613149208854</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.382209171369258</v>
+        <v>-7.28107040180387</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1598957574267388</v>
+        <v>0.2003512652528943</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.852613149208854</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.765210560111889</v>
+        <v>-7.664071790546501</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.006593100608102365</v>
+        <v>0.04704860843425784</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.852613149208854</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.769697005313278</v>
+        <v>-7.66855823574789</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.007370038498977216</v>
+        <v>0.04782554632513225</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.8570995944102426</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737168</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.129227327817279</v>
+        <v>-8.028088558251891</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1310917872045736</v>
+        <v>-0.09063627937841856</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.8570995944102426</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.179576391271501</v>
+        <v>-8.078437621706113</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1433153926290851</v>
+        <v>-0.1028598848029296</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.9074486578644647</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.501052558539462</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.277195668692897</v>
+        <v>-8.176056899127509</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1793213529758746</v>
+        <v>-0.1388658451497196</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.005067935285861</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.331267168201256</v>
+        <v>-8.230128398635868</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1980563964576461</v>
+        <v>-0.1576008886314906</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.059139434794221</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.334842954293004</v>
+        <v>-8.233704184727616</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1939735137757026</v>
+        <v>-0.1535180059495476</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.084668356710713</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.368495792801477</v>
+        <v>-8.267357023236089</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2029520946946559</v>
+        <v>-0.1624965868685009</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.185081724627751</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.507581907420334</v>
+        <v>-8.406443137854946</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2432148390487776</v>
+        <v>-0.2027593312226226</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.324167839246607</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.682706324806878</v>
+        <v>-8.58156755524149</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2987093852558784</v>
+        <v>-0.2582538774297229</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.499292256633151</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.917158418821368</v>
+        <v>-8.816019649255979</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.39970938776327</v>
+        <v>-0.359253879937115</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.499292256633151</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.021533149847814</v>
+        <v>-8.920394380282426</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4481314709478248</v>
+        <v>-0.4076759631216698</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.603666987659597</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.184046615546398</v>
+        <v>-9.08290784598101</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5120210673887025</v>
+        <v>-0.471565559562547</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.701300418078284</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.310083408914688</v>
+        <v>-9.2089446393493</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5597420561069035</v>
+        <v>-0.5192865482807481</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.676048795268541</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.253011637018757</v>
+        <v>-9.151872867453369</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5329230116621302</v>
+        <v>-0.4924675038359752</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.676048795268541</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.394683478742877</v>
+        <v>-9.293544709177489</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.59106697525052</v>
+        <v>-0.550611467424365</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.676048795268541</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.345092634318043</v>
+        <v>-9.243953864752655</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5561772273157142</v>
+        <v>-0.5157217194895587</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.626457950843708</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.196174299846186</v>
+        <v>-9.095035530280798</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5096610271736544</v>
+        <v>-0.4692055193474993</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.595208360108535</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.970329147126774</v>
+        <v>-8.869190377561386</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4097438930496811</v>
+        <v>-0.3692883852235256</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.553281684521371</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.845750490789182</v>
+        <v>-8.744611721223794</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3587732859585855</v>
+        <v>-0.31831777813243</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.553281684521371</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.820713809220672</v>
+        <v>-8.719575039655284</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3461248391690734</v>
+        <v>-0.3056693313429184</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.527952596970635</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.748580633932791</v>
+        <v>-8.647441864367403</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3115378648152847</v>
+        <v>-0.2710823569891296</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.527952596970635</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.745376973506986</v>
+        <v>-8.644238203941597</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3199936630388276</v>
+        <v>-0.2795381552126726</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.524748936544829</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.651917939521761</v>
+        <v>-8.550779169956373</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2924935307576453</v>
+        <v>-0.2520380229314902</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.524748936544829</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.641264757968329</v>
+        <v>-8.540125988402941</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2900668186356463</v>
+        <v>-0.2496113108094913</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.524748936544829</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.543357719291839</v>
+        <v>-8.442218949726451</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2512043181385111</v>
+        <v>-0.210748810312356</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.456763186684273</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.519404178315881</v>
+        <v>-8.418265408750493</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2409543956026341</v>
+        <v>-0.2004988877764791</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.432809645708315</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.255344239993084</v>
+        <v>-8.154205470427696</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1485907364352679</v>
+        <v>-0.1081352286091124</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.168749707385519</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.548264616488246</v>
+        <v>-7.447125846922858</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1314540793063665</v>
+        <v>0.171909587132522</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.168749707385519</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388729</v>
+        <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.508080318122055</v>
+        <v>-7.406941548556667</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1478714225406841</v>
+        <v>0.1883269303668396</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.128565409019328</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626475</v>
+        <v>3.856161751626476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.344680447182693</v>
+        <v>-7.243541677617305</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.212598192137186</v>
+        <v>0.2530536999633415</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.9651655380799653</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.186563067803918</v>
+        <v>-7.08542429823853</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2837695727265488</v>
+        <v>0.3242250805527038</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.8070481587011898</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.036896676796403</v>
+        <v>-6.935757907231014</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3407439188165955</v>
+        <v>0.381199426642751</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.7141446674586539</v>
@@ -45366,10 +45366,10 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.904621203165516</v>
+        <v>-6.803482433600128</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2949148942761046</v>
+        <v>0.3353704021022601</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.5818691938277673</v>
@@ -45389,10 +45389,10 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.732759987600613</v>
+        <v>-6.631621218035225</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3664744411897027</v>
+        <v>0.4069299490158578</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.4100079782628644</v>
@@ -45412,10 +45412,10 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.647795320871294</v>
+        <v>-6.546656551305906</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4133666491050891</v>
+        <v>0.4538221569312442</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.3250433115335448</v>
@@ -45435,10 +45435,10 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.753385310644399</v>
+        <v>-6.652246541079011</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2431547235966285</v>
+        <v>0.2836102314227835</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.4306333013066492</v>
@@ -45458,10 +45458,10 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.685150726018971</v>
+        <v>-6.584011956453583</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3189928993238857</v>
+        <v>0.3594484071500412</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.4122179784341132</v>
@@ -45481,10 +45481,10 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.537210684611372</v>
+        <v>-6.436071915045984</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2615481072485184</v>
+        <v>0.3020036150746739</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.3918970625255556</v>
@@ -45504,10 +45504,10 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.484241162357383</v>
+        <v>-6.383102392791995</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2740219298966355</v>
+        <v>0.314477437722791</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.3389275402715667</v>
@@ -45527,10 +45527,10 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.318452966397093</v>
+        <v>-6.217314196831705</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.333376596185659</v>
+        <v>0.373832104011814</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.3389275402715667</v>
@@ -45550,10 +45550,10 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.285089759918324</v>
+        <v>-6.183950990352936</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3611842331583093</v>
+        <v>0.4016397409844648</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.3389275402715667</v>
@@ -45573,10 +45573,10 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.176830622795802</v>
+        <v>-6.075691853230414</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.399020008466513</v>
+        <v>0.4394755162926685</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.3389275402715667</v>
@@ -45596,10 +45596,10 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.053539487978671</v>
+        <v>-5.952400718413283</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4458345564039425</v>
+        <v>0.4862900642300976</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.2156364054544362</v>
@@ -45619,10 +45619,10 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.00084262084738</v>
+        <v>-5.899703851281992</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4746142814937842</v>
+        <v>0.5150697893199392</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.1629395383231451</v>
@@ -45642,10 +45642,10 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.757077178863936</v>
+        <v>-5.655938409298548</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5679011666342126</v>
+        <v>0.6083566744603677</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.1629395383231451</v>
@@ -45665,10 +45665,10 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.667301506487464</v>
+        <v>-5.566162736922076</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6059357495048174</v>
+        <v>0.6463912573309725</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.101340093408835</v>
@@ -45688,10 +45688,10 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.417451112538389</v>
+        <v>-5.316312342973001</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6986179820681495</v>
+        <v>0.7390734898943045</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.101340093408835</v>
@@ -45711,10 +45711,10 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.241559020070957</v>
+        <v>-5.140420250505569</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7725739425757712</v>
+        <v>0.8130294504019262</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.101340093408835</v>
@@ -45734,10 +45734,10 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.070112557048494</v>
+        <v>-4.968973787483105</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8544800338393101</v>
+        <v>0.8949355416654652</v>
       </c>
       <c r="F1921" t="n">
         <v>0.07010636961362809</v>
@@ -45757,10 +45757,10 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.990090269939373</v>
+        <v>-4.888951500373985</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8855094262992553</v>
+        <v>0.9259649341254106</v>
       </c>
       <c r="F1922" t="n">
         <v>0.1501286567227491</v>
@@ -45780,10 +45780,10 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.926454527705438</v>
+        <v>-4.82531575814005</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9156585242471464</v>
+        <v>0.9561140320733017</v>
       </c>
       <c r="F1923" t="n">
         <v>0.2137643989566836</v>
@@ -45803,10 +45803,10 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.832757209489043</v>
+        <v>-4.731618439923655</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9343317103175002</v>
+        <v>0.9747872181436554</v>
       </c>
       <c r="F1924" t="n">
         <v>0.2137643989566836</v>
@@ -45826,10 +45826,10 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.843259832554332</v>
+        <v>-4.742121062988944</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.931873737716262</v>
+        <v>0.9723292455424173</v>
       </c>
       <c r="F1925" t="n">
         <v>0.2032617758913947</v>
@@ -45849,10 +45849,10 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.730773571885457</v>
+        <v>-4.629634802320069</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9807975558186319</v>
+        <v>1.021253063644787</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2032617758913947</v>
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.6277643696278</v>
+        <v>-4.611921115442204</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.022679820639035</v>
+        <v>1.029017122313273</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.255817562044439</v>
+        <v>0.2064431047883115</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.027632530030567</v>
+        <v>2.99800785567689</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.504290098314782</v>
+        <v>-4.488446844129186</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.069067600384236</v>
+        <v>1.075404902058474</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.255817562044439</v>
+        <v>0.2064431047883115</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.02463060125056</v>
+        <v>2.995005926896884</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.446354266316566</v>
+        <v>-4.43051101213097</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.093820970194136</v>
+        <v>1.100158271868374</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2813794367271882</v>
+        <v>0.2320049794710608</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.041546763070824</v>
+        <v>3.011922088717147</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.843274527539953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.313486577253289</v>
+        <v>-4.297643323067692</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.16286222862127</v>
+        <v>1.169199530295509</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2813794367271882</v>
+        <v>0.2320049794710608</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.057440945872647</v>
+        <v>3.02781627151897</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.19331349388879</v>
+        <v>-4.177470239703194</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.212077306407372</v>
+        <v>1.21841460808161</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4015525200916872</v>
+        <v>0.3521780628355597</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.130690640331648</v>
+        <v>3.101065965977972</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.058060132558813</v>
+        <v>-4.042216878373217</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.276266753500802</v>
+        <v>1.282604055175041</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5368058814216643</v>
+        <v>0.4874314241655369</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.221930759691074</v>
+        <v>3.192306085337398</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.117934959916505</v>
+        <v>-4.102091705730909</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.238354313959151</v>
+        <v>1.24469161563339</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4769310540639722</v>
+        <v>0.4275565968078447</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.172043354677885</v>
+        <v>3.142418680324209</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.998114729005668</v>
+        <v>-3.982271474820072</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.301571575557695</v>
+        <v>1.307908877231933</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4769310540639722</v>
+        <v>0.4275565968078447</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.187332523912094</v>
+        <v>3.157707849558417</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.000584435467474</v>
+        <v>-3.984741181281878</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.208227892295414</v>
+        <v>1.214565193969652</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.474461347602166</v>
+        <v>0.4250868903460386</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.093494899357451</v>
+        <v>3.063870225003775</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.068954621791484</v>
+        <v>-4.053111367605887</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.100141679251111</v>
+        <v>1.10647898092535</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.483737046638381</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.018322180264482</v>
+        <v>2.988697505910805</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.180826901417634</v>
+        <v>-4.164983647232038</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.045829476032542</v>
+        <v>1.052166777706781</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.483737046638381</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.008758888896373</v>
+        <v>2.979134214542697</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.164852235931367</v>
+        <v>-4.14900898174577</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.018793867151077</v>
+        <v>1.025131168825316</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.483737046638381</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.975333413820401</v>
+        <v>2.945708739466724</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.168946782602364</v>
+        <v>-4.153103528416768</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.021723280474466</v>
+        <v>1.028060582148704</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.483737046638381</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.979900645812188</v>
+        <v>2.950275971458512</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.16102240801745</v>
+        <v>-4.145179153831854</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.000635059069638</v>
+        <v>1.006972360743877</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.483737046638381</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.955642674573395</v>
+        <v>2.926018000219719</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.154744205447601</v>
+        <v>-4.138900951262005</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9316846534990277</v>
+        <v>0.9380219551732663</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.49001524920823</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.887947909516754</v>
+        <v>2.858323235163078</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264165</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.094891586243878</v>
+        <v>-4.079048332058282</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9657980876126495</v>
+        <v>0.972135389286888</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.49001524920823</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.898120295948887</v>
+        <v>2.86849562159521</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.0086481232175</v>
+        <v>-3.992804869031904</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9952417433970608</v>
+        <v>1.001579045071299</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.49001524920823</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.893066566522747</v>
+        <v>2.863441892169071</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.05395494261648</v>
+        <v>-4.038111688430884</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9688947910819945</v>
+        <v>0.975232092756233</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4492050861989992</v>
+        <v>0.3998306289428718</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.860356244161734</v>
+        <v>2.830731569808058</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.082988047318781</v>
+        <v>-4.067144793133185</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9578334222341756</v>
+        <v>0.9641707239084141</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4492050861989992</v>
+        <v>0.3998306289428718</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.860908117194836</v>
+        <v>2.831283442841159</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.990177565867922</v>
+        <v>-3.974334311682326</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9242303067058848</v>
+        <v>0.9305676083801235</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5420155676498586</v>
+        <v>0.4926411103937312</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.845867097956717</v>
+        <v>2.816242423603041</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.03456703519735</v>
+        <v>-4.018723781011754</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9083479948987145</v>
+        <v>0.9146852965729531</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4976260983204309</v>
+        <v>0.4482516410643035</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.821106892283662</v>
+        <v>2.791482217929985</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.014063341311853</v>
+        <v>-3.998220087126256</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9116251809646365</v>
+        <v>0.917962482638875</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5181297922059283</v>
+        <v>0.4687553349498008</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.828484817126683</v>
+        <v>2.798860142773006</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.097735438024185</v>
+        <v>-4.081892183838589</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8836476381103706</v>
+        <v>0.8899849397846094</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5181297922059283</v>
+        <v>0.4687553349498008</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.83397611295735</v>
+        <v>2.804351438603673</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.125515835925538</v>
+        <v>-4.109672581739941</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8840326807183687</v>
+        <v>0.8903699823926072</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4903493943045751</v>
+        <v>0.4409749370484478</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.828805075985077</v>
+        <v>2.799180401631401</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.243896508655676</v>
+        <v>-4.22805325447008</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6750361316269666</v>
+        <v>0.6813734333012051</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4231315421535989</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.626830084695145</v>
+        <v>2.597205410341468</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.352510587099007</v>
+        <v>-4.336667332913411</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7517401609688399</v>
+        <v>0.7580774626430784</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4231315421535989</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.74697974541435</v>
+        <v>2.717355071060674</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.317101548850864</v>
+        <v>-4.301258294665268</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7804168023704199</v>
+        <v>0.7867541040446584</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4231315421535989</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.761492771516673</v>
+        <v>2.731868097162997</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.325562717506325</v>
+        <v>-4.309719463320729</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7744517762506042</v>
+        <v>0.780789077924843</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4146703734981379</v>
+        <v>0.3652959162420105</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.753835511665765</v>
+        <v>2.724210837312089</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.148446387471159</v>
+        <v>-4.132603133285563</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8420273371099731</v>
+        <v>0.8483646387842116</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4146703734981379</v>
+        <v>0.3652959162420105</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.750564540511068</v>
+        <v>2.720939866157391</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.193538632304705</v>
+        <v>-4.177695378119108</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.824673830938468</v>
+        <v>0.8310111326127065</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3527743303287481</v>
+        <v>0.3033998730726207</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.714110306371347</v>
+        <v>2.684485632017671</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.172431643188397</v>
+        <v>-3.998319956880341</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8269036018914053</v>
+        <v>0.896548276414628</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.3674276684026466</v>
+        <v>0.4601766312433394</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.7166892845221</v>
+        <v>2.772338662226516</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.217445856709004</v>
+        <v>-4.043334170400946</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7897053718147524</v>
+        <v>0.8593500463379753</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.337078773088042</v>
+        <v>0.4298277359287348</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.679287402664928</v>
+        <v>2.734936780369343</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509539</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.305457043267701</v>
+        <v>-4.131345356959644</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7601924595302192</v>
+        <v>0.8298371340534423</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.271602265228869</v>
+        <v>0.3643512280695618</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.645693060288369</v>
+        <v>2.701342437992785</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.406654824704874</v>
+        <v>-4.232543138396816</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7189172688518517</v>
+        <v>0.7885619433750746</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2031934516835498</v>
+        <v>0.2959424145242426</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.603851694057679</v>
+        <v>2.659501071762095</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.400143858090561</v>
+        <v>-4.226032171782504</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7191216170518935</v>
+        <v>0.7887662915751164</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2031934516835498</v>
+        <v>0.2959424145242426</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.601451655611996</v>
+        <v>2.657101033316412</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.381105730383264</v>
+        <v>-4.206994044075206</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7232615873430572</v>
+        <v>0.7929062618662801</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1450098403523553</v>
+        <v>0.2377588031930481</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.563066208021524</v>
+        <v>2.61871558572594</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.433621532658084</v>
+        <v>-4.259509846350027</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8215496680673193</v>
+        <v>0.8911943425905424</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1450098403523553</v>
+        <v>0.2377588031930481</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.682360609655714</v>
+        <v>2.73800998736013</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.437029844092664</v>
+        <v>-4.262918157784607</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.821019672479621</v>
+        <v>0.8906643470028439</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1775264093617326</v>
+        <v>0.2702753722024255</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.702703880047475</v>
+        <v>2.75835325775189</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.417673708198817</v>
+        <v>-4.243562021890759</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8347706572340861</v>
+        <v>0.9044153317573089</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1775264093617326</v>
+        <v>0.2702753722024255</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.7087124104444</v>
+        <v>2.764361788148816</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.491003236936909</v>
+        <v>-4.316891550628852</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7033890670160483</v>
+        <v>0.7730337415392714</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.1779210717813546</v>
+        <v>0.2706700346220474</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.606899429173373</v>
+        <v>2.662548806877789</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.409870503348191</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.574824458211608</v>
+        <v>-4.40071277190355</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.5795842957498003</v>
+        <v>0.6492289702730232</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.1779210717813546</v>
+        <v>0.2706700346220474</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.516623146417004</v>
+        <v>2.57227252412142</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.41053285173985</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.568671752158823</v>
+        <v>-4.394560065850766</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.5827077265625724</v>
+        <v>0.6523524010857953</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.1840737778341389</v>
+        <v>0.2768227406748317</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.520977118440333</v>
+        <v>2.576626496144749</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.40961332847996</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.585481050309325</v>
+        <v>-4.411369364001268</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.5750644840424819</v>
+        <v>0.6447091585657048</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.1672644796836372</v>
+        <v>0.2600134425243301</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.509972016290142</v>
+        <v>2.565621393994558</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.475948882276781</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.523183051533203</v>
+        <v>-4.349071365225146</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.6663192373497515</v>
+        <v>0.7359639118729746</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2125587439580793</v>
+        <v>0.3053077067987721</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.603484128651629</v>
+        <v>2.659133506356044</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.278240883990908</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.321392853868045</v>
+        <v>-4.147281167559988</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.5493273181299418</v>
+        <v>0.6189719926531647</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4105769361272337</v>
+        <v>0.5033258989679266</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.524587045667248</v>
+        <v>2.580236423371664</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.348531116313083</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.37227956655424</v>
+        <v>-4.198167880246182</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.5992628653776393</v>
+        <v>0.6689075399008622</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.3596902234410391</v>
+        <v>0.452439186281732</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.564345250377707</v>
+        <v>2.619994628082122</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.363158852429127</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.285668823904433</v>
+        <v>-4.111557137596376</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6485348985536055</v>
+        <v>0.7181795730768286</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4383159546461974</v>
+        <v>0.5310649174868902</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.626148425216845</v>
+        <v>2.681797802921261</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.361694833253798</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.345878121909718</v>
+        <v>-4.17176643560166</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6229871601761632</v>
+        <v>0.6926318346993863</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3781066566409129</v>
+        <v>0.4708556194816057</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.588558827238346</v>
+        <v>2.644208204942762</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.360186451293727</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.296691473225366</v>
+        <v>-4.122579786917309</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6411534376898325</v>
+        <v>0.7107981122130553</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3781066566409129</v>
+        <v>0.4708556194816057</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.587050445278275</v>
+        <v>2.642699822982691</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316252</v>
+        <v>3.833513460316251</v>
       </c>
       <c r="C1976" t="n">
         <v>2.360049318729163</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.252318341586798</v>
+        <v>-4.07820665527874</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6587655577806961</v>
+        <v>0.728410232303919</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4224797882794815</v>
+        <v>0.5152287511201743</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.613537191696852</v>
+        <v>2.669186569401268</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
         <v>2.354443112867754</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.217587020268297</v>
+        <v>-4.04347533396024</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6670518804466867</v>
+        <v>0.7366965549699098</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4224797882794815</v>
+        <v>0.5152287511201743</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.607930985835443</v>
+        <v>2.663580363539858</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.360824869895558</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.169931289707241</v>
+        <v>-3.995819603399184</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.6924959296989137</v>
+        <v>0.7621406042221368</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4701355188405371</v>
+        <v>0.56288448168123</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.642906181199881</v>
+        <v>2.698555558904296</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.365717243270283</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.069413131208487</v>
+        <v>-3.895301444900429</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7375955664731404</v>
+        <v>0.8072402409963635</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5706536773392916</v>
+        <v>0.6634026401799845</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.708109449673858</v>
+        <v>2.763758827378274</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.352471915746155</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.053507801776134</v>
+        <v>-3.879396115468077</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7307123707219536</v>
+        <v>0.8003570452451767</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4915410166300527</v>
+        <v>0.5842899794707457</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.647396525724187</v>
+        <v>2.703045903428603</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.356569618356784</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.008669400167737</v>
+        <v>-3.834557713859679</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7527454339759414</v>
+        <v>0.8223901084991645</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4960844495749221</v>
+        <v>0.5888334124156152</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.654220288101738</v>
+        <v>2.709869665806153</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.360730557987862</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.028167856409745</v>
+        <v>-3.854056170101687</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7491069911102159</v>
+        <v>0.8187516656334393</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4479998082950178</v>
+        <v>0.5407487711357108</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.629530442964873</v>
+        <v>2.685179820669289</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.366610160515699</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.983965019323844</v>
+        <v>-3.809853333015786</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7726677284724133</v>
+        <v>0.8423124029956366</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4922026453809183</v>
+        <v>0.5849516082216113</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.66193174774425</v>
+        <v>2.717581125448666</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.365020160984947</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.991524685160891</v>
+        <v>-3.817412998852833</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7680538626068421</v>
+        <v>0.8376985371300654</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5470060493907376</v>
+        <v>0.6397550122314306</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.693223790619389</v>
+        <v>2.748873168323805</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.416267926167986</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.833233267621619</v>
+        <v>-3.659121581313561</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8826181948055907</v>
+        <v>0.9522628693288138</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5470060493907376</v>
+        <v>0.6397550122314306</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.744471555802429</v>
+        <v>2.800120933506845</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.414708630762239</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.625591263987143</v>
+        <v>-3.451479577679085</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9641157008536343</v>
+        <v>1.033760375376857</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7546480530252138</v>
+        <v>0.8473970158659068</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.867497462577368</v>
+        <v>2.923146840281784</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.409656859000509</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.574559171264615</v>
+        <v>-3.400447484956557</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9794767661809156</v>
+        <v>1.049121440704139</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8056801457477417</v>
+        <v>0.8984291085884347</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.893064946449154</v>
+        <v>2.94871432415357</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.426844263093214</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.509334990137409</v>
+        <v>-3.335223303829351</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.022753842724503</v>
+        <v>1.092398517247726</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8709043268749473</v>
+        <v>0.9636532897156403</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.949386859218183</v>
+        <v>3.005036236922599</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.422805235392495</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.471907970066276</v>
+        <v>-3.297796283758217</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.033685623052236</v>
+        <v>1.10333029757546</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.876155864904129</v>
+        <v>0.968904827744822</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.948498754334972</v>
+        <v>3.004148132039388</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
         <v>2.424062027723735</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.47054998509273</v>
+        <v>-3.296438298784672</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.035485609372895</v>
+        <v>1.105130283896118</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9504939904419476</v>
+        <v>1.043242953282641</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.994358421988904</v>
+        <v>3.050007799693319</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.584619798744946</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.442136721992846</v>
+        <v>-3.268025035684788</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.207408685634059</v>
+        <v>1.277053360157282</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8915184276955188</v>
+        <v>0.9842673905362118</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.119530855362257</v>
+        <v>3.175180233066673</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957627</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
         <v>2.704732707962763</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.367354460967834</v>
+        <v>-3.193242774659776</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.357434499261881</v>
+        <v>1.427079173785105</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9663006887205314</v>
+        <v>1.059049651561224</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.284513121195082</v>
+        <v>3.340162498899498</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>2.696440683976622</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.341270376704026</v>
+        <v>-3.167158690395968</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.359576108981264</v>
+        <v>1.429220783504487</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9663006887205314</v>
+        <v>1.059049651561224</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.276221097208941</v>
+        <v>3.331870474913357</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.694633879560401</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.253392463594905</v>
+        <v>-3.079280777286847</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.392920469808691</v>
+        <v>1.462565144331915</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.082226331143882</v>
+        <v>1.174975293984576</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.343969678246731</v>
+        <v>3.399619055951147</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959858</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.712188285287193</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.244500002201622</v>
+        <v>-3.070388315893564</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.414031860092796</v>
+        <v>1.483676534616019</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.082226331143882</v>
+        <v>1.174975293984576</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.361524083973523</v>
+        <v>3.417173461677939</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.704043332691777</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.4129761191715</v>
+        <v>-3.238864432863442</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.338496460709429</v>
+        <v>1.408141135232652</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.054278495427302</v>
+        <v>1.147027458267995</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.336610429948158</v>
+        <v>3.392259807652574</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.685313029879639</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.96671992654206</v>
+        <v>-2.792608240234002</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.498268634949067</v>
+        <v>1.56791330947229</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.959559825757669</v>
+        <v>1.052308788598362</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.26104892533424</v>
+        <v>3.316698303038656</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.675977052376543</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.943998822858908</v>
+        <v>-2.76988713655085</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.498021098919232</v>
+        <v>1.567665773442456</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.959559825757669</v>
+        <v>1.052308788598362</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.251712947831145</v>
+        <v>3.307362325535561</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777674</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>2.834883178227712</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.07320063615295</v>
+        <v>-2.899088949844892</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.605246499452784</v>
+        <v>1.674891173976008</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8303580124636267</v>
+        <v>0.92310697530432</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.333097985705888</v>
+        <v>3.388747363410304</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644414</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>2.871961000721359</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.099075034626976</v>
+        <v>-2.924963348318918</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.63197456255682</v>
+        <v>1.701619237080044</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8752696211753679</v>
+        <v>0.9680185840160611</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.39712277342658</v>
+        <v>3.452772151130996</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.868636356710904</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.092020344411802</v>
+        <v>-2.917908658103744</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.631471794632435</v>
+        <v>1.701116469155658</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8823243113905417</v>
+        <v>0.9750732742312349</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.398030943545229</v>
+        <v>3.453680321249645</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>2.878642510355645</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.065069120085314</v>
+        <v>-2.890957433777256</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.652258438007772</v>
+        <v>1.721903112530995</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8972046574182608</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.416965304806602</v>
+        <v>3.472614682511018</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.062745642500605</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.086613347916102</v>
+        <v>-2.912501661608043</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.827743879020417</v>
+        <v>1.89738855354364</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8972046574182608</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.601068436951562</v>
+        <v>3.656717814655978</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.054862337403598</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.109021465720974</v>
+        <v>-2.934909779412915</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.810897326801461</v>
+        <v>1.880542001324684</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8972046574182608</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.593185131854555</v>
+        <v>3.648834509558971</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.056916336953236</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.137245701298574</v>
+        <v>-2.963134014990516</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.801661632120058</v>
+        <v>1.871306306643282</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9151814098695694</v>
+        <v>1.007930372710263</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.606025182874978</v>
+        <v>3.661674560579394</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.113170054675083</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.146686627187104</v>
+        <v>-2.972574940879046</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.854138979486493</v>
+        <v>1.923783654009717</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.037608527412961</v>
+        <v>1.130357490253654</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.73573517112286</v>
+        <v>3.791384548827275</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321636</v>
       </c>
       <c r="C2007" t="n">
         <v>3.116061149220384</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.352925564975537</v>
+        <v>-3.178813878667479</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.774534498916421</v>
+        <v>1.844179173439644</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8313695896245272</v>
+        <v>0.9241185524652205</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.614882902995101</v>
+        <v>3.670532280699516</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347708</v>
+        <v>3.727898186347706</v>
       </c>
       <c r="C2008" t="n">
         <v>3.114172962114159</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.429255542576443</v>
+        <v>-3.255143856268385</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.742114320769834</v>
+        <v>1.811758995293057</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8313695896245272</v>
+        <v>0.9241185524652205</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.612994715888876</v>
+        <v>3.668644093593291</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887753</v>
+        <v>3.710654104887752</v>
       </c>
       <c r="C2009" t="n">
         <v>3.108993191717021</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.584212327976573</v>
+        <v>-3.410100641668514</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.674951836212644</v>
+        <v>1.744596510735868</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.676412804224398</v>
+        <v>0.7691617670650912</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.51484087425166</v>
+        <v>3.570490251956076</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343071</v>
+        <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
         <v>3.107427201927174</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.745780753503828</v>
+        <v>-3.571669067195769</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.608758476211894</v>
+        <v>1.678403150735118</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.5496298804265186</v>
+        <v>0.6423788432672118</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.437205130183085</v>
+        <v>3.492854507887501</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389354</v>
+        <v>3.754596135389352</v>
       </c>
       <c r="C2011" t="n">
         <v>3.120500608793092</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.854081415373947</v>
+        <v>-3.679969729065889</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.578511618329765</v>
+        <v>1.648156292852989</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.5496298804265186</v>
+        <v>0.6423788432672118</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.450278537049003</v>
+        <v>3.505927914753419</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378388</v>
       </c>
       <c r="C2012" t="n">
         <v>3.112505805576032</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.013632488137464</v>
+        <v>-3.839520801829406</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.506696386007299</v>
+        <v>1.576341060530522</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3973522135647671</v>
+        <v>0.4901011764054604</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.350917133714893</v>
+        <v>3.406566511419308</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.111029846703034</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.041533275246937</v>
+        <v>-3.867421588938879</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.494060112290511</v>
+        <v>1.563704786813735</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3627552894218323</v>
+        <v>0.4555042522625256</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.328683020356134</v>
+        <v>3.38433239806055</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.107794290680233</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.16405937794983</v>
+        <v>-3.989947691641773</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.441814115186553</v>
+        <v>1.511458789709776</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2402291867189384</v>
+        <v>0.3329781495596317</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.251931802711596</v>
+        <v>3.307581180416012</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
         <v>3.174500250270737</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.394573874135419</v>
+        <v>-4.220462187827361</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.416314276302821</v>
+        <v>1.485958950826044</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.009714690533349724</v>
+        <v>0.102463653374043</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.180329064590747</v>
+        <v>3.235978442295163</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814666</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.314811969272584</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.743318959359863</v>
+        <v>-4.569207273051805</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.417127961214891</v>
+        <v>1.486772635738114</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.09903326338554808</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.255392011241255</v>
+        <v>3.311041388945671</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.383792238418224</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.897305377136004</v>
+        <v>-4.723193690827945</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.424513663250074</v>
+        <v>1.494158337773297</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.09903326338554808</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.324372280386895</v>
+        <v>3.380021658091311</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.369843440538344</v>
       </c>
       <c r="D2018" t="n">
-        <v>-5.101904811999012</v>
+        <v>-4.927793125690954</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.328725091424992</v>
+        <v>1.398369765948215</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.09903326338554808</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.310423482507016</v>
+        <v>3.366072860211432</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.381713929593758</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.354379966006737</v>
+        <v>-5.180268279698678</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.239605518877316</v>
+        <v>1.309250193400539</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.09903326338554808</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.32229397156243</v>
+        <v>3.377943349266846</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.382924464112702</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.647275722486149</v>
+        <v>-5.47316403617809</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.123657750804495</v>
+        <v>1.193302425327718</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.09903326338554808</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.323504506081373</v>
+        <v>3.37915388378579</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.387046206340024</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.833939850620957</v>
+        <v>-5.659828164312898</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.053113841777893</v>
+        <v>1.122758516301116</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.125772234210108</v>
+        <v>-0.03302327136941474</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.311582865813959</v>
+        <v>3.367232243518375</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.382124059076213</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.979960537534919</v>
+        <v>-5.805848851226861</v>
       </c>
       <c r="E2022" t="n">
-        <v>0.9897834197484974</v>
+        <v>1.059428094271721</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.1348553260039649</v>
+        <v>-0.04210636316327171</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.301210863473834</v>
+        <v>3.35686024117825</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.544328115775257</v>
       </c>
       <c r="D2023" t="n">
-        <v>-6.071674546644504</v>
+        <v>-5.897562860336446</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.115301872803708</v>
+        <v>1.18494654732693</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.1348553260039649</v>
+        <v>-0.04210636316327171</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.463414920172879</v>
+        <v>3.519064297877294</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071552</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
         <v>3.539174753739071</v>
       </c>
       <c r="D2024" t="n">
-        <v>-6.103326205704473</v>
+        <v>-5.929214519396416</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.097487847143534</v>
+        <v>1.167132521666757</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.1400237832484051</v>
+        <v>-0.04727482040771191</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.455160483790028</v>
+        <v>3.510809861494444</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868149</v>
+        <v>3.750044015868148</v>
       </c>
       <c r="C2025" t="n">
         <v>3.549404171307562</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.17239226027741</v>
+        <v>-5.998280573969352</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.08009084288285</v>
+        <v>1.149735517406073</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.2023946607420152</v>
+        <v>-0.1096456979013219</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.427967374862353</v>
+        <v>3.483616752566769</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332695</v>
+        <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
         <v>3.558329809763465</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.274368382525817</v>
+        <v>-6.10025669621776</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.04822603243939</v>
+        <v>1.117870706962613</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.3043707829904228</v>
+        <v>-0.2116218201497295</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.375707339969211</v>
+        <v>3.431356717673627</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231812</v>
+        <v>3.798296784231811</v>
       </c>
       <c r="C2027" t="n">
         <v>3.55048269700764</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.164362099048596</v>
+        <v>-5.990250412740538</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.084381433074454</v>
+        <v>1.154026107597677</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2811662110731475</v>
+        <v>-0.1884172482324543</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.381782970363752</v>
+        <v>3.437432348068168</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.554732707729614</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.176891804160475</v>
+        <v>-6.002780117852417</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.083619561751676</v>
+        <v>1.1532642362749</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2949927105396706</v>
+        <v>-0.2022437476989773</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.377737081405813</v>
+        <v>3.433386459110229</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
         <v>3.56199359061215</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.875445078688637</v>
+        <v>-5.70133339238058</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.211459134822948</v>
+        <v>1.281103809346171</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.006454014932166685</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.565865999571451</v>
+        <v>3.621515377275867</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.562964768364861</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.900035322923821</v>
+        <v>-5.725923636615764</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.202594214881585</v>
+        <v>1.272238889404808</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.006454014932166685</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.566837177324161</v>
+        <v>3.622486555028577</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
         <v>3.563807672744617</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.848996946917301</v>
+        <v>-5.674885260609243</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.223852469663949</v>
+        <v>1.293497144187171</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.006454014932166685</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.567680081703917</v>
+        <v>3.623329459408333</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.582845771618762</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.82014827009384</v>
+        <v>-5.646036583785783</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.254430039267478</v>
+        <v>1.324074713790701</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.03530269175562695</v>
+        <v>0.1280516545963202</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.604027386672139</v>
+        <v>3.659676764376554</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
         <v>3.399029767742697</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.7235133580752</v>
+        <v>-5.549401671767143</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.109268000198869</v>
+        <v>1.178912674722091</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1319376037742669</v>
+        <v>0.2246865666149601</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.478192330007257</v>
+        <v>3.533841707711673</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077642</v>
+        <v>3.80468896107764</v>
       </c>
       <c r="C2034" t="n">
         <v>3.402531811816661</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.654475347126732</v>
+        <v>-5.480363660818675</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.14038524865222</v>
+        <v>1.210029923175443</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.200975614722735</v>
+        <v>0.2937245775634282</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.523117180650302</v>
+        <v>3.578766558354718</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833462</v>
+        <v>3.77502886083346</v>
       </c>
       <c r="C2035" t="n">
         <v>3.386958630892743</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.635688246757794</v>
+        <v>-5.461576560449736</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.132326907875878</v>
+        <v>1.201971582399101</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.2197627150916734</v>
+        <v>0.3125116779323667</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.518816259947747</v>
+        <v>3.574465637652164</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
         <v>3.386146341329173</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.558589645215921</v>
+        <v>-5.384477958907864</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.162354058929056</v>
+        <v>1.23199873345228</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.2197627150916734</v>
+        <v>0.3125116779323667</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.518003970384177</v>
+        <v>3.573653348088593</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.396015120454245</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.568974840105811</v>
+        <v>-5.394863153797753</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.168068760098173</v>
+        <v>1.237713434621396</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2093775202017841</v>
+        <v>0.3021264830424774</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.521641632575316</v>
+        <v>3.577291010279732</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735285</v>
+        <v>3.834415493735283</v>
       </c>
       <c r="C2038" t="n">
         <v>3.466852126230671</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.587562998828036</v>
+        <v>-5.413451312519978</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.231470502385708</v>
+        <v>1.301115176908931</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1907893614795588</v>
+        <v>0.283538324320252</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.581325743118406</v>
+        <v>3.636975120822822</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.463721137048969</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.587861545524071</v>
+        <v>-5.413749859216014</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.228220094525593</v>
+        <v>1.297864769048815</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.1904908147835229</v>
+        <v>0.2832397776242161</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.578015625919083</v>
+        <v>3.633665003623499</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.81564321210886</v>
+        <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
         <v>3.468252031988361</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.487038411833644</v>
+        <v>-5.312926725525586</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.273080242941155</v>
+        <v>1.342724917464378</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2029550302678767</v>
+        <v>0.2957039931085699</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.590025050149087</v>
+        <v>3.645674427853503</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121471</v>
+        <v>3.807356168121469</v>
       </c>
       <c r="C2041" t="n">
         <v>3.468381285466904</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.296257051081236</v>
+        <v>-5.122145364773178</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.349522040720661</v>
+        <v>1.419166715243884</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.3937363910202841</v>
+        <v>0.4864853538609773</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.704623120079074</v>
+        <v>3.76027249778349</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906084</v>
+        <v>3.775233033906082</v>
       </c>
       <c r="C2042" t="n">
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.189293693231814</v>
+        <v>-5.015182006923757</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.372144229598027</v>
+        <v>1.44178890412125</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.4522009989800855</v>
+        <v>0.5449499618207787</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.719538730592552</v>
+        <v>3.775188108296968</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912989</v>
+        <v>3.785761685912987</v>
       </c>
       <c r="C2043" t="n">
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.133963105330052</v>
+        <v>-4.959851419021994</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.42924340137079</v>
+        <v>1.498888075894013</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5075315868818477</v>
+        <v>0.6002805497225409</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.787704019945668</v>
+        <v>3.843353397650084</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539898</v>
+        <v>3.743767956539896</v>
       </c>
       <c r="C2044" t="n">
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-5.121908978417089</v>
+        <v>-4.947797292109032</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.427751620037413</v>
+        <v>1.497396294560636</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.5195857137948106</v>
+        <v>0.6123346766355037</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.788623063994883</v>
+        <v>3.844272441699299</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811013</v>
+        <v>3.725010844811012</v>
       </c>
       <c r="C2045" t="n">
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.199264468545058</v>
+        <v>-5.025152782237001</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.398690054170361</v>
+        <v>1.468334728693584</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.4422302236668412</v>
+        <v>0.5349791865075343</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.744090400102237</v>
+        <v>3.799739777806653</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382924</v>
+        <v>3.612322444382922</v>
       </c>
       <c r="C2046" t="n">
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-5.131215905853528</v>
+        <v>-4.957104219545471</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.438760505124856</v>
+        <v>1.508405179648078</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.510278786358371</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.797770563595038</v>
+        <v>3.853419941299454</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013431</v>
+        <v>3.64525678001343</v>
       </c>
       <c r="C2047" t="n">
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.362816299023029</v>
+        <v>-5.188704612714972</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.366323018030649</v>
+        <v>1.435967692553872</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.510278786358371</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.817973233768632</v>
+        <v>3.873622611473048</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.412867844552249</v>
+        <v>-5.238756158244191</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.329908635885844</v>
+        <v>1.399553310409066</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.510278786358371</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.801579469835514</v>
+        <v>3.85722884753993</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800098</v>
+        <v>3.670048702800096</v>
       </c>
       <c r="C2049" t="n">
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.587974677128694</v>
+        <v>-5.413862990820636</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.220117816448732</v>
+        <v>1.289762490971955</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.510278786358371</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.76183138342898</v>
+        <v>3.817480761133397</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.74557314866085</v>
+        <v>3.745573148660848</v>
       </c>
       <c r="C2050" t="n">
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.391874523698171</v>
+        <v>-5.217762837390113</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.305580496817881</v>
+        <v>1.375225171341104</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7063789397888939</v>
+        <v>0.799127902629587</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.886514094484234</v>
+        <v>3.94216347218865</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.238849131584886</v>
+        <v>-5.064737445276829</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.4659616532361</v>
+        <v>1.535606327759323</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.859404331902178</v>
+        <v>0.9521532947428711</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.077500329325109</v>
+        <v>4.133149707029525</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791147</v>
       </c>
       <c r="C2052" t="n">
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.267156445458157</v>
+        <v>-5.093044759150099</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.642104952595084</v>
+        <v>1.711749627118307</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.859404331902178</v>
+        <v>0.9521532947428711</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.264966554233402</v>
+        <v>4.320615931937818</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620433</v>
       </c>
       <c r="C2053" t="n">
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.433749670571679</v>
+        <v>-5.259637984263621</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.544870613903758</v>
+        <v>1.614515288426981</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.6928111067886555</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.134413570519371</v>
+        <v>4.190062948223787</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.410713877210113</v>
+        <v>-5.236602190902055</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.557761333910102</v>
+        <v>1.627406008433325</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.6928111067886555</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.138089973181089</v>
+        <v>4.193739350885505</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.381467896754416</v>
+        <v>-5.207356210446359</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.567077781215876</v>
+        <v>1.636722455739099</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.6928111067886555</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.135708028304584</v>
+        <v>4.191357406009</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.488393444632267</v>
+        <v>-5.31428175832421</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.521600801222371</v>
+        <v>1.591245475745593</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.5858855589108042</v>
+        <v>0.6786345217514974</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.068845938735508</v>
+        <v>4.124495316439925</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701002</v>
+        <v>3.689942600701001</v>
       </c>
       <c r="C2057" t="n">
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.633412003139516</v>
+        <v>-5.459300316831459</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.465022179962705</v>
+        <v>1.534666854485928</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.4408670004035556</v>
+        <v>0.5336159632442489</v>
       </c>
       <c r="G2057" t="n">
-        <v>3.983263605774393</v>
+        <v>4.038912983478809</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.751753768924234</v>
+        <v>-5.577642082616176</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.517616712906571</v>
+        <v>1.587261387429794</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.4515530389664457</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.08960646816988</v>
+        <v>4.145255845874297</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790806</v>
+        <v>3.714879051790804</v>
       </c>
       <c r="C2059" t="n">
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.803164191244941</v>
+        <v>-5.629052504936884</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.494838241104227</v>
+        <v>1.56448291562745</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.4515530389664457</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.087392165295819</v>
+        <v>4.143041543000235</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437335</v>
+        <v>3.704757949437333</v>
       </c>
       <c r="C2060" t="n">
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.882583642452693</v>
+        <v>-5.708471956144636</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.462973588695416</v>
+        <v>1.532618263218639</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.4515530389664457</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.087295293370109</v>
+        <v>4.142944671074525</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298403</v>
+        <v>3.736804952298401</v>
       </c>
       <c r="C2061" t="n">
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.978046640369911</v>
+        <v>-5.803934954061853</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.424782283086572</v>
+        <v>1.494426957609794</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.4515530389664457</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.087289186928151</v>
+        <v>4.142938564632567</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218005</v>
+        <v>3.715372960218003</v>
       </c>
       <c r="C2062" t="n">
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.913670729519196</v>
+        <v>-5.739559043211139</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.448629043989468</v>
+        <v>1.518273718512691</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.5159289498171609</v>
+        <v>0.6086779126578541</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.124011130001191</v>
+        <v>4.179660507705607</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353541</v>
+        <v>3.736089413353539</v>
       </c>
       <c r="C2063" t="n">
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.96903989165139</v>
+        <v>-5.794928205343332</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.432215196884318</v>
+        <v>1.50185987140754</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.5159289498171609</v>
+        <v>0.6086779126578541</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.129744947748918</v>
+        <v>4.185394325453334</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113284</v>
+        <v>3.736822870113282</v>
       </c>
       <c r="C2064" t="n">
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.987258358648998</v>
+        <v>-5.813146672340941</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.424466173428206</v>
+        <v>1.494110847951429</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.4908225125613187</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.114219448738345</v>
+        <v>4.169868826442761</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113692</v>
+        <v>3.79027250011369</v>
       </c>
       <c r="C2065" t="n">
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.948574923305068</v>
+        <v>-5.77446323699701</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.459813940416097</v>
+        <v>1.52945861493932</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.4908225125613187</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.134093841588664</v>
+        <v>4.18974321929308</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016437</v>
+        <v>3.794486844016435</v>
       </c>
       <c r="C2066" t="n">
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.842539928099758</v>
+        <v>-5.668428241791701</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.485928639022949</v>
+        <v>1.555573313546172</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.4908225125613187</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.117794542113391</v>
+        <v>4.173443919817807</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307669</v>
+        <v>3.794705093307667</v>
       </c>
       <c r="C2067" t="n">
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.659328264966663</v>
+        <v>-5.485216578658606</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.561644253740233</v>
+        <v>1.631288928263456</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.4908225125613187</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.120225491577438</v>
+        <v>4.175874869281854</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863548</v>
       </c>
       <c r="C2068" t="n">
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.587606817952812</v>
+        <v>-5.413495131644755</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.57327723862515</v>
+        <v>1.642921913148373</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.5625439595751693</v>
+        <v>0.6552929224158626</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.146202765865125</v>
+        <v>4.201852143569541</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394111</v>
+        <v>3.723789705394109</v>
       </c>
       <c r="C2069" t="n">
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.565233792345106</v>
+        <v>-5.391122106037049</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.529142194789404</v>
+        <v>1.598786869312627</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.5737997106880709</v>
+        <v>0.6665486735287641</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.099871962454038</v>
+        <v>4.155521340158454</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456728</v>
       </c>
       <c r="C2070" t="n">
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.598250088255851</v>
+        <v>-5.424138401947793</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.701133881310462</v>
+        <v>1.770778555833684</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5043623340213192</v>
+        <v>0.5971112968620125</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.243407741339341</v>
+        <v>4.299057119043757</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.71376253688368</v>
+        <v>3.713762536883678</v>
       </c>
       <c r="C2071" t="n">
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.586722452606242</v>
+        <v>-5.412610766298185</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.697666161398554</v>
+        <v>1.767310835921777</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.5633629922226817</v>
+        <v>0.6561119550633749</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.270729362088408</v>
+        <v>4.326378739792824</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236301</v>
+        <v>3.717150699236299</v>
       </c>
       <c r="C2072" t="n">
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.684063953948611</v>
+        <v>-5.509952267640553</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.662397673383395</v>
+        <v>1.732042347906618</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.5189428100571933</v>
+        <v>0.6116917728978866</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.247745365310903</v>
+        <v>4.303394743015319</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427688</v>
+        <v>3.705201079427686</v>
       </c>
       <c r="C2073" t="n">
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.769919983288577</v>
+        <v>-5.59580829698052</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.629306343840247</v>
+        <v>1.69895101836347</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.4765667408310583</v>
+        <v>0.5693157036717515</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.223570805968061</v>
+        <v>4.279220183672477</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610378</v>
       </c>
       <c r="C2074" t="n">
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.778756780704697</v>
+        <v>-5.604645094396639</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.608190826694301</v>
+        <v>1.677835501217524</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.4691245681897075</v>
+        <v>0.5618735310304008</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.201524704203752</v>
+        <v>4.257174081908168</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667458</v>
+        <v>3.715544411667456</v>
       </c>
       <c r="C2075" t="n">
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.870139343270155</v>
+        <v>-5.696027656962098</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.581802312713167</v>
+        <v>1.65144698723639</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.4325596834703629</v>
+        <v>0.5253086463110561</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.189750284417195</v>
+        <v>4.245399662121611</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889195</v>
+        <v>3.673978374889193</v>
       </c>
       <c r="C2076" t="n">
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.858432625283149</v>
+        <v>-5.684320938975092</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.688613257732237</v>
+        <v>1.75825793225546</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.4442664014573693</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.298902573033667</v>
+        <v>4.354551950738083</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409571</v>
+        <v>3.682476099409569</v>
       </c>
       <c r="C2077" t="n">
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.929344699025426</v>
+        <v>-5.755233012717369</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.663280766966731</v>
+        <v>1.732925441489954</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.4442664014573693</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.301934911765072</v>
+        <v>4.357584289469488</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452568</v>
       </c>
       <c r="C2078" t="n">
         <v>4.248279904168708</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.939660797191778</v>
+        <v>-5.765549110883721</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.872059160978249</v>
+        <v>1.941703835501472</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.4442664014573693</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.51483974504313</v>
+        <v>4.570489122747546</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762291</v>
+        <v>3.623960959762289</v>
       </c>
       <c r="C2079" t="n">
         <v>4.247458571080798</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.939566829174406</v>
+        <v>-5.765455142866348</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.871275415097287</v>
+        <v>1.94092008962051</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.4446362628046873</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.51424032876361</v>
+        <v>4.569889706468026</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884084</v>
+        <v>3.800870306884082</v>
       </c>
       <c r="C2080" t="n">
         <v>4.241690557025152</v>
       </c>
       <c r="D2080" t="n">
-        <v>-6.083167993197791</v>
+        <v>-5.909056306889734</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.808066935432287</v>
+        <v>1.87771160995551</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.4446362628046873</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.508472314707964</v>
+        <v>4.56412169241238</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129648</v>
+        <v>3.671015692129646</v>
       </c>
       <c r="C2081" t="n">
         <v>4.241690557025152</v>
       </c>
       <c r="D2081" t="n">
-        <v>-6.082219570079753</v>
+        <v>-5.908107883771695</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.808446304679503</v>
+        <v>1.878090979202725</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.4446362628046873</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.508472314707964</v>
+        <v>4.56412169241238</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052351</v>
+        <v>3.904173816052349</v>
       </c>
       <c r="C2082" t="n">
         <v>4.254418165006244</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.182489388038773</v>
+        <v>-6.008377701730716</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.781065985476986</v>
+        <v>1.850710660000209</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.4446362628046873</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.521199922689056</v>
+        <v>4.576849300393472</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813495</v>
+        <v>3.740179607813493</v>
       </c>
       <c r="C2083" t="n">
         <v>4.256364163430631</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.176497141249961</v>
+        <v>-6.002385454941904</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.785408882616899</v>
+        <v>1.855053557140122</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.4446362628046873</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.523145921113444</v>
+        <v>4.57879529881786</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537944</v>
+        <v>3.765050796537942</v>
       </c>
       <c r="C2084" t="n">
         <v>4.2500182994484</v>
       </c>
       <c r="D2084" t="n">
-        <v>-6.087939180119194</v>
+        <v>-5.913827493811136</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.814486203086974</v>
+        <v>1.884130877610198</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.4446362628046873</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.516800057131213</v>
+        <v>4.572449434835629</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771816</v>
+        <v>3.758409170771814</v>
       </c>
       <c r="C2085" t="n">
         <v>4.249326976887396</v>
       </c>
       <c r="D2085" t="n">
-        <v>-6.07018010261612</v>
+        <v>-5.896068416308062</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.8208985115272</v>
+        <v>1.890543186050423</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.4446362628046873</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.516108734570208</v>
+        <v>4.571758112274624</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.801340597109721</v>
+        <v>3.80134059710972</v>
       </c>
       <c r="C2086" t="n">
         <v>4.262109162795983</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.970549951567052</v>
+        <v>-5.796438265258995</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.873532757855414</v>
+        <v>1.943177432378637</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.5442664138537547</v>
+        <v>0.637015376694448</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.588669011108236</v>
+        <v>4.644318388812652</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546843996</v>
+        <v>3.798465546843994</v>
       </c>
       <c r="C2087" t="n">
         <v>4.451263428294709</v>
       </c>
       <c r="D2087" t="n">
-        <v>-6.019949460256063</v>
+        <v>-5.845837773948006</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.042927219878536</v>
+        <v>2.112571894401759</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.5545252472854995</v>
+        <v>0.6472742101261927</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.783978576666009</v>
+        <v>4.839627954370425</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.77218650835186</v>
+        <v>3.772186508351858</v>
       </c>
       <c r="C2088" t="n">
         <v>4.438452101397571</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.813264986613687</v>
+        <v>-5.63915330030563</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.112789682438348</v>
+        <v>2.182434356961571</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.7612097209278751</v>
+        <v>0.8539586837685683</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.895177933954296</v>
+        <v>4.950827311658712</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.440453615051676</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.847421881611213</v>
+        <v>-5.60535229650209</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.101128438093443</v>
+        <v>2.197956272137092</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.6776259513870626</v>
+        <v>0.8323384425147884</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.847029185883914</v>
+        <v>4.939856680560549</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041111</v>
+        <v>3.805590565041109</v>
       </c>
       <c r="C2090" t="n">
         <v>4.793950729041343</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.754832402549757</v>
+        <v>-5.512762817440634</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.491661343707693</v>
+        <v>2.588489177751342</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.6776259513870626</v>
+        <v>0.8323384425147884</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.200526299873581</v>
+        <v>5.293353794550216</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497403</v>
+        <v>3.832164354497401</v>
       </c>
       <c r="C2091" t="n">
         <v>4.798513840608447</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.827993006322902</v>
+        <v>-5.585923421213779</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.466960213765538</v>
+        <v>2.563788047809187</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.6496047513528196</v>
+        <v>0.8043172424805454</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.188276691420139</v>
+        <v>5.281104186096774</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492295</v>
+        <v>3.858310890492294</v>
       </c>
       <c r="C2092" t="n">
         <v>4.848343781931974</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.77577669652656</v>
+        <v>-5.533707111417437</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.537676679007602</v>
+        <v>2.634504513051251</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.6496047513528196</v>
+        <v>0.8043172424805454</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.238106632743667</v>
+        <v>5.330934127420302</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436477</v>
+        <v>3.844935596436475</v>
       </c>
       <c r="C2093" t="n">
         <v>4.857157752141985</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.743879179441314</v>
+        <v>-5.501809594332191</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.559249656051712</v>
+        <v>2.656077490095361</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.6815022684380654</v>
+        <v>0.8362147595657912</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.266059113204824</v>
+        <v>5.35888660788146</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039486</v>
+        <v>3.848376866039485</v>
       </c>
       <c r="C2094" t="n">
         <v>4.852795336181182</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.758634503641455</v>
+        <v>-5.516564918532332</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.548985110410852</v>
+        <v>2.645812944454501</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.6815022684380654</v>
+        <v>0.8362147595657912</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.261696697244021</v>
+        <v>5.354524191920657</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524481</v>
+        <v>3.868153115524479</v>
       </c>
       <c r="C2095" t="n">
         <v>4.843719839597462</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.709169880271543</v>
+        <v>-5.46710029516242</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.559695463175097</v>
+        <v>2.656523297218746</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.730966891807977</v>
+        <v>0.8856793829357028</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.282299974682249</v>
+        <v>5.375127469358884</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867955</v>
+        <v>3.849040239867954</v>
       </c>
       <c r="C2096" t="n">
         <v>4.840127507312396</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.546061888117928</v>
+        <v>-5.303992303008805</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.621346327751477</v>
+        <v>2.718174161795126</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.8940748839615923</v>
+        <v>1.048787375089318</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.376572437689352</v>
+        <v>5.469399932365987</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232972</v>
+        <v>3.87020492823297</v>
       </c>
       <c r="C2097" t="n">
         <v>4.849174544003525</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.5254187973167</v>
+        <v>-5.283349212207577</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.638650600763097</v>
+        <v>2.735478434806746</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.8940748839615923</v>
+        <v>1.048787375089318</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.38561947438048</v>
+        <v>5.478446969057115</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179675</v>
+        <v>3.855534437179673</v>
       </c>
       <c r="C2098" t="n">
         <v>4.850032008989646</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.588126713791258</v>
+        <v>-5.346057128682135</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.614424899159395</v>
+        <v>2.711252733203044</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.8313669674870345</v>
+        <v>0.9860794586147604</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.348852189481867</v>
+        <v>5.441679684158503</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967722</v>
+        <v>3.884687848967721</v>
       </c>
       <c r="C2099" t="n">
         <v>4.812941425779998</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.540118589947565</v>
+        <v>-5.298049004838442</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.596537565487224</v>
+        <v>2.693365399530873</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.8313669674870345</v>
+        <v>0.9860794586147604</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.311761606272219</v>
+        <v>5.404589100948855</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018613</v>
+        <v>3.895362357018612</v>
       </c>
       <c r="C2100" t="n">
         <v>4.816873679337949</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.461292932763975</v>
+        <v>-5.219223347654852</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.632000081918611</v>
+        <v>2.72882791596226</v>
       </c>
       <c r="F2100" t="n">
-        <v>0.910192624670625</v>
+        <v>1.064905115798351</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.362989254140324</v>
+        <v>5.455816748816959</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075137</v>
+        <v>3.891610981075135</v>
       </c>
       <c r="C2101" t="n">
         <v>4.811772771944986</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.269358131510101</v>
+        <v>-5.108952144481885</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.703673095027197</v>
+        <v>2.767835489838484</v>
       </c>
       <c r="F2101" t="n">
-        <v>0.910192624670625</v>
+        <v>1.064905115798351</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.357888346747361</v>
+        <v>5.450715841423996</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435446</v>
+        <v>3.872432493435444</v>
       </c>
       <c r="C2102" t="n">
         <v>4.807126681334081</v>
       </c>
       <c r="D2102" t="n">
-        <v>-5.151184753492174</v>
+        <v>-4.990778766463958</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.746296355623463</v>
+        <v>2.81045875043475</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.028366002688552</v>
+        <v>1.183078493816278</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.424146282947213</v>
+        <v>5.516973777623848</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917735</v>
+        <v>3.859571723917733</v>
       </c>
       <c r="C2103" t="n">
         <v>4.836215274197108</v>
       </c>
       <c r="D2103" t="n">
-        <v>-5.037770070709443</v>
+        <v>-4.877364083681226</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.820750821599583</v>
+        <v>2.884913216410869</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.141780685471284</v>
+        <v>1.29649317659901</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.521283685479879</v>
+        <v>5.614111180156514</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.82800627401364</v>
+        <v>3.828006274013639</v>
       </c>
       <c r="C2104" t="n">
         <v>4.829775497208285</v>
       </c>
       <c r="D2104" t="n">
-        <v>-5.010721033016189</v>
+        <v>-4.850315045987973</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.825130659688061</v>
+        <v>2.889293054499348</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.168829723164537</v>
+        <v>1.323542214292263</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.531073331107008</v>
+        <v>5.623900825783643</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.823987445263771</v>
+        <v>3.82398744526377</v>
       </c>
       <c r="C2105" t="n">
         <v>4.829775497208285</v>
       </c>
       <c r="D2105" t="n">
-        <v>-5.016754313202959</v>
+        <v>-4.856348326174743</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.822717347613353</v>
+        <v>2.88687974242464</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.168829723164537</v>
+        <v>1.323542214292263</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.531073331107008</v>
+        <v>5.623900825783643</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.815657203170837</v>
+        <v>3.815657203170833</v>
       </c>
       <c r="C2106" t="n">
         <v>4.833413664350697</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.916956950629122</v>
+        <v>-4.908200101747904</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.8662744597853</v>
+        <v>2.869777199337788</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.268627085738374</v>
+        <v>1.271690438719102</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.594589915793722</v>
+        <v>5.596427927582159</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.918689114023954</v>
+        <v>3.634617831035486</v>
       </c>
       <c r="C2107" t="n">
-        <v>5.041541421513127</v>
+        <v>4.800017965830405</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.916956950629122</v>
+        <v>-4.908200101747904</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.8662744597853</v>
+        <v>2.869777199337788</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.268627085738374</v>
+        <v>1.271690438719102</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.034605218499495</v>
+        <v>4.793081762816773</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241004.xlsx
+++ b/tame_output/ON/bt/strategyON_20241004.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>50.1%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>111.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>168.4%</t>
+          <t>174.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.1%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-73.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>419.1%</t>
+          <t>420.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-652.4%</t>
+          <t>-642.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-89.2%</t>
+          <t>-85.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.5%</t>
+          <t>-362.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-96.8%</t>
+          <t>-99.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
     </row>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737168</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341311</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539462</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.176056899127509</v>
+        <v>-8.123567156606317</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1388658451497196</v>
+        <v>-0.1178699481412422</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.005067935285861</v>
+        <v>-0.9525781927646679</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.528872577643516</v>
+        <v>2.560366423156232</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.230128398635868</v>
+        <v>-8.177638656114675</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1576008886314906</v>
+        <v>-0.1366049916230136</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.059139434794221</v>
+        <v>-1.006649692273027</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.499323234260073</v>
+        <v>2.530817079772788</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.233704184727616</v>
+        <v>-8.181214442206423</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1535180059495476</v>
+        <v>-0.1325221089410702</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.084668356710713</v>
+        <v>-1.03217861418952</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.489519078228819</v>
+        <v>2.521012923741536</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.267357023236089</v>
+        <v>-8.214867280714897</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1624965868685009</v>
+        <v>-0.1415006898600235</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.185081724627751</v>
+        <v>-1.132591982106557</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.433753611963033</v>
+        <v>2.465247457475749</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.406443137854946</v>
+        <v>-8.353953395333754</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2027593312226226</v>
+        <v>-0.1817634342141456</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.324167839246607</v>
+        <v>-1.271678096725414</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.36567364468514</v>
+        <v>2.397167490197856</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.58156755524149</v>
+        <v>-8.529077812720297</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2582538774297229</v>
+        <v>-0.237257980421246</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.499292256633151</v>
+        <v>-1.446802514111958</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.275154215000731</v>
+        <v>2.306648060513447</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.816019649255979</v>
+        <v>-8.763529906734787</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.359253879937115</v>
+        <v>-0.3382579829286381</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.499292256633151</v>
+        <v>-1.446802514111958</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.267935050099135</v>
+        <v>2.299428895611851</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.920394380282426</v>
+        <v>-8.867904637761233</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4076759631216698</v>
+        <v>-0.3866800661131928</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.603666987659597</v>
+        <v>-1.551177245138403</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.198638020709291</v>
+        <v>2.230131866222007</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.08290784598101</v>
+        <v>-9.030418103459818</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.471565559562547</v>
+        <v>-0.45056966255407</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.701300418078284</v>
+        <v>-1.64881067555709</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.141173752296635</v>
+        <v>2.172667597809351</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.2089446393493</v>
+        <v>-9.156454896828107</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5192865482807481</v>
+        <v>-0.4982906512722711</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.623559052747348</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.159018454611595</v>
+        <v>2.190512300124311</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.151872867453369</v>
+        <v>-9.099383124932176</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4924675038359752</v>
+        <v>-0.4714716068274978</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.623559052747348</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.163008790297996</v>
+        <v>2.194502635810712</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.293544709177489</v>
+        <v>-9.241054966656296</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.550611467424365</v>
+        <v>-0.5296155704158876</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.623559052747348</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.161533563399254</v>
+        <v>2.19302740891197</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.243953864752655</v>
+        <v>-9.191464122231462</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5157217194895587</v>
+        <v>-0.4947258224810818</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.626457950843708</v>
+        <v>-1.573968208322514</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.206341480219027</v>
+        <v>2.237835325731743</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.095035530280798</v>
+        <v>-9.042545787759606</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4692055193474993</v>
+        <v>-0.448209622339022</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.595208360108535</v>
+        <v>-1.542718617587341</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.212040101013448</v>
+        <v>2.243533946526164</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.869190377561386</v>
+        <v>-8.816700635040194</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3692883852235256</v>
+        <v>-0.3482924882150487</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.500791942000177</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.246775179401955</v>
+        <v>2.278269024914671</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.744611721223794</v>
+        <v>-8.692121978702602</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.31831777813243</v>
+        <v>-0.2973218811239531</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.500791942000177</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.247914323958013</v>
+        <v>2.27940816947073</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.719575039655284</v>
+        <v>-8.667085297134092</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3056693313429184</v>
+        <v>-0.2846734343344415</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.475462854449441</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.265745550650562</v>
+        <v>2.297239396163278</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.647441864367403</v>
+        <v>-8.594952121846211</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2710823569891296</v>
+        <v>-0.2500864599806523</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.475462854449441</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.271479254889199</v>
+        <v>2.302973100401915</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.644238203941597</v>
+        <v>-8.591748461420405</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2795381552126726</v>
+        <v>-0.2585422582041952</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.524748936544829</v>
+        <v>-1.472259194023635</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.263664188750818</v>
+        <v>2.295158034263534</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.550779169956373</v>
+        <v>-8.49828942743518</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2520380229314902</v>
+        <v>-0.2310421259230133</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.524748936544829</v>
+        <v>-1.472259194023635</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.25378070743791</v>
+        <v>2.285274552950626</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.540125988402941</v>
+        <v>-8.487636245881749</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2496113108094913</v>
+        <v>-0.2286154138010144</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.524748936544829</v>
+        <v>-1.472259194023635</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.251946146938536</v>
+        <v>2.283439992451252</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.442218949726451</v>
+        <v>-8.389729207205258</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.210748810312356</v>
+        <v>-0.1897529133038787</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.456763186684273</v>
+        <v>-1.404273444163079</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.292437281881409</v>
+        <v>2.323931127394125</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.418265408750493</v>
+        <v>-8.3657756662293</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2004988877764791</v>
+        <v>-0.1795029907680021</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.432809645708315</v>
+        <v>-1.380319903187121</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.307477912612478</v>
+        <v>2.338971758125194</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.154205470427696</v>
+        <v>-8.101715727906504</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1081352286091124</v>
+        <v>-0.08713933160063547</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.168749707385519</v>
+        <v>-1.116259964864325</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.452653559444403</v>
+        <v>2.484147404957119</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.447125846922858</v>
+        <v>-7.394636104401665</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.171909587132522</v>
+        <v>0.192905484140999</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.168749707385519</v>
+        <v>-1.116259964864325</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.449866525784102</v>
+        <v>2.481360371296818</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937444738873</v>
+        <v>3.839374447388729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.406941548556667</v>
+        <v>-7.354451806035475</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1883269303668396</v>
+        <v>0.2093228273753165</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.128565409019328</v>
+        <v>-1.076075666498134</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.474320728691658</v>
+        <v>2.505814574204374</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626476</v>
+        <v>3.856161751626475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.243541677617305</v>
+        <v>-7.191051935096112</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2530536999633415</v>
+        <v>0.2740495969718184</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9651655380799653</v>
+        <v>-0.9126757955587717</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.571727472476033</v>
+        <v>2.603221317988749</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.08542429823853</v>
+        <v>-7.032934555717337</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3242250805527038</v>
+        <v>0.3452209775611808</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8070481587011898</v>
+        <v>-0.7545584161799962</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.67452232894115</v>
+        <v>2.706016174453866</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.935757907231014</v>
+        <v>-6.883268164709822</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.381199426642751</v>
+        <v>0.4021953236512279</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7141446674586539</v>
+        <v>-0.6616549249374603</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.727372213373712</v>
+        <v>2.758866058886428</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.803482433600128</v>
+        <v>-6.750992691078936</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3353704021022601</v>
+        <v>0.356366299110737</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5818691938277673</v>
+        <v>-0.5293794513065736</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.707998283559399</v>
+        <v>2.739492129072115</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.631621218035225</v>
+        <v>-6.579131475514033</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4069299490158578</v>
+        <v>0.4279258460243347</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4100079782628644</v>
+        <v>-0.3575182357416707</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.813930073585978</v>
+        <v>2.845423919098694</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.546656551305906</v>
+        <v>-6.494166808784714</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4538221569312442</v>
+        <v>0.4748180539397211</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.3250433115335448</v>
+        <v>-0.2725535690123512</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.877815214847228</v>
+        <v>2.909309060359944</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.652246541079011</v>
+        <v>-6.599756798557818</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2836102314227835</v>
+        <v>0.3046061284312609</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.4306333013066492</v>
+        <v>-0.3781435587854555</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.686485291384147</v>
+        <v>2.717979136896863</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.584011956453583</v>
+        <v>-6.531522213932391</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3594484071500412</v>
+        <v>0.3804443041585182</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.4122179784341132</v>
+        <v>-0.3597282359129195</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.746078826984755</v>
+        <v>2.777572672497471</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.436071915045984</v>
+        <v>-6.383582172524791</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3020036150746739</v>
+        <v>0.3229995120831508</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3918970625255556</v>
+        <v>-0.339407320004362</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.641650567891482</v>
+        <v>2.673144413404198</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.383102392791995</v>
+        <v>-6.330612650270803</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.314477437722791</v>
+        <v>0.3354733347312679</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.2864377977503731</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.664718294990398</v>
+        <v>2.696212140503114</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.217314196831705</v>
+        <v>-6.164824454310512</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.373832104011814</v>
+        <v>0.3948280010202909</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.2864377977503731</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.657757682895304</v>
+        <v>2.689251528408021</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.183950990352936</v>
+        <v>-6.131461247831743</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4016397409844648</v>
+        <v>0.4226356379929417</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.2864377977503731</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.672220037276448</v>
+        <v>2.703713882789164</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.075691853230414</v>
+        <v>-6.023202110709222</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4394755162926685</v>
+        <v>0.4604714133011454</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.2864377977503731</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.666752157735643</v>
+        <v>2.698246003248359</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.952400718413283</v>
+        <v>-5.899910975892091</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4862900642300976</v>
+        <v>0.5072859612385745</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2156364054544362</v>
+        <v>-0.1631466629332426</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.738224932636498</v>
+        <v>2.769718778149214</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.899703851281992</v>
+        <v>-5.8472141087608</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5150697893199392</v>
+        <v>0.5360656863284166</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1629395383231451</v>
+        <v>-0.1104497958019514</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.777544031152598</v>
+        <v>2.809037876665314</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.655938409298548</v>
+        <v>-5.603448666777355</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6083566744603677</v>
+        <v>0.6293525714688446</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1629395383231451</v>
+        <v>-0.1104497958019514</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.773324739499648</v>
+        <v>2.804818585012364</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.566162736922076</v>
+        <v>-5.513672994400883</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6463912573309725</v>
+        <v>0.6673871543394498</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.101340093408835</v>
+        <v>-0.04885035088764139</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.81240872036825</v>
+        <v>2.843902565880966</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.316312342973001</v>
+        <v>-5.263822600451808</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7390734898943045</v>
+        <v>0.7600693869027815</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.101340093408835</v>
+        <v>-0.04885035088764139</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.805150795351952</v>
+        <v>2.836644640864668</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.140420250505569</v>
+        <v>-5.087930507984376</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8130294504019262</v>
+        <v>0.8340253474104031</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.101340093408835</v>
+        <v>-0.04885035088764139</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.808749918872601</v>
+        <v>2.840243764385317</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.968973787483105</v>
+        <v>-4.916484044961913</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8949355416654652</v>
+        <v>0.9159314386739423</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.07010636961362809</v>
+        <v>0.1225961121348217</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.924945302740633</v>
+        <v>2.956439148253349</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.888951500373985</v>
+        <v>-4.836461757852792</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9259649341254106</v>
+        <v>0.9469608311338877</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1501286567227491</v>
+        <v>0.2026183992439427</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.971979152622402</v>
+        <v>3.003472998135118</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.82531575814005</v>
+        <v>-4.772826015618858</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9561140320733017</v>
+        <v>0.9771099290817786</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2137643989566836</v>
+        <v>0.2662541414778772</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.01485539901708</v>
+        <v>3.046349244529796</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.731618439923655</v>
+        <v>-4.679128697402462</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9747872181436554</v>
+        <v>0.9957831151521324</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2137643989566836</v>
+        <v>0.2662541414778772</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.996049657800876</v>
+        <v>3.027543503313592</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.742121062988944</v>
+        <v>-4.689631320467751</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9723292455424173</v>
+        <v>0.9933251425508942</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2032617758913947</v>
+        <v>0.2557515184125884</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.99149116058658</v>
+        <v>3.022985006099296</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.629634802320069</v>
+        <v>-4.577145059798877</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.021253063644787</v>
+        <v>1.042248960653264</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2032617758913947</v>
+        <v>0.2557515184125884</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.9954204744214</v>
+        <v>3.026914319934116</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.611921115442204</v>
+        <v>-4.559431372921011</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.029017122313273</v>
+        <v>1.05001301932175</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.2589328473095052</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.99800785567689</v>
+        <v>3.029501701189606</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.488446844129186</v>
+        <v>-4.435957101607993</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.075404902058474</v>
+        <v>1.096400799066951</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.2589328473095052</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.995005926896884</v>
+        <v>3.0264997724096</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675942</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.43051101213097</v>
+        <v>-4.378021269609778</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.100158271868374</v>
+        <v>1.121154168876852</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2320049794710608</v>
+        <v>0.2844947219922545</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.011922088717147</v>
+        <v>3.043415934229863</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539953</v>
+        <v>3.843274527539951</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.297643323067692</v>
+        <v>-4.229405000967461</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.169199530295509</v>
+        <v>1.196494859135602</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2320049794710608</v>
+        <v>0.2844947219922545</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.02781627151897</v>
+        <v>3.059310117031687</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.177470239703194</v>
+        <v>-4.109231917602962</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.21841460808161</v>
+        <v>1.245709936921703</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3521780628355597</v>
+        <v>0.4046678053567534</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.101065965977972</v>
+        <v>3.132559811490688</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.042216878373217</v>
+        <v>-3.973978556272985</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.282604055175041</v>
+        <v>1.309899384015134</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.4874314241655369</v>
+        <v>0.5399211666867305</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.192306085337398</v>
+        <v>3.223799930850114</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.102091705730909</v>
+        <v>-4.033853383630677</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.24469161563339</v>
+        <v>1.271986944473483</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4275565968078447</v>
+        <v>0.4800463393290384</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.142418680324209</v>
+        <v>3.173912525836925</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674515</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.982271474820072</v>
+        <v>-3.91403315271984</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.307908877231933</v>
+        <v>1.335204206072026</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4275565968078447</v>
+        <v>0.4800463393290384</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.157707849558417</v>
+        <v>3.189201695071133</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.984741181281878</v>
+        <v>-3.916502859181646</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.214565193969652</v>
+        <v>1.241860522809745</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4250868903460386</v>
+        <v>0.4775766328672322</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.063870225003775</v>
+        <v>3.095364070516491</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.053111367605887</v>
+        <v>-3.984873045505656</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.10647898092535</v>
+        <v>1.133774309765443</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4868523319034472</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.988697505910805</v>
+        <v>3.020191351423521</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.164983647232038</v>
+        <v>-4.096745325131806</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.052166777706781</v>
+        <v>1.079462106546874</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4868523319034472</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.979134214542697</v>
+        <v>3.010628060055413</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.14900898174577</v>
+        <v>-4.080770659645538</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.025131168825316</v>
+        <v>1.052426497665408</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4868523319034472</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.945708739466724</v>
+        <v>2.97720258497944</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.7460425262059</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.153103528416768</v>
+        <v>-4.084865206316536</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.028060582148704</v>
+        <v>1.055355910988797</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4868523319034472</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.950275971458512</v>
+        <v>2.981769816971228</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.145179153831854</v>
+        <v>-4.076940831731622</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.006972360743877</v>
+        <v>1.03426768958397</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4868523319034472</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.926018000219719</v>
+        <v>2.957511845732435</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.138900951262005</v>
+        <v>-4.070662629161773</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9380219551732663</v>
+        <v>0.965317284013359</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.4931305344732962</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.858323235163078</v>
+        <v>2.889817080675794</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.079048332058282</v>
+        <v>-4.01081000995805</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.972135389286888</v>
+        <v>0.9994307181269808</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.4931305344732962</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.86849562159521</v>
+        <v>2.899989467107926</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.992804869031904</v>
+        <v>-3.924566546931672</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.001579045071299</v>
+        <v>1.028874373911392</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.4931305344732962</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.863441892169071</v>
+        <v>2.894935737681787</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.038111688430884</v>
+        <v>-3.969873366330652</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.975232092756233</v>
+        <v>1.002527421596326</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3998306289428718</v>
+        <v>0.4523203714640655</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.830731569808058</v>
+        <v>2.862225415320774</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.067144793133185</v>
+        <v>-3.998906471032953</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9641707239084141</v>
+        <v>0.9914660527485066</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3998306289428718</v>
+        <v>0.4523203714640655</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.831283442841159</v>
+        <v>2.862777288353875</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.974334311682326</v>
+        <v>-3.906095989582094</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9305676083801235</v>
+        <v>0.9578629372202161</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4926411103937312</v>
+        <v>0.5451308529149248</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.816242423603041</v>
+        <v>2.847736269115757</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.018723781011754</v>
+        <v>-3.950485458911522</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9146852965729531</v>
+        <v>0.9419806254130458</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4482516410643035</v>
+        <v>0.5007413835854971</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.791482217929985</v>
+        <v>2.822976063442701</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.998220087126256</v>
+        <v>-3.929981765026024</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.917962482638875</v>
+        <v>0.9452578114789678</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4687553349498008</v>
+        <v>0.5212450774709945</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.798860142773006</v>
+        <v>2.830353988285722</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.081892183838589</v>
+        <v>-4.013653861738357</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8899849397846094</v>
+        <v>0.9172802686247019</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4687553349498008</v>
+        <v>0.5212450774709945</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.804351438603673</v>
+        <v>2.835845284116389</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.109672581739941</v>
+        <v>-4.041434259639709</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8903699823926072</v>
+        <v>0.9176653112327</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4409749370484478</v>
+        <v>0.4934646795696414</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.799180401631401</v>
+        <v>2.830674247144117</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.22805325447008</v>
+        <v>-4.159814932369848</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6813734333012051</v>
+        <v>0.7086687621412979</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.4262468274186652</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.597205410341468</v>
+        <v>2.628699255854184</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.336667332913411</v>
+        <v>-4.268429010813179</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7580774626430784</v>
+        <v>0.7853727914831712</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.4262468274186652</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.717355071060674</v>
+        <v>2.74884891657339</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.301258294665268</v>
+        <v>-4.233019972565036</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7867541040446584</v>
+        <v>0.8140494328847512</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.4262468274186652</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.731868097162997</v>
+        <v>2.763361942675713</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.309719463320729</v>
+        <v>-4.241481141220497</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.780789077924843</v>
+        <v>0.8080844067649355</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3652959162420105</v>
+        <v>0.4177856587632041</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.724210837312089</v>
+        <v>2.755704682824805</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.132603133285563</v>
+        <v>-4.064364811185331</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8483646387842116</v>
+        <v>0.8756599676243044</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3652959162420105</v>
+        <v>0.4177856587632041</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.720939866157391</v>
+        <v>2.752433711670107</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.177695378119108</v>
+        <v>-4.109457056018877</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8310111326127065</v>
+        <v>0.8583064614527993</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3033998730726207</v>
+        <v>0.3558896155938143</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.684485632017671</v>
+        <v>2.715979477530387</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.998319956880341</v>
+        <v>-3.930081634780109</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.896548276414628</v>
+        <v>0.9238436052547208</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4601766312433394</v>
+        <v>0.5126663737645329</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.772338662226516</v>
+        <v>2.803832507739232</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.043334170400946</v>
+        <v>-3.975095848300715</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8593500463379753</v>
+        <v>0.8866453751780679</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4298277359287348</v>
+        <v>0.4823174784499283</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.734936780369343</v>
+        <v>2.766430625882059</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.131345356959644</v>
+        <v>-4.063107034859412</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8298371340534423</v>
+        <v>0.8571324628935351</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3643512280695618</v>
+        <v>0.4168409705907554</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.701342437992785</v>
+        <v>2.732836283505501</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.232543138396816</v>
+        <v>-4.164304816296585</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7885619433750746</v>
+        <v>0.8158572722151674</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2959424145242426</v>
+        <v>0.3484321570454362</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.659501071762095</v>
+        <v>2.690994917274811</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.226032171782504</v>
+        <v>-4.157793849682272</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7887662915751164</v>
+        <v>0.8160616204152091</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2959424145242426</v>
+        <v>0.3484321570454362</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.657101033316412</v>
+        <v>2.688594878829128</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.206994044075206</v>
+        <v>-4.138755721974975</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7929062618662801</v>
+        <v>0.8202015907063729</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2377588031930481</v>
+        <v>0.2902485457142416</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.61871558572594</v>
+        <v>2.650209431238656</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.259509846350027</v>
+        <v>-4.191271524249795</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8911943425905424</v>
+        <v>0.9184896714306352</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2377588031930481</v>
+        <v>0.2902485457142416</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.73800998736013</v>
+        <v>2.769503832872846</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.262918157784607</v>
+        <v>-4.194679835684375</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8906643470028439</v>
+        <v>0.9179596758429367</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2702753722024255</v>
+        <v>0.322765114723619</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.75835325775189</v>
+        <v>2.789847103264606</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.243562021890759</v>
+        <v>-4.175323699790527</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9044153317573089</v>
+        <v>0.9317106605974017</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2702753722024255</v>
+        <v>0.322765114723619</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.764361788148816</v>
+        <v>2.795855633661532</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.316891550628852</v>
+        <v>-4.24865322852862</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7730337415392714</v>
+        <v>0.8003290703793642</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2706700346220474</v>
+        <v>0.323159777143241</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.662548806877789</v>
+        <v>2.694042652390505</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.409870503348191</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.40071277190355</v>
+        <v>-4.332474449803319</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.6492289702730232</v>
+        <v>0.676524299113116</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2706700346220474</v>
+        <v>0.323159777143241</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.57227252412142</v>
+        <v>2.603766369634136</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.41053285173985</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.394560065850766</v>
+        <v>-4.326321743750534</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.6523524010857953</v>
+        <v>0.6796477299258881</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2768227406748317</v>
+        <v>0.3293124831960252</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.576626496144749</v>
+        <v>2.608120341657465</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.40961332847996</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.411369364001268</v>
+        <v>-4.343131041901036</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.6447091585657048</v>
+        <v>0.6720044874057975</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2600134425243301</v>
+        <v>0.3125031850455236</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.565621393994558</v>
+        <v>2.597115239507274</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>2.475948882276781</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.349071365225146</v>
+        <v>-4.280833043124914</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.7359639118729746</v>
+        <v>0.7632592407130674</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3053077067987721</v>
+        <v>0.3577974493199657</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.659133506356044</v>
+        <v>2.69062735186876</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.278240883990908</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.147281167559988</v>
+        <v>-4.079042845459756</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6189719926531647</v>
+        <v>0.6462673214932575</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5033258989679266</v>
+        <v>0.55581564148912</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.580236423371664</v>
+        <v>2.61173026888438</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.348531116313083</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.198167880246182</v>
+        <v>-4.129929558145951</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6689075399008622</v>
+        <v>0.6962028687409549</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.452439186281732</v>
+        <v>0.5049289288029255</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.619994628082122</v>
+        <v>2.651488473594839</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
         <v>2.363158852429127</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.111557137596376</v>
+        <v>-4.043318815496144</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7181795730768286</v>
+        <v>0.7454749019169213</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5310649174868902</v>
+        <v>0.5835546600080838</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.681797802921261</v>
+        <v>2.713291648433977</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.361694833253798</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.17176643560166</v>
+        <v>-4.103528113501429</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6926318346993863</v>
+        <v>0.7199271635394791</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4708556194816057</v>
+        <v>0.5233453620027992</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.644208204942762</v>
+        <v>2.675702050455478</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
         <v>2.360186451293727</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.122579786917309</v>
+        <v>-4.054341464817077</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7107981122130553</v>
+        <v>0.7380934410531481</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4708556194816057</v>
+        <v>0.5233453620027992</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.642699822982691</v>
+        <v>2.674193668495406</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316251</v>
+        <v>3.833513460316253</v>
       </c>
       <c r="C1976" t="n">
         <v>2.360049318729163</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.07820665527874</v>
+        <v>-4.009968333178509</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.728410232303919</v>
+        <v>0.7557055611440118</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5152287511201743</v>
+        <v>0.5677184936413678</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.669186569401268</v>
+        <v>2.700680414913984</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105965</v>
+        <v>3.821562117105967</v>
       </c>
       <c r="C1977" t="n">
         <v>2.354443112867754</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.04347533396024</v>
+        <v>-3.975237011860008</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7366965549699098</v>
+        <v>0.7639918838100026</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5152287511201743</v>
+        <v>0.5677184936413678</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.663580363539858</v>
+        <v>2.695074209052574</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.360824869895558</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.995819603399184</v>
+        <v>-3.927581281298952</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7621406042221368</v>
+        <v>0.7894359330622294</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.56288448168123</v>
+        <v>0.6153742242024235</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.698555558904296</v>
+        <v>2.730049404417012</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.365717243270283</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.895301444900429</v>
+        <v>-3.827063122800197</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8072402409963635</v>
+        <v>0.834535569836456</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6634026401799845</v>
+        <v>0.7158923827011781</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.763758827378274</v>
+        <v>2.79525267289099</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.352471915746155</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.879396115468077</v>
+        <v>-3.811157793367845</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8003570452451767</v>
+        <v>0.8276523740852695</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5842899794707457</v>
+        <v>0.6367797219919391</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.703045903428603</v>
+        <v>2.734539748941319</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.356569618356784</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.834557713859679</v>
+        <v>-3.766319391759447</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8223901084991645</v>
+        <v>0.8496854373392573</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5888334124156152</v>
+        <v>0.6413231549368086</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.709869665806153</v>
+        <v>2.741363511318869</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.360730557987862</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.854056170101687</v>
+        <v>-3.785817848001455</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8187516656334393</v>
+        <v>0.8460469944735318</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5407487711357108</v>
+        <v>0.5932385136569043</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.685179820669289</v>
+        <v>2.716673666182005</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.366610160515699</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.809853333015786</v>
+        <v>-3.741615010915555</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8423124029956366</v>
+        <v>0.8696077318357291</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5849516082216113</v>
+        <v>0.6374413507428047</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.717581125448666</v>
+        <v>2.749074970961382</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.365020160984947</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.817412998852833</v>
+        <v>-3.749174676752602</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8376985371300654</v>
+        <v>0.8649938659701579</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6397550122314306</v>
+        <v>0.692244754752624</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.748873168323805</v>
+        <v>2.780367013836521</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.416267926167986</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.659121581313561</v>
+        <v>-3.590883259213329</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9522628693288138</v>
+        <v>0.9795581981689065</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6397550122314306</v>
+        <v>0.692244754752624</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.800120933506845</v>
+        <v>2.831614779019561</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.414708630762239</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.451479577679085</v>
+        <v>-3.383241255578853</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.033760375376857</v>
+        <v>1.06105570421695</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8473970158659068</v>
+        <v>0.8998867583871002</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.923146840281784</v>
+        <v>2.9546406857945</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.409656859000509</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.400447484956557</v>
+        <v>-3.332209162856325</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.049121440704139</v>
+        <v>1.076416769544231</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8984291085884347</v>
+        <v>0.9509188511096281</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.94871432415357</v>
+        <v>2.980208169666287</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.426844263093214</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.335223303829351</v>
+        <v>-3.266984981729119</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.092398517247726</v>
+        <v>1.119693846087819</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9636532897156403</v>
+        <v>1.016143032236834</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.005036236922599</v>
+        <v>3.036530082435315</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.422805235392495</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.297796283758217</v>
+        <v>-3.229557961657985</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.10333029757546</v>
+        <v>1.130625626415553</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.968904827744822</v>
+        <v>1.021394570266015</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.004148132039388</v>
+        <v>3.035641977552104</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992661</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.424062027723735</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.296438298784672</v>
+        <v>-3.22819997668444</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.105130283896118</v>
+        <v>1.132425612736211</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.043242953282641</v>
+        <v>1.095732695803834</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.050007799693319</v>
+        <v>3.081501645206036</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.584619798744946</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.268025035684788</v>
+        <v>-3.199786713584556</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.277053360157282</v>
+        <v>1.304348688997375</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9842673905362118</v>
+        <v>1.036757133057405</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.175180233066673</v>
+        <v>3.206674078579389</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.813222820957628</v>
       </c>
       <c r="C1992" t="n">
         <v>2.704732707962763</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.193242774659776</v>
+        <v>-3.125004452559544</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.427079173785105</v>
+        <v>1.454374502625198</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.059049651561224</v>
+        <v>1.111539394082418</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.340162498899498</v>
+        <v>3.371656344412214</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>2.696440683976622</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.167158690395968</v>
+        <v>-3.098920368295736</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.429220783504487</v>
+        <v>1.45651611234458</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.059049651561224</v>
+        <v>1.111539394082418</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.331870474913357</v>
+        <v>3.363364320426073</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
         <v>2.694633879560401</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.079280777286847</v>
+        <v>-3.011042455186615</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.462565144331915</v>
+        <v>1.489860473172007</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.174975293984576</v>
+        <v>1.227465036505769</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.399619055951147</v>
+        <v>3.431112901463863</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959858</v>
       </c>
       <c r="C1995" t="n">
         <v>2.712188285287193</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.070388315893564</v>
+        <v>-3.002149993793332</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.483676534616019</v>
+        <v>1.510971863456112</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.174975293984576</v>
+        <v>1.227465036505769</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.417173461677939</v>
+        <v>3.448667307190654</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
         <v>2.704043332691777</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.238864432863442</v>
+        <v>-3.17062611076321</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.408141135232652</v>
+        <v>1.435436464072745</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.147027458267995</v>
+        <v>1.199517200789188</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.392259807652574</v>
+        <v>3.42375365316529</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>2.685313029879639</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.792608240234002</v>
+        <v>-2.72436991813377</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.56791330947229</v>
+        <v>1.595208638312383</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.052308788598362</v>
+        <v>1.104798531119555</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.316698303038656</v>
+        <v>3.348192148551372</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>2.675977052376543</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.76988713655085</v>
+        <v>-2.701648814450618</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.567665773442456</v>
+        <v>1.594961102282548</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.052308788598362</v>
+        <v>1.104798531119555</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.307362325535561</v>
+        <v>3.338856171048277</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777674</v>
       </c>
       <c r="C1999" t="n">
         <v>2.834883178227712</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.899088949844892</v>
+        <v>-2.83085062774466</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.674891173976008</v>
+        <v>1.7021865028161</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.92310697530432</v>
+        <v>0.9755967178255132</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.388747363410304</v>
+        <v>3.42024120892302</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>2.871961000721359</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.924963348318918</v>
+        <v>-2.856725026218686</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.701619237080044</v>
+        <v>1.728914565920136</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9680185840160611</v>
+        <v>1.020508326537254</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.452772151130996</v>
+        <v>3.484265996643711</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>2.868636356710904</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.917908658103744</v>
+        <v>-2.849670336003512</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.701116469155658</v>
+        <v>1.728411797995751</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9750732742312349</v>
+        <v>1.027563016752428</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.453680321249645</v>
+        <v>3.485174166762361</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>2.878642510355645</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.890957433777256</v>
+        <v>-2.822719111677024</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.721903112530995</v>
+        <v>1.749198441371088</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9899536202589541</v>
+        <v>1.042443362780147</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.472614682511018</v>
+        <v>3.504108528023734</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784109</v>
       </c>
       <c r="C2003" t="n">
         <v>3.062745642500605</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.912501661608043</v>
+        <v>-2.844263339507811</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.89738855354364</v>
+        <v>1.924683882383733</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9899536202589541</v>
+        <v>1.042443362780147</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.656717814655978</v>
+        <v>3.688211660168694</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.054862337403598</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.934909779412915</v>
+        <v>-2.866671457312683</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.880542001324684</v>
+        <v>1.907837330164777</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9899536202589541</v>
+        <v>1.042443362780147</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.648834509558971</v>
+        <v>3.680328355071687</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155035</v>
       </c>
       <c r="C2005" t="n">
         <v>3.056916336953236</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.963134014990516</v>
+        <v>-2.894895692890284</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.871306306643282</v>
+        <v>1.898601635483374</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.007930372710263</v>
+        <v>1.060420115231456</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.661674560579394</v>
+        <v>3.693168406092109</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161981</v>
       </c>
       <c r="C2006" t="n">
         <v>3.113170054675083</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.972574940879046</v>
+        <v>-2.904336618778814</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.923783654009717</v>
+        <v>1.951078982849809</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.130357490253654</v>
+        <v>1.182847232774847</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.791384548827275</v>
+        <v>3.822878394339992</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321636</v>
+        <v>3.714941193321639</v>
       </c>
       <c r="C2007" t="n">
         <v>3.116061149220384</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.178813878667479</v>
+        <v>-3.110575556567247</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.844179173439644</v>
+        <v>1.871474502279737</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9241185524652205</v>
+        <v>0.9766082949864137</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.670532280699516</v>
+        <v>3.702026126212232</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347706</v>
+        <v>3.727898186347709</v>
       </c>
       <c r="C2008" t="n">
         <v>3.114172962114159</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.255143856268385</v>
+        <v>-3.186905534168153</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.811758995293057</v>
+        <v>1.83905432413315</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9241185524652205</v>
+        <v>0.9766082949864137</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.668644093593291</v>
+        <v>3.700137939106007</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887752</v>
+        <v>3.710654104887755</v>
       </c>
       <c r="C2009" t="n">
         <v>3.108993191717021</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.410100641668514</v>
+        <v>-3.341862319568282</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.744596510735868</v>
+        <v>1.77189183957596</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7691617670650912</v>
+        <v>0.8216515095862844</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.570490251956076</v>
+        <v>3.601984097468792</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.712897612343073</v>
       </c>
       <c r="C2010" t="n">
         <v>3.107427201927174</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.571669067195769</v>
+        <v>-3.503430745095538</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.678403150735118</v>
+        <v>1.705698479575211</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6423788432672118</v>
+        <v>0.694868585788405</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.492854507887501</v>
+        <v>3.524348353400217</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389352</v>
+        <v>3.754596135389356</v>
       </c>
       <c r="C2011" t="n">
         <v>3.120500608793092</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.679969729065889</v>
+        <v>-3.611731406965657</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.648156292852989</v>
+        <v>1.675451621693081</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6423788432672118</v>
+        <v>0.694868585788405</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.505927914753419</v>
+        <v>3.537421760266136</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378388</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.112505805576032</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.839520801829406</v>
+        <v>-3.771282479729174</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.576341060530522</v>
+        <v>1.603636389370615</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4901011764054604</v>
+        <v>0.5425909189266536</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.406566511419308</v>
+        <v>3.438060356932024</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.111029846703034</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.867421588938879</v>
+        <v>-3.799183266838647</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.563704786813735</v>
+        <v>1.591000115653827</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4555042522625256</v>
+        <v>0.5079939947837188</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.38433239806055</v>
+        <v>3.415826243573266</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.107794290680233</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.989947691641773</v>
+        <v>-3.921709369541541</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.511458789709776</v>
+        <v>1.538754118549869</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3329781495596317</v>
+        <v>0.3854678920808249</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.307581180416012</v>
+        <v>3.339075025928728</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.174500250270737</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.220462187827361</v>
+        <v>-4.152223865727129</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.485958950826044</v>
+        <v>1.513254279666137</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.102463653374043</v>
+        <v>0.1549533958952362</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.235978442295163</v>
+        <v>3.267472287807879</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814668</v>
       </c>
       <c r="C2016" t="n">
         <v>3.314811969272584</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.569207273051805</v>
+        <v>-4.500968950951573</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.486772635738114</v>
+        <v>1.514067964578206</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.04620544197633836</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.311041388945671</v>
+        <v>3.342535234458387</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237097</v>
       </c>
       <c r="C2017" t="n">
         <v>3.383792238418224</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.723193690827945</v>
+        <v>-4.654955368727713</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.494158337773297</v>
+        <v>1.52145366661339</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.04620544197633836</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.380021658091311</v>
+        <v>3.411515503604027</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.61992301642339</v>
       </c>
       <c r="C2018" t="n">
         <v>3.369843440538344</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.927793125690954</v>
+        <v>-4.859554803590722</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.398369765948215</v>
+        <v>1.425665094788308</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.04620544197633836</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.366072860211432</v>
+        <v>3.397566705724147</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609755</v>
       </c>
       <c r="C2019" t="n">
         <v>3.381713929593758</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.180268279698678</v>
+        <v>-5.112029957598446</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.309250193400539</v>
+        <v>1.336545522240632</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.04620544197633836</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.377943349266846</v>
+        <v>3.409437194779561</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.382924464112702</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.47316403617809</v>
+        <v>-5.404925714077859</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.193302425327718</v>
+        <v>1.220597754167811</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.04620544197633836</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.37915388378579</v>
+        <v>3.410647729298505</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251948</v>
       </c>
       <c r="C2021" t="n">
         <v>3.387046206340024</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.659828164312898</v>
+        <v>-5.591589842212667</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.122758516301116</v>
+        <v>1.150053845141209</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.03302327136941474</v>
+        <v>0.01946647115177846</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.367232243518375</v>
+        <v>3.398726089031091</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916203</v>
       </c>
       <c r="C2022" t="n">
         <v>3.382124059076213</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.805848851226861</v>
+        <v>-5.737610529126629</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.059428094271721</v>
+        <v>1.086723423111813</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.04210636316327171</v>
+        <v>0.0103833793579215</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.35686024117825</v>
+        <v>3.388354086690966</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.66796230683033</v>
       </c>
       <c r="C2023" t="n">
         <v>3.544328115775257</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.897562860336446</v>
+        <v>-5.829324538236214</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.18494654732693</v>
+        <v>1.212241876167024</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.04210636316327171</v>
+        <v>0.0103833793579215</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.519064297877294</v>
+        <v>3.55055814339001</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071554</v>
       </c>
       <c r="C2024" t="n">
         <v>3.539174753739071</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.929214519396416</v>
+        <v>-5.841926914261958</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.167132521666757</v>
+        <v>1.20204756372054</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.04727482040771191</v>
+        <v>-0.01499407952921528</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.510809861494444</v>
+        <v>3.530178306021542</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868148</v>
+        <v>3.750044015868152</v>
       </c>
       <c r="C2025" t="n">
         <v>3.549404171307562</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.998280573969352</v>
+        <v>-5.910992968834894</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.149735517406073</v>
+        <v>1.184650559459857</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1096456979013219</v>
+        <v>-0.07736495702282531</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.483616752566769</v>
+        <v>3.502985197093867</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332694</v>
+        <v>3.783632867332699</v>
       </c>
       <c r="C2026" t="n">
         <v>3.558329809763465</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.10025669621776</v>
+        <v>-6.012969091083302</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.117870706962613</v>
+        <v>1.152785749016396</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2116218201497295</v>
+        <v>-0.1793410792712329</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.431356717673627</v>
+        <v>3.450725162200725</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231811</v>
+        <v>3.798296784231816</v>
       </c>
       <c r="C2027" t="n">
         <v>3.55048269700764</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.990250412740538</v>
+        <v>-5.90296280760608</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.154026107597677</v>
+        <v>1.18894114965146</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1884172482324543</v>
+        <v>-0.1561365073539577</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.437432348068168</v>
+        <v>3.456800792595266</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818523</v>
       </c>
       <c r="C2028" t="n">
         <v>3.554732707729614</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.002780117852417</v>
+        <v>-5.915492512717959</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.1532642362749</v>
+        <v>1.188179278328683</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2022437476989773</v>
+        <v>-0.1699630068204807</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.433386459110229</v>
+        <v>3.452754903637326</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051784</v>
+        <v>3.77723741205179</v>
       </c>
       <c r="C2029" t="n">
         <v>3.56199359061215</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.70133339238058</v>
+        <v>-5.614045787246122</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.281103809346171</v>
+        <v>1.316018851399954</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.09920297777285991</v>
+        <v>0.1314837186513566</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.621515377275867</v>
+        <v>3.640883821802964</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679627</v>
       </c>
       <c r="C2030" t="n">
         <v>3.562964768364861</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.725923636615764</v>
+        <v>-5.638636031481306</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.272238889404808</v>
+        <v>1.307153931458591</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.09920297777285991</v>
+        <v>0.1314837186513566</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.622486555028577</v>
+        <v>3.641854999555675</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474156</v>
+        <v>3.821184182474162</v>
       </c>
       <c r="C2031" t="n">
         <v>3.563807672744617</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.674885260609243</v>
+        <v>-5.587597655474785</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.293497144187171</v>
+        <v>1.328412186240954</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.09920297777285991</v>
+        <v>0.1314837186513566</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.623329459408333</v>
+        <v>3.642697903935431</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969546</v>
       </c>
       <c r="C2032" t="n">
         <v>3.582845771618762</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.646036583785783</v>
+        <v>-5.558748978651325</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.324074713790701</v>
+        <v>1.358989755844484</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1280516545963202</v>
+        <v>0.1603323954748168</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.659676764376554</v>
+        <v>3.679045208903652</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700482</v>
       </c>
       <c r="C2033" t="n">
         <v>3.399029767742697</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.549401671767143</v>
+        <v>-5.462114066632685</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.178912674722091</v>
+        <v>1.213827716775875</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2246865666149601</v>
+        <v>0.2569673074934568</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.533841707711673</v>
+        <v>3.553210152238771</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80468896107764</v>
+        <v>3.804688961077646</v>
       </c>
       <c r="C2034" t="n">
         <v>3.402531811816661</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.480363660818675</v>
+        <v>-5.393076055684217</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.210029923175443</v>
+        <v>1.244944965229226</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2937245775634282</v>
+        <v>0.3260053184419248</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.578766558354718</v>
+        <v>3.598135002881816</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.77502886083346</v>
+        <v>3.775028860833466</v>
       </c>
       <c r="C2035" t="n">
         <v>3.386958630892743</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.461576560449736</v>
+        <v>-5.374288955315278</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.201971582399101</v>
+        <v>1.236886624452884</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3125116779323667</v>
+        <v>0.3447924188108633</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.574465637652164</v>
+        <v>3.593834082179261</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.82103066007763</v>
       </c>
       <c r="C2036" t="n">
         <v>3.386146341329173</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.384477958907864</v>
+        <v>-5.297190353773406</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.23199873345228</v>
+        <v>1.266913775506063</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3125116779323667</v>
+        <v>0.3447924188108633</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.573653348088593</v>
+        <v>3.593021792615691</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147912</v>
       </c>
       <c r="C2037" t="n">
         <v>3.396015120454245</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.394863153797753</v>
+        <v>-5.307575548663295</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.237713434621396</v>
+        <v>1.272628476675179</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3021264830424774</v>
+        <v>0.334407223920974</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.577291010279732</v>
+        <v>3.59665945480683</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735283</v>
+        <v>3.834415493735288</v>
       </c>
       <c r="C2038" t="n">
         <v>3.466852126230671</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.413451312519978</v>
+        <v>-5.32616370738552</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.301115176908931</v>
+        <v>1.336030218962715</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.283538324320252</v>
+        <v>0.3158190651987486</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.636975120822822</v>
+        <v>3.65634356534992</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496557</v>
       </c>
       <c r="C2039" t="n">
         <v>3.463721137048969</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.413749859216014</v>
+        <v>-5.326462254081556</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.297864769048815</v>
+        <v>1.332779811102599</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2832397776242161</v>
+        <v>0.3155205185027127</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.633665003623499</v>
+        <v>3.653033448150597</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108858</v>
+        <v>3.815643212108863</v>
       </c>
       <c r="C2040" t="n">
         <v>3.468252031988361</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.312926725525586</v>
+        <v>-5.225639120391128</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.342724917464378</v>
+        <v>1.377639959518161</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2957039931085699</v>
+        <v>0.3279847339870666</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.645674427853503</v>
+        <v>3.665042872380601</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121469</v>
+        <v>3.807356168121474</v>
       </c>
       <c r="C2041" t="n">
         <v>3.468381285466904</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.122145364773178</v>
+        <v>-5.034857759638721</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.419166715243884</v>
+        <v>1.454081757297668</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4864853538609773</v>
+        <v>0.5187660947394739</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.76027249778349</v>
+        <v>3.779640942310588</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906082</v>
+        <v>3.775233033906088</v>
       </c>
       <c r="C2042" t="n">
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.015182006923757</v>
+        <v>-4.927894401789299</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.44178890412125</v>
+        <v>1.476703946175033</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5449499618207787</v>
+        <v>0.5772307026992753</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.775188108296968</v>
+        <v>3.794556552824066</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912987</v>
+        <v>3.785761685912992</v>
       </c>
       <c r="C2043" t="n">
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.959851419021994</v>
+        <v>-4.872563813887536</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.498888075894013</v>
+        <v>1.533803117947796</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6002805497225409</v>
+        <v>0.6325612906010375</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.843353397650084</v>
+        <v>3.862721842177181</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539896</v>
+        <v>3.743767956539902</v>
       </c>
       <c r="C2044" t="n">
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.947797292109032</v>
+        <v>-4.860509686974574</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.497396294560636</v>
+        <v>1.532311336614419</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6123346766355037</v>
+        <v>0.6446154175140003</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.844272441699299</v>
+        <v>3.863640886226397</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811012</v>
+        <v>3.725010844811017</v>
       </c>
       <c r="C2045" t="n">
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.025152782237001</v>
+        <v>-4.937865177102543</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.468334728693584</v>
+        <v>1.503249770747367</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5349791865075343</v>
+        <v>0.5672599273860309</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.799739777806653</v>
+        <v>3.819108222333751</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382922</v>
+        <v>3.612322444382928</v>
       </c>
       <c r="C2046" t="n">
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.957104219545471</v>
+        <v>-4.869816614411013</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.508405179648078</v>
+        <v>1.543320221701862</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6353084900775607</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.853419941299454</v>
+        <v>3.872788385826551</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.64525678001343</v>
+        <v>3.645256780013435</v>
       </c>
       <c r="C2047" t="n">
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.188704612714972</v>
+        <v>-5.101417007580514</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.435967692553872</v>
+        <v>1.470882734607656</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6353084900775607</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.873622611473048</v>
+        <v>3.892991056000146</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498966</v>
+        <v>3.666747201498972</v>
       </c>
       <c r="C2048" t="n">
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.238756158244191</v>
+        <v>-5.151468553109734</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.399553310409066</v>
+        <v>1.43446835246285</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6353084900775607</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.85722884753993</v>
+        <v>3.876597292067028</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800096</v>
+        <v>3.670048702800101</v>
       </c>
       <c r="C2049" t="n">
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.413862990820636</v>
+        <v>-5.326575385686178</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.289762490971955</v>
+        <v>1.324677533025739</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6353084900775607</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.817480761133397</v>
+        <v>3.836849205660494</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660848</v>
+        <v>3.745573148660854</v>
       </c>
       <c r="C2050" t="n">
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.217762837390113</v>
+        <v>-5.130475232255655</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.375225171341104</v>
+        <v>1.410140213394888</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.799127902629587</v>
+        <v>0.8314086435080836</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.94216347218865</v>
+        <v>3.961531916715748</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395085</v>
+        <v>3.73057047339509</v>
       </c>
       <c r="C2051" t="n">
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.064737445276829</v>
+        <v>-4.977449840142371</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.535606327759323</v>
+        <v>1.570521369813106</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9521532947428711</v>
+        <v>0.9844340356213678</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.133149707029525</v>
+        <v>4.152518151556623</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791147</v>
+        <v>3.741278332791152</v>
       </c>
       <c r="C2052" t="n">
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.093044759150099</v>
+        <v>-5.005757154015641</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.711749627118307</v>
+        <v>1.74666466917209</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9521532947428711</v>
+        <v>0.9844340356213678</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.320615931937818</v>
+        <v>4.339984376464916</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620433</v>
+        <v>3.699115615620438</v>
       </c>
       <c r="C2053" t="n">
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.259637984263621</v>
+        <v>-5.172350379129163</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.614515288426981</v>
+        <v>1.649430330480764</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.8178408105078454</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.190062948223787</v>
+        <v>4.209431392750885</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285651</v>
       </c>
       <c r="C2054" t="n">
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.236602190902055</v>
+        <v>-5.149314585767597</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.627406008433325</v>
+        <v>1.662321050487108</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.8178408105078454</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.193739350885505</v>
+        <v>4.213107795412602</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.740581401399472</v>
       </c>
       <c r="C2055" t="n">
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.207356210446359</v>
+        <v>-5.120068605311901</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.636722455739099</v>
+        <v>1.671637497792882</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.8178408105078454</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.191357406009</v>
+        <v>4.210725850536098</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256376</v>
       </c>
       <c r="C2056" t="n">
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.31428175832421</v>
+        <v>-5.226994153189752</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.591245475745593</v>
+        <v>1.626160517799377</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6786345217514974</v>
+        <v>0.710915262629994</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.124495316439925</v>
+        <v>4.143863760967022</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701001</v>
+        <v>3.689942600701006</v>
       </c>
       <c r="C2057" t="n">
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.459300316831459</v>
+        <v>-5.372012711697001</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.534666854485928</v>
+        <v>1.569581896539711</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5336159632442489</v>
+        <v>0.5658967041227455</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.038912983478809</v>
+        <v>4.058281428005907</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.711852429687018</v>
       </c>
       <c r="C2058" t="n">
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.577642082616176</v>
+        <v>-5.490354477481718</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.587261387429794</v>
+        <v>1.622176429483577</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5765827426856356</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.145255845874297</v>
+        <v>4.164624290401394</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790804</v>
+        <v>3.71487905179081</v>
       </c>
       <c r="C2059" t="n">
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.629052504936884</v>
+        <v>-5.541764899802426</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.56448291562745</v>
+        <v>1.599397957681233</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5765827426856356</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.143041543000235</v>
+        <v>4.162409987527333</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437333</v>
+        <v>3.704757949437338</v>
       </c>
       <c r="C2060" t="n">
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.708471956144636</v>
+        <v>-5.621184351010178</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.532618263218639</v>
+        <v>1.567533305272422</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5765827426856356</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.142944671074525</v>
+        <v>4.162313115601623</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298401</v>
+        <v>3.736804952298407</v>
       </c>
       <c r="C2061" t="n">
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.803934954061853</v>
+        <v>-5.716647348927395</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.494426957609794</v>
+        <v>1.529341999663578</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5765827426856356</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.142938564632567</v>
+        <v>4.162307009159665</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218003</v>
+        <v>3.715372960218009</v>
       </c>
       <c r="C2062" t="n">
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.739559043211139</v>
+        <v>-5.652271438076681</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.518273718512691</v>
+        <v>1.553188760566474</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6086779126578541</v>
+        <v>0.6409586535363507</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.179660507705607</v>
+        <v>4.199028952232705</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353539</v>
+        <v>3.736089413353544</v>
       </c>
       <c r="C2063" t="n">
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.794928205343332</v>
+        <v>-5.707640600208874</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.50185987140754</v>
+        <v>1.536774913461323</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6086779126578541</v>
+        <v>0.6409586535363507</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.185394325453334</v>
+        <v>4.204762769980432</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113282</v>
+        <v>3.736822870113287</v>
       </c>
       <c r="C2064" t="n">
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.813146672340941</v>
+        <v>-5.725859067206483</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.494110847951429</v>
+        <v>1.529025890005212</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6158522162805086</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.169868826442761</v>
+        <v>4.189237270969858</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.79027250011369</v>
+        <v>3.790272500113695</v>
       </c>
       <c r="C2065" t="n">
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.77446323699701</v>
+        <v>-5.687175631862552</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.52945861493932</v>
+        <v>1.564373656993103</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6158522162805086</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.18974321929308</v>
+        <v>4.209111663820178</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016435</v>
+        <v>3.794486844016441</v>
       </c>
       <c r="C2066" t="n">
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.668428241791701</v>
+        <v>-5.581140636657243</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.555573313546172</v>
+        <v>1.590488355599955</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6158522162805086</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.173443919817807</v>
+        <v>4.192812364344905</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307667</v>
+        <v>3.794705093307672</v>
       </c>
       <c r="C2067" t="n">
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.485216578658606</v>
+        <v>-5.397928973524148</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.631288928263456</v>
+        <v>1.666203970317239</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6158522162805086</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.175874869281854</v>
+        <v>4.195243313808952</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863548</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.413495131644755</v>
+        <v>-5.326207526510297</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.642921913148373</v>
+        <v>1.677836955202157</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6552929224158626</v>
+        <v>0.6875736632943592</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.201852143569541</v>
+        <v>4.221220588096639</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394109</v>
+        <v>3.723789705394115</v>
       </c>
       <c r="C2069" t="n">
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.391122106037049</v>
+        <v>-5.303834500902591</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.598786869312627</v>
+        <v>1.633701911366411</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6665486735287641</v>
+        <v>0.6988294144072608</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.155521340158454</v>
+        <v>4.174889784685551</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456728</v>
+        <v>3.715607446456733</v>
       </c>
       <c r="C2070" t="n">
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.424138401947793</v>
+        <v>-5.336850796813335</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.770778555833684</v>
+        <v>1.805693597887468</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5971112968620125</v>
+        <v>0.6293920377405091</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.299057119043757</v>
+        <v>4.318425563570855</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883678</v>
+        <v>3.713762536883683</v>
       </c>
       <c r="C2071" t="n">
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.412610766298185</v>
+        <v>-5.325323161163727</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.767310835921777</v>
+        <v>1.80222587797556</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6561119550633749</v>
+        <v>0.6883926959418716</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.326378739792824</v>
+        <v>4.345747184319922</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236299</v>
+        <v>3.717150699236305</v>
       </c>
       <c r="C2072" t="n">
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.509952267640553</v>
+        <v>-5.422664662506095</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.732042347906618</v>
+        <v>1.766957389960401</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6116917728978866</v>
+        <v>0.6439725137763832</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.303394743015319</v>
+        <v>4.322763187542417</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427686</v>
+        <v>3.705201079427692</v>
       </c>
       <c r="C2073" t="n">
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.59580829698052</v>
+        <v>-5.508520691846062</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.69895101836347</v>
+        <v>1.733866060417253</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5693157036717515</v>
+        <v>0.6015964445502482</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.279220183672477</v>
+        <v>4.298588628199575</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610378</v>
+        <v>3.691835499610383</v>
       </c>
       <c r="C2074" t="n">
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.604645094396639</v>
+        <v>-5.517357489262182</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.677835501217524</v>
+        <v>1.712750543271307</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5618735310304008</v>
+        <v>0.5941542719088975</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.257174081908168</v>
+        <v>4.276542526435266</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667456</v>
+        <v>3.715544411667461</v>
       </c>
       <c r="C2075" t="n">
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.696027656962098</v>
+        <v>-5.60874005182764</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.65144698723639</v>
+        <v>1.686362029290173</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5253086463110561</v>
+        <v>0.5575893871895528</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.245399662121611</v>
+        <v>4.264768106648709</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889193</v>
+        <v>3.673978374889198</v>
       </c>
       <c r="C2076" t="n">
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.684320938975092</v>
+        <v>-5.597033333840634</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.75825793225546</v>
+        <v>1.793172974309244</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5692961051765592</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.354551950738083</v>
+        <v>4.373920395265181</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409569</v>
+        <v>3.682476099409575</v>
       </c>
       <c r="C2077" t="n">
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.755233012717369</v>
+        <v>-5.667945407582911</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.732925441489954</v>
+        <v>1.767840483543738</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5692961051765592</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.357584289469488</v>
+        <v>4.376952733996585</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452568</v>
+        <v>3.672895177452574</v>
       </c>
       <c r="C2078" t="n">
         <v>4.248279904168708</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.765549110883721</v>
+        <v>-5.678261505749263</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.941703835501472</v>
+        <v>1.976618877555255</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5692961051765592</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.570489122747546</v>
+        <v>4.589857567274644</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762289</v>
+        <v>3.623960959762295</v>
       </c>
       <c r="C2079" t="n">
         <v>4.247458571080798</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.765455142866348</v>
+        <v>-5.67816753773189</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.94092008962051</v>
+        <v>1.975835131674294</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5696659665238771</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.569889706468026</v>
+        <v>4.589258150995124</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884082</v>
+        <v>3.800870306884088</v>
       </c>
       <c r="C2080" t="n">
         <v>4.241690557025152</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.909056306889734</v>
+        <v>-5.821768701755276</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.87771160995551</v>
+        <v>1.912626652009293</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5696659665238771</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.56412169241238</v>
+        <v>4.583490136939478</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129646</v>
+        <v>3.671015692129652</v>
       </c>
       <c r="C2081" t="n">
         <v>4.241690557025152</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.908107883771695</v>
+        <v>-5.820820278637237</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.878090979202725</v>
+        <v>1.913006021256509</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5696659665238771</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.56412169241238</v>
+        <v>4.583490136939478</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052349</v>
+        <v>3.904173816052355</v>
       </c>
       <c r="C2082" t="n">
         <v>4.254418165006244</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.008377701730716</v>
+        <v>-5.921090096596258</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.850710660000209</v>
+        <v>1.885625702053992</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5696659665238771</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.576849300393472</v>
+        <v>4.59621774492057</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813493</v>
+        <v>3.740179607813499</v>
       </c>
       <c r="C2083" t="n">
         <v>4.256364163430631</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.002385454941904</v>
+        <v>-5.915097849807446</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.855053557140122</v>
+        <v>1.889968599193905</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5696659665238771</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.57879529881786</v>
+        <v>4.598163743344958</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537942</v>
+        <v>3.765050796537947</v>
       </c>
       <c r="C2084" t="n">
         <v>4.2500182994484</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.913827493811136</v>
+        <v>-5.826539888676678</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.884130877610198</v>
+        <v>1.919045919663981</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5696659665238771</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.572449434835629</v>
+        <v>4.591817879362726</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771814</v>
+        <v>3.758409170771819</v>
       </c>
       <c r="C2085" t="n">
         <v>4.249326976887396</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.896068416308062</v>
+        <v>-5.808780811173604</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.890543186050423</v>
+        <v>1.925458228104206</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5696659665238771</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.571758112274624</v>
+        <v>4.591126556801722</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.80134059710972</v>
+        <v>3.801340597109725</v>
       </c>
       <c r="C2086" t="n">
         <v>4.262109162795983</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.796438265258995</v>
+        <v>-5.709150660124537</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.943177432378637</v>
+        <v>1.97809247443242</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.637015376694448</v>
+        <v>0.6692961175729446</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.644318388812652</v>
+        <v>4.663686833339749</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546843994</v>
+        <v>3.798465546844</v>
       </c>
       <c r="C2087" t="n">
         <v>4.451263428294709</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.845837773948006</v>
+        <v>-5.758550168813548</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.112571894401759</v>
+        <v>2.147486936455542</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6472742101261927</v>
+        <v>0.6795549510046893</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.839627954370425</v>
+        <v>4.858996398897522</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.772186508351858</v>
+        <v>3.772186508351863</v>
       </c>
       <c r="C2088" t="n">
         <v>4.438452101397571</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.63915330030563</v>
+        <v>-5.551865695171172</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.182434356961571</v>
+        <v>2.217349399015355</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8539586837685683</v>
+        <v>0.886239424647065</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.950827311658712</v>
+        <v>4.97019575618581</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.76339283855127</v>
+        <v>3.763392838551273</v>
       </c>
       <c r="C2089" t="n">
         <v>4.440453615051676</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.60535229650209</v>
+        <v>-5.586022590168698</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.197956272137092</v>
+        <v>2.205688154670449</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.8323384425147884</v>
+        <v>0.8026556551062525</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.939856680560549</v>
+        <v>4.922047008115428</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041109</v>
+        <v>3.805590565041115</v>
       </c>
       <c r="C2090" t="n">
         <v>4.793950729041343</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.512762817440634</v>
+        <v>-5.493433111107241</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.588489177751342</v>
+        <v>2.596221060284699</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.8323384425147884</v>
+        <v>0.8026556551062525</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.293353794550216</v>
+        <v>5.275544122105095</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497401</v>
+        <v>3.832164354497406</v>
       </c>
       <c r="C2091" t="n">
         <v>4.798513840608447</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.585923421213779</v>
+        <v>-5.566593714880386</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.563788047809187</v>
+        <v>2.571519930342544</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.8043172424805454</v>
+        <v>0.7746344550720095</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.281104186096774</v>
+        <v>5.263294513651653</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492294</v>
+        <v>3.858310890492299</v>
       </c>
       <c r="C2092" t="n">
         <v>4.848343781931974</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.533707111417437</v>
+        <v>-5.514377405084044</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.634504513051251</v>
+        <v>2.642236395584609</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.8043172424805454</v>
+        <v>0.7746344550720095</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.330934127420302</v>
+        <v>5.313124454975179</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436475</v>
+        <v>3.84493559643648</v>
       </c>
       <c r="C2093" t="n">
         <v>4.857157752141985</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.501809594332191</v>
+        <v>-5.482479887998799</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.656077490095361</v>
+        <v>2.663809372628718</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.8362147595657912</v>
+        <v>0.8065319721572553</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.35888660788146</v>
+        <v>5.341076935436338</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039485</v>
+        <v>3.84837686603949</v>
       </c>
       <c r="C2094" t="n">
         <v>4.852795336181182</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.516564918532332</v>
+        <v>-5.497235212198939</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.645812944454501</v>
+        <v>2.653544826987858</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.8362147595657912</v>
+        <v>0.8065319721572553</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.354524191920657</v>
+        <v>5.336714519475535</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524479</v>
+        <v>3.868153115524485</v>
       </c>
       <c r="C2095" t="n">
         <v>4.843719839597462</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.46710029516242</v>
+        <v>-5.447770588829028</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.656523297218746</v>
+        <v>2.664255179752103</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8856793829357028</v>
+        <v>0.8559965955271669</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.375127469358884</v>
+        <v>5.357317796913762</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867954</v>
+        <v>3.849040239867959</v>
       </c>
       <c r="C2096" t="n">
         <v>4.840127507312396</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.303992303008805</v>
+        <v>-5.284662596675412</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.718174161795126</v>
+        <v>2.725906044328484</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.048787375089318</v>
+        <v>1.019104587680782</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.469399932365987</v>
+        <v>5.451590259920866</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.87020492823297</v>
+        <v>3.870204928232975</v>
       </c>
       <c r="C2097" t="n">
         <v>4.849174544003525</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.283349212207577</v>
+        <v>-5.264019505874185</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.735478434806746</v>
+        <v>2.743210317340103</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.048787375089318</v>
+        <v>1.019104587680782</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.478446969057115</v>
+        <v>5.460637296611994</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179673</v>
+        <v>3.855534437179679</v>
       </c>
       <c r="C2098" t="n">
         <v>4.850032008989646</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.346057128682135</v>
+        <v>-5.326727422348743</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.711252733203044</v>
+        <v>2.718984615736401</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9860794586147604</v>
+        <v>0.9563966712062243</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.441679684158503</v>
+        <v>5.42387001171338</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967721</v>
+        <v>3.884687848967726</v>
       </c>
       <c r="C2099" t="n">
         <v>4.812941425779998</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.298049004838442</v>
+        <v>-5.27871929850505</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.693365399530873</v>
+        <v>2.70109728206423</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9860794586147604</v>
+        <v>0.9563966712062243</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.404589100948855</v>
+        <v>5.386779428503733</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018612</v>
+        <v>3.895362357018617</v>
       </c>
       <c r="C2100" t="n">
         <v>4.816873679337949</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.219223347654852</v>
+        <v>-5.199893641321459</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.72882791596226</v>
+        <v>2.736559798495617</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.064905115798351</v>
+        <v>1.035222328389815</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.455816748816959</v>
+        <v>5.438007076371838</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075135</v>
+        <v>3.89161098107514</v>
       </c>
       <c r="C2101" t="n">
         <v>4.811772771944986</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.108952144481885</v>
+        <v>-5.007958840067586</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.767835489838484</v>
+        <v>2.808232811604204</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.064905115798351</v>
+        <v>1.035222328389815</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.450715841423996</v>
+        <v>5.432906168978874</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435444</v>
+        <v>3.87243249343545</v>
       </c>
       <c r="C2102" t="n">
         <v>4.807126681334081</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.990778766463958</v>
+        <v>-4.889785462049659</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.81045875043475</v>
+        <v>2.850856072200469</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.183078493816278</v>
+        <v>1.153395706407742</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.516973777623848</v>
+        <v>5.499164105178727</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917733</v>
+        <v>3.859571723917738</v>
       </c>
       <c r="C2103" t="n">
         <v>4.836215274197108</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.877364083681226</v>
+        <v>-4.776370779266927</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.884913216410869</v>
+        <v>2.925310538176589</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.29649317659901</v>
+        <v>1.266810389190473</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.614111180156514</v>
+        <v>5.596301507711392</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.828006274013639</v>
+        <v>3.828006274013644</v>
       </c>
       <c r="C2104" t="n">
         <v>4.829775497208285</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.850315045987973</v>
+        <v>-4.749321741573674</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.889293054499348</v>
+        <v>2.929690376265067</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.323542214292263</v>
+        <v>1.293859426883727</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.623900825783643</v>
+        <v>5.606091153338522</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.82398744526377</v>
+        <v>3.823987445263775</v>
       </c>
       <c r="C2105" t="n">
         <v>4.829775497208285</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.856348326174743</v>
+        <v>-4.755355021760444</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.88687974242464</v>
+        <v>2.927277064190359</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.323542214292263</v>
+        <v>1.293859426883727</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.623900825783643</v>
+        <v>5.606091153338522</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.815657203170833</v>
+        <v>3.815657203170841</v>
       </c>
       <c r="C2106" t="n">
         <v>4.833413664350697</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.908200101747904</v>
+        <v>-4.807206797333605</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.869777199337788</v>
+        <v>2.910174521103507</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.271690438719102</v>
+        <v>1.242007651310566</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.596427927582159</v>
+        <v>5.578618255137037</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.634617831035486</v>
+        <v>3.781574640813158</v>
       </c>
       <c r="C2107" t="n">
-        <v>4.800017965830405</v>
+        <v>4.858939388032587</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.908200101747904</v>
+        <v>-4.807206797333605</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.869777199337788</v>
+        <v>2.910174521103507</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.271690438719102</v>
+        <v>1.242007651310566</v>
       </c>
       <c r="G2107" t="n">
-        <v>4.793081762816773</v>
+        <v>4.852003185018955</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241004.xlsx
+++ b/tame_output/ON/bt/strategyON_20241004.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.3%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>111.0%</t>
+          <t>110.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>174.3%</t>
+          <t>173.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-77.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-642.3%</t>
+          <t>-647.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-85.2%</t>
+          <t>-87.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-362.3%</t>
+          <t>-204.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-99.8%</t>
+          <t>-103.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.7%</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341311</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.123567156606317</v>
+        <v>-8.176056899127509</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1178699481412422</v>
+        <v>-0.1388658451497196</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9525781927646679</v>
+        <v>-1.005067935285861</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.560366423156232</v>
+        <v>2.528872577643516</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.177638656114675</v>
+        <v>-8.230128398635868</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1366049916230136</v>
+        <v>-0.1576008886314906</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.006649692273027</v>
+        <v>-1.059139434794221</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.530817079772788</v>
+        <v>2.499323234260073</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.181214442206423</v>
+        <v>-8.233704184727616</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1325221089410702</v>
+        <v>-0.1535180059495476</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.03217861418952</v>
+        <v>-1.084668356710713</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.521012923741536</v>
+        <v>2.489519078228819</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.214867280714897</v>
+        <v>-8.267357023236089</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1415006898600235</v>
+        <v>-0.1624965868685009</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.132591982106557</v>
+        <v>-1.185081724627751</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.465247457475749</v>
+        <v>2.433753611963033</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.353953395333754</v>
+        <v>-8.406443137854946</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1817634342141456</v>
+        <v>-0.2027593312226226</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.271678096725414</v>
+        <v>-1.324167839246607</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.397167490197856</v>
+        <v>2.36567364468514</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.529077812720297</v>
+        <v>-8.58156755524149</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.237257980421246</v>
+        <v>-0.2582538774297229</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.446802514111958</v>
+        <v>-1.499292256633151</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.306648060513447</v>
+        <v>2.275154215000731</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.763529906734787</v>
+        <v>-8.816019649255979</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3382579829286381</v>
+        <v>-0.359253879937115</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.446802514111958</v>
+        <v>-1.499292256633151</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.299428895611851</v>
+        <v>2.267935050099135</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.867904637761233</v>
+        <v>-8.920394380282426</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3866800661131928</v>
+        <v>-0.4076759631216698</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.551177245138403</v>
+        <v>-1.603666987659597</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.230131866222007</v>
+        <v>2.198638020709291</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.030418103459818</v>
+        <v>-9.08290784598101</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.45056966255407</v>
+        <v>-0.471565559562547</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.64881067555709</v>
+        <v>-1.701300418078284</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.172667597809351</v>
+        <v>2.141173752296635</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.156454896828107</v>
+        <v>-9.2089446393493</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.4982906512722711</v>
+        <v>-0.5192865482807481</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.623559052747348</v>
+        <v>-1.676048795268541</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.190512300124311</v>
+        <v>2.159018454611595</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.099383124932176</v>
+        <v>-9.151872867453369</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4714716068274978</v>
+        <v>-0.4924675038359752</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.623559052747348</v>
+        <v>-1.676048795268541</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.194502635810712</v>
+        <v>2.163008790297996</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.241054966656296</v>
+        <v>-9.293544709177489</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5296155704158876</v>
+        <v>-0.550611467424365</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.623559052747348</v>
+        <v>-1.676048795268541</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.19302740891197</v>
+        <v>2.161533563399254</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.191464122231462</v>
+        <v>-9.243953864752655</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.4947258224810818</v>
+        <v>-0.5157217194895587</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.573968208322514</v>
+        <v>-1.626457950843708</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.237835325731743</v>
+        <v>2.206341480219027</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.042545787759606</v>
+        <v>-9.095035530280798</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.448209622339022</v>
+        <v>-0.4692055193474993</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.542718617587341</v>
+        <v>-1.595208360108535</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.243533946526164</v>
+        <v>2.212040101013448</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.816700635040194</v>
+        <v>-8.869190377561386</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3482924882150487</v>
+        <v>-0.3692883852235256</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.500791942000177</v>
+        <v>-1.553281684521371</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.278269024914671</v>
+        <v>2.246775179401955</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.692121978702602</v>
+        <v>-8.744611721223794</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.2973218811239531</v>
+        <v>-0.31831777813243</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.500791942000177</v>
+        <v>-1.553281684521371</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.27940816947073</v>
+        <v>2.247914323958013</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.667085297134092</v>
+        <v>-8.719575039655284</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2846734343344415</v>
+        <v>-0.3056693313429184</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.475462854449441</v>
+        <v>-1.527952596970635</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.297239396163278</v>
+        <v>2.265745550650562</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.594952121846211</v>
+        <v>-8.647441864367403</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2500864599806523</v>
+        <v>-0.2710823569891296</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.475462854449441</v>
+        <v>-1.527952596970635</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.302973100401915</v>
+        <v>2.271479254889199</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.591748461420405</v>
+        <v>-8.644238203941597</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2585422582041952</v>
+        <v>-0.2795381552126726</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.472259194023635</v>
+        <v>-1.524748936544829</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.295158034263534</v>
+        <v>2.263664188750818</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.49828942743518</v>
+        <v>-8.550779169956373</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2310421259230133</v>
+        <v>-0.2520380229314902</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.472259194023635</v>
+        <v>-1.524748936544829</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.285274552950626</v>
+        <v>2.25378070743791</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.487636245881749</v>
+        <v>-8.540125988402941</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2286154138010144</v>
+        <v>-0.2496113108094913</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.472259194023635</v>
+        <v>-1.524748936544829</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.283439992451252</v>
+        <v>2.251946146938536</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.389729207205258</v>
+        <v>-8.442218949726451</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1897529133038787</v>
+        <v>-0.210748810312356</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.404273444163079</v>
+        <v>-1.456763186684273</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.323931127394125</v>
+        <v>2.292437281881409</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.3657756662293</v>
+        <v>-8.418265408750493</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1795029907680021</v>
+        <v>-0.2004988877764791</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.380319903187121</v>
+        <v>-1.432809645708315</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.338971758125194</v>
+        <v>2.307477912612478</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.101715727906504</v>
+        <v>-8.154205470427696</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.08713933160063547</v>
+        <v>-0.1081352286091124</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.116259964864325</v>
+        <v>-1.168749707385519</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.484147404957119</v>
+        <v>2.452653559444403</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.394636104401665</v>
+        <v>-7.447125846922858</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.192905484140999</v>
+        <v>0.171909587132522</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.116259964864325</v>
+        <v>-1.168749707385519</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.481360371296818</v>
+        <v>2.449866525784102</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.354451806035475</v>
+        <v>-7.406941548556667</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2093228273753165</v>
+        <v>0.1883269303668396</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.076075666498134</v>
+        <v>-1.128565409019328</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.505814574204374</v>
+        <v>2.474320728691658</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.191051935096112</v>
+        <v>-7.243541677617305</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2740495969718184</v>
+        <v>0.2530536999633415</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9126757955587717</v>
+        <v>-0.9651655380799653</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.603221317988749</v>
+        <v>2.571727472476033</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.032934555717337</v>
+        <v>-7.08542429823853</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3452209775611808</v>
+        <v>0.3242250805527038</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.7545584161799962</v>
+        <v>-0.8070481587011898</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.706016174453866</v>
+        <v>2.67452232894115</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.883268164709822</v>
+        <v>-6.935757907231014</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4021953236512279</v>
+        <v>0.381199426642751</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.6616549249374603</v>
+        <v>-0.7141446674586539</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.758866058886428</v>
+        <v>2.727372213373712</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.750992691078936</v>
+        <v>-6.803482433600128</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.356366299110737</v>
+        <v>0.3353704021022601</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5293794513065736</v>
+        <v>-0.5818691938277673</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.739492129072115</v>
+        <v>2.707998283559399</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.579131475514033</v>
+        <v>-6.631621218035225</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4279258460243347</v>
+        <v>0.4069299490158578</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3575182357416707</v>
+        <v>-0.4100079782628644</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.845423919098694</v>
+        <v>2.813930073585978</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.494166808784714</v>
+        <v>-6.546656551305906</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4748180539397211</v>
+        <v>0.4538221569312442</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2725535690123512</v>
+        <v>-0.3250433115335448</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.909309060359944</v>
+        <v>2.877815214847228</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.599756798557818</v>
+        <v>-6.652246541079011</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3046061284312609</v>
+        <v>0.2836102314227835</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3781435587854555</v>
+        <v>-0.4306333013066492</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.717979136896863</v>
+        <v>2.686485291384147</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.531522213932391</v>
+        <v>-6.584011956453583</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3804443041585182</v>
+        <v>0.3594484071500412</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3597282359129195</v>
+        <v>-0.4122179784341132</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.777572672497471</v>
+        <v>2.746078826984755</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.383582172524791</v>
+        <v>-6.436071915045984</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3229995120831508</v>
+        <v>0.3020036150746739</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.339407320004362</v>
+        <v>-0.3918970625255556</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.673144413404198</v>
+        <v>2.641650567891482</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.330612650270803</v>
+        <v>-6.383102392791995</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3354733347312679</v>
+        <v>0.314477437722791</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2864377977503731</v>
+        <v>-0.3389275402715667</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.696212140503114</v>
+        <v>2.664718294990398</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.164824454310512</v>
+        <v>-6.217314196831705</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3948280010202909</v>
+        <v>0.373832104011814</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2864377977503731</v>
+        <v>-0.3389275402715667</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.689251528408021</v>
+        <v>2.657757682895304</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.131461247831743</v>
+        <v>-6.183950990352936</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4226356379929417</v>
+        <v>0.4016397409844648</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2864377977503731</v>
+        <v>-0.3389275402715667</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.703713882789164</v>
+        <v>2.672220037276448</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.023202110709222</v>
+        <v>-6.075691853230414</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4604714133011454</v>
+        <v>0.4394755162926685</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2864377977503731</v>
+        <v>-0.3389275402715667</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.698246003248359</v>
+        <v>2.666752157735643</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.899910975892091</v>
+        <v>-5.952400718413283</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5072859612385745</v>
+        <v>0.4862900642300976</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1631466629332426</v>
+        <v>-0.2156364054544362</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.769718778149214</v>
+        <v>2.738224932636498</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.8472141087608</v>
+        <v>-5.899703851281992</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5360656863284166</v>
+        <v>0.5150697893199392</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1104497958019514</v>
+        <v>-0.1629395383231451</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.809037876665314</v>
+        <v>2.777544031152598</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.603448666777355</v>
+        <v>-5.655938409298548</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6293525714688446</v>
+        <v>0.6083566744603677</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1104497958019514</v>
+        <v>-0.1629395383231451</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.804818585012364</v>
+        <v>2.773324739499648</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.513672994400883</v>
+        <v>-5.566162736922076</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6673871543394498</v>
+        <v>0.6463912573309725</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.04885035088764139</v>
+        <v>-0.101340093408835</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.843902565880966</v>
+        <v>2.81240872036825</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.263822600451808</v>
+        <v>-5.316312342973001</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7600693869027815</v>
+        <v>0.7390734898943045</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.04885035088764139</v>
+        <v>-0.101340093408835</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.836644640864668</v>
+        <v>2.805150795351952</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.087930507984376</v>
+        <v>-5.140420250505569</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8340253474104031</v>
+        <v>0.8130294504019262</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.04885035088764139</v>
+        <v>-0.101340093408835</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.840243764385317</v>
+        <v>2.808749918872601</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.916484044961913</v>
+        <v>-4.968973787483105</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9159314386739423</v>
+        <v>0.8949355416654652</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1225961121348217</v>
+        <v>0.07010636961362809</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.956439148253349</v>
+        <v>2.924945302740633</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.836461757852792</v>
+        <v>-4.888951500373985</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9469608311338877</v>
+        <v>0.9259649341254106</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2026183992439427</v>
+        <v>0.1501286567227491</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.003472998135118</v>
+        <v>2.971979152622402</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.772826015618858</v>
+        <v>-4.82531575814005</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9771099290817786</v>
+        <v>0.9561140320733017</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2662541414778772</v>
+        <v>0.2137643989566836</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.046349244529796</v>
+        <v>3.01485539901708</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.679128697402462</v>
+        <v>-4.731618439923655</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9957831151521324</v>
+        <v>0.9747872181436554</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2662541414778772</v>
+        <v>0.2137643989566836</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.027543503313592</v>
+        <v>2.996049657800876</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.689631320467751</v>
+        <v>-4.742121062988944</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9933251425508942</v>
+        <v>0.9723292455424173</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2557515184125884</v>
+        <v>0.2032617758913947</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.022985006099296</v>
+        <v>2.99149116058658</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.577145059798877</v>
+        <v>-4.629634802320069</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.042248960653264</v>
+        <v>1.021253063644787</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2557515184125884</v>
+        <v>0.2032617758913947</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.026914319934116</v>
+        <v>2.9954204744214</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.559431372921011</v>
+        <v>-4.611921115442204</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.05001301932175</v>
+        <v>1.029017122313273</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2589328473095052</v>
+        <v>0.2064431047883115</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.029501701189606</v>
+        <v>2.99800785567689</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.435957101607993</v>
+        <v>-4.488446844129186</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.096400799066951</v>
+        <v>1.075404902058474</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2589328473095052</v>
+        <v>0.2064431047883115</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.0264997724096</v>
+        <v>2.995005926896884</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.378021269609778</v>
+        <v>-4.43051101213097</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.121154168876852</v>
+        <v>1.100158271868374</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2844947219922545</v>
+        <v>0.2320049794710608</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.043415934229863</v>
+        <v>3.011922088717147</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539951</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.229405000967461</v>
+        <v>-4.297643323067692</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.196494859135602</v>
+        <v>1.169199530295509</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2844947219922545</v>
+        <v>0.2320049794710608</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.059310117031687</v>
+        <v>3.02781627151897</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.109231917602962</v>
+        <v>-4.177470239703194</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.245709936921703</v>
+        <v>1.21841460808161</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4046678053567534</v>
+        <v>0.3521780628355597</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.132559811490688</v>
+        <v>3.101065965977972</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.973978556272985</v>
+        <v>-4.042216878373217</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.309899384015134</v>
+        <v>1.282604055175041</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5399211666867305</v>
+        <v>0.4874314241655369</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.223799930850114</v>
+        <v>3.192306085337398</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942105</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.033853383630677</v>
+        <v>-4.102091705730909</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.271986944473483</v>
+        <v>1.24469161563339</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4800463393290384</v>
+        <v>0.4275565968078447</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.173912525836925</v>
+        <v>3.142418680324209</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.91403315271984</v>
+        <v>-3.982271474820072</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.335204206072026</v>
+        <v>1.307908877231933</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4800463393290384</v>
+        <v>0.4275565968078447</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.189201695071133</v>
+        <v>3.157707849558417</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.916502859181646</v>
+        <v>-3.984741181281878</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.241860522809745</v>
+        <v>1.214565193969652</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4775766328672322</v>
+        <v>0.4250868903460386</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.095364070516491</v>
+        <v>3.063870225003775</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.984873045505656</v>
+        <v>-4.053111367605887</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.133774309765443</v>
+        <v>1.10647898092535</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4868523319034472</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.020191351423521</v>
+        <v>2.988697505910805</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.096745325131806</v>
+        <v>-4.164983647232038</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.079462106546874</v>
+        <v>1.052166777706781</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4868523319034472</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.010628060055413</v>
+        <v>2.979134214542697</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.080770659645538</v>
+        <v>-4.14900898174577</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.052426497665408</v>
+        <v>1.025131168825316</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4868523319034472</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.97720258497944</v>
+        <v>2.945708739466724</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460425262059</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.084865206316536</v>
+        <v>-4.153103528416768</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.055355910988797</v>
+        <v>1.028060582148704</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4868523319034472</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.981769816971228</v>
+        <v>2.950275971458512</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.076940831731622</v>
+        <v>-4.145179153831854</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.03426768958397</v>
+        <v>1.006972360743877</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4868523319034472</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.957511845732435</v>
+        <v>2.926018000219719</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.070662629161773</v>
+        <v>-4.138900951262005</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.965317284013359</v>
+        <v>0.9380219551732663</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4931305344732962</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.889817080675794</v>
+        <v>2.858323235163078</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264165</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.01081000995805</v>
+        <v>-4.079048332058282</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9994307181269808</v>
+        <v>0.972135389286888</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4931305344732962</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.899989467107926</v>
+        <v>2.86849562159521</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.924566546931672</v>
+        <v>-3.992804869031904</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.028874373911392</v>
+        <v>1.001579045071299</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4931305344732962</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.894935737681787</v>
+        <v>2.863441892169071</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.969873366330652</v>
+        <v>-4.038111688430884</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.002527421596326</v>
+        <v>0.975232092756233</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4523203714640655</v>
+        <v>0.3998306289428718</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.862225415320774</v>
+        <v>2.830731569808058</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.998906471032953</v>
+        <v>-4.067144793133185</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9914660527485066</v>
+        <v>0.9641707239084141</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4523203714640655</v>
+        <v>0.3998306289428718</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.862777288353875</v>
+        <v>2.831283442841159</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.906095989582094</v>
+        <v>-3.974334311682326</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9578629372202161</v>
+        <v>0.9305676083801235</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5451308529149248</v>
+        <v>0.4926411103937312</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.847736269115757</v>
+        <v>2.816242423603041</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.950485458911522</v>
+        <v>-4.018723781011754</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9419806254130458</v>
+        <v>0.9146852965729531</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5007413835854971</v>
+        <v>0.4482516410643035</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.822976063442701</v>
+        <v>2.791482217929985</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.929981765026024</v>
+        <v>-3.998220087126256</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9452578114789678</v>
+        <v>0.917962482638875</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5212450774709945</v>
+        <v>0.4687553349498008</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.830353988285722</v>
+        <v>2.798860142773006</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.013653861738357</v>
+        <v>-4.081892183838589</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9172802686247019</v>
+        <v>0.8899849397846094</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5212450774709945</v>
+        <v>0.4687553349498008</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.835845284116389</v>
+        <v>2.804351438603673</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.041434259639709</v>
+        <v>-4.109672581739941</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9176653112327</v>
+        <v>0.8903699823926072</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4934646795696414</v>
+        <v>0.4409749370484478</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.830674247144117</v>
+        <v>2.799180401631401</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.159814932369848</v>
+        <v>-4.22805325447008</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7086687621412979</v>
+        <v>0.6813734333012051</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4262468274186652</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.628699255854184</v>
+        <v>2.597205410341468</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.268429010813179</v>
+        <v>-4.336667332913411</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7853727914831712</v>
+        <v>0.7580774626430784</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4262468274186652</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.74884891657339</v>
+        <v>2.717355071060674</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.233019972565036</v>
+        <v>-4.301258294665268</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8140494328847512</v>
+        <v>0.7867541040446584</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4262468274186652</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.763361942675713</v>
+        <v>2.731868097162997</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.241481141220497</v>
+        <v>-4.309719463320729</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8080844067649355</v>
+        <v>0.780789077924843</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4177856587632041</v>
+        <v>0.3652959162420105</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.755704682824805</v>
+        <v>2.724210837312089</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.064364811185331</v>
+        <v>-4.132603133285563</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8756599676243044</v>
+        <v>0.8483646387842116</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4177856587632041</v>
+        <v>0.3652959162420105</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.752433711670107</v>
+        <v>2.720939866157391</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.109457056018877</v>
+        <v>-4.177695378119108</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8583064614527993</v>
+        <v>0.8310111326127065</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3558896155938143</v>
+        <v>0.3033998730726207</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.715979477530387</v>
+        <v>2.684485632017671</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.930081634780109</v>
+        <v>-3.998319956880341</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9238436052547208</v>
+        <v>0.896548276414628</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5126663737645329</v>
+        <v>0.4601766312433394</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.803832507739232</v>
+        <v>2.772338662226516</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.975095848300715</v>
+        <v>-4.043334170400946</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8866453751780679</v>
+        <v>0.8593500463379753</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4823174784499283</v>
+        <v>0.4298277359287348</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.766430625882059</v>
+        <v>2.734936780369343</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850954</v>
+        <v>3.737026608509539</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.063107034859412</v>
+        <v>-4.131345356959644</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8571324628935351</v>
+        <v>0.8298371340534423</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4168409705907554</v>
+        <v>0.3643512280695618</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.732836283505501</v>
+        <v>2.701342437992785</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.164304816296585</v>
+        <v>-4.232543138396816</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8158572722151674</v>
+        <v>0.7885619433750746</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3484321570454362</v>
+        <v>0.2959424145242426</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.690994917274811</v>
+        <v>2.659501071762095</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.157793849682272</v>
+        <v>-4.226032171782504</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8160616204152091</v>
+        <v>0.7887662915751164</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3484321570454362</v>
+        <v>0.2959424145242426</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.688594878829128</v>
+        <v>2.657101033316412</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.138755721974975</v>
+        <v>-4.206994044075206</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8202015907063729</v>
+        <v>0.7929062618662801</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2902485457142416</v>
+        <v>0.2377588031930481</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.650209431238656</v>
+        <v>2.61871558572594</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.191271524249795</v>
+        <v>-4.259509846350027</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9184896714306352</v>
+        <v>0.8911943425905424</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2902485457142416</v>
+        <v>0.2377588031930481</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.769503832872846</v>
+        <v>2.73800998736013</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.194679835684375</v>
+        <v>-4.262918157784607</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9179596758429367</v>
+        <v>0.8906643470028439</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.322765114723619</v>
+        <v>0.2702753722024255</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.789847103264606</v>
+        <v>2.75835325775189</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.175323699790527</v>
+        <v>-4.243562021890759</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9317106605974017</v>
+        <v>0.9044153317573089</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.322765114723619</v>
+        <v>0.2702753722024255</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.795855633661532</v>
+        <v>2.764361788148816</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.24865322852862</v>
+        <v>-4.316891550628852</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8003290703793642</v>
+        <v>0.7730337415392714</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.323159777143241</v>
+        <v>0.2706700346220474</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.694042652390505</v>
+        <v>2.662548806877789</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.409870503348191</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.332474449803319</v>
+        <v>-4.40071277190355</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.676524299113116</v>
+        <v>0.6492289702730232</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.323159777143241</v>
+        <v>0.2706700346220474</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.603766369634136</v>
+        <v>2.57227252412142</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.41053285173985</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.326321743750534</v>
+        <v>-4.394560065850766</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.6796477299258881</v>
+        <v>0.6523524010857953</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3293124831960252</v>
+        <v>0.2768227406748317</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.608120341657465</v>
+        <v>2.576626496144749</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.40961332847996</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.343131041901036</v>
+        <v>-4.411369364001268</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.6720044874057975</v>
+        <v>0.6447091585657048</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3125031850455236</v>
+        <v>0.2600134425243301</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.597115239507274</v>
+        <v>2.565621393994558</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.475948882276781</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.280833043124914</v>
+        <v>-4.349071365225146</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.7632592407130674</v>
+        <v>0.7359639118729746</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3577974493199657</v>
+        <v>0.3053077067987721</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.69062735186876</v>
+        <v>2.659133506356044</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.278240883990908</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.079042845459756</v>
+        <v>-4.147281167559988</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6462673214932575</v>
+        <v>0.6189719926531647</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.55581564148912</v>
+        <v>0.5033258989679266</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.61173026888438</v>
+        <v>2.580236423371664</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.348531116313083</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.129929558145951</v>
+        <v>-4.198167880246182</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6962028687409549</v>
+        <v>0.6689075399008622</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5049289288029255</v>
+        <v>0.452439186281732</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.651488473594839</v>
+        <v>2.619994628082122</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.363158852429127</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.043318815496144</v>
+        <v>-4.111557137596376</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7454749019169213</v>
+        <v>0.7181795730768286</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5835546600080838</v>
+        <v>0.5310649174868902</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.713291648433977</v>
+        <v>2.681797802921261</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.361694833253798</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.103528113501429</v>
+        <v>-4.17176643560166</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7199271635394791</v>
+        <v>0.6926318346993863</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5233453620027992</v>
+        <v>0.4708556194816057</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.675702050455478</v>
+        <v>2.644208204942762</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.360186451293727</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.054341464817077</v>
+        <v>-4.091205653566755</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7380934410531481</v>
+        <v>0.723347765553277</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5233453620027992</v>
+        <v>0.4708556194816057</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.674193668495406</v>
+        <v>2.642699822982691</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316253</v>
+        <v>3.833513460316251</v>
       </c>
       <c r="C1976" t="n">
         <v>2.360049318729163</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.009968333178509</v>
+        <v>-4.046832521928186</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7557055611440118</v>
+        <v>0.7409598856441406</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5677184936413678</v>
+        <v>0.5152287511201743</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.700680414913984</v>
+        <v>2.669186569401268</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105967</v>
+        <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
         <v>2.354443112867754</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.975237011860008</v>
+        <v>-4.012101200609686</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7639918838100026</v>
+        <v>0.7492462083101314</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5677184936413678</v>
+        <v>0.5152287511201743</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.695074209052574</v>
+        <v>2.663580363539858</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.360824869895558</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.927581281298952</v>
+        <v>-3.96444547004863</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7894359330622294</v>
+        <v>0.7746902575623584</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6153742242024235</v>
+        <v>0.56288448168123</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.730049404417012</v>
+        <v>2.698555558904296</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.365717243270283</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.827063122800197</v>
+        <v>-3.863927311549875</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.834535569836456</v>
+        <v>0.8197898943365851</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7158923827011781</v>
+        <v>0.6634026401799845</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.79525267289099</v>
+        <v>2.763758827378274</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.352471915746155</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.811157793367845</v>
+        <v>-3.848021982117523</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8276523740852695</v>
+        <v>0.8129066985853983</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6367797219919391</v>
+        <v>0.5842899794707457</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.734539748941319</v>
+        <v>2.703045903428603</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.356569618356784</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.766319391759447</v>
+        <v>-3.803183580509125</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8496854373392573</v>
+        <v>0.8349397618393861</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6413231549368086</v>
+        <v>0.5888334124156152</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.741363511318869</v>
+        <v>2.709869665806153</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.360730557987862</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.785817848001455</v>
+        <v>-3.822682036751133</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8460469944735318</v>
+        <v>0.8313013189736609</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5932385136569043</v>
+        <v>0.5407487711357108</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.716673666182005</v>
+        <v>2.685179820669289</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.366610160515699</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.741615010915555</v>
+        <v>-3.778479199665232</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8696077318357291</v>
+        <v>0.8548620563358582</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6374413507428047</v>
+        <v>0.5849516082216113</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.749074970961382</v>
+        <v>2.717581125448666</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.365020160984947</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.749174676752602</v>
+        <v>-3.786038865502279</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8649938659701579</v>
+        <v>0.850248190470287</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.692244754752624</v>
+        <v>0.6397550122314306</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.780367013836521</v>
+        <v>2.748873168323805</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.416267926167986</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.590883259213329</v>
+        <v>-3.627747447963007</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9795581981689065</v>
+        <v>0.9648125226690354</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.692244754752624</v>
+        <v>0.6397550122314306</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.831614779019561</v>
+        <v>2.800120933506845</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.414708630762239</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.383241255578853</v>
+        <v>-3.420105444328531</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.06105570421695</v>
+        <v>1.046310028717079</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8998867583871002</v>
+        <v>0.8473970158659068</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.9546406857945</v>
+        <v>2.923146840281784</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.409656859000509</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.332209162856325</v>
+        <v>-3.369073351606003</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.076416769544231</v>
+        <v>1.06167109404436</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9509188511096281</v>
+        <v>0.8984291085884347</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.980208169666287</v>
+        <v>2.94871432415357</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.426844263093214</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.266984981729119</v>
+        <v>-3.303849170478797</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.119693846087819</v>
+        <v>1.104948170587948</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.016143032236834</v>
+        <v>0.9636532897156403</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.036530082435315</v>
+        <v>3.005036236922599</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.422805235392495</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.229557961657985</v>
+        <v>-3.266422150407663</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.130625626415553</v>
+        <v>1.115879950915681</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.021394570266015</v>
+        <v>0.968904827744822</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.035641977552104</v>
+        <v>3.004148132039388</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.424062027723735</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.22819997668444</v>
+        <v>-3.265064165434118</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.132425612736211</v>
+        <v>1.11767993723634</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.095732695803834</v>
+        <v>1.043242953282641</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.081501645206036</v>
+        <v>3.050007799693319</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.584619798744946</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.199786713584556</v>
+        <v>-3.236650902334234</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.304348688997375</v>
+        <v>1.289603013497504</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.036757133057405</v>
+        <v>0.9842673905362118</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.206674078579389</v>
+        <v>3.175180233066673</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957628</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
         <v>2.704732707962763</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.125004452559544</v>
+        <v>-3.161868641309221</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.454374502625198</v>
+        <v>1.439628827125326</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.111539394082418</v>
+        <v>1.059049651561224</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.371656344412214</v>
+        <v>3.340162498899498</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>2.696440683976622</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.098920368295736</v>
+        <v>-3.135784557045413</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.45651611234458</v>
+        <v>1.441770436844709</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.111539394082418</v>
+        <v>1.059049651561224</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.363364320426073</v>
+        <v>3.331870474913357</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.694633879560401</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.011042455186615</v>
+        <v>-3.047906643936293</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.489860473172007</v>
+        <v>1.475114797672136</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.227465036505769</v>
+        <v>1.174975293984576</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.431112901463863</v>
+        <v>3.399619055951147</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959858</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.712188285287193</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.002149993793332</v>
+        <v>-3.03901418254301</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.510971863456112</v>
+        <v>1.496226187956241</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.227465036505769</v>
+        <v>1.174975293984576</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.448667307190654</v>
+        <v>3.417173461677939</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.704043332691777</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.17062611076321</v>
+        <v>-3.207490299512888</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.435436464072745</v>
+        <v>1.420690788572874</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.199517200789188</v>
+        <v>1.147027458267995</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.42375365316529</v>
+        <v>3.392259807652574</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.685313029879639</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.72436991813377</v>
+        <v>-2.761234106883448</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.595208638312383</v>
+        <v>1.580462962812512</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.104798531119555</v>
+        <v>1.052308788598362</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.348192148551372</v>
+        <v>3.316698303038656</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.675977052376543</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.701648814450618</v>
+        <v>-2.738513003200295</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.594961102282548</v>
+        <v>1.580215426782677</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.104798531119555</v>
+        <v>1.052308788598362</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.338856171048277</v>
+        <v>3.307362325535561</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777674</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>2.834883178227712</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.83085062774466</v>
+        <v>-2.867714816494338</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.7021865028161</v>
+        <v>1.687440827316229</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9755967178255132</v>
+        <v>0.92310697530432</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.42024120892302</v>
+        <v>3.388747363410304</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>2.871961000721359</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.856725026218686</v>
+        <v>-2.893589214968364</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.728914565920136</v>
+        <v>1.714168890420265</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.020508326537254</v>
+        <v>0.9680185840160611</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.484265996643711</v>
+        <v>3.452772151130996</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.868636356710904</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.849670336003512</v>
+        <v>-2.88653452475319</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.728411797995751</v>
+        <v>1.71366612249588</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.027563016752428</v>
+        <v>0.9750732742312349</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.485174166762361</v>
+        <v>3.453680321249645</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>2.878642510355645</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.822719111677024</v>
+        <v>-2.859583300426702</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.749198441371088</v>
+        <v>1.734452765871217</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.042443362780147</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.504108528023734</v>
+        <v>3.472614682511018</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784109</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.062745642500605</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.844263339507811</v>
+        <v>-2.881127528257489</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.924683882383733</v>
+        <v>1.909938206883862</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.042443362780147</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.688211660168694</v>
+        <v>3.656717814655978</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.054862337403598</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.866671457312683</v>
+        <v>-2.903535646062361</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.907837330164777</v>
+        <v>1.893091654664906</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.042443362780147</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.680328355071687</v>
+        <v>3.648834509558971</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155035</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.056916336953236</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.894895692890284</v>
+        <v>-2.931759881639961</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.898601635483374</v>
+        <v>1.883855959983503</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.060420115231456</v>
+        <v>1.007930372710263</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.693168406092109</v>
+        <v>3.661674560579394</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161981</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
         <v>3.113170054675083</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.904336618778814</v>
+        <v>-2.941200807528491</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.951078982849809</v>
+        <v>1.936333307349939</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.182847232774847</v>
+        <v>1.130357490253654</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.822878394339992</v>
+        <v>3.791384548827275</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321639</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
         <v>3.116061149220384</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.110575556567247</v>
+        <v>-3.147439745316925</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.871474502279737</v>
+        <v>1.856728826779866</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9766082949864137</v>
+        <v>0.9241185524652205</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.702026126212232</v>
+        <v>3.670532280699516</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347709</v>
+        <v>3.727898186347708</v>
       </c>
       <c r="C2008" t="n">
         <v>3.114172962114159</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.186905534168153</v>
+        <v>-3.223769722917831</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.83905432413315</v>
+        <v>1.824308648633279</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9766082949864137</v>
+        <v>0.9241185524652205</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.700137939106007</v>
+        <v>3.668644093593291</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887755</v>
+        <v>3.710654104887753</v>
       </c>
       <c r="C2009" t="n">
         <v>3.108993191717021</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.341862319568282</v>
+        <v>-3.37872650831796</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.77189183957596</v>
+        <v>1.757146164076089</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8216515095862844</v>
+        <v>0.7691617670650912</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.601984097468792</v>
+        <v>3.570490251956076</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343073</v>
+        <v>3.712897612343071</v>
       </c>
       <c r="C2010" t="n">
         <v>3.107427201927174</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.503430745095538</v>
+        <v>-3.540294933845215</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.705698479575211</v>
+        <v>1.690952804075339</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.694868585788405</v>
+        <v>0.6423788432672118</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.524348353400217</v>
+        <v>3.492854507887501</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389356</v>
+        <v>3.754596135389354</v>
       </c>
       <c r="C2011" t="n">
         <v>3.120500608793092</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.611731406965657</v>
+        <v>-3.648595595715335</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.675451621693081</v>
+        <v>1.66070594619321</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.694868585788405</v>
+        <v>0.6423788432672118</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.537421760266136</v>
+        <v>3.505927914753419</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.112505805576032</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.771282479729174</v>
+        <v>-3.808146668478852</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.603636389370615</v>
+        <v>1.588890713870744</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5425909189266536</v>
+        <v>0.4901011764054604</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.438060356932024</v>
+        <v>3.406566511419308</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.111029846703034</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.799183266838647</v>
+        <v>-3.836047455588325</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.591000115653827</v>
+        <v>1.576254440153956</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5079939947837188</v>
+        <v>0.4555042522625256</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.415826243573266</v>
+        <v>3.38433239806055</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787388</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.107794290680233</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.921709369541541</v>
+        <v>-3.958573558291218</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.538754118549869</v>
+        <v>1.524008443049998</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3854678920808249</v>
+        <v>0.3329781495596317</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.339075025928728</v>
+        <v>3.307581180416012</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.174500250270737</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.152223865727129</v>
+        <v>-4.189088054476807</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.513254279666137</v>
+        <v>1.498508604166266</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1549533958952362</v>
+        <v>0.102463653374043</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.267472287807879</v>
+        <v>3.235978442295163</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814668</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
         <v>3.314811969272584</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.500968950951573</v>
+        <v>-4.537833139701251</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.514067964578206</v>
+        <v>1.499322289078336</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.04620544197633836</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.342535234458387</v>
+        <v>3.311041388945671</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237097</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.383792238418224</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.654955368727713</v>
+        <v>-4.691819557477391</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.52145366661339</v>
+        <v>1.506707991113519</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.04620544197633836</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.411515503604027</v>
+        <v>3.380021658091311</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.61992301642339</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
         <v>3.369843440538344</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.859554803590722</v>
+        <v>-4.8964189923404</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.425665094788308</v>
+        <v>1.410919419288436</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.04620544197633836</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.397566705724147</v>
+        <v>3.366072860211432</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609755</v>
+        <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
         <v>3.381713929593758</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.112029957598446</v>
+        <v>-5.148894146348124</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.336545522240632</v>
+        <v>1.321799846740761</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.04620544197633836</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.409437194779561</v>
+        <v>3.377943349266846</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973159</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.382924464112702</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.404925714077859</v>
+        <v>-5.441789902827536</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.220597754167811</v>
+        <v>1.205852078667939</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.04620544197633836</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.410647729298505</v>
+        <v>3.37915388378579</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251948</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.387046206340024</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.591589842212667</v>
+        <v>-5.628454030962344</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.150053845141209</v>
+        <v>1.135308169641338</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.01946647115177846</v>
+        <v>-0.03302327136941474</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.398726089031091</v>
+        <v>3.367232243518375</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916203</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.382124059076213</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.737610529126629</v>
+        <v>-5.774474717876307</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.086723423111813</v>
+        <v>1.071977747611943</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.0103833793579215</v>
+        <v>-0.04210636316327171</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.388354086690966</v>
+        <v>3.35686024117825</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.66796230683033</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.544328115775257</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.829324538236214</v>
+        <v>-5.866188726985891</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.212241876167024</v>
+        <v>1.197496200667153</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.0103833793579215</v>
+        <v>-0.04210636316327171</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.55055814339001</v>
+        <v>3.519064297877294</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071554</v>
+        <v>3.696539468071552</v>
       </c>
       <c r="C2024" t="n">
         <v>3.539174753739071</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.841926914261958</v>
+        <v>-5.897840386045861</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.20204756372054</v>
+        <v>1.179682175006979</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.01499407952921528</v>
+        <v>-0.04727482040771191</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.530178306021542</v>
+        <v>3.510809861494444</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868152</v>
+        <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
         <v>3.549404171307562</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.910992968834894</v>
+        <v>-5.966906440618797</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.184650559459857</v>
+        <v>1.162285170746296</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.07736495702282531</v>
+        <v>-0.1096456979013219</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.502985197093867</v>
+        <v>3.483616752566769</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332699</v>
+        <v>3.783632867332695</v>
       </c>
       <c r="C2026" t="n">
         <v>3.558329809763465</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.012969091083302</v>
+        <v>-6.068882562867205</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.152785749016396</v>
+        <v>1.130420360302835</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1793410792712329</v>
+        <v>-0.2116218201497295</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.450725162200725</v>
+        <v>3.431356717673627</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231816</v>
+        <v>3.798296784231812</v>
       </c>
       <c r="C2027" t="n">
         <v>3.55048269700764</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.90296280760608</v>
+        <v>-5.958876279389983</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.18894114965146</v>
+        <v>1.166575760937899</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1561365073539577</v>
+        <v>-0.1884172482324543</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.456800792595266</v>
+        <v>3.437432348068168</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818523</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.554732707729614</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.915492512717959</v>
+        <v>-5.971405984501862</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.188179278328683</v>
+        <v>1.165813889615122</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1699630068204807</v>
+        <v>-0.2022437476989773</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.452754903637326</v>
+        <v>3.433386459110229</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77723741205179</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.56199359061215</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.614045787246122</v>
+        <v>-5.669959259030025</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.316018851399954</v>
+        <v>1.293653462686393</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1314837186513566</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.640883821802964</v>
+        <v>3.621515377275867</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679627</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.562964768364861</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.638636031481306</v>
+        <v>-5.694549503265208</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.307153931458591</v>
+        <v>1.28478854274503</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1314837186513566</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.641854999555675</v>
+        <v>3.622486555028577</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474162</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.563807672744617</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.587597655474785</v>
+        <v>-5.643511127258688</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.328412186240954</v>
+        <v>1.306046797527393</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1314837186513566</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.642697903935431</v>
+        <v>3.623329459408333</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969546</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
         <v>3.582845771618762</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.558748978651325</v>
+        <v>-5.614662450435228</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.358989755844484</v>
+        <v>1.336624367130923</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1603323954748168</v>
+        <v>0.1280516545963202</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.679045208903652</v>
+        <v>3.659676764376554</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700482</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
         <v>3.399029767742697</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.462114066632685</v>
+        <v>-5.518027538416588</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.213827716775875</v>
+        <v>1.191462328062313</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2569673074934568</v>
+        <v>0.2246865666149601</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.553210152238771</v>
+        <v>3.533841707711673</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077646</v>
+        <v>3.804688961077642</v>
       </c>
       <c r="C2034" t="n">
         <v>3.402531811816661</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.393076055684217</v>
+        <v>-5.44898952746812</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.244944965229226</v>
+        <v>1.222579576515665</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3260053184419248</v>
+        <v>0.2937245775634282</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.598135002881816</v>
+        <v>3.578766558354718</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833466</v>
+        <v>3.775028860833462</v>
       </c>
       <c r="C2035" t="n">
         <v>3.386958630892743</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.374288955315278</v>
+        <v>-5.430202427099181</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.236886624452884</v>
+        <v>1.214521235739323</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3447924188108633</v>
+        <v>0.3125116779323667</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.593834082179261</v>
+        <v>3.574465637652164</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.82103066007763</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.386146341329173</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.297190353773406</v>
+        <v>-5.353103825557309</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.266913775506063</v>
+        <v>1.244548386792502</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3447924188108633</v>
+        <v>0.3125116779323667</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.593021792615691</v>
+        <v>3.573653348088593</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147912</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.396015120454245</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.307575548663295</v>
+        <v>-5.363489020447198</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.272628476675179</v>
+        <v>1.250263087961618</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.334407223920974</v>
+        <v>0.3021264830424774</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.59665945480683</v>
+        <v>3.577291010279732</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735288</v>
+        <v>3.834415493735285</v>
       </c>
       <c r="C2038" t="n">
         <v>3.466852126230671</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.32616370738552</v>
+        <v>-5.382077179169423</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.336030218962715</v>
+        <v>1.313664830249154</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3158190651987486</v>
+        <v>0.283538324320252</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.65634356534992</v>
+        <v>3.636975120822822</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496557</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.463721137048969</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.326462254081556</v>
+        <v>-5.382375725865459</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.332779811102599</v>
+        <v>1.310414422389038</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3155205185027127</v>
+        <v>0.2832397776242161</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.653033448150597</v>
+        <v>3.633665003623499</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108863</v>
+        <v>3.81564321210886</v>
       </c>
       <c r="C2040" t="n">
         <v>3.468252031988361</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.225639120391128</v>
+        <v>-5.281552592175031</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.377639959518161</v>
+        <v>1.3552745708046</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3279847339870666</v>
+        <v>0.2957039931085699</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.665042872380601</v>
+        <v>3.645674427853503</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121474</v>
+        <v>3.807356168121471</v>
       </c>
       <c r="C2041" t="n">
         <v>3.468381285466904</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.034857759638721</v>
+        <v>-5.090771231422623</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.454081757297668</v>
+        <v>1.431716368584107</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5187660947394739</v>
+        <v>0.4864853538609773</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.779640942310588</v>
+        <v>3.76027249778349</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906088</v>
+        <v>3.775233033906084</v>
       </c>
       <c r="C2042" t="n">
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.927894401789299</v>
+        <v>-4.983807873573202</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.476703946175033</v>
+        <v>1.454338557461472</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5772307026992753</v>
+        <v>0.5449499618207787</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.794556552824066</v>
+        <v>3.775188108296968</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912992</v>
+        <v>3.785761685912989</v>
       </c>
       <c r="C2043" t="n">
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.872563813887536</v>
+        <v>-4.928477285671439</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.533803117947796</v>
+        <v>1.511437729234235</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6325612906010375</v>
+        <v>0.6002805497225409</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.862721842177181</v>
+        <v>3.843353397650084</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539902</v>
+        <v>3.743767956539898</v>
       </c>
       <c r="C2044" t="n">
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.860509686974574</v>
+        <v>-4.916423158758477</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.532311336614419</v>
+        <v>1.509945947900858</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6446154175140003</v>
+        <v>0.6123346766355037</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.863640886226397</v>
+        <v>3.844272441699299</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811017</v>
+        <v>3.725010844811013</v>
       </c>
       <c r="C2045" t="n">
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.937865177102543</v>
+        <v>-4.993778648886446</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.503249770747367</v>
+        <v>1.480884382033806</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5672599273860309</v>
+        <v>0.5349791865075343</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.819108222333751</v>
+        <v>3.799739777806653</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382928</v>
+        <v>3.612322444382924</v>
       </c>
       <c r="C2046" t="n">
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.869816614411013</v>
+        <v>-4.925730086194916</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.543320221701862</v>
+        <v>1.5209548329883</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6353084900775607</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.872788385826551</v>
+        <v>3.853419941299454</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013435</v>
+        <v>3.645256780013431</v>
       </c>
       <c r="C2047" t="n">
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.101417007580514</v>
+        <v>-5.157330479364417</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.470882734607656</v>
+        <v>1.448517345894095</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6353084900775607</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.892991056000146</v>
+        <v>3.873622611473048</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498972</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.151468553109734</v>
+        <v>-5.207382024893636</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.43446835246285</v>
+        <v>1.412102963749288</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6353084900775607</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.876597292067028</v>
+        <v>3.85722884753993</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800101</v>
+        <v>3.670048702800098</v>
       </c>
       <c r="C2049" t="n">
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.326575385686178</v>
+        <v>-5.382488857470081</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.324677533025739</v>
+        <v>1.302312144312177</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6353084900775607</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.836849205660494</v>
+        <v>3.817480761133397</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660854</v>
+        <v>3.74557314866085</v>
       </c>
       <c r="C2050" t="n">
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.130475232255655</v>
+        <v>-5.186388704039558</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.410140213394888</v>
+        <v>1.387774824681327</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8314086435080836</v>
+        <v>0.799127902629587</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.961531916715748</v>
+        <v>3.94216347218865</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73057047339509</v>
+        <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.977449840142371</v>
+        <v>-5.033363311926274</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.570521369813106</v>
+        <v>1.548155981099545</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9844340356213678</v>
+        <v>0.9521532947428711</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.152518151556623</v>
+        <v>4.133149707029525</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791152</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.005757154015641</v>
+        <v>-5.061670625799544</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.74666466917209</v>
+        <v>1.724299280458529</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9844340356213678</v>
+        <v>0.9521532947428711</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.339984376464916</v>
+        <v>4.320615931937818</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620438</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.172350379129163</v>
+        <v>-5.228263850913066</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.649430330480764</v>
+        <v>1.627064941767203</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8178408105078454</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.209431392750885</v>
+        <v>4.190062948223787</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285651</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.149314585767597</v>
+        <v>-5.2052280575515</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.662321050487108</v>
+        <v>1.639955661773547</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8178408105078454</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.213107795412602</v>
+        <v>4.193739350885505</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399472</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.120068605311901</v>
+        <v>-5.175982077095804</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.671637497792882</v>
+        <v>1.649272109079321</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8178408105078454</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.210725850536098</v>
+        <v>4.191357406009</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256376</v>
+        <v>3.699404642256372</v>
       </c>
       <c r="C2056" t="n">
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.226994153189752</v>
+        <v>-5.282907624973655</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.626160517799377</v>
+        <v>1.603795129085816</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.710915262629994</v>
+        <v>0.6786345217514974</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.143863760967022</v>
+        <v>4.124495316439925</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701006</v>
+        <v>3.689942600701002</v>
       </c>
       <c r="C2057" t="n">
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.372012711697001</v>
+        <v>-5.427926183480904</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.569581896539711</v>
+        <v>1.54721650782615</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5658967041227455</v>
+        <v>0.5336159632442489</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.058281428005907</v>
+        <v>4.038912983478809</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687018</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.490354477481718</v>
+        <v>-5.546267949265621</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.622176429483577</v>
+        <v>1.599811040770016</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5765827426856356</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.164624290401394</v>
+        <v>4.145255845874297</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.71487905179081</v>
+        <v>3.714879051790806</v>
       </c>
       <c r="C2059" t="n">
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.541764899802426</v>
+        <v>-5.597678371586329</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.599397957681233</v>
+        <v>1.577032568967672</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5765827426856356</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.162409987527333</v>
+        <v>4.143041543000235</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437338</v>
+        <v>3.704757949437335</v>
       </c>
       <c r="C2060" t="n">
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.621184351010178</v>
+        <v>-5.677097822794081</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.567533305272422</v>
+        <v>1.545167916558861</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5765827426856356</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.162313115601623</v>
+        <v>4.142944671074525</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298407</v>
+        <v>3.736804952298403</v>
       </c>
       <c r="C2061" t="n">
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.716647348927395</v>
+        <v>-5.772560820711298</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.529341999663578</v>
+        <v>1.506976610950017</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5765827426856356</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.162307009159665</v>
+        <v>4.142938564632567</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218009</v>
+        <v>3.715372960218005</v>
       </c>
       <c r="C2062" t="n">
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.652271438076681</v>
+        <v>-5.708184909860583</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.553188760566474</v>
+        <v>1.530823371852913</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6409586535363507</v>
+        <v>0.6086779126578541</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.199028952232705</v>
+        <v>4.179660507705607</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353544</v>
+        <v>3.736089413353541</v>
       </c>
       <c r="C2063" t="n">
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.707640600208874</v>
+        <v>-5.763554071992777</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.536774913461323</v>
+        <v>1.514409524747762</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6409586535363507</v>
+        <v>0.6086779126578541</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.204762769980432</v>
+        <v>4.185394325453334</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113287</v>
+        <v>3.736822870113284</v>
       </c>
       <c r="C2064" t="n">
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.725859067206483</v>
+        <v>-5.781772538990386</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.529025890005212</v>
+        <v>1.506660501291651</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6158522162805086</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.189237270969858</v>
+        <v>4.169868826442761</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113695</v>
+        <v>3.790272500113692</v>
       </c>
       <c r="C2065" t="n">
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.687175631862552</v>
+        <v>-5.743089103646455</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.564373656993103</v>
+        <v>1.542008268279542</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6158522162805086</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.209111663820178</v>
+        <v>4.18974321929308</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016441</v>
+        <v>3.794486844016437</v>
       </c>
       <c r="C2066" t="n">
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.581140636657243</v>
+        <v>-5.637054108441146</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.590488355599955</v>
+        <v>1.568122966886394</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6158522162805086</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.192812364344905</v>
+        <v>4.173443919817807</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307672</v>
+        <v>3.794705093307669</v>
       </c>
       <c r="C2067" t="n">
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.397928973524148</v>
+        <v>-5.453842445308051</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.666203970317239</v>
+        <v>1.643838581603678</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6158522162805086</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.195243313808952</v>
+        <v>4.175874869281854</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.77684655786355</v>
       </c>
       <c r="C2068" t="n">
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.326207526510297</v>
+        <v>-5.3821209982942</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.677836955202157</v>
+        <v>1.655471566488595</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6875736632943592</v>
+        <v>0.6552929224158626</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.221220588096639</v>
+        <v>4.201852143569541</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394115</v>
+        <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.303834500902591</v>
+        <v>-5.359747972686494</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.633701911366411</v>
+        <v>1.61133652265285</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6988294144072608</v>
+        <v>0.6665486735287641</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.174889784685551</v>
+        <v>4.155521340158454</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456733</v>
+        <v>3.71560744645673</v>
       </c>
       <c r="C2070" t="n">
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.336850796813335</v>
+        <v>-5.392764268597238</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.805693597887468</v>
+        <v>1.783328209173907</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6293920377405091</v>
+        <v>0.5971112968620125</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.318425563570855</v>
+        <v>4.299057119043757</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883683</v>
+        <v>3.71376253688368</v>
       </c>
       <c r="C2071" t="n">
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.325323161163727</v>
+        <v>-5.38123663294763</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.80222587797556</v>
+        <v>1.779860489261999</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6883926959418716</v>
+        <v>0.6561119550633749</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.345747184319922</v>
+        <v>4.326378739792824</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236305</v>
+        <v>3.717150699236301</v>
       </c>
       <c r="C2072" t="n">
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.422664662506095</v>
+        <v>-5.478578134289998</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.766957389960401</v>
+        <v>1.74459200124684</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6439725137763832</v>
+        <v>0.6116917728978866</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.322763187542417</v>
+        <v>4.303394743015319</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427692</v>
+        <v>3.705201079427688</v>
       </c>
       <c r="C2073" t="n">
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.508520691846062</v>
+        <v>-5.564434163629965</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.733866060417253</v>
+        <v>1.711500671703692</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6015964445502482</v>
+        <v>0.5693157036717515</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.298588628199575</v>
+        <v>4.279220183672477</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610383</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.517357489262182</v>
+        <v>-5.573270961046084</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.712750543271307</v>
+        <v>1.690385154557746</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5941542719088975</v>
+        <v>0.5618735310304008</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.276542526435266</v>
+        <v>4.257174081908168</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667461</v>
+        <v>3.715544411667458</v>
       </c>
       <c r="C2075" t="n">
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.60874005182764</v>
+        <v>-5.664653523611543</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.686362029290173</v>
+        <v>1.663996640576612</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5575893871895528</v>
+        <v>0.5253086463110561</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.264768106648709</v>
+        <v>4.245399662121611</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889198</v>
+        <v>3.673978374889195</v>
       </c>
       <c r="C2076" t="n">
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.597033333840634</v>
+        <v>-5.652946805624537</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.793172974309244</v>
+        <v>1.770807585595682</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5692961051765592</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.373920395265181</v>
+        <v>4.354551950738083</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409575</v>
+        <v>3.682476099409571</v>
       </c>
       <c r="C2077" t="n">
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.667945407582911</v>
+        <v>-5.723858879366814</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.767840483543738</v>
+        <v>1.745475094830176</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5692961051765592</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.376952733996585</v>
+        <v>4.357584289469488</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452574</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
         <v>4.248279904168708</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.678261505749263</v>
+        <v>-5.734174977533166</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.976618877555255</v>
+        <v>1.954253488841694</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5692961051765592</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.589857567274644</v>
+        <v>4.570489122747546</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762295</v>
+        <v>3.623960959762291</v>
       </c>
       <c r="C2079" t="n">
         <v>4.247458571080798</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.67816753773189</v>
+        <v>-5.734081009515793</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.975835131674294</v>
+        <v>1.953469742960733</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5696659665238771</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.589258150995124</v>
+        <v>4.569889706468026</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884088</v>
+        <v>3.800870306884084</v>
       </c>
       <c r="C2080" t="n">
         <v>4.241690557025152</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.821768701755276</v>
+        <v>-5.877682173539179</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.912626652009293</v>
+        <v>1.890261263295732</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5696659665238771</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.583490136939478</v>
+        <v>4.56412169241238</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129652</v>
+        <v>3.671015692129648</v>
       </c>
       <c r="C2081" t="n">
         <v>4.241690557025152</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.820820278637237</v>
+        <v>-5.87673375042114</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.913006021256509</v>
+        <v>1.890640632542948</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5696659665238771</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.583490136939478</v>
+        <v>4.56412169241238</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052355</v>
+        <v>3.904173816052351</v>
       </c>
       <c r="C2082" t="n">
         <v>4.254418165006244</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.921090096596258</v>
+        <v>-5.977003568380161</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.885625702053992</v>
+        <v>1.863260313340431</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5696659665238771</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.59621774492057</v>
+        <v>4.576849300393472</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813499</v>
+        <v>3.740179607813495</v>
       </c>
       <c r="C2083" t="n">
         <v>4.256364163430631</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.915097849807446</v>
+        <v>-5.971011321591349</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.889968599193905</v>
+        <v>1.867603210480344</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5696659665238771</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.598163743344958</v>
+        <v>4.57879529881786</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537947</v>
+        <v>3.765050796537944</v>
       </c>
       <c r="C2084" t="n">
         <v>4.2500182994484</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.826539888676678</v>
+        <v>-5.882453360460581</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.919045919663981</v>
+        <v>1.89668053095042</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5696659665238771</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.591817879362726</v>
+        <v>4.572449434835629</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771819</v>
+        <v>3.758409170771816</v>
       </c>
       <c r="C2085" t="n">
         <v>4.249326976887396</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.808780811173604</v>
+        <v>-5.864694282957507</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.925458228104206</v>
+        <v>1.903092839390645</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5696659665238771</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.591126556801722</v>
+        <v>4.571758112274624</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.801340597109725</v>
+        <v>3.801340597109721</v>
       </c>
       <c r="C2086" t="n">
         <v>4.262109162795983</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.709150660124537</v>
+        <v>-5.765064131908439</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.97809247443242</v>
+        <v>1.955727085718859</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.6692961175729446</v>
+        <v>0.637015376694448</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.663686833339749</v>
+        <v>4.644318388812652</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546844</v>
+        <v>3.798465546843996</v>
       </c>
       <c r="C2087" t="n">
         <v>4.451263428294709</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.758550168813548</v>
+        <v>-5.814463640597451</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.147486936455542</v>
+        <v>2.125121547741981</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6795549510046893</v>
+        <v>0.6472742101261927</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.858996398897522</v>
+        <v>4.839627954370425</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.772186508351863</v>
+        <v>3.77218650835186</v>
       </c>
       <c r="C2088" t="n">
         <v>4.438452101397571</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.551865695171172</v>
+        <v>-5.607779166955075</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.217349399015355</v>
+        <v>2.194984010301793</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.886239424647065</v>
+        <v>0.8539586837685683</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.97019575618581</v>
+        <v>4.950827311658712</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.763392838551273</v>
+        <v>3.76339283855127</v>
       </c>
       <c r="C2089" t="n">
         <v>4.440453615051676</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.586022590168698</v>
+        <v>-5.641936061952601</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.205688154670449</v>
+        <v>2.183322765956888</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.8026556551062525</v>
+        <v>0.7703749142277558</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.922047008115428</v>
+        <v>4.90267856358833</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041115</v>
+        <v>3.805590565041111</v>
       </c>
       <c r="C2090" t="n">
         <v>4.793950729041343</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.493433111107241</v>
+        <v>-5.549346582891144</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.596221060284699</v>
+        <v>2.573855671571138</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.8026556551062525</v>
+        <v>0.7703749142277558</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.275544122105095</v>
+        <v>5.256175677577997</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497406</v>
+        <v>3.832164354497403</v>
       </c>
       <c r="C2091" t="n">
         <v>4.798513840608447</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.566593714880386</v>
+        <v>-5.622507186664289</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.571519930342544</v>
+        <v>2.549154541628983</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7746344550720095</v>
+        <v>0.7423537141935128</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.263294513651653</v>
+        <v>5.243926069124555</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492299</v>
+        <v>3.858310890492295</v>
       </c>
       <c r="C2092" t="n">
         <v>4.848343781931974</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.514377405084044</v>
+        <v>-5.570290876867947</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.642236395584609</v>
+        <v>2.619871006871047</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7746344550720095</v>
+        <v>0.7423537141935128</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.313124454975179</v>
+        <v>5.293756010448082</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.84493559643648</v>
+        <v>3.844935596436477</v>
       </c>
       <c r="C2093" t="n">
         <v>4.857157752141985</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.482479887998799</v>
+        <v>-5.538393359782702</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.663809372628718</v>
+        <v>2.641443983915157</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.8065319721572553</v>
+        <v>0.7742512312787586</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.341076935436338</v>
+        <v>5.32170849090924</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.84837686603949</v>
+        <v>3.848376866039486</v>
       </c>
       <c r="C2094" t="n">
         <v>4.852795336181182</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.497235212198939</v>
+        <v>-5.553148683982842</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.653544826987858</v>
+        <v>2.631179438274297</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.8065319721572553</v>
+        <v>0.7742512312787586</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.336714519475535</v>
+        <v>5.317346074948437</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524485</v>
+        <v>3.868153115524481</v>
       </c>
       <c r="C2095" t="n">
         <v>4.843719839597462</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.447770588829028</v>
+        <v>-5.50368406061293</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.664255179752103</v>
+        <v>2.641889791038542</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8559965955271669</v>
+        <v>0.8237158546486703</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.357317796913762</v>
+        <v>5.337949352386664</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867959</v>
+        <v>3.849040239867955</v>
       </c>
       <c r="C2096" t="n">
         <v>4.840127507312396</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.284662596675412</v>
+        <v>-5.340576068459315</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.725906044328484</v>
+        <v>2.703540655614922</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.019104587680782</v>
+        <v>0.9868238468022855</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.451590259920866</v>
+        <v>5.432221815393768</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232975</v>
+        <v>3.870204928232972</v>
       </c>
       <c r="C2097" t="n">
         <v>4.849174544003525</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.264019505874185</v>
+        <v>-5.319932977658087</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.743210317340103</v>
+        <v>2.720844928626541</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.019104587680782</v>
+        <v>0.9868238468022855</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.460637296611994</v>
+        <v>5.441268852084896</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179679</v>
+        <v>3.855534437179675</v>
       </c>
       <c r="C2098" t="n">
         <v>4.850032008989646</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.326727422348743</v>
+        <v>-5.382640894132646</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.718984615736401</v>
+        <v>2.69661922702284</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9563966712062243</v>
+        <v>0.9241159303277278</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.42387001171338</v>
+        <v>5.404501567186283</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967726</v>
+        <v>3.884687848967722</v>
       </c>
       <c r="C2099" t="n">
         <v>4.812941425779998</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.27871929850505</v>
+        <v>-5.334632770288953</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.70109728206423</v>
+        <v>2.678731893350669</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9563966712062243</v>
+        <v>0.9241159303277278</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.386779428503733</v>
+        <v>5.367410983976635</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018617</v>
+        <v>3.895362357018613</v>
       </c>
       <c r="C2100" t="n">
         <v>4.816873679337949</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.199893641321459</v>
+        <v>-5.255807113105362</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.736559798495617</v>
+        <v>2.714194409782056</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.035222328389815</v>
+        <v>1.002941587511318</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.438007076371838</v>
+        <v>5.41863863184474</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.89161098107514</v>
+        <v>3.891610981075137</v>
       </c>
       <c r="C2101" t="n">
         <v>4.811772771944986</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.007958840067586</v>
+        <v>-5.063872311851489</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.808232811604204</v>
+        <v>2.785867422890642</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.035222328389815</v>
+        <v>1.002941587511318</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.432906168978874</v>
+        <v>5.413537724451777</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.87243249343545</v>
+        <v>3.872432493435446</v>
       </c>
       <c r="C2102" t="n">
         <v>4.807126681334081</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.889785462049659</v>
+        <v>-4.945698933833562</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.850856072200469</v>
+        <v>2.828490683486908</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.153395706407742</v>
+        <v>1.121114965529245</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.499164105178727</v>
+        <v>5.479795660651629</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917738</v>
+        <v>3.859571723917735</v>
       </c>
       <c r="C2103" t="n">
         <v>4.836215274197108</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.776370779266927</v>
+        <v>-4.83228425105083</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.925310538176589</v>
+        <v>2.902945149463028</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.266810389190473</v>
+        <v>1.234529648311977</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.596301507711392</v>
+        <v>5.576933063184294</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.828006274013644</v>
+        <v>3.82800627401364</v>
       </c>
       <c r="C2104" t="n">
         <v>4.829775497208285</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.749321741573674</v>
+        <v>-4.805235213357577</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.929690376265067</v>
+        <v>2.907324987551506</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.293859426883727</v>
+        <v>1.26157868600523</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.606091153338522</v>
+        <v>5.586722708811424</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.823987445263775</v>
+        <v>3.823987445263771</v>
       </c>
       <c r="C2105" t="n">
         <v>4.829775497208285</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.755355021760444</v>
+        <v>-4.811268493544347</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.927277064190359</v>
+        <v>2.904911675476798</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.293859426883727</v>
+        <v>1.26157868600523</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.606091153338522</v>
+        <v>5.586722708811424</v>
       </c>
     </row>
     <row r="2106">
@@ -49989,16 +49989,16 @@
         <v>4.833413664350697</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.807206797333605</v>
+        <v>-4.863120269117508</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.910174521103507</v>
+        <v>2.887809132389946</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.242007651310566</v>
+        <v>1.209726910432069</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.578618255137037</v>
+        <v>5.55924981060994</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.781574640813158</v>
+        <v>3.7842047436203</v>
       </c>
       <c r="C2107" t="n">
-        <v>4.858939388032587</v>
+        <v>4.854371717450096</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.807206797333605</v>
+        <v>-4.863120269117508</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.910174521103507</v>
+        <v>2.887809132389946</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.242007651310566</v>
+        <v>1.209726910432069</v>
       </c>
       <c r="G2107" t="n">
-        <v>4.852003185018955</v>
+        <v>4.847435514436464</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241004.xlsx
+++ b/tame_output/ON/bt/strategyON_20241004.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>64.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>110.9%</t>
+          <t>106.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>173.8%</t>
+          <t>162.6%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,17 +982,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-38.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.8%</t>
+          <t>421.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-647.9%</t>
+          <t>-650.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-87.4%</t>
+          <t>-97.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.8%</t>
+          <t>-292.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-103.0%</t>
+          <t>-96.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>118.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-18.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>104.5%</t>
         </is>
       </c>
     </row>
@@ -46976,10 +46976,10 @@
         <v>2.360186451293727</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.091205653566755</v>
+        <v>-4.122579786917309</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.723347765553277</v>
+        <v>0.7107981122130553</v>
       </c>
       <c r="F1975" t="n">
         <v>0.4708556194816057</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316251</v>
+        <v>3.833513460316252</v>
       </c>
       <c r="C1976" t="n">
         <v>2.360049318729163</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.046832521928186</v>
+        <v>-4.07820665527874</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7409598856441406</v>
+        <v>0.728410232303919</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5152287511201743</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105965</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.354443112867754</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.012101200609686</v>
+        <v>-4.04347533396024</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7492462083101314</v>
+        <v>0.7366965549699098</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5152287511201743</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.360824869895558</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.96444547004863</v>
+        <v>-3.995819603399184</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7746902575623584</v>
+        <v>0.7621406042221368</v>
       </c>
       <c r="F1978" t="n">
         <v>0.56288448168123</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.365717243270283</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.863927311549875</v>
+        <v>-3.895301444900429</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8197898943365851</v>
+        <v>0.8072402409963635</v>
       </c>
       <c r="F1979" t="n">
         <v>0.6634026401799845</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.352471915746155</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.848021982117523</v>
+        <v>-3.879396115468077</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8129066985853983</v>
+        <v>0.8003570452451767</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5842899794707457</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.356569618356784</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.803183580509125</v>
+        <v>-3.834557713859679</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8349397618393861</v>
+        <v>0.8223901084991645</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5888334124156152</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.360730557987862</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.822682036751133</v>
+        <v>-3.854056170101687</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8313013189736609</v>
+        <v>0.8187516656334393</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5407487711357108</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.366610160515699</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.778479199665232</v>
+        <v>-3.809853333015786</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8548620563358582</v>
+        <v>0.8423124029956366</v>
       </c>
       <c r="F1983" t="n">
         <v>0.5849516082216113</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.365020160984947</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.786038865502279</v>
+        <v>-3.817412998852833</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.850248190470287</v>
+        <v>0.8376985371300654</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6397550122314306</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.416267926167986</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.627747447963007</v>
+        <v>-3.659121581313561</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9648125226690354</v>
+        <v>0.9522628693288138</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6397550122314306</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.414708630762239</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.420105444328531</v>
+        <v>-3.451479577679085</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.046310028717079</v>
+        <v>1.033760375376857</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8473970158659068</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.409656859000509</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.369073351606003</v>
+        <v>-3.400447484956557</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.06167109404436</v>
+        <v>1.049121440704139</v>
       </c>
       <c r="F1987" t="n">
         <v>0.8984291085884347</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.426844263093214</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.303849170478797</v>
+        <v>-3.335223303829351</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.104948170587948</v>
+        <v>1.092398517247726</v>
       </c>
       <c r="F1988" t="n">
         <v>0.9636532897156403</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.422805235392495</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.266422150407663</v>
+        <v>-3.297796283758217</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.115879950915681</v>
+        <v>1.10333029757546</v>
       </c>
       <c r="F1989" t="n">
         <v>0.968904827744822</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.424062027723735</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.265064165434118</v>
+        <v>-3.296438298784672</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.11767993723634</v>
+        <v>1.105130283896118</v>
       </c>
       <c r="F1990" t="n">
         <v>1.043242953282641</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.584619798744946</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.236650902334234</v>
+        <v>-3.268025035684788</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.289603013497504</v>
+        <v>1.277053360157282</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9842673905362118</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
         <v>2.704732707962763</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.161868641309221</v>
+        <v>-3.193242774659776</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.439628827125326</v>
+        <v>1.427079173785105</v>
       </c>
       <c r="F1992" t="n">
         <v>1.059049651561224</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>2.696440683976622</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.135784557045413</v>
+        <v>-3.167158690395968</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.441770436844709</v>
+        <v>1.429220783504487</v>
       </c>
       <c r="F1993" t="n">
         <v>1.059049651561224</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
         <v>2.694633879560401</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.047906643936293</v>
+        <v>-3.079280777286847</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.475114797672136</v>
+        <v>1.462565144331915</v>
       </c>
       <c r="F1994" t="n">
         <v>1.174975293984576</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959858</v>
       </c>
       <c r="C1995" t="n">
         <v>2.712188285287193</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.03901418254301</v>
+        <v>-3.070388315893564</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.496226187956241</v>
+        <v>1.483676534616019</v>
       </c>
       <c r="F1995" t="n">
         <v>1.174975293984576</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
         <v>2.704043332691777</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.207490299512888</v>
+        <v>-3.238864432863442</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.420690788572874</v>
+        <v>1.408141135232652</v>
       </c>
       <c r="F1996" t="n">
         <v>1.147027458267995</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>2.685313029879639</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.761234106883448</v>
+        <v>-2.792608240234002</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.580462962812512</v>
+        <v>1.56791330947229</v>
       </c>
       <c r="F1997" t="n">
         <v>1.052308788598362</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>2.675977052376543</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.738513003200295</v>
+        <v>-2.76988713655085</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.580215426782677</v>
+        <v>1.567665773442456</v>
       </c>
       <c r="F1998" t="n">
         <v>1.052308788598362</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777674</v>
       </c>
       <c r="C1999" t="n">
         <v>2.834883178227712</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.867714816494338</v>
+        <v>-2.899088949844892</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.687440827316229</v>
+        <v>1.674891173976008</v>
       </c>
       <c r="F1999" t="n">
         <v>0.92310697530432</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644414</v>
       </c>
       <c r="C2000" t="n">
         <v>2.871961000721359</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.893589214968364</v>
+        <v>-2.924963348318918</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.714168890420265</v>
+        <v>1.701619237080044</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9680185840160611</v>
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.868636356710904</v>
+        <v>2.75516893185157</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.88653452475319</v>
+        <v>-2.928849488181983</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.71366612249588</v>
+        <v>1.583272712265029</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9750732742312349</v>
+        <v>0.9641324441529955</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.453680321249645</v>
+        <v>3.333648398343368</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.878642510355645</v>
+        <v>2.765175085496312</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.859583300426702</v>
+        <v>-2.901898263855495</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.734452765871217</v>
+        <v>1.604059355640366</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9899536202589541</v>
+        <v>0.9790127901807146</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.472614682511018</v>
+        <v>3.352582759604741</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.062745642500605</v>
+        <v>2.949278217641272</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.881127528257489</v>
+        <v>-2.923442491686282</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.909938206883862</v>
+        <v>1.779544796653011</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9899536202589541</v>
+        <v>0.9790127901807146</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.656717814655978</v>
+        <v>3.536685891749701</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.054862337403598</v>
+        <v>2.941394912544265</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.903535646062361</v>
+        <v>-2.945850609491155</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.893091654664906</v>
+        <v>1.762698244434055</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9899536202589541</v>
+        <v>0.9790127901807146</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.648834509558971</v>
+        <v>3.528802586652694</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.056916336953236</v>
+        <v>2.943448912093902</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.931759881639961</v>
+        <v>-2.974074845068755</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.883855959983503</v>
+        <v>1.753462549752652</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.007930372710263</v>
+        <v>0.9969895426320232</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.661674560579394</v>
+        <v>3.541642637673116</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.113170054675083</v>
+        <v>2.999702629815749</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.941200807528491</v>
+        <v>-2.983515770957285</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.936333307349939</v>
+        <v>1.805939897119088</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.130357490253654</v>
+        <v>1.119416660175415</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.791384548827275</v>
+        <v>3.671352625920998</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.116061149220384</v>
+        <v>3.00259372436105</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.147439745316925</v>
+        <v>-3.189754708745718</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.856728826779866</v>
+        <v>1.726335416549015</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9241185524652205</v>
+        <v>0.9131777223869808</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.670532280699516</v>
+        <v>3.550500357793239</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347708</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.114172962114159</v>
+        <v>3.000705537254825</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.223769722917831</v>
+        <v>-3.266084686346624</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.824308648633279</v>
+        <v>1.693915238402428</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9241185524652205</v>
+        <v>0.9131777223869808</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.668644093593291</v>
+        <v>3.548612170687014</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887753</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.108993191717021</v>
+        <v>2.995525766857688</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.37872650831796</v>
+        <v>-3.421041471746753</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.757146164076089</v>
+        <v>1.626752753845238</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7691617670650912</v>
+        <v>0.7582209369868516</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.570490251956076</v>
+        <v>3.450458329049799</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343071</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.107427201927174</v>
+        <v>2.99395977706784</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.540294933845215</v>
+        <v>-3.582609897274009</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.690952804075339</v>
+        <v>1.560559393844489</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6423788432672118</v>
+        <v>0.6314380131889722</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.492854507887501</v>
+        <v>3.372822584981224</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389354</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.120500608793092</v>
+        <v>3.007033183933759</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.648595595715335</v>
+        <v>-3.690910559144128</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.66070594619321</v>
+        <v>1.530312535962359</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6423788432672118</v>
+        <v>0.6314380131889722</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.505927914753419</v>
+        <v>3.385895991847142</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.112505805576032</v>
+        <v>2.999038380716699</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.808146668478852</v>
+        <v>-3.850461631907645</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.588890713870744</v>
+        <v>1.458497303639892</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4901011764054604</v>
+        <v>0.4791603463272207</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.406566511419308</v>
+        <v>3.286534588513031</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.111029846703034</v>
+        <v>2.997562421843701</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.836047455588325</v>
+        <v>-3.878362419017118</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.576254440153956</v>
+        <v>1.445861029923105</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4555042522625256</v>
+        <v>0.4445634221842859</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.38433239806055</v>
+        <v>3.264300475154272</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.107794290680233</v>
+        <v>2.994326865820899</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.958573558291218</v>
+        <v>-4.000888521720013</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.524008443049998</v>
+        <v>1.393615032819147</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3329781495596317</v>
+        <v>0.322037319481392</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.307581180416012</v>
+        <v>3.187549257509735</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.174500250270737</v>
+        <v>3.061032825411403</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.189088054476807</v>
+        <v>-4.231403017905601</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.498508604166266</v>
+        <v>1.368115193935415</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.102463653374043</v>
+        <v>0.0915228232958033</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.235978442295163</v>
+        <v>3.115946519388885</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814666</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.314811969272584</v>
+        <v>3.20134454441325</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.537833139701251</v>
+        <v>-4.580148103130044</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.499322289078336</v>
+        <v>1.368928878847484</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.0172251306230945</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.311041388945671</v>
+        <v>3.191009466039394</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.383792238418224</v>
+        <v>3.27032481355889</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.691819557477391</v>
+        <v>-4.734134520906185</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.506707991113519</v>
+        <v>1.376314580882668</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.0172251306230945</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.380021658091311</v>
+        <v>3.259989735185034</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.369843440538344</v>
+        <v>3.256376015679011</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.8964189923404</v>
+        <v>-4.938733955769194</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.410919419288436</v>
+        <v>1.280526009057585</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.0172251306230945</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.366072860211432</v>
+        <v>3.246040937305155</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.381713929593758</v>
+        <v>3.268246504734425</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.148894146348124</v>
+        <v>-5.191209109776918</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.321799846740761</v>
+        <v>1.19140643650991</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.0172251306230945</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.377943349266846</v>
+        <v>3.257911426360569</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.382924464112702</v>
+        <v>3.269457039253369</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.441789902827536</v>
+        <v>-5.48410486625633</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.205852078667939</v>
+        <v>1.075458668437089</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.0172251306230945</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.37915388378579</v>
+        <v>3.259121960879512</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.387046206340024</v>
+        <v>3.27357878148069</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.628454030962344</v>
+        <v>-5.670768994391138</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.135308169641338</v>
+        <v>1.004914759410487</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.03302327136941474</v>
+        <v>-0.04396410144765439</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.367232243518375</v>
+        <v>3.247200320612098</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.382124059076213</v>
+        <v>3.268656634216879</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.774474717876307</v>
+        <v>-5.8167896813051</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.071977747611943</v>
+        <v>0.9415843373810913</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.04210636316327171</v>
+        <v>-0.05304719324151136</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.35686024117825</v>
+        <v>3.236828318271973</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.544328115775257</v>
+        <v>3.430860690915924</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.866188726985891</v>
+        <v>-5.908503690414685</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.197496200667153</v>
+        <v>1.067102790436302</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.04210636316327171</v>
+        <v>-0.05304719324151136</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.519064297877294</v>
+        <v>3.399032374971017</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071552</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.539174753739071</v>
+        <v>3.425707328879738</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.897840386045861</v>
+        <v>-5.940155349474654</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.179682175006979</v>
+        <v>1.049288764776128</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.04727482040771191</v>
+        <v>-0.05821565048595156</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.510809861494444</v>
+        <v>3.390777938588167</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.549404171307562</v>
+        <v>3.435936746448229</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.966906440618797</v>
+        <v>-6.009221404047591</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.162285170746296</v>
+        <v>1.031891760515444</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1096456979013219</v>
+        <v>-0.1205865279795616</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.483616752566769</v>
+        <v>3.363584829660492</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332695</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.558329809763465</v>
+        <v>3.444862384904131</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.068882562867205</v>
+        <v>-6.012879377696163</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.130420360302835</v>
+        <v>1.039354209511918</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2116218201497295</v>
+        <v>-0.1242445016281334</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.431356717673627</v>
+        <v>3.370315683927251</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231812</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.55048269700764</v>
+        <v>3.437015272148307</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.958876279389983</v>
+        <v>-5.902873094218942</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.166575760937899</v>
+        <v>1.075509610146982</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1884172482324543</v>
+        <v>-0.1010399297108582</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.437432348068168</v>
+        <v>3.376391314321792</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.554732707729614</v>
+        <v>3.441265282870281</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.971405984501862</v>
+        <v>-5.91540279933082</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.165813889615122</v>
+        <v>1.074747738824205</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2022437476989773</v>
+        <v>-0.1148664291773812</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.433386459110229</v>
+        <v>3.372345425363853</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.56199359061215</v>
+        <v>3.448526165752817</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.669959259030025</v>
+        <v>-5.613956073858983</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.293653462686393</v>
+        <v>1.202587311895476</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.09920297777285991</v>
+        <v>0.186580296294456</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.621515377275867</v>
+        <v>3.560474343529491</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.562964768364861</v>
+        <v>3.449497343505528</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.694549503265208</v>
+        <v>-5.638546318094167</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.28478854274503</v>
+        <v>1.193722391954113</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.09920297777285991</v>
+        <v>0.186580296294456</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.622486555028577</v>
+        <v>3.561445521282201</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.563807672744617</v>
+        <v>3.450340247885283</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.643511127258688</v>
+        <v>-5.587507942087647</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.306046797527393</v>
+        <v>1.214980646736477</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.09920297777285991</v>
+        <v>0.186580296294456</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.623329459408333</v>
+        <v>3.562288425661957</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.582845771618762</v>
+        <v>3.469378346759429</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.614662450435228</v>
+        <v>-5.558659265264186</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.336624367130923</v>
+        <v>1.245558216340006</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1280516545963202</v>
+        <v>0.2154289731179163</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.659676764376554</v>
+        <v>3.598635730630179</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.399029767742697</v>
+        <v>3.285562342883363</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.518027538416588</v>
+        <v>-5.462024353245546</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.191462328062313</v>
+        <v>1.100396177271397</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2246865666149601</v>
+        <v>0.3120638851365563</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.533841707711673</v>
+        <v>3.472800673965297</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077642</v>
+        <v>3.80468896107764</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.402531811816661</v>
+        <v>3.289064386957327</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.44898952746812</v>
+        <v>-5.392986342297078</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.222579576515665</v>
+        <v>1.131513425724748</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2937245775634282</v>
+        <v>0.3811018960850243</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.578766558354718</v>
+        <v>3.517725524608342</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833462</v>
+        <v>3.77502886083346</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.386958630892743</v>
+        <v>3.27349120603341</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.430202427099181</v>
+        <v>-5.37419924192814</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.214521235739323</v>
+        <v>1.123455084948406</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3125116779323667</v>
+        <v>0.3998889964539628</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.574465637652164</v>
+        <v>3.513424603905788</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077624</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.386146341329173</v>
+        <v>3.27267891646984</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.353103825557309</v>
+        <v>-5.297100640386267</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.244548386792502</v>
+        <v>1.153482236001585</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3125116779323667</v>
+        <v>0.3998889964539628</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.573653348088593</v>
+        <v>3.512612314342217</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147906</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.396015120454245</v>
+        <v>3.282547695594912</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.363489020447198</v>
+        <v>-5.307485835276156</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.250263087961618</v>
+        <v>1.159196937170702</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3021264830424774</v>
+        <v>0.3895038015640735</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.577291010279732</v>
+        <v>3.516249976533357</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735285</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.466852126230671</v>
+        <v>3.353384701371337</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.382077179169423</v>
+        <v>-5.326073993998381</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.313664830249154</v>
+        <v>1.222598679458236</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.283538324320252</v>
+        <v>0.3709156428418481</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.636975120822822</v>
+        <v>3.575934087076446</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.85512053549655</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.463721137048969</v>
+        <v>3.350253712189636</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.382375725865459</v>
+        <v>-5.326372540694417</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.310414422389038</v>
+        <v>1.219348271598121</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2832397776242161</v>
+        <v>0.3706170961458122</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.633665003623499</v>
+        <v>3.572623969877123</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.81564321210886</v>
+        <v>3.815643212108856</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.468252031988361</v>
+        <v>3.354784607129027</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.281552592175031</v>
+        <v>-5.22554940700399</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.3552745708046</v>
+        <v>1.264208420013683</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2957039931085699</v>
+        <v>0.3830813116301661</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.645674427853503</v>
+        <v>3.584633394107127</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121471</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.468381285466904</v>
+        <v>3.35491386060757</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.090771231422623</v>
+        <v>-5.034768046251582</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.431716368584107</v>
+        <v>1.34065021779319</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4864853538609773</v>
+        <v>0.5738626723825735</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.76027249778349</v>
+        <v>3.699231464037115</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906084</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.4482181312045</v>
+        <v>3.334750706345167</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.983807873573202</v>
+        <v>-4.92780468840216</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.454338557461472</v>
+        <v>1.363272406670555</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5449499618207787</v>
+        <v>0.632327280342375</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.775188108296968</v>
+        <v>3.714147074550592</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912989</v>
+        <v>3.785761685912985</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.483185067816559</v>
+        <v>3.369717642957225</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.928477285671439</v>
+        <v>-4.872474100500398</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.511437729234235</v>
+        <v>1.420371578443318</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6002805497225409</v>
+        <v>0.6876578682441371</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.843353397650084</v>
+        <v>3.782312363903708</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539898</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.476871635717997</v>
+        <v>3.363404210858663</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.916423158758477</v>
+        <v>-4.860419973587435</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.509945947900858</v>
+        <v>1.418879797109941</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6123346766355037</v>
+        <v>0.6997119951570999</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.844272441699299</v>
+        <v>3.783231407952923</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811013</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.478752265902132</v>
+        <v>3.365284841042799</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.993778648886446</v>
+        <v>-4.937775463715404</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.480884382033806</v>
+        <v>1.389818231242889</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5349791865075343</v>
+        <v>0.6223565050291305</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.799739777806653</v>
+        <v>3.738698744060278</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382924</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.491603291780015</v>
+        <v>3.378135866920681</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.925730086194916</v>
+        <v>-4.869726901023874</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.5209548329883</v>
+        <v>1.429888682197384</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6904050677206603</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.853419941299454</v>
+        <v>3.792378907553078</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013431</v>
+        <v>3.645256780013428</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.511805961953609</v>
+        <v>3.398338537094276</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.157330479364417</v>
+        <v>-5.101327294193375</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.448517345894095</v>
+        <v>1.357451195103178</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6904050677206603</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.873622611473048</v>
+        <v>3.812581577726672</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498964</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.495412198020491</v>
+        <v>3.381944773161158</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.207382024893636</v>
+        <v>-5.151378839722595</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.412102963749288</v>
+        <v>1.321036812958372</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6904050677206603</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.85722884753993</v>
+        <v>3.796187813793554</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800098</v>
+        <v>3.670048702800093</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.455664111613958</v>
+        <v>3.342196686754624</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.382488857470081</v>
+        <v>-5.326485672299039</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.302312144312177</v>
+        <v>1.21124599352126</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6904050677206603</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.817480761133397</v>
+        <v>3.756439727387021</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.74557314866085</v>
+        <v>3.745573148660846</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.462686730610898</v>
+        <v>3.349219305751564</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.186388704039558</v>
+        <v>-5.130385518868517</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.387774824681327</v>
+        <v>1.296708673890409</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.799127902629587</v>
+        <v>0.8865052211511832</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.94216347218865</v>
+        <v>3.881122438442274</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.730570473395083</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.561857730183802</v>
+        <v>3.448390305324469</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.033363311926274</v>
+        <v>-4.977360126755232</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.548155981099545</v>
+        <v>1.457089830308628</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9521532947428711</v>
+        <v>1.039530613264467</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.133149707029525</v>
+        <v>4.072108673283149</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791145</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.749323955092095</v>
+        <v>3.635856530232761</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.061670625799544</v>
+        <v>-5.005667440628502</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.724299280458529</v>
+        <v>1.633233129667612</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9521532947428711</v>
+        <v>1.039530613264467</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.320615931937818</v>
+        <v>4.259574898191442</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620431</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.718726906446177</v>
+        <v>3.605259481586844</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.228263850913066</v>
+        <v>-5.172260665742025</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.627064941767203</v>
+        <v>1.535998790976286</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.8729373881509448</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.190062948223787</v>
+        <v>4.129021914477411</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285644</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.722403309107895</v>
+        <v>3.608935884248562</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.2052280575515</v>
+        <v>-5.149224872380459</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.639955661773547</v>
+        <v>1.54888951098263</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.8729373881509448</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.193739350885505</v>
+        <v>4.132698317139129</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399465</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.72002136423139</v>
+        <v>3.606553939372057</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.175982077095804</v>
+        <v>-5.119978891924762</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.649272109079321</v>
+        <v>1.558205958288404</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.8729373881509448</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.191357406009</v>
+        <v>4.130316372262624</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.717314603389025</v>
+        <v>3.603847178529692</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.282907624973655</v>
+        <v>-5.226904439802613</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.603795129085816</v>
+        <v>1.512728978294898</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6786345217514974</v>
+        <v>0.7660118402730934</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.124495316439925</v>
+        <v>4.063454282693549</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701002</v>
+        <v>3.689942600700999</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.71874340553226</v>
+        <v>3.605275980672926</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.427926183480904</v>
+        <v>-5.371922998309862</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.54721650782615</v>
+        <v>1.456150357035233</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5336159632442489</v>
+        <v>0.6209932817658449</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.038912983478809</v>
+        <v>3.977871949732434</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.818674644790013</v>
+        <v>3.705207219930679</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.546267949265621</v>
+        <v>-5.490264764094579</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.599811040770016</v>
+        <v>1.508744889979099</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.631679320328735</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.145255845874297</v>
+        <v>4.084214812127921</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790806</v>
+        <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.816460341915952</v>
+        <v>3.702992917056618</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.597678371586329</v>
+        <v>-5.541675186415287</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.577032568967672</v>
+        <v>1.485966418176755</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.631679320328735</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.143041543000235</v>
+        <v>4.082000509253859</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437335</v>
+        <v>3.704757949437332</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.816363469990241</v>
+        <v>3.702896045130907</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.677097822794081</v>
+        <v>-5.621094637623039</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.545167916558861</v>
+        <v>1.454101765767944</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.631679320328735</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.142944671074525</v>
+        <v>4.081903637328149</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298403</v>
+        <v>3.736804952298401</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.816357363548284</v>
+        <v>3.70288993868895</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.772560820711298</v>
+        <v>-5.716557635540257</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.506976610950017</v>
+        <v>1.4159104601591</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.631679320328735</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.142938564632567</v>
+        <v>4.081897530886192</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218005</v>
+        <v>3.715372960218003</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.814453760110895</v>
+        <v>3.700986335251561</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.708184909860583</v>
+        <v>-5.652181724689542</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.530823371852913</v>
+        <v>1.439757221061996</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6086779126578541</v>
+        <v>0.6960552311794501</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.179660507705607</v>
+        <v>4.118619473959232</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353541</v>
+        <v>3.736089413353539</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.820187577858621</v>
+        <v>3.706720152999288</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.763554071992777</v>
+        <v>-5.707550886821736</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.514409524747762</v>
+        <v>1.423343373956846</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6086779126578541</v>
+        <v>0.6960552311794501</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.185394325453334</v>
+        <v>4.124353291706958</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113284</v>
+        <v>3.736822870113282</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.819725941201554</v>
+        <v>3.70625851634222</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.781772538990386</v>
+        <v>-5.725769353819344</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.506660501291651</v>
+        <v>1.415594350500735</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.670948793923608</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.169868826442761</v>
+        <v>4.108827792696385</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113692</v>
+        <v>3.790272500113691</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.839600334051872</v>
+        <v>3.726132909192539</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.743089103646455</v>
+        <v>-5.687085918475414</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.542008268279542</v>
+        <v>1.450942117488625</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.670948793923608</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.18974321929308</v>
+        <v>4.128702185546704</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016437</v>
+        <v>3.794486844016436</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.8233010345766</v>
+        <v>3.709833609717267</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.637054108441146</v>
+        <v>-5.581050923270104</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.568122966886394</v>
+        <v>1.477056816095477</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.670948793923608</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.173443919817807</v>
+        <v>4.112402886071432</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307669</v>
+        <v>3.794705093307668</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.825731984040646</v>
+        <v>3.712264559181313</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.453842445308051</v>
+        <v>-5.397839260137009</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.643838581603678</v>
+        <v>1.552772430812761</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.670948793923608</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.175874869281854</v>
+        <v>4.114833835535477</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863549</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.808676390120023</v>
+        <v>3.69520896526069</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.3821209982942</v>
+        <v>-5.326117813123158</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.655471566488595</v>
+        <v>1.564405415697678</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6552929224158626</v>
+        <v>0.7426702409374586</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.201852143569541</v>
+        <v>4.140811109823165</v>
       </c>
     </row>
     <row r="2069">
@@ -49135,19 +49135,19 @@
         <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.755592136041195</v>
+        <v>3.642124711181861</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.359747972686494</v>
+        <v>-5.303744787515452</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.61133652265285</v>
+        <v>1.520270371861932</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6665486735287641</v>
+        <v>0.7539259920503601</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.155521340158454</v>
+        <v>4.094480306412078</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.71560744645673</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
-        <v>3.94079034092655</v>
+        <v>3.827322916067216</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.392764268597238</v>
+        <v>-5.336761083426197</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.783328209173907</v>
+        <v>1.69226205838299</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5971112968620125</v>
+        <v>0.6844886153836085</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.299057119043757</v>
+        <v>4.238016085297382</v>
       </c>
     </row>
     <row r="2071">
@@ -49181,19 +49181,19 @@
         <v>3.71376253688368</v>
       </c>
       <c r="C2071" t="n">
-        <v>3.932711566754799</v>
+        <v>3.819244141895466</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.38123663294763</v>
+        <v>-5.325233447776588</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.779860489261999</v>
+        <v>1.688794338471083</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6561119550633749</v>
+        <v>0.743489273584971</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.326378739792824</v>
+        <v>4.265337706046449</v>
       </c>
     </row>
     <row r="2072">
@@ -49204,19 +49204,19 @@
         <v>3.717150699236301</v>
       </c>
       <c r="C2072" t="n">
-        <v>3.936379679276587</v>
+        <v>3.822912254417254</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.478578134289998</v>
+        <v>-5.422574949118957</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.74459200124684</v>
+        <v>1.653525850455924</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6116917728978866</v>
+        <v>0.6990690914194826</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.303394743015319</v>
+        <v>4.242353709268945</v>
       </c>
     </row>
     <row r="2073">
@@ -49227,19 +49227,19 @@
         <v>3.705201079427688</v>
       </c>
       <c r="C2073" t="n">
-        <v>3.937630761469426</v>
+        <v>3.824163336610093</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.564434163629965</v>
+        <v>-5.508430978458923</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.711500671703692</v>
+        <v>1.620434520912776</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5693157036717515</v>
+        <v>0.6566930221933476</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.279220183672477</v>
+        <v>4.218179149926102</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.920049963289927</v>
+        <v>3.806582538430595</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.573270961046084</v>
+        <v>-5.517267775875043</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.690385154557746</v>
+        <v>1.59931900376683</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5618735310304008</v>
+        <v>0.6492508495519969</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.257174081908168</v>
+        <v>4.196133048161793</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.715544411667458</v>
       </c>
       <c r="C2075" t="n">
-        <v>3.930214474334977</v>
+        <v>3.816747049475644</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.664653523611543</v>
+        <v>-5.608650338440501</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.663996640576612</v>
+        <v>1.572930489785696</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5253086463110561</v>
+        <v>0.6126859648326521</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.245399662121611</v>
+        <v>4.184358628375236</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889195</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.032342732159245</v>
+        <v>3.918875307299912</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.652946805624537</v>
+        <v>-5.596943620453495</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.770807585595682</v>
+        <v>1.679741434804765</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.6243926828196585</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.354551950738083</v>
+        <v>4.293510916991707</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409571</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.03537507089065</v>
+        <v>3.921907646031316</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.723858879366814</v>
+        <v>-5.667855694195772</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.745475094830176</v>
+        <v>1.65440894403926</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.6243926828196585</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.357584289469488</v>
+        <v>4.296543255723112</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.248279904168708</v>
+        <v>4.134812479309375</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.734174977533166</v>
+        <v>-5.678171792362124</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.954253488841694</v>
+        <v>1.863187338050777</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.6243926828196585</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.570489122747546</v>
+        <v>4.50944808900117</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762291</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.247458571080798</v>
+        <v>4.133991146221464</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.734081009515793</v>
+        <v>-5.678077824344752</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.953469742960733</v>
+        <v>1.862403592169815</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.6247625441669765</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.569889706468026</v>
+        <v>4.50884867272165</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884084</v>
+        <v>3.800870306884083</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.241690557025152</v>
+        <v>4.128223132165818</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.877682173539179</v>
+        <v>-5.821678988368137</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.890261263295732</v>
+        <v>1.799195112504815</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.6247625441669765</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.56412169241238</v>
+        <v>4.503080658666004</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129648</v>
+        <v>3.671015692129647</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.241690557025152</v>
+        <v>4.128223132165818</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.87673375042114</v>
+        <v>-5.820730565250098</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.890640632542948</v>
+        <v>1.79957448175203</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.6247625441669765</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.56412169241238</v>
+        <v>4.503080658666004</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052351</v>
+        <v>3.904173816052349</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.254418165006244</v>
+        <v>4.14095074014691</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.977003568380161</v>
+        <v>-5.921000383209119</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.863260313340431</v>
+        <v>1.772194162549515</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.6247625441669765</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.576849300393472</v>
+        <v>4.515808266647096</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813495</v>
+        <v>3.740179607813493</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.256364163430631</v>
+        <v>4.142896738571298</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.971011321591349</v>
+        <v>-5.915008136420307</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.867603210480344</v>
+        <v>1.776537059689427</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.6247625441669765</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.57879529881786</v>
+        <v>4.517754265071484</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537944</v>
+        <v>3.765050796537942</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.2500182994484</v>
+        <v>4.136550874589067</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.882453360460581</v>
+        <v>-5.82645017528954</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.89668053095042</v>
+        <v>1.805614380159503</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.6247625441669765</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.572449434835629</v>
+        <v>4.511408401089253</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771816</v>
+        <v>3.758409170771814</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.249326976887396</v>
+        <v>4.135859552028062</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.864694282957507</v>
+        <v>-5.808691097786466</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.903092839390645</v>
+        <v>1.812026688599728</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.6247625441669765</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.571758112274624</v>
+        <v>4.510717078528248</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.801340597109721</v>
+        <v>3.80134059710972</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.262109162795983</v>
+        <v>4.148641737936649</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.765064131908439</v>
+        <v>-5.709060946737398</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.955727085718859</v>
+        <v>1.864660934927942</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.637015376694448</v>
+        <v>0.724392695216044</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.644318388812652</v>
+        <v>4.583277355066276</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546843996</v>
+        <v>3.798465546843994</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.451263428294709</v>
+        <v>4.337796003435376</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.814463640597451</v>
+        <v>-5.758460455426409</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.125121547741981</v>
+        <v>2.034055396951064</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6472742101261927</v>
+        <v>0.7346515286477887</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.839627954370425</v>
+        <v>4.778586920624049</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.77218650835186</v>
+        <v>3.772186508351858</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.438452101397571</v>
+        <v>4.324984676538238</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.607779166955075</v>
+        <v>-5.551775981784033</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.194984010301793</v>
+        <v>2.103917859510876</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8539586837685683</v>
+        <v>0.9413360022901643</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.950827311658712</v>
+        <v>4.889786277912337</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.76339283855127</v>
+        <v>3.763392838551268</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.440453615051676</v>
+        <v>4.326986190192343</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.641936061952601</v>
+        <v>-5.585932876781559</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.183322765956888</v>
+        <v>2.092256615165971</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.8577522327493519</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.90267856358833</v>
+        <v>4.841637529841954</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041111</v>
+        <v>3.805590565041109</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.793950729041343</v>
+        <v>4.68048330418201</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.549346582891144</v>
+        <v>-5.493343397720102</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.573855671571138</v>
+        <v>2.482789520780221</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.8577522327493519</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.256175677577997</v>
+        <v>5.195134643831621</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497403</v>
+        <v>3.832164354497402</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.798513840608447</v>
+        <v>4.685046415749113</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.622507186664289</v>
+        <v>-5.566504001493247</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.549154541628983</v>
+        <v>2.458088390838066</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.8297310327151088</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.243926069124555</v>
+        <v>5.182885035378178</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492295</v>
+        <v>3.858310890492294</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.848343781931974</v>
+        <v>4.734876357072641</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.570290876867947</v>
+        <v>-5.514287691696905</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.619871006871047</v>
+        <v>2.52880485608013</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.8297310327151088</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.293756010448082</v>
+        <v>5.232714976701706</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436477</v>
+        <v>3.844935596436476</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.857157752141985</v>
+        <v>4.743690327282652</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.538393359782702</v>
+        <v>-5.48239017461166</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.641443983915157</v>
+        <v>2.550377833124239</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7742512312787586</v>
+        <v>0.8616285498003546</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.32170849090924</v>
+        <v>5.260667457162865</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039486</v>
+        <v>3.848376866039485</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.852795336181182</v>
+        <v>4.739327911321848</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.553148683982842</v>
+        <v>-5.4971454988118</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.631179438274297</v>
+        <v>2.54011328748338</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7742512312787586</v>
+        <v>0.8616285498003546</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.317346074948437</v>
+        <v>5.256305041202062</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524481</v>
+        <v>3.86815311552448</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.843719839597462</v>
+        <v>4.730252414738128</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.50368406061293</v>
+        <v>-5.447680875441889</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.641889791038542</v>
+        <v>2.550823640247625</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8237158546486703</v>
+        <v>0.9110931731702663</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.337949352386664</v>
+        <v>5.276908318640288</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867955</v>
+        <v>3.849040239867954</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.840127507312396</v>
+        <v>4.726660082453063</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.340576068459315</v>
+        <v>-5.284572883288273</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.703540655614922</v>
+        <v>2.612474504824005</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.9868238468022855</v>
+        <v>1.074201165323882</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.432221815393768</v>
+        <v>5.371180781647392</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232972</v>
+        <v>3.870204928232969</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.849174544003525</v>
+        <v>4.735707119144191</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.319932977658087</v>
+        <v>-5.263929792487046</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.720844928626541</v>
+        <v>2.629778777835625</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.9868238468022855</v>
+        <v>1.074201165323882</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.441268852084896</v>
+        <v>5.38022781833852</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179675</v>
+        <v>3.855534437179672</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.850032008989646</v>
+        <v>4.736564584130313</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.382640894132646</v>
+        <v>-5.326637708961604</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.69661922702284</v>
+        <v>2.605553076231923</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9241159303277278</v>
+        <v>1.011493248849324</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.404501567186283</v>
+        <v>5.343460533439908</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967722</v>
+        <v>3.884687848967719</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.812941425779998</v>
+        <v>4.699474000920665</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.334632770288953</v>
+        <v>-5.278629585117911</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.678731893350669</v>
+        <v>2.587665742559752</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9241159303277278</v>
+        <v>1.011493248849324</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.367410983976635</v>
+        <v>5.306369950230259</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018613</v>
+        <v>3.89536235701861</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.816873679337949</v>
+        <v>4.703406254478615</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.255807113105362</v>
+        <v>-5.199803927934321</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.714194409782056</v>
+        <v>2.623128258991139</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.002941587511318</v>
+        <v>1.090318906032914</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.41863863184474</v>
+        <v>5.357597598098364</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075137</v>
+        <v>3.891610981075133</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.811772771944986</v>
+        <v>4.698305347085652</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.063872311851489</v>
+        <v>-5.007869126680447</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.785867422890642</v>
+        <v>2.694801272099725</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.002941587511318</v>
+        <v>1.090318906032914</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.413537724451777</v>
+        <v>5.352496690705401</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435446</v>
+        <v>3.872432493435443</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.807126681334081</v>
+        <v>4.693659256474747</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.945698933833562</v>
+        <v>-4.864506935193671</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.828490683486908</v>
+        <v>2.747500058083531</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.121114965529245</v>
+        <v>1.23368109751969</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.479795660651629</v>
+        <v>5.433867914986562</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917735</v>
+        <v>3.859571723917731</v>
       </c>
       <c r="C2103" t="n">
-        <v>4.836215274197108</v>
+        <v>4.722747849337774</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.83228425105083</v>
+        <v>-4.751092252410939</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.902945149463028</v>
+        <v>2.821954524059651</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.234529648311977</v>
+        <v>1.347095780302422</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.576933063184294</v>
+        <v>5.531005317519227</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.82800627401364</v>
+        <v>3.828006274013637</v>
       </c>
       <c r="C2104" t="n">
-        <v>4.829775497208285</v>
+        <v>4.716308072348951</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.805235213357577</v>
+        <v>-4.724043214717685</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.907324987551506</v>
+        <v>2.826334362148129</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.26157868600523</v>
+        <v>1.374144817995675</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.586722708811424</v>
+        <v>5.540794963146357</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.823987445263771</v>
+        <v>3.823987445263767</v>
       </c>
       <c r="C2105" t="n">
-        <v>4.829775497208285</v>
+        <v>4.716308072348951</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.811268493544347</v>
+        <v>-4.730076494904456</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.904911675476798</v>
+        <v>2.823921050073421</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.26157868600523</v>
+        <v>1.374144817995675</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.586722708811424</v>
+        <v>5.540794963146357</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.815657203170841</v>
+        <v>3.815657203170836</v>
       </c>
       <c r="C2106" t="n">
-        <v>4.833413664350697</v>
+        <v>4.719946239491364</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.863120269117508</v>
+        <v>-4.787537092154509</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.887809132389946</v>
+        <v>2.804574978315812</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.209726910432069</v>
+        <v>1.316684220745622</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.55924981060994</v>
+        <v>5.509956771938738</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.7842047436203</v>
+        <v>3.929591137075212</v>
       </c>
       <c r="C2107" t="n">
-        <v>4.854371717450096</v>
+        <v>4.741819126661224</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.863120269117508</v>
+        <v>-4.889938374116333</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.887809132389946</v>
+        <v>2.785487352700943</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.209726910432069</v>
+        <v>1.271960841405521</v>
       </c>
       <c r="G2107" t="n">
-        <v>4.847435514436464</v>
+        <v>5.504995631504537</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241004.xlsx
+++ b/tame_output/ON/bt/strategyON_20241004.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>106.5%</t>
+          <t>115.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>162.6%</t>
+          <t>189.2%</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-38.2%</t>
+          <t>-32.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-73.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.6%</t>
+          <t>421.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-650.6%</t>
+          <t>-649.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,37 +1145,37 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-97.7%</t>
+          <t>-70.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-292.9%</t>
+          <t>-204.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-96.8%</t>
+          <t>-96.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>118.3%</t>
+          <t>128.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-19.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>115.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>104.5%</t>
+          <t>131.4%</t>
         </is>
       </c>
     </row>
@@ -47571,19 +47571,19 @@
         <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.75516893185157</v>
+        <v>2.868636356710904</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.928849488181983</v>
+        <v>-2.917908658103744</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.583272712265029</v>
+        <v>1.701116469155658</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9641324441529955</v>
+        <v>0.9750732742312349</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.333648398343368</v>
+        <v>3.453680321249645</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.765175085496312</v>
+        <v>2.878642510355645</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.901898263855495</v>
+        <v>-2.890957433777256</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.604059355640366</v>
+        <v>1.721903112530995</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9790127901807146</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.352582759604741</v>
+        <v>3.472614682511018</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>2.949278217641272</v>
+        <v>3.062745642500605</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.923442491686282</v>
+        <v>-2.912501661608043</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.779544796653011</v>
+        <v>1.89738855354364</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9790127901807146</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.536685891749701</v>
+        <v>3.656717814655978</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
-        <v>2.941394912544265</v>
+        <v>3.054862337403598</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.945850609491155</v>
+        <v>-2.934909779412915</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.762698244434055</v>
+        <v>1.880542001324684</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9790127901807146</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.528802586652694</v>
+        <v>3.648834509558971</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
-        <v>2.943448912093902</v>
+        <v>3.056916336953236</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.974074845068755</v>
+        <v>-2.963134014990516</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.753462549752652</v>
+        <v>1.871306306643282</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9969895426320232</v>
+        <v>1.007930372710263</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.541642637673116</v>
+        <v>3.661674560579394</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
-        <v>2.999702629815749</v>
+        <v>3.113170054675083</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.983515770957285</v>
+        <v>-2.972574940879046</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.805939897119088</v>
+        <v>1.923783654009717</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.119416660175415</v>
+        <v>1.130357490253654</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.671352625920998</v>
+        <v>3.791384548827275</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.00259372436105</v>
+        <v>3.116061149220384</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.189754708745718</v>
+        <v>-3.178813878667479</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.726335416549015</v>
+        <v>1.844179173439644</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9131777223869808</v>
+        <v>0.9241185524652205</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.550500357793239</v>
+        <v>3.670532280699516</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347708</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.000705537254825</v>
+        <v>3.114172962114159</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.266084686346624</v>
+        <v>-3.255143856268385</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.693915238402428</v>
+        <v>1.811758995293057</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9131777223869808</v>
+        <v>0.9241185524652205</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.548612170687014</v>
+        <v>3.668644093593291</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887753</v>
+        <v>3.710654104887754</v>
       </c>
       <c r="C2009" t="n">
-        <v>2.995525766857688</v>
+        <v>3.108993191717021</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.421041471746753</v>
+        <v>-3.410100641668514</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.626752753845238</v>
+        <v>1.744596510735868</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7582209369868516</v>
+        <v>0.7691617670650912</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.450458329049799</v>
+        <v>3.570490251956076</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343071</v>
+        <v>3.712897612343072</v>
       </c>
       <c r="C2010" t="n">
-        <v>2.99395977706784</v>
+        <v>3.107427201927174</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.582609897274009</v>
+        <v>-3.571669067195769</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.560559393844489</v>
+        <v>1.678403150735118</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6314380131889722</v>
+        <v>0.6423788432672118</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.372822584981224</v>
+        <v>3.492854507887501</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389354</v>
+        <v>3.754596135389355</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.007033183933759</v>
+        <v>3.120500608793092</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.690910559144128</v>
+        <v>-3.679969729065889</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.530312535962359</v>
+        <v>1.648156292852989</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6314380131889722</v>
+        <v>0.6423788432672118</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.385895991847142</v>
+        <v>3.505927914753419</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
-        <v>2.999038380716699</v>
+        <v>3.112505805576032</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.850461631907645</v>
+        <v>-3.839520801829406</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.458497303639892</v>
+        <v>1.576341060530522</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4791603463272207</v>
+        <v>0.4901011764054604</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.286534588513031</v>
+        <v>3.406566511419308</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
-        <v>2.997562421843701</v>
+        <v>3.111029846703034</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.878362419017118</v>
+        <v>-3.867421588938879</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.445861029923105</v>
+        <v>1.563704786813735</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4445634221842859</v>
+        <v>0.4555042522625256</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.264300475154272</v>
+        <v>3.38433239806055</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
-        <v>2.994326865820899</v>
+        <v>3.107794290680233</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.000888521720013</v>
+        <v>-3.989947691641773</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.393615032819147</v>
+        <v>1.511458789709776</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.322037319481392</v>
+        <v>0.3329781495596317</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.187549257509735</v>
+        <v>3.307581180416012</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.061032825411403</v>
+        <v>3.174500250270737</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.231403017905601</v>
+        <v>-4.220462187827361</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.368115193935415</v>
+        <v>1.485958950826044</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.0915228232958033</v>
+        <v>0.102463653374043</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.115946519388885</v>
+        <v>3.235978442295163</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.20134454441325</v>
+        <v>3.314811969272584</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.580148103130044</v>
+        <v>-4.569207273051805</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.368928878847484</v>
+        <v>1.486772635738114</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.0172251306230945</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.191009466039394</v>
+        <v>3.311041388945671</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.27032481355889</v>
+        <v>3.383792238418224</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.734134520906185</v>
+        <v>-4.723193690827945</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.376314580882668</v>
+        <v>1.494158337773297</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.0172251306230945</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.259989735185034</v>
+        <v>3.380021658091311</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.256376015679011</v>
+        <v>3.369843440538344</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.938733955769194</v>
+        <v>-4.927793125690954</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.280526009057585</v>
+        <v>1.398369765948215</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.0172251306230945</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.246040937305155</v>
+        <v>3.366072860211432</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.268246504734425</v>
+        <v>3.381713929593758</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.191209109776918</v>
+        <v>-5.180268279698678</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.19140643650991</v>
+        <v>1.309250193400539</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.0172251306230945</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.257911426360569</v>
+        <v>3.377943349266846</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.269457039253369</v>
+        <v>3.382924464112702</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.48410486625633</v>
+        <v>-5.47316403617809</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.075458668437089</v>
+        <v>1.193302425327718</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.0172251306230945</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.259121960879512</v>
+        <v>3.37915388378579</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251945</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.27357878148069</v>
+        <v>3.387046206340024</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.670768994391138</v>
+        <v>-5.659828164312898</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.004914759410487</v>
+        <v>1.122758516301116</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.04396410144765439</v>
+        <v>-0.03302327136941474</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.247200320612098</v>
+        <v>3.367232243518375</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.268656634216879</v>
+        <v>3.382124059076213</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.8167896813051</v>
+        <v>-5.805848851226861</v>
       </c>
       <c r="E2022" t="n">
-        <v>0.9415843373810913</v>
+        <v>1.059428094271721</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.05304719324151136</v>
+        <v>-0.04210636316327171</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.236828318271973</v>
+        <v>3.35686024117825</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.430860690915924</v>
+        <v>3.544328115775257</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.908503690414685</v>
+        <v>-5.897562860336446</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.067102790436302</v>
+        <v>1.18494654732693</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.05304719324151136</v>
+        <v>-0.04210636316327171</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.399032374971017</v>
+        <v>3.519064297877294</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071552</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.425707328879738</v>
+        <v>3.539174753739071</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.940155349474654</v>
+        <v>-5.929214519396416</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.049288764776128</v>
+        <v>1.167132521666757</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.05821565048595156</v>
+        <v>-0.04727482040771191</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.390777938588167</v>
+        <v>3.510809861494444</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.435936746448229</v>
+        <v>3.549404171307562</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.009221404047591</v>
+        <v>-5.998280573969352</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.031891760515444</v>
+        <v>1.149735517406073</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1205865279795616</v>
+        <v>-0.1096456979013219</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.363584829660492</v>
+        <v>3.483616752566769</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332695</v>
+        <v>3.783632867332696</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.444862384904131</v>
+        <v>3.558329809763465</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.012879377696163</v>
+        <v>-6.10025669621776</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.039354209511918</v>
+        <v>1.117870706962613</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1242445016281334</v>
+        <v>-0.2116218201497295</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.370315683927251</v>
+        <v>3.431356717673627</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231812</v>
+        <v>3.798296784231813</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.437015272148307</v>
+        <v>3.55048269700764</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.902873094218942</v>
+        <v>-5.990250412740538</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.075509610146982</v>
+        <v>1.154026107597677</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1010399297108582</v>
+        <v>-0.1884172482324543</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.376391314321792</v>
+        <v>3.437432348068168</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.441265282870281</v>
+        <v>3.554732707729614</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.91540279933082</v>
+        <v>-6.002780117852417</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.074747738824205</v>
+        <v>1.1532642362749</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1148664291773812</v>
+        <v>-0.2022437476989773</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.372345425363853</v>
+        <v>3.433386459110229</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.448526165752817</v>
+        <v>3.56199359061215</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.613956073858983</v>
+        <v>-5.70133339238058</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.202587311895476</v>
+        <v>1.281103809346171</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.186580296294456</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.560474343529491</v>
+        <v>3.621515377275867</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.449497343505528</v>
+        <v>3.562964768364861</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.638546318094167</v>
+        <v>-5.725923636615764</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.193722391954113</v>
+        <v>1.272238889404808</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.186580296294456</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.561445521282201</v>
+        <v>3.622486555028577</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.450340247885283</v>
+        <v>3.563807672744617</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.587507942087647</v>
+        <v>-5.674885260609243</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.214980646736477</v>
+        <v>1.293497144187171</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.186580296294456</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.562288425661957</v>
+        <v>3.623329459408333</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.469378346759429</v>
+        <v>3.582845771618762</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.558659265264186</v>
+        <v>-5.646036583785783</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.245558216340006</v>
+        <v>1.324074713790701</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2154289731179163</v>
+        <v>0.1280516545963202</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.598635730630179</v>
+        <v>3.659676764376554</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.285562342883363</v>
+        <v>3.399029767742697</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.462024353245546</v>
+        <v>-5.549401671767143</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.100396177271397</v>
+        <v>1.178912674722091</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3120638851365563</v>
+        <v>0.2246865666149601</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.472800673965297</v>
+        <v>3.533841707711673</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80468896107764</v>
+        <v>3.804688961077642</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.289064386957327</v>
+        <v>3.402531811816661</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.392986342297078</v>
+        <v>-5.480363660818675</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.131513425724748</v>
+        <v>1.210029923175443</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3811018960850243</v>
+        <v>0.2937245775634282</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.517725524608342</v>
+        <v>3.578766558354718</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.77502886083346</v>
+        <v>3.775028860833463</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.27349120603341</v>
+        <v>3.386958630892743</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.37419924192814</v>
+        <v>-5.461576560449736</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.123455084948406</v>
+        <v>1.201971582399101</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3998889964539628</v>
+        <v>0.3125116779323667</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.513424603905788</v>
+        <v>3.574465637652164</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077624</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.27267891646984</v>
+        <v>3.386146341329173</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.297100640386267</v>
+        <v>-5.384477958907864</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.153482236001585</v>
+        <v>1.23199873345228</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3998889964539628</v>
+        <v>0.3125116779323667</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.512612314342217</v>
+        <v>3.573653348088593</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147906</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.282547695594912</v>
+        <v>3.396015120454245</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.307485835276156</v>
+        <v>-5.394863153797753</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.159196937170702</v>
+        <v>1.237713434621396</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3895038015640735</v>
+        <v>0.3021264830424774</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.516249976533357</v>
+        <v>3.577291010279732</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.834415493735285</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.353384701371337</v>
+        <v>3.466852126230671</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.326073993998381</v>
+        <v>-5.413451312519978</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.222598679458236</v>
+        <v>1.301115176908931</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3709156428418481</v>
+        <v>0.283538324320252</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.575934087076446</v>
+        <v>3.636975120822822</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.85512053549655</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.350253712189636</v>
+        <v>3.463721137048969</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.326372540694417</v>
+        <v>-5.413749859216014</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.219348271598121</v>
+        <v>1.297864769048815</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3706170961458122</v>
+        <v>0.2832397776242161</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.572623969877123</v>
+        <v>3.633665003623499</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108856</v>
+        <v>3.81564321210886</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.354784607129027</v>
+        <v>3.468252031988361</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.22554940700399</v>
+        <v>-5.312926725525586</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.264208420013683</v>
+        <v>1.342724917464378</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3830813116301661</v>
+        <v>0.2957039931085699</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.584633394107127</v>
+        <v>3.645674427853503</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121472</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.35491386060757</v>
+        <v>3.468381285466904</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.034768046251582</v>
+        <v>-5.122145364773178</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.34065021779319</v>
+        <v>1.419166715243884</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5738626723825735</v>
+        <v>0.4864853538609773</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.699231464037115</v>
+        <v>3.76027249778349</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906085</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.334750706345167</v>
+        <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.92780468840216</v>
+        <v>-5.015182006923757</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.363272406670555</v>
+        <v>1.44178890412125</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.632327280342375</v>
+        <v>0.5449499618207787</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.714147074550592</v>
+        <v>3.775188108296968</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912985</v>
+        <v>3.785761685912989</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.369717642957225</v>
+        <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.872474100500398</v>
+        <v>-4.959851419021994</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.420371578443318</v>
+        <v>1.498888075894013</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6876578682441371</v>
+        <v>0.6002805497225409</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.782312363903708</v>
+        <v>3.843353397650084</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539899</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.363404210858663</v>
+        <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.860419973587435</v>
+        <v>-4.947797292109032</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.418879797109941</v>
+        <v>1.497396294560636</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6997119951570999</v>
+        <v>0.6123346766355037</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.783231407952923</v>
+        <v>3.844272441699299</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811014</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.365284841042799</v>
+        <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.937775463715404</v>
+        <v>-5.025152782237001</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.389818231242889</v>
+        <v>1.468334728693584</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6223565050291305</v>
+        <v>0.5349791865075343</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.738698744060278</v>
+        <v>3.799739777806653</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382925</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.378135866920681</v>
+        <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.869726901023874</v>
+        <v>-4.957104219545471</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.429888682197384</v>
+        <v>1.508405179648078</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6904050677206603</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.792378907553078</v>
+        <v>3.853419941299454</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013428</v>
+        <v>3.645256780013432</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.398338537094276</v>
+        <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.101327294193375</v>
+        <v>-5.188704612714972</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.357451195103178</v>
+        <v>1.435967692553872</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6904050677206603</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.812581577726672</v>
+        <v>3.873622611473048</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498964</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.381944773161158</v>
+        <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.151378839722595</v>
+        <v>-5.238756158244191</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.321036812958372</v>
+        <v>1.399553310409066</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6904050677206603</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.796187813793554</v>
+        <v>3.85722884753993</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800093</v>
+        <v>3.670048702800098</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.342196686754624</v>
+        <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.326485672299039</v>
+        <v>-5.413862990820636</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.21124599352126</v>
+        <v>1.289762490971955</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6904050677206603</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.756439727387021</v>
+        <v>3.817480761133397</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660846</v>
+        <v>3.74557314866085</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.349219305751564</v>
+        <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.130385518868517</v>
+        <v>-5.217762837390113</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.296708673890409</v>
+        <v>1.375225171341104</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8865052211511832</v>
+        <v>0.799127902629587</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.881122438442274</v>
+        <v>3.94216347218865</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395083</v>
+        <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.448390305324469</v>
+        <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.977360126755232</v>
+        <v>-5.064737445276829</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.457089830308628</v>
+        <v>1.535606327759323</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.039530613264467</v>
+        <v>0.9521532947428711</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.072108673283149</v>
+        <v>4.133149707029525</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791145</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.635856530232761</v>
+        <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.005667440628502</v>
+        <v>-5.093044759150099</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.633233129667612</v>
+        <v>1.711749627118307</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.039530613264467</v>
+        <v>0.9521532947428711</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.259574898191442</v>
+        <v>4.320615931937818</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620431</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.605259481586844</v>
+        <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.172260665742025</v>
+        <v>-5.259637984263621</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.535998790976286</v>
+        <v>1.614515288426981</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8729373881509448</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.129021914477411</v>
+        <v>4.190062948223787</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285644</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.608935884248562</v>
+        <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.149224872380459</v>
+        <v>-5.236602190902055</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.54888951098263</v>
+        <v>1.627406008433325</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8729373881509448</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.132698317139129</v>
+        <v>4.193739350885505</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399465</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.606553939372057</v>
+        <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.119978891924762</v>
+        <v>-5.207356210446359</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.558205958288404</v>
+        <v>1.636722455739099</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8729373881509448</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.130316372262624</v>
+        <v>4.191357406009</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.699404642256372</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.603847178529692</v>
+        <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.226904439802613</v>
+        <v>-5.31428175832421</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.512728978294898</v>
+        <v>1.591245475745593</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7660118402730934</v>
+        <v>0.6786345217514974</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.063454282693549</v>
+        <v>4.124495316439925</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700999</v>
+        <v>3.689942600701002</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.605275980672926</v>
+        <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.371922998309862</v>
+        <v>-5.459300316831459</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.456150357035233</v>
+        <v>1.534666854485928</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6209932817658449</v>
+        <v>0.5336159632442489</v>
       </c>
       <c r="G2057" t="n">
-        <v>3.977871949732434</v>
+        <v>4.038912983478809</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71185242968701</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.705207219930679</v>
+        <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.490264764094579</v>
+        <v>-5.577642082616176</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.508744889979099</v>
+        <v>1.587261387429794</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.631679320328735</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.084214812127921</v>
+        <v>4.145255845874297</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790803</v>
+        <v>3.714879051790806</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.702992917056618</v>
+        <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.541675186415287</v>
+        <v>-5.629052504936884</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.485966418176755</v>
+        <v>1.56448291562745</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.631679320328735</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.082000509253859</v>
+        <v>4.143041543000235</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437332</v>
+        <v>3.704757949437335</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.702896045130907</v>
+        <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.621094637623039</v>
+        <v>-5.708471956144636</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.454101765767944</v>
+        <v>1.532618263218639</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.631679320328735</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.081903637328149</v>
+        <v>4.142944671074525</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298401</v>
+        <v>3.736804952298404</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.70288993868895</v>
+        <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.716557635540257</v>
+        <v>-5.803934954061853</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.4159104601591</v>
+        <v>1.494426957609794</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.631679320328735</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.081897530886192</v>
+        <v>4.142938564632567</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218003</v>
+        <v>3.715372960218006</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.700986335251561</v>
+        <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.652181724689542</v>
+        <v>-5.739559043211139</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.439757221061996</v>
+        <v>1.518273718512691</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6960552311794501</v>
+        <v>0.6086779126578541</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.118619473959232</v>
+        <v>4.179660507705607</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353539</v>
+        <v>3.736089413353541</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.706720152999288</v>
+        <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.707550886821736</v>
+        <v>-5.794928205343332</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.423343373956846</v>
+        <v>1.50185987140754</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6960552311794501</v>
+        <v>0.6086779126578541</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.124353291706958</v>
+        <v>4.185394325453334</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113282</v>
+        <v>3.736822870113285</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.70625851634222</v>
+        <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.725769353819344</v>
+        <v>-5.813146672340941</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.415594350500735</v>
+        <v>1.494110847951429</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.670948793923608</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.108827792696385</v>
+        <v>4.169868826442761</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113691</v>
+        <v>3.790272500113693</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.726132909192539</v>
+        <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.687085918475414</v>
+        <v>-5.77446323699701</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.450942117488625</v>
+        <v>1.52945861493932</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.670948793923608</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.128702185546704</v>
+        <v>4.18974321929308</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016436</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.709833609717267</v>
+        <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.581050923270104</v>
+        <v>-5.668428241791701</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.477056816095477</v>
+        <v>1.555573313546172</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.670948793923608</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.112402886071432</v>
+        <v>4.173443919817807</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307668</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.712264559181313</v>
+        <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.397839260137009</v>
+        <v>-5.485216578658606</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.552772430812761</v>
+        <v>1.631288928263456</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.670948793923608</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.114833835535477</v>
+        <v>4.175874869281854</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863549</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.69520896526069</v>
+        <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.326117813123158</v>
+        <v>-5.413495131644755</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.564405415697678</v>
+        <v>1.642921913148373</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7426702409374586</v>
+        <v>0.6552929224158626</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.140811109823165</v>
+        <v>4.201852143569541</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394111</v>
+        <v>3.723789705394113</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.642124711181861</v>
+        <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.303744787515452</v>
+        <v>-5.391122106037049</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.520270371861932</v>
+        <v>1.598786869312627</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7539259920503601</v>
+        <v>0.6665486735287641</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.094480306412078</v>
+        <v>4.155521340158454</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456731</v>
       </c>
       <c r="C2070" t="n">
-        <v>3.827322916067216</v>
+        <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.336761083426197</v>
+        <v>-5.424138401947793</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.69226205838299</v>
+        <v>1.770778555833684</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6844886153836085</v>
+        <v>0.5971112968620125</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.238016085297382</v>
+        <v>4.299057119043757</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.71376253688368</v>
+        <v>3.713762536883682</v>
       </c>
       <c r="C2071" t="n">
-        <v>3.819244141895466</v>
+        <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.325233447776588</v>
+        <v>-5.412610766298185</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.688794338471083</v>
+        <v>1.767310835921777</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.743489273584971</v>
+        <v>0.6561119550633749</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.265337706046449</v>
+        <v>4.326378739792824</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236301</v>
+        <v>3.717150699236303</v>
       </c>
       <c r="C2072" t="n">
-        <v>3.822912254417254</v>
+        <v>3.902472176292027</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.422574949118957</v>
+        <v>-5.414554002833341</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.653525850455924</v>
+        <v>1.736294150844943</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6990690914194826</v>
+        <v>0.6815432239362853</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.242353709268945</v>
+        <v>4.311398110653799</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427688</v>
+        <v>3.70520107942769</v>
       </c>
       <c r="C2073" t="n">
-        <v>3.824163336610093</v>
+        <v>3.903723258484865</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.508430978458923</v>
+        <v>-5.500410032173308</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.620434520912776</v>
+        <v>1.703202821301794</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6566930221933476</v>
+        <v>0.6391671547101503</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.218179149926102</v>
+        <v>4.287223551310956</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.806582538430595</v>
+        <v>3.886142460305368</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.517267775875043</v>
+        <v>-5.509246829589427</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.59931900376683</v>
+        <v>1.682087304155849</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6492508495519969</v>
+        <v>0.6317249820687996</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.196133048161793</v>
+        <v>4.265177449546647</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667458</v>
+        <v>3.71554441166746</v>
       </c>
       <c r="C2075" t="n">
-        <v>3.816747049475644</v>
+        <v>3.896306971350417</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.608650338440501</v>
+        <v>-5.600629392154886</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.572930489785696</v>
+        <v>1.655698790174715</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.6126859648326521</v>
+        <v>0.5951600973494549</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.184358628375236</v>
+        <v>4.25340302976009</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889195</v>
+        <v>3.673978374889197</v>
       </c>
       <c r="C2076" t="n">
-        <v>3.918875307299912</v>
+        <v>3.998435229174685</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.596943620453495</v>
+        <v>-5.58892267416788</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.679741434804765</v>
+        <v>1.762509735193785</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6243926828196585</v>
+        <v>0.6068668153364613</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.293510916991707</v>
+        <v>4.362555318376562</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409571</v>
+        <v>3.682476099409573</v>
       </c>
       <c r="C2077" t="n">
-        <v>3.921907646031316</v>
+        <v>4.00146756790609</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.667855694195772</v>
+        <v>-5.659834747910157</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.65440894403926</v>
+        <v>1.737177244428279</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.6243926828196585</v>
+        <v>0.6068668153364613</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.296543255723112</v>
+        <v>4.365587657107967</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452572</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.134812479309375</v>
+        <v>4.214372401184148</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.678171792362124</v>
+        <v>-5.670150846076509</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.863187338050777</v>
+        <v>1.945955638439797</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.6243926828196585</v>
+        <v>0.6036291346635666</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.50944808900117</v>
+        <v>4.576549881982288</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762291</v>
+        <v>3.623960959762293</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.133991146221464</v>
+        <v>4.213551068096238</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.678077824344752</v>
+        <v>-5.670056878059136</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.862403592169815</v>
+        <v>1.945171892558835</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.6247625441669765</v>
+        <v>0.6039989960108846</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.50884867272165</v>
+        <v>4.575950465702769</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884083</v>
+        <v>3.800870306884086</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.128223132165818</v>
+        <v>4.207783054040592</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.821678988368137</v>
+        <v>-5.813658042082522</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.799195112504815</v>
+        <v>1.881963412893835</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.6247625441669765</v>
+        <v>0.6039989960108846</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.503080658666004</v>
+        <v>4.570182451647122</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129647</v>
+        <v>3.671015692129649</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.128223132165818</v>
+        <v>4.207783054040592</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.820730565250098</v>
+        <v>-5.812709618964483</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.79957448175203</v>
+        <v>1.882342782141051</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.6247625441669765</v>
+        <v>0.6039989960108846</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.503080658666004</v>
+        <v>4.570182451647122</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052349</v>
+        <v>3.904173816052353</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.14095074014691</v>
+        <v>4.220510662021684</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.921000383209119</v>
+        <v>-5.912979436923504</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.772194162549515</v>
+        <v>1.854962462938534</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.6247625441669765</v>
+        <v>0.6039989960108846</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.515808266647096</v>
+        <v>4.582910059628214</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813493</v>
+        <v>3.740179607813497</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.142896738571298</v>
+        <v>4.222456660446071</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.915008136420307</v>
+        <v>-5.906987190134692</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.776537059689427</v>
+        <v>1.859305360078447</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.6247625441669765</v>
+        <v>0.6039989960108846</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.517754265071484</v>
+        <v>4.584856058052602</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537942</v>
+        <v>3.765050796537945</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.136550874589067</v>
+        <v>4.21611079646384</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.82645017528954</v>
+        <v>-5.818429229003924</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.805614380159503</v>
+        <v>1.888382680548522</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.6247625441669765</v>
+        <v>0.6039989960108846</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.511408401089253</v>
+        <v>4.578510194070371</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771814</v>
+        <v>3.758409170771817</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.135859552028062</v>
+        <v>4.215419473902836</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.808691097786466</v>
+        <v>-5.80067015150085</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.812026688599728</v>
+        <v>1.894794988988748</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.6247625441669765</v>
+        <v>0.6039989960108846</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.510717078528248</v>
+        <v>4.577818871509367</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.80134059710972</v>
+        <v>3.801340597109723</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.148641737936649</v>
+        <v>4.228201659811423</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.709060946737398</v>
+        <v>-5.701040000451782</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.864660934927942</v>
+        <v>1.947429235316962</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.724392695216044</v>
+        <v>0.7036291470599521</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.583277355066276</v>
+        <v>4.650379148047394</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546843994</v>
+        <v>3.798465546843998</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.337796003435376</v>
+        <v>4.417355925310149</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.758460455426409</v>
+        <v>-5.750439509140794</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.034055396951064</v>
+        <v>2.116823697340084</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.7346515286477887</v>
+        <v>0.7138879804916968</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.778586920624049</v>
+        <v>4.845688713605167</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.772186508351858</v>
+        <v>3.772186508351862</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.324984676538238</v>
+        <v>4.404544598413011</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.551775981784033</v>
+        <v>-5.543755035498418</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.103917859510876</v>
+        <v>2.186686159899896</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.9413360022901643</v>
+        <v>0.9205724541340724</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.889786277912337</v>
+        <v>4.956888070893455</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.763392838551268</v>
+        <v>3.763392838551272</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.326986190192343</v>
+        <v>4.406546112067116</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.585932876781559</v>
+        <v>-5.577911930495944</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.092256615165971</v>
+        <v>2.175024915554991</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.8577522327493519</v>
+        <v>0.8369886845932599</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.841637529841954</v>
+        <v>4.908739322823072</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041109</v>
+        <v>3.805590565041113</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.68048330418201</v>
+        <v>4.760043226056784</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.493343397720102</v>
+        <v>-5.485322451434487</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.482789520780221</v>
+        <v>2.565557821169241</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.8577522327493519</v>
+        <v>0.8369886845932599</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.195134643831621</v>
+        <v>5.262236436812739</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497402</v>
+        <v>3.832164354497404</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.685046415749113</v>
+        <v>4.764606337623887</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.566504001493247</v>
+        <v>-5.558483055207632</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.458088390838066</v>
+        <v>2.540856691227086</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.8297310327151088</v>
+        <v>0.8089674845590169</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.182885035378178</v>
+        <v>5.249986828359297</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492294</v>
+        <v>3.858310890492298</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.734876357072641</v>
+        <v>4.814436278947414</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.514287691696905</v>
+        <v>-5.483030570956118</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.52880485608013</v>
+        <v>2.620867626251219</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.8297310327151088</v>
+        <v>0.8089674845590169</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.232714976701706</v>
+        <v>5.299816769682825</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436476</v>
+        <v>3.844935596436478</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.743690327282652</v>
+        <v>4.823250249157425</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.48239017461166</v>
+        <v>-5.451133053870873</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.550377833124239</v>
+        <v>2.642440603295328</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.8616285498003546</v>
+        <v>0.8408650016442627</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.260667457162865</v>
+        <v>5.327769250143983</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039485</v>
+        <v>3.848376866039488</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.739327911321848</v>
+        <v>4.818887833196622</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.4971454988118</v>
+        <v>-5.465888378071013</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.54011328748338</v>
+        <v>2.632176057654469</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.8616285498003546</v>
+        <v>0.8408650016442627</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.256305041202062</v>
+        <v>5.32340683418318</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.86815311552448</v>
+        <v>3.868153115524483</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.730252414738128</v>
+        <v>4.809812336612902</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.447680875441889</v>
+        <v>-5.416423754701102</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.550823640247625</v>
+        <v>2.642886410418714</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.9110931731702663</v>
+        <v>0.8903296250141743</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.276908318640288</v>
+        <v>5.344010111621407</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867954</v>
+        <v>3.849040239867956</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.726660082453063</v>
+        <v>4.806220004327836</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.284572883288273</v>
+        <v>-5.253315762547486</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.612474504824005</v>
+        <v>2.704537274995094</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.074201165323882</v>
+        <v>1.053437617167789</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.371180781647392</v>
+        <v>5.43828257462851</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232969</v>
+        <v>3.870204928232972</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.735707119144191</v>
+        <v>4.815267041018965</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.263929792487046</v>
+        <v>-5.232672671746259</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.629778777835625</v>
+        <v>2.721841548006713</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.074201165323882</v>
+        <v>1.053437617167789</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.38022781833852</v>
+        <v>5.447329611319638</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179672</v>
+        <v>3.855534437179676</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.736564584130313</v>
+        <v>4.816124506005086</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.326637708961604</v>
+        <v>-5.295380588220817</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.605553076231923</v>
+        <v>2.697615846403012</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.011493248849324</v>
+        <v>0.9907297006932319</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.343460533439908</v>
+        <v>5.410562326421026</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967719</v>
+        <v>3.884687848967722</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.699474000920665</v>
+        <v>4.779033922795438</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.278629585117911</v>
+        <v>-5.247372464377124</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.587665742559752</v>
+        <v>2.679728512730841</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.011493248849324</v>
+        <v>0.9907297006932319</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.306369950230259</v>
+        <v>5.373471743211378</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.89536235701861</v>
+        <v>3.895362357018613</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.703406254478615</v>
+        <v>4.782966176353389</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.199803927934321</v>
+        <v>-5.168546807193533</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.623128258991139</v>
+        <v>2.715191029162228</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.090318906032914</v>
+        <v>1.069555357876822</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.357597598098364</v>
+        <v>5.424699391079482</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075133</v>
+        <v>3.891610981075137</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.698305347085652</v>
+        <v>4.777865268960426</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.007869126680447</v>
+        <v>-4.97661200593966</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.694801272099725</v>
+        <v>2.786864042270814</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.090318906032914</v>
+        <v>1.069555357876822</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.352496690705401</v>
+        <v>5.419598483686519</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435443</v>
+        <v>3.872432493435447</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.693659256474747</v>
+        <v>4.773219178349521</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.864506935193671</v>
+        <v>-4.858438627921732</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.747500058083531</v>
+        <v>2.82948730286708</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.23368109751969</v>
+        <v>1.187728735894749</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.433867914986562</v>
+        <v>5.485856419886371</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917731</v>
+        <v>3.859571723917735</v>
       </c>
       <c r="C2103" t="n">
-        <v>4.722747849337774</v>
+        <v>4.802307771212548</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.751092252410939</v>
+        <v>-4.745023945139001</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.821954524059651</v>
+        <v>2.903941768843199</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.347095780302422</v>
+        <v>1.301143418677481</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.531005317519227</v>
+        <v>5.582993822419037</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.828006274013637</v>
+        <v>3.82800627401364</v>
       </c>
       <c r="C2104" t="n">
-        <v>4.716308072348951</v>
+        <v>4.795867994223725</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.724043214717685</v>
+        <v>-4.717974907445747</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.826334362148129</v>
+        <v>2.908321606931678</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.374144817995675</v>
+        <v>1.328192456370735</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.540794963146357</v>
+        <v>5.592783468046166</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.823987445263767</v>
+        <v>3.823987445263771</v>
       </c>
       <c r="C2105" t="n">
-        <v>4.716308072348951</v>
+        <v>4.795867994223725</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.730076494904456</v>
+        <v>-4.724008187632517</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.823921050073421</v>
+        <v>2.90590829485697</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.374144817995675</v>
+        <v>1.328192456370735</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.540794963146357</v>
+        <v>5.592783468046166</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.815657203170836</v>
+        <v>3.815657203170844</v>
       </c>
       <c r="C2106" t="n">
-        <v>4.719946239491364</v>
+        <v>4.799506161366137</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.787537092154509</v>
+        <v>-4.775859963205678</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.804574978315812</v>
+        <v>2.888805751770118</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.316684220745622</v>
+        <v>1.276340680797573</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.509956771938738</v>
+        <v>5.565310569844682</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.929591137075212</v>
+        <v>3.90845187648668</v>
       </c>
       <c r="C2107" t="n">
-        <v>4.741819126661224</v>
+        <v>5.008696894677957</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.889938374116333</v>
+        <v>-4.878407607690741</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.785487352700943</v>
+        <v>3.056977427287912</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.271960841405521</v>
+        <v>1.276340680797573</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.504995631504537</v>
+        <v>5.774501303156502</v>
       </c>
     </row>
   </sheetData>
